--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -750,7 +750,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -890,10 +891,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>699.8</v>
+        <v>673.7</v>
       </c>
       <c r="D2">
-        <v>-2.24</v>
+        <v>-3.73</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,46 +903,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-23.83</v>
+        <v>-26.67</v>
       </c>
       <c r="H2">
-        <v>34.1</v>
+        <v>29.1</v>
       </c>
       <c r="I2">
-        <v>26.22</v>
+        <v>21.97</v>
       </c>
       <c r="J2">
-        <v>16.24</v>
+        <v>13.43</v>
       </c>
       <c r="K2">
-        <v>-8.279999999999999</v>
+        <v>-14.71</v>
       </c>
       <c r="L2">
-        <v>-19.24</v>
+        <v>-20.97</v>
       </c>
       <c r="M2">
-        <v>-12.1</v>
+        <v>-13.5</v>
       </c>
       <c r="N2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="P2">
-        <v>678.35</v>
+        <v>702.62</v>
       </c>
       <c r="Q2">
-        <v>607.64</v>
+        <v>611.63</v>
       </c>
       <c r="R2">
-        <v>635.54</v>
+        <v>635.02</v>
       </c>
       <c r="S2">
-        <v>672.17</v>
+        <v>671.08</v>
       </c>
       <c r="T2">
-        <v>4.11</v>
+        <v>0.39</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -956,34 +957,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>62.56</v>
+        <v>57.38</v>
       </c>
       <c r="Z2">
-        <v>14.01</v>
+        <v>15.58</v>
       </c>
       <c r="AA2">
-        <v>-5.92</v>
+        <v>-1.62</v>
       </c>
       <c r="AB2">
-        <v>19.93</v>
+        <v>17.2</v>
       </c>
       <c r="AC2">
-        <v>83.95</v>
+        <v>71.55</v>
       </c>
       <c r="AD2">
-        <v>83.73999999999999</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="AE2">
-        <v>37.67</v>
+        <v>38.24</v>
       </c>
       <c r="AF2">
-        <v>-77.78</v>
+        <v>-87.48</v>
       </c>
       <c r="AG2">
-        <v>721.66</v>
+        <v>729.16</v>
       </c>
       <c r="AH2">
-        <v>493.62</v>
+        <v>494.1</v>
       </c>
       <c r="AI2">
         <v>626.27</v>
@@ -992,7 +993,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>60.66</v>
+        <v>58.06</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,58 +1004,58 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>675.85</v>
+        <v>645.3</v>
       </c>
       <c r="D3">
-        <v>0.42</v>
+        <v>-4.52</v>
       </c>
       <c r="E3">
-        <v>740.6</v>
+        <v>736.85</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-8.74</v>
+        <v>-12.42</v>
       </c>
       <c r="H3">
-        <v>31.74</v>
+        <v>25.79</v>
       </c>
       <c r="I3">
-        <v>4.81</v>
+        <v>-3.04</v>
       </c>
       <c r="J3">
-        <v>20.22</v>
+        <v>11.16</v>
       </c>
       <c r="K3">
-        <v>18.39</v>
+        <v>12.13</v>
       </c>
       <c r="L3">
-        <v>-8.220000000000001</v>
+        <v>-12.87</v>
       </c>
       <c r="M3">
-        <v>1.93</v>
+        <v>0.72</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="P3">
-        <v>672.53</v>
+        <v>668.49</v>
       </c>
       <c r="Q3">
-        <v>626.89</v>
+        <v>630.13</v>
       </c>
       <c r="R3">
-        <v>588.9400000000001</v>
+        <v>590.48</v>
       </c>
       <c r="S3">
-        <v>581.67</v>
+        <v>581.91</v>
       </c>
       <c r="T3">
-        <v>16.19</v>
+        <v>10.89</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1069,34 +1070,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>69.61</v>
+        <v>56.61</v>
       </c>
       <c r="Z3">
-        <v>27.37</v>
+        <v>24.77</v>
       </c>
       <c r="AA3">
-        <v>23.01</v>
+        <v>23.36</v>
       </c>
       <c r="AB3">
-        <v>4.36</v>
+        <v>1.41</v>
       </c>
       <c r="AC3">
-        <v>71.08</v>
+        <v>45.2</v>
       </c>
       <c r="AD3">
-        <v>74.05</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="AE3">
-        <v>22.42</v>
+        <v>23.67</v>
       </c>
       <c r="AF3">
-        <v>-79.56</v>
+        <v>-80.19</v>
       </c>
       <c r="AG3">
-        <v>705.75</v>
+        <v>706.24</v>
       </c>
       <c r="AH3">
-        <v>548.03</v>
+        <v>554.02</v>
       </c>
       <c r="AI3">
         <v>606.01</v>
@@ -1105,7 +1106,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>55.68</v>
+        <v>50.68</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,58 +1117,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="D4">
-        <v>-0.5600000000000001</v>
+        <v>-0.92</v>
       </c>
       <c r="E4">
         <v>1249.31</v>
       </c>
       <c r="F4">
-        <v>861.9</v>
+        <v>857</v>
       </c>
       <c r="G4">
-        <v>-30.76</v>
+        <v>-31.4</v>
       </c>
       <c r="H4">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-1.48</v>
+        <v>-0.57</v>
       </c>
       <c r="J4">
-        <v>-7.67</v>
+        <v>-8.27</v>
       </c>
       <c r="K4">
-        <v>-16.57</v>
+        <v>-17.16</v>
       </c>
       <c r="L4">
-        <v>-29.56</v>
+        <v>-30.84</v>
       </c>
       <c r="M4">
-        <v>-4.19</v>
+        <v>-4.46</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P4">
-        <v>865.12</v>
+        <v>864.14</v>
       </c>
       <c r="Q4">
-        <v>904.46</v>
+        <v>900.59</v>
       </c>
       <c r="R4">
-        <v>993.91</v>
+        <v>989.04</v>
       </c>
       <c r="S4">
-        <v>1078.16</v>
+        <v>1076.73</v>
       </c>
       <c r="T4">
-        <v>-19.77</v>
+        <v>-20.41</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1182,34 +1183,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>25.57</v>
+        <v>24</v>
       </c>
       <c r="Z4">
-        <v>-36.38</v>
+        <v>-36.01</v>
       </c>
       <c r="AA4">
-        <v>-36.27</v>
+        <v>-36.22</v>
       </c>
       <c r="AB4">
-        <v>-0.11</v>
+        <v>0.21</v>
       </c>
       <c r="AC4">
-        <v>31.93</v>
+        <v>35.74</v>
       </c>
       <c r="AD4">
-        <v>21.33</v>
+        <v>30.46</v>
       </c>
       <c r="AE4">
-        <v>19.86</v>
+        <v>19.9</v>
       </c>
       <c r="AF4">
-        <v>-58.9</v>
+        <v>-26.13</v>
       </c>
       <c r="AG4">
-        <v>962.41</v>
+        <v>960.4400000000001</v>
       </c>
       <c r="AH4">
-        <v>846.5</v>
+        <v>840.74</v>
       </c>
       <c r="AI4">
         <v>924.5700000000001</v>
@@ -1218,7 +1219,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>72.62</v>
+        <v>69.84999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1230,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1126.8</v>
+        <v>1104</v>
       </c>
       <c r="D5">
-        <v>0.4</v>
+        <v>-2.02</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,25 +1242,25 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-20.52</v>
+        <v>-22.13</v>
       </c>
       <c r="H5">
-        <v>50.44</v>
+        <v>47.4</v>
       </c>
       <c r="I5">
-        <v>-3.15</v>
+        <v>-4.81</v>
       </c>
       <c r="J5">
-        <v>-10.26</v>
+        <v>-11.86</v>
       </c>
       <c r="K5">
-        <v>5.05</v>
+        <v>4.04</v>
       </c>
       <c r="L5">
-        <v>-7.37</v>
+        <v>-8.51</v>
       </c>
       <c r="M5">
-        <v>15.29</v>
+        <v>14.8</v>
       </c>
       <c r="N5">
         <v>79</v>
@@ -1268,19 +1269,19 @@
         <v>53</v>
       </c>
       <c r="P5">
-        <v>1137.26</v>
+        <v>1126.1</v>
       </c>
       <c r="Q5">
-        <v>1168.05</v>
+        <v>1162.1</v>
       </c>
       <c r="R5">
-        <v>1253.14</v>
+        <v>1251.04</v>
       </c>
       <c r="S5">
-        <v>1068.8</v>
+        <v>1069.05</v>
       </c>
       <c r="T5">
-        <v>5.43</v>
+        <v>3.27</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1295,34 +1296,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>35.73</v>
+        <v>32.11</v>
       </c>
       <c r="Z5">
-        <v>-32.37</v>
+        <v>-33.7</v>
       </c>
       <c r="AA5">
-        <v>-31.23</v>
+        <v>-31.72</v>
       </c>
       <c r="AB5">
-        <v>-1.14</v>
+        <v>-1.97</v>
       </c>
       <c r="AC5">
-        <v>49.48</v>
+        <v>39.94</v>
       </c>
       <c r="AD5">
-        <v>56.61</v>
+        <v>47.49</v>
       </c>
       <c r="AE5">
-        <v>37.6</v>
+        <v>37.61</v>
       </c>
       <c r="AF5">
-        <v>-66.93000000000001</v>
+        <v>-57.09</v>
       </c>
       <c r="AG5">
-        <v>1241.74</v>
+        <v>1236.32</v>
       </c>
       <c r="AH5">
-        <v>1094.36</v>
+        <v>1087.88</v>
       </c>
       <c r="AI5">
         <v>1228.34</v>
@@ -1331,7 +1332,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>27.86</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1343,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1748</v>
+        <v>1659.3</v>
       </c>
       <c r="D6">
-        <v>-6.62</v>
+        <v>-5.07</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,46 +1355,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-24.66</v>
+        <v>-28.49</v>
       </c>
       <c r="H6">
-        <v>18.81</v>
+        <v>12.78</v>
       </c>
       <c r="I6">
-        <v>-11.81</v>
+        <v>-13.68</v>
       </c>
       <c r="J6">
-        <v>-13.81</v>
+        <v>-16.62</v>
       </c>
       <c r="K6">
-        <v>-1.03</v>
+        <v>-7.53</v>
       </c>
       <c r="L6">
-        <v>-10.35</v>
+        <v>-16.58</v>
       </c>
       <c r="M6">
-        <v>1.71</v>
+        <v>0.32</v>
       </c>
       <c r="N6">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O6">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P6">
-        <v>1861.18</v>
+        <v>1808.6</v>
       </c>
       <c r="Q6">
-        <v>1979.45</v>
+        <v>1959.71</v>
       </c>
       <c r="R6">
-        <v>2039.26</v>
+        <v>2031.52</v>
       </c>
       <c r="S6">
-        <v>1860.94</v>
+        <v>1858.67</v>
       </c>
       <c r="T6">
-        <v>-6.07</v>
+        <v>-10.73</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1408,43 +1409,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>25.96</v>
+        <v>21.8</v>
       </c>
       <c r="Z6">
-        <v>-50.86</v>
+        <v>-67.79000000000001</v>
       </c>
       <c r="AA6">
-        <v>-25.96</v>
+        <v>-34.33</v>
       </c>
       <c r="AB6">
-        <v>-24.9</v>
+        <v>-33.46</v>
       </c>
       <c r="AC6">
         <v>3.79</v>
       </c>
       <c r="AD6">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="AE6">
-        <v>65.19</v>
+        <v>67.84</v>
       </c>
       <c r="AF6">
-        <v>372.1</v>
+        <v>57.13</v>
       </c>
       <c r="AG6">
-        <v>2141.03</v>
+        <v>2171.55</v>
       </c>
       <c r="AH6">
-        <v>1817.87</v>
+        <v>1747.88</v>
       </c>
       <c r="AI6">
-        <v>1982.58</v>
+        <v>1912.08</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>31.42</v>
+        <v>36.86</v>
       </c>
     </row>
   </sheetData>
@@ -1642,13 +1643,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>17.76</v>
+        <v>16.24</v>
       </c>
       <c r="D7" s="5">
-        <v>16.24</v>
+        <v>13.43</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.52</v>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1659,13 +1660,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>21.87</v>
+        <v>20.22</v>
       </c>
       <c r="D8" s="5">
-        <v>20.22</v>
+        <v>11.16</v>
       </c>
       <c r="E8" s="6">
-        <v>-1.65</v>
+        <v>-9.06</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1676,13 +1677,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-4.41</v>
+        <v>-7.67</v>
       </c>
       <c r="D9" s="5">
-        <v>-7.67</v>
+        <v>-8.27</v>
       </c>
       <c r="E9" s="6">
-        <v>-3.26</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1693,13 +1694,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-9.140000000000001</v>
+        <v>-10.26</v>
       </c>
       <c r="D10" s="5">
-        <v>-10.26</v>
+        <v>-11.86</v>
       </c>
       <c r="E10" s="6">
-        <v>-1.12</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1710,13 +1711,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-7.1</v>
+        <v>-13.81</v>
       </c>
       <c r="D11" s="5">
-        <v>-13.81</v>
+        <v>-16.62</v>
       </c>
       <c r="E11" s="6">
-        <v>-6.71</v>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1727,13 +1728,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>24.87</v>
+        <v>26.22</v>
       </c>
       <c r="D12" s="5">
-        <v>26.22</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.35</v>
+        <v>21.97</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-4.25</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1744,13 +1745,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>2.14</v>
+        <v>4.81</v>
       </c>
       <c r="D13" s="5">
-        <v>4.81</v>
-      </c>
-      <c r="E13" s="7">
-        <v>2.67</v>
+        <v>-3.04</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-7.85</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1761,13 +1762,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-1.15</v>
+        <v>-1.48</v>
       </c>
       <c r="D14" s="5">
-        <v>-1.48</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-0.33</v>
+        <v>-0.57</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.91</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1778,13 +1779,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-2.77</v>
+        <v>-3.15</v>
       </c>
       <c r="D15" s="5">
-        <v>-3.15</v>
+        <v>-4.81</v>
       </c>
       <c r="E15" s="6">
-        <v>-0.38</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1795,13 +1796,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-6.47</v>
+        <v>-11.81</v>
       </c>
       <c r="D16" s="5">
-        <v>-11.81</v>
+        <v>-13.68</v>
       </c>
       <c r="E16" s="6">
-        <v>-5.34</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1812,13 +1813,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>-15.41</v>
+        <v>-19.24</v>
       </c>
       <c r="D17" s="5">
-        <v>-19.24</v>
+        <v>-20.97</v>
       </c>
       <c r="E17" s="6">
-        <v>-3.83</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1829,13 +1830,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-8.359999999999999</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="D18" s="5">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.14</v>
+        <v>-12.87</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-4.65</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1846,13 +1847,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-28.3</v>
+        <v>-29.56</v>
       </c>
       <c r="D19" s="5">
-        <v>-29.56</v>
+        <v>-30.84</v>
       </c>
       <c r="E19" s="6">
-        <v>-1.26</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1863,13 +1864,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-6.95</v>
+        <v>-7.37</v>
       </c>
       <c r="D20" s="5">
-        <v>-7.37</v>
+        <v>-8.51</v>
       </c>
       <c r="E20" s="6">
-        <v>-0.42</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1880,13 +1881,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-4.7</v>
+        <v>-10.35</v>
       </c>
       <c r="D21" s="5">
-        <v>-10.35</v>
+        <v>-16.58</v>
       </c>
       <c r="E21" s="6">
-        <v>-5.65</v>
+        <v>-6.23</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1897,13 +1898,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-6.99</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="D22" s="5">
-        <v>-8.279999999999999</v>
+        <v>-14.71</v>
       </c>
       <c r="E22" s="6">
-        <v>-1.29</v>
+        <v>-6.43</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1914,13 +1915,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>19.13</v>
+        <v>18.39</v>
       </c>
       <c r="D23" s="5">
-        <v>18.39</v>
+        <v>12.13</v>
       </c>
       <c r="E23" s="6">
-        <v>-0.74</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1931,13 +1932,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-15.81</v>
+        <v>-16.57</v>
       </c>
       <c r="D24" s="5">
-        <v>-16.57</v>
+        <v>-17.16</v>
       </c>
       <c r="E24" s="6">
-        <v>-0.76</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1948,13 +1949,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>8.130000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="D25" s="5">
-        <v>5.05</v>
+        <v>4.04</v>
       </c>
       <c r="E25" s="6">
-        <v>-3.08</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1965,13 +1966,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>10.68</v>
+        <v>-1.03</v>
       </c>
       <c r="D26" s="5">
-        <v>-1.03</v>
+        <v>-7.53</v>
       </c>
       <c r="E26" s="6">
-        <v>-11.71</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1982,13 +1983,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-22.09</v>
+        <v>-23.83</v>
       </c>
       <c r="D27" s="5">
-        <v>-23.83</v>
+        <v>-26.67</v>
       </c>
       <c r="E27" s="6">
-        <v>-1.74</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1999,13 +2000,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-9.119999999999999</v>
+        <v>-8.74</v>
       </c>
       <c r="D28" s="5">
-        <v>-8.74</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.38</v>
+        <v>-12.42</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-3.68</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2016,13 +2017,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-30.37</v>
+        <v>-30.76</v>
       </c>
       <c r="D29" s="5">
-        <v>-30.76</v>
+        <v>-31.4</v>
       </c>
       <c r="E29" s="6">
-        <v>-0.39</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2033,13 +2034,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-20.84</v>
+        <v>-20.52</v>
       </c>
       <c r="D30" s="5">
-        <v>-20.52</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.32</v>
+        <v>-22.13</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2050,13 +2051,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-19.32</v>
+        <v>-24.66</v>
       </c>
       <c r="D31" s="5">
-        <v>-24.66</v>
+        <v>-28.49</v>
       </c>
       <c r="E31" s="6">
-        <v>-5.34</v>
+        <v>-3.83</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2067,13 +2068,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>715.8</v>
+        <v>699.8</v>
       </c>
       <c r="D32" s="5">
-        <v>699.8</v>
+        <v>673.7</v>
       </c>
       <c r="E32" s="6">
-        <v>-16</v>
+        <v>-26.1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2084,13 +2085,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>673.05</v>
+        <v>675.85</v>
       </c>
       <c r="D33" s="5">
-        <v>675.85</v>
-      </c>
-      <c r="E33" s="7">
-        <v>2.8</v>
+        <v>645.3</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-30.55</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2101,13 +2102,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>869.9</v>
+        <v>865</v>
       </c>
       <c r="D34" s="5">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="E34" s="6">
-        <v>-4.9</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2118,13 +2119,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>1122.3</v>
+        <v>1126.8</v>
       </c>
       <c r="D35" s="5">
-        <v>1126.8</v>
-      </c>
-      <c r="E35" s="7">
-        <v>4.5</v>
+        <v>1104</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-22.8</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2135,30 +2136,30 @@
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>1872</v>
+        <v>1748</v>
       </c>
       <c r="D36" s="5">
-        <v>1748</v>
+        <v>1659.3</v>
       </c>
       <c r="E36" s="6">
-        <v>-124</v>
+        <v>-88.7</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C37" s="5">
+        <v>40</v>
+      </c>
+      <c r="D37" s="5">
         <v>60</v>
       </c>
-      <c r="D37" s="5">
-        <v>79</v>
-      </c>
       <c r="E37" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2169,13 +2170,13 @@
         <v>13</v>
       </c>
       <c r="C38" s="5">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="D38" s="5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E38" s="6">
-        <v>-19</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2186,13 +2187,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>65.95</v>
+        <v>62.56</v>
       </c>
       <c r="D39" s="5">
-        <v>62.56</v>
+        <v>57.38</v>
       </c>
       <c r="E39" s="6">
-        <v>-3.39</v>
+        <v>-5.18</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2203,13 +2204,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>69</v>
+        <v>69.61</v>
       </c>
       <c r="D40" s="5">
-        <v>69.61</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.61</v>
+        <v>56.61</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-13</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2220,13 +2221,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>26.56</v>
+        <v>25.57</v>
       </c>
       <c r="D41" s="5">
-        <v>25.57</v>
+        <v>24</v>
       </c>
       <c r="E41" s="6">
-        <v>-0.99</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2237,13 +2238,13 @@
         <v>24</v>
       </c>
       <c r="C42" s="5">
-        <v>34.37</v>
+        <v>35.73</v>
       </c>
       <c r="D42" s="5">
-        <v>35.73</v>
-      </c>
-      <c r="E42" s="7">
-        <v>1.36</v>
+        <v>32.11</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-3.62</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2254,13 +2255,13 @@
         <v>24</v>
       </c>
       <c r="C43" s="5">
-        <v>34.53</v>
+        <v>25.96</v>
       </c>
       <c r="D43" s="5">
-        <v>25.96</v>
+        <v>21.8</v>
       </c>
       <c r="E43" s="6">
-        <v>-8.57</v>
+        <v>-4.16</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2271,13 +2272,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>49.71</v>
+        <v>-77.78</v>
       </c>
       <c r="D44" s="5">
-        <v>-77.78</v>
+        <v>-87.48</v>
       </c>
       <c r="E44" s="6">
-        <v>-127.49</v>
+        <v>-9.699999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2288,13 +2289,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-59.56</v>
+        <v>-79.56</v>
       </c>
       <c r="D45" s="5">
-        <v>-79.56</v>
+        <v>-80.19</v>
       </c>
       <c r="E45" s="6">
-        <v>-20</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2305,13 +2306,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>-76.14</v>
+        <v>-58.9</v>
       </c>
       <c r="D46" s="5">
-        <v>-58.9</v>
+        <v>-26.13</v>
       </c>
       <c r="E46" s="7">
-        <v>17.24</v>
+        <v>32.77</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2322,13 +2323,13 @@
         <v>31</v>
       </c>
       <c r="C47" s="5">
-        <v>-35.81</v>
+        <v>-66.93000000000001</v>
       </c>
       <c r="D47" s="5">
-        <v>-66.93000000000001</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-31.12</v>
+        <v>-57.09</v>
+      </c>
+      <c r="E47" s="7">
+        <v>9.84</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2339,13 +2340,13 @@
         <v>31</v>
       </c>
       <c r="C48" s="5">
-        <v>22.97</v>
+        <v>372.1</v>
       </c>
       <c r="D48" s="5">
-        <v>372.1</v>
-      </c>
-      <c r="E48" s="7">
-        <v>349.13</v>
+        <v>57.13</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-314.97</v>
       </c>
     </row>
   </sheetData>
@@ -2410,16 +2411,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>43.9</v>
+        <v>38.4</v>
       </c>
       <c r="E2" s="10">
         <v>60</v>
       </c>
       <c r="F2" s="10">
-        <v>0.9</v>
+        <v>-2.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-0.5</v>
+        <v>-4.6</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2544,19 +2545,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.1529</v>
+        <v>0.148</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0193</v>
+        <v>0.0072</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0171</v>
+        <v>0.0032</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.04190000000000001</v>
+        <v>-0.0446</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.121</v>
+        <v>-0.135</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -750,8 +750,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -891,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>673.7</v>
+        <v>661.95</v>
       </c>
       <c r="D2">
-        <v>-3.73</v>
+        <v>-1.74</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -903,46 +902,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-26.67</v>
+        <v>-27.95</v>
       </c>
       <c r="H2">
-        <v>29.1</v>
+        <v>26.85</v>
       </c>
       <c r="I2">
-        <v>21.97</v>
+        <v>-0.13</v>
       </c>
       <c r="J2">
-        <v>13.43</v>
+        <v>11.45</v>
       </c>
       <c r="K2">
-        <v>-14.71</v>
+        <v>-16.15</v>
       </c>
       <c r="L2">
-        <v>-20.97</v>
+        <v>-22.84</v>
       </c>
       <c r="M2">
-        <v>-13.5</v>
+        <v>-13.71</v>
       </c>
       <c r="N2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P2">
-        <v>702.62</v>
+        <v>702.45</v>
       </c>
       <c r="Q2">
-        <v>611.63</v>
+        <v>615.45</v>
       </c>
       <c r="R2">
-        <v>635.02</v>
+        <v>634.52</v>
       </c>
       <c r="S2">
-        <v>671.08</v>
+        <v>670.11</v>
       </c>
       <c r="T2">
-        <v>0.39</v>
+        <v>-1.22</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -954,37 +953,37 @@
         <v>43</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>57.38</v>
+        <v>55.17</v>
       </c>
       <c r="Z2">
-        <v>15.58</v>
+        <v>15.7</v>
       </c>
       <c r="AA2">
-        <v>-1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AB2">
-        <v>17.2</v>
+        <v>13.85</v>
       </c>
       <c r="AC2">
-        <v>71.55</v>
+        <v>64.69</v>
       </c>
       <c r="AD2">
-        <v>82.84999999999999</v>
+        <v>73.39</v>
       </c>
       <c r="AE2">
-        <v>38.24</v>
+        <v>37.87</v>
       </c>
       <c r="AF2">
-        <v>-87.48</v>
+        <v>-90.94</v>
       </c>
       <c r="AG2">
-        <v>729.16</v>
+        <v>734.37</v>
       </c>
       <c r="AH2">
-        <v>494.1</v>
+        <v>496.53</v>
       </c>
       <c r="AI2">
         <v>626.27</v>
@@ -993,7 +992,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>58.06</v>
+        <v>53.62</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1004,10 +1003,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>645.3</v>
+        <v>647.35</v>
       </c>
       <c r="D3">
-        <v>-4.52</v>
+        <v>0.32</v>
       </c>
       <c r="E3">
         <v>736.85</v>
@@ -1016,25 +1015,25 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-12.42</v>
+        <v>-12.15</v>
       </c>
       <c r="H3">
-        <v>25.79</v>
+        <v>26.19</v>
       </c>
       <c r="I3">
-        <v>-3.04</v>
+        <v>-3.9</v>
       </c>
       <c r="J3">
-        <v>11.16</v>
+        <v>11.52</v>
       </c>
       <c r="K3">
-        <v>12.13</v>
+        <v>12.81</v>
       </c>
       <c r="L3">
-        <v>-12.87</v>
+        <v>-12.01</v>
       </c>
       <c r="M3">
-        <v>0.72</v>
+        <v>0.96</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1043,19 +1042,19 @@
         <v>65</v>
       </c>
       <c r="P3">
-        <v>668.49</v>
+        <v>663.24</v>
       </c>
       <c r="Q3">
-        <v>630.13</v>
+        <v>633.0599999999999</v>
       </c>
       <c r="R3">
-        <v>590.48</v>
+        <v>592.21</v>
       </c>
       <c r="S3">
-        <v>581.91</v>
+        <v>582.15</v>
       </c>
       <c r="T3">
-        <v>10.89</v>
+        <v>11.2</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1070,34 +1069,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>56.61</v>
+        <v>57.19</v>
       </c>
       <c r="Z3">
-        <v>24.77</v>
+        <v>22.62</v>
       </c>
       <c r="AA3">
-        <v>23.36</v>
+        <v>23.21</v>
       </c>
       <c r="AB3">
-        <v>1.41</v>
+        <v>-0.59</v>
       </c>
       <c r="AC3">
-        <v>45.2</v>
+        <v>21.48</v>
       </c>
       <c r="AD3">
-        <v>64.18000000000001</v>
+        <v>45.92</v>
       </c>
       <c r="AE3">
-        <v>23.67</v>
+        <v>23.4</v>
       </c>
       <c r="AF3">
-        <v>-80.19</v>
+        <v>-87.90000000000001</v>
       </c>
       <c r="AG3">
-        <v>706.24</v>
+        <v>706.9400000000001</v>
       </c>
       <c r="AH3">
-        <v>554.02</v>
+        <v>559.1900000000001</v>
       </c>
       <c r="AI3">
         <v>606.01</v>
@@ -1106,7 +1105,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>50.68</v>
+        <v>44.18</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1117,58 +1116,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="D4">
-        <v>-0.92</v>
+        <v>0.7</v>
       </c>
       <c r="E4">
-        <v>1249.31</v>
+        <v>1242.4</v>
       </c>
       <c r="F4">
         <v>857</v>
       </c>
       <c r="G4">
-        <v>-31.4</v>
+        <v>-30.54</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I4">
-        <v>-0.57</v>
+        <v>-0.23</v>
       </c>
       <c r="J4">
-        <v>-8.27</v>
+        <v>-7.63</v>
       </c>
       <c r="K4">
-        <v>-17.16</v>
+        <v>-15.39</v>
       </c>
       <c r="L4">
-        <v>-30.84</v>
+        <v>-30.92</v>
       </c>
       <c r="M4">
-        <v>-4.46</v>
+        <v>-3.94</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P4">
-        <v>864.14</v>
+        <v>863.74</v>
       </c>
       <c r="Q4">
-        <v>900.59</v>
+        <v>897.1900000000001</v>
       </c>
       <c r="R4">
-        <v>989.04</v>
+        <v>984.36</v>
       </c>
       <c r="S4">
-        <v>1076.73</v>
+        <v>1075.38</v>
       </c>
       <c r="T4">
-        <v>-20.41</v>
+        <v>-19.75</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1183,34 +1182,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>24</v>
+        <v>27.59</v>
       </c>
       <c r="Z4">
-        <v>-36.01</v>
+        <v>-34.83</v>
       </c>
       <c r="AA4">
-        <v>-36.22</v>
+        <v>-35.94</v>
       </c>
       <c r="AB4">
-        <v>0.21</v>
+        <v>1.11</v>
       </c>
       <c r="AC4">
-        <v>35.74</v>
+        <v>41.08</v>
       </c>
       <c r="AD4">
-        <v>30.46</v>
+        <v>36.25</v>
       </c>
       <c r="AE4">
-        <v>19.9</v>
+        <v>19.97</v>
       </c>
       <c r="AF4">
-        <v>-26.13</v>
+        <v>-7.89</v>
       </c>
       <c r="AG4">
-        <v>960.4400000000001</v>
+        <v>957.49</v>
       </c>
       <c r="AH4">
-        <v>840.74</v>
+        <v>836.89</v>
       </c>
       <c r="AI4">
         <v>924.5700000000001</v>
@@ -1219,7 +1218,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>69.84999999999999</v>
+        <v>67.54000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1230,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1104</v>
+        <v>1136.5</v>
       </c>
       <c r="D5">
-        <v>-2.02</v>
+        <v>2.94</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1242,46 +1241,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-22.13</v>
+        <v>-19.83</v>
       </c>
       <c r="H5">
-        <v>47.4</v>
+        <v>51.74</v>
       </c>
       <c r="I5">
-        <v>-4.81</v>
+        <v>-0.66</v>
       </c>
       <c r="J5">
-        <v>-11.86</v>
+        <v>-7.07</v>
       </c>
       <c r="K5">
-        <v>4.04</v>
+        <v>8.01</v>
       </c>
       <c r="L5">
-        <v>-8.51</v>
+        <v>-5.9</v>
       </c>
       <c r="M5">
-        <v>14.8</v>
+        <v>15.42</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="P5">
-        <v>1126.1</v>
+        <v>1124.6</v>
       </c>
       <c r="Q5">
-        <v>1162.1</v>
+        <v>1157.43</v>
       </c>
       <c r="R5">
-        <v>1251.04</v>
+        <v>1249.51</v>
       </c>
       <c r="S5">
-        <v>1069.05</v>
+        <v>1069.49</v>
       </c>
       <c r="T5">
-        <v>3.27</v>
+        <v>6.27</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1296,34 +1295,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>32.11</v>
+        <v>41.23</v>
       </c>
       <c r="Z5">
-        <v>-33.7</v>
+        <v>-31.76</v>
       </c>
       <c r="AA5">
-        <v>-31.72</v>
+        <v>-31.73</v>
       </c>
       <c r="AB5">
-        <v>-1.97</v>
+        <v>-0.03</v>
       </c>
       <c r="AC5">
-        <v>39.94</v>
+        <v>59.1</v>
       </c>
       <c r="AD5">
-        <v>47.49</v>
+        <v>49.51</v>
       </c>
       <c r="AE5">
-        <v>37.61</v>
+        <v>41.63</v>
       </c>
       <c r="AF5">
-        <v>-57.09</v>
+        <v>289.45</v>
       </c>
       <c r="AG5">
-        <v>1236.32</v>
+        <v>1225.16</v>
       </c>
       <c r="AH5">
-        <v>1087.88</v>
+        <v>1089.7</v>
       </c>
       <c r="AI5">
         <v>1228.34</v>
@@ -1332,7 +1331,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>26.8</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1343,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1659.3</v>
+        <v>1665.3</v>
       </c>
       <c r="D6">
-        <v>-5.07</v>
+        <v>0.36</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1355,46 +1354,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-28.49</v>
+        <v>-28.23</v>
       </c>
       <c r="H6">
-        <v>12.78</v>
+        <v>13.19</v>
       </c>
       <c r="I6">
-        <v>-13.68</v>
+        <v>-12.66</v>
       </c>
       <c r="J6">
-        <v>-16.62</v>
+        <v>-18.92</v>
       </c>
       <c r="K6">
-        <v>-7.53</v>
+        <v>-6.88</v>
       </c>
       <c r="L6">
-        <v>-16.58</v>
+        <v>-16.44</v>
       </c>
       <c r="M6">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="N6">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O6">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P6">
-        <v>1808.6</v>
+        <v>1760.34</v>
       </c>
       <c r="Q6">
-        <v>1959.71</v>
+        <v>1943.11</v>
       </c>
       <c r="R6">
-        <v>2031.52</v>
+        <v>2023.96</v>
       </c>
       <c r="S6">
-        <v>1858.67</v>
+        <v>1856.51</v>
       </c>
       <c r="T6">
-        <v>-10.73</v>
+        <v>-10.3</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1409,43 +1408,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>21.8</v>
+        <v>22.7</v>
       </c>
       <c r="Z6">
-        <v>-67.79000000000001</v>
+        <v>-79.8</v>
       </c>
       <c r="AA6">
-        <v>-34.33</v>
+        <v>-43.42</v>
       </c>
       <c r="AB6">
-        <v>-33.46</v>
+        <v>-36.37</v>
       </c>
       <c r="AC6">
-        <v>3.79</v>
+        <v>0.93</v>
       </c>
       <c r="AD6">
-        <v>3.79</v>
+        <v>2.84</v>
       </c>
       <c r="AE6">
-        <v>67.84</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="AF6">
-        <v>57.13</v>
+        <v>10.13</v>
       </c>
       <c r="AG6">
-        <v>2171.55</v>
+        <v>2191.43</v>
       </c>
       <c r="AH6">
-        <v>1747.88</v>
+        <v>1694.79</v>
       </c>
       <c r="AI6">
-        <v>1912.08</v>
+        <v>1876.67</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>36.86</v>
+        <v>41.7</v>
       </c>
     </row>
   </sheetData>
@@ -1643,13 +1642,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>16.24</v>
+        <v>13.43</v>
       </c>
       <c r="D7" s="5">
-        <v>13.43</v>
+        <v>11.45</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.81</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1660,13 +1659,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>20.22</v>
+        <v>11.16</v>
       </c>
       <c r="D8" s="5">
-        <v>11.16</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-9.06</v>
+        <v>11.52</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.36</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1677,13 +1676,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-7.67</v>
+        <v>-8.27</v>
       </c>
       <c r="D9" s="5">
-        <v>-8.27</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-0.6</v>
+        <v>-7.63</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.64</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1694,13 +1693,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-10.26</v>
+        <v>-11.86</v>
       </c>
       <c r="D10" s="5">
-        <v>-11.86</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-1.6</v>
+        <v>-7.07</v>
+      </c>
+      <c r="E10" s="7">
+        <v>4.79</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1711,13 +1710,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-13.81</v>
+        <v>-16.62</v>
       </c>
       <c r="D11" s="5">
-        <v>-16.62</v>
+        <v>-18.92</v>
       </c>
       <c r="E11" s="6">
-        <v>-2.81</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1728,13 +1727,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>26.22</v>
+        <v>21.97</v>
       </c>
       <c r="D12" s="5">
-        <v>21.97</v>
+        <v>-0.13</v>
       </c>
       <c r="E12" s="6">
-        <v>-4.25</v>
+        <v>-22.1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1745,13 +1744,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>4.81</v>
+        <v>-3.04</v>
       </c>
       <c r="D13" s="5">
-        <v>-3.04</v>
+        <v>-3.9</v>
       </c>
       <c r="E13" s="6">
-        <v>-7.85</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1762,13 +1761,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-1.48</v>
+        <v>-0.57</v>
       </c>
       <c r="D14" s="5">
-        <v>-0.57</v>
+        <v>-0.23</v>
       </c>
       <c r="E14" s="7">
-        <v>0.91</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1779,13 +1778,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-3.15</v>
+        <v>-4.81</v>
       </c>
       <c r="D15" s="5">
-        <v>-4.81</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-1.66</v>
+        <v>-0.66</v>
+      </c>
+      <c r="E15" s="7">
+        <v>4.15</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1796,13 +1795,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-11.81</v>
+        <v>-13.68</v>
       </c>
       <c r="D16" s="5">
-        <v>-13.68</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-1.87</v>
+        <v>-12.66</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.02</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1813,13 +1812,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>-19.24</v>
+        <v>-20.97</v>
       </c>
       <c r="D17" s="5">
-        <v>-20.97</v>
+        <v>-22.84</v>
       </c>
       <c r="E17" s="6">
-        <v>-1.73</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1830,13 +1829,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-8.220000000000001</v>
+        <v>-12.87</v>
       </c>
       <c r="D18" s="5">
-        <v>-12.87</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-4.65</v>
+        <v>-12.01</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.86</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1847,13 +1846,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-29.56</v>
+        <v>-30.84</v>
       </c>
       <c r="D19" s="5">
-        <v>-30.84</v>
+        <v>-30.92</v>
       </c>
       <c r="E19" s="6">
-        <v>-1.28</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1864,13 +1863,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-7.37</v>
+        <v>-8.51</v>
       </c>
       <c r="D20" s="5">
-        <v>-8.51</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-1.14</v>
+        <v>-5.9</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.61</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1881,13 +1880,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-10.35</v>
+        <v>-16.58</v>
       </c>
       <c r="D21" s="5">
-        <v>-16.58</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-6.23</v>
+        <v>-16.44</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.14</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1898,13 +1897,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-8.279999999999999</v>
+        <v>-14.71</v>
       </c>
       <c r="D22" s="5">
-        <v>-14.71</v>
+        <v>-16.15</v>
       </c>
       <c r="E22" s="6">
-        <v>-6.43</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1915,13 +1914,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>18.39</v>
+        <v>12.13</v>
       </c>
       <c r="D23" s="5">
-        <v>12.13</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-6.26</v>
+        <v>12.81</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.68</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1932,13 +1931,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-16.57</v>
+        <v>-17.16</v>
       </c>
       <c r="D24" s="5">
-        <v>-17.16</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.59</v>
+        <v>-15.39</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.77</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1949,13 +1948,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>5.05</v>
+        <v>4.04</v>
       </c>
       <c r="D25" s="5">
-        <v>4.04</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1.01</v>
+        <v>8.01</v>
+      </c>
+      <c r="E25" s="7">
+        <v>3.97</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1966,13 +1965,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-1.03</v>
+        <v>-7.53</v>
       </c>
       <c r="D26" s="5">
-        <v>-7.53</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-6.5</v>
+        <v>-6.88</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.65</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1983,13 +1982,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-23.83</v>
+        <v>-26.67</v>
       </c>
       <c r="D27" s="5">
-        <v>-26.67</v>
+        <v>-27.95</v>
       </c>
       <c r="E27" s="6">
-        <v>-2.84</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2000,13 +1999,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-8.74</v>
+        <v>-12.42</v>
       </c>
       <c r="D28" s="5">
-        <v>-12.42</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-3.68</v>
+        <v>-12.15</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.27</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2017,13 +2016,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-30.76</v>
+        <v>-31.4</v>
       </c>
       <c r="D29" s="5">
-        <v>-31.4</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.64</v>
+        <v>-30.54</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.86</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2034,13 +2033,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-20.52</v>
+        <v>-22.13</v>
       </c>
       <c r="D30" s="5">
-        <v>-22.13</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-1.61</v>
+        <v>-19.83</v>
+      </c>
+      <c r="E30" s="7">
+        <v>2.3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2051,13 +2050,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-24.66</v>
+        <v>-28.49</v>
       </c>
       <c r="D31" s="5">
-        <v>-28.49</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-3.83</v>
+        <v>-28.23</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.26</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2068,13 +2067,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>699.8</v>
+        <v>673.7</v>
       </c>
       <c r="D32" s="5">
-        <v>673.7</v>
+        <v>661.95</v>
       </c>
       <c r="E32" s="6">
-        <v>-26.1</v>
+        <v>-11.75</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2085,13 +2084,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>675.85</v>
+        <v>645.3</v>
       </c>
       <c r="D33" s="5">
-        <v>645.3</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-30.55</v>
+        <v>647.35</v>
+      </c>
+      <c r="E33" s="7">
+        <v>2.05</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2102,13 +2101,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="D34" s="5">
-        <v>857</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-8</v>
+        <v>863</v>
+      </c>
+      <c r="E34" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2119,13 +2118,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>1126.8</v>
+        <v>1104</v>
       </c>
       <c r="D35" s="5">
-        <v>1104</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-22.8</v>
+        <v>1136.5</v>
+      </c>
+      <c r="E35" s="7">
+        <v>32.5</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2136,13 +2135,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>1748</v>
+        <v>1659.3</v>
       </c>
       <c r="D36" s="5">
-        <v>1659.3</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-88.7</v>
+        <v>1665.3</v>
+      </c>
+      <c r="E36" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2153,13 +2152,13 @@
         <v>13</v>
       </c>
       <c r="C37" s="5">
+        <v>60</v>
+      </c>
+      <c r="D37" s="5">
         <v>40</v>
       </c>
-      <c r="D37" s="5">
-        <v>60</v>
-      </c>
-      <c r="E37" s="7">
-        <v>20</v>
+      <c r="E37" s="6">
+        <v>-20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2170,13 +2169,13 @@
         <v>13</v>
       </c>
       <c r="C38" s="5">
+        <v>40</v>
+      </c>
+      <c r="D38" s="5">
         <v>60</v>
       </c>
-      <c r="D38" s="5">
-        <v>40</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-20</v>
+      <c r="E38" s="7">
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2187,13 +2186,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>62.56</v>
+        <v>57.38</v>
       </c>
       <c r="D39" s="5">
-        <v>57.38</v>
+        <v>55.17</v>
       </c>
       <c r="E39" s="6">
-        <v>-5.18</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2204,13 +2203,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>69.61</v>
+        <v>56.61</v>
       </c>
       <c r="D40" s="5">
-        <v>56.61</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-13</v>
+        <v>57.19</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.58</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2221,13 +2220,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>25.57</v>
+        <v>24</v>
       </c>
       <c r="D41" s="5">
-        <v>24</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-1.57</v>
+        <v>27.59</v>
+      </c>
+      <c r="E41" s="7">
+        <v>3.59</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2238,13 +2237,13 @@
         <v>24</v>
       </c>
       <c r="C42" s="5">
-        <v>35.73</v>
+        <v>32.11</v>
       </c>
       <c r="D42" s="5">
-        <v>32.11</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-3.62</v>
+        <v>41.23</v>
+      </c>
+      <c r="E42" s="7">
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2255,13 +2254,13 @@
         <v>24</v>
       </c>
       <c r="C43" s="5">
-        <v>25.96</v>
+        <v>21.8</v>
       </c>
       <c r="D43" s="5">
-        <v>21.8</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-4.16</v>
+        <v>22.7</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.9</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2272,13 +2271,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>-77.78</v>
+        <v>-87.48</v>
       </c>
       <c r="D44" s="5">
-        <v>-87.48</v>
+        <v>-90.94</v>
       </c>
       <c r="E44" s="6">
-        <v>-9.699999999999999</v>
+        <v>-3.46</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2289,13 +2288,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-79.56</v>
+        <v>-80.19</v>
       </c>
       <c r="D45" s="5">
-        <v>-80.19</v>
+        <v>-87.90000000000001</v>
       </c>
       <c r="E45" s="6">
-        <v>-0.63</v>
+        <v>-7.71</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2306,13 +2305,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>-58.9</v>
+        <v>-26.13</v>
       </c>
       <c r="D46" s="5">
-        <v>-26.13</v>
+        <v>-7.89</v>
       </c>
       <c r="E46" s="7">
-        <v>32.77</v>
+        <v>18.24</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2323,13 +2322,13 @@
         <v>31</v>
       </c>
       <c r="C47" s="5">
-        <v>-66.93000000000001</v>
+        <v>-57.09</v>
       </c>
       <c r="D47" s="5">
-        <v>-57.09</v>
+        <v>289.45</v>
       </c>
       <c r="E47" s="7">
-        <v>9.84</v>
+        <v>346.54</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2340,13 +2339,13 @@
         <v>31</v>
       </c>
       <c r="C48" s="5">
-        <v>372.1</v>
+        <v>57.13</v>
       </c>
       <c r="D48" s="5">
-        <v>57.13</v>
+        <v>10.13</v>
       </c>
       <c r="E48" s="6">
-        <v>-314.97</v>
+        <v>-47</v>
       </c>
     </row>
   </sheetData>
@@ -2405,22 +2404,22 @@
         <v>42</v>
       </c>
       <c r="B2" s="10">
-        <v>57.92</v>
+        <v>49.92</v>
       </c>
       <c r="C2" s="11">
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>38.4</v>
+        <v>40.8</v>
       </c>
       <c r="E2" s="10">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F2" s="10">
-        <v>-2.4</v>
+        <v>-2.1</v>
       </c>
       <c r="G2" s="10">
-        <v>-4.6</v>
+        <v>-3.5</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2545,19 +2544,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.148</v>
+        <v>0.1542</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0072</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0032</v>
+        <v>0.003</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.0446</v>
+        <v>-0.0394</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.135</v>
+        <v>-0.1371</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>27.6 → 33.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>27.6</t>
+  </si>
+  <si>
+    <t>33.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -252,14 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,14 +395,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -890,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>661.95</v>
+        <v>755.15</v>
       </c>
       <c r="D2">
-        <v>-1.74</v>
+        <v>14.08</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,46 +930,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-27.95</v>
+        <v>-17.81</v>
       </c>
       <c r="H2">
-        <v>26.85</v>
+        <v>44.71</v>
       </c>
       <c r="I2">
-        <v>-0.13</v>
+        <v>-0.77</v>
       </c>
       <c r="J2">
-        <v>11.45</v>
+        <v>28.96</v>
       </c>
       <c r="K2">
-        <v>-16.15</v>
+        <v>-4.87</v>
       </c>
       <c r="L2">
-        <v>-22.84</v>
+        <v>-11.22</v>
       </c>
       <c r="M2">
-        <v>-13.71</v>
+        <v>-10.87</v>
       </c>
       <c r="N2">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="O2">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="P2">
-        <v>702.45</v>
+        <v>701.28</v>
       </c>
       <c r="Q2">
-        <v>615.45</v>
+        <v>623.02</v>
       </c>
       <c r="R2">
-        <v>634.52</v>
+        <v>636.22</v>
       </c>
       <c r="S2">
-        <v>670.11</v>
+        <v>669.6900000000001</v>
       </c>
       <c r="T2">
-        <v>-1.22</v>
+        <v>12.76</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -953,37 +981,37 @@
         <v>43</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>55.17</v>
+        <v>66.28</v>
       </c>
       <c r="Z2">
-        <v>15.7</v>
+        <v>23.05</v>
       </c>
       <c r="AA2">
-        <v>1.84</v>
+        <v>6.08</v>
       </c>
       <c r="AB2">
-        <v>13.85</v>
+        <v>16.96</v>
       </c>
       <c r="AC2">
-        <v>64.69</v>
+        <v>67.05</v>
       </c>
       <c r="AD2">
-        <v>73.39</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="AE2">
-        <v>37.87</v>
+        <v>43.59</v>
       </c>
       <c r="AF2">
-        <v>-90.94</v>
+        <v>164.41</v>
       </c>
       <c r="AG2">
-        <v>734.37</v>
+        <v>757.11</v>
       </c>
       <c r="AH2">
-        <v>496.53</v>
+        <v>488.93</v>
       </c>
       <c r="AI2">
         <v>626.27</v>
@@ -992,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>53.62</v>
+        <v>53.65</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,10 +1031,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>647.35</v>
+        <v>653.6</v>
       </c>
       <c r="D3">
-        <v>0.32</v>
+        <v>0.97</v>
       </c>
       <c r="E3">
         <v>736.85</v>
@@ -1015,46 +1043,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-12.15</v>
+        <v>-11.3</v>
       </c>
       <c r="H3">
-        <v>26.19</v>
+        <v>27.41</v>
       </c>
       <c r="I3">
-        <v>-3.9</v>
+        <v>-3.12</v>
       </c>
       <c r="J3">
-        <v>11.52</v>
+        <v>11.02</v>
       </c>
       <c r="K3">
-        <v>12.81</v>
+        <v>13.43</v>
       </c>
       <c r="L3">
-        <v>-12.01</v>
+        <v>-10.97</v>
       </c>
       <c r="M3">
-        <v>0.96</v>
+        <v>0.76</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P3">
-        <v>663.24</v>
+        <v>659.03</v>
       </c>
       <c r="Q3">
-        <v>633.0599999999999</v>
+        <v>637.0700000000001</v>
       </c>
       <c r="R3">
-        <v>592.21</v>
+        <v>594.21</v>
       </c>
       <c r="S3">
-        <v>582.15</v>
+        <v>582.45</v>
       </c>
       <c r="T3">
-        <v>11.2</v>
+        <v>12.22</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1069,34 +1097,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>57.19</v>
+        <v>58.98</v>
       </c>
       <c r="Z3">
-        <v>22.62</v>
+        <v>21.18</v>
       </c>
       <c r="AA3">
-        <v>23.21</v>
+        <v>22.81</v>
       </c>
       <c r="AB3">
-        <v>-0.59</v>
+        <v>-1.63</v>
       </c>
       <c r="AC3">
-        <v>21.48</v>
+        <v>5.42</v>
       </c>
       <c r="AD3">
-        <v>45.92</v>
+        <v>24.04</v>
       </c>
       <c r="AE3">
-        <v>23.4</v>
+        <v>22.59</v>
       </c>
       <c r="AF3">
-        <v>-87.90000000000001</v>
+        <v>-88.45999999999999</v>
       </c>
       <c r="AG3">
-        <v>706.9400000000001</v>
+        <v>705.83</v>
       </c>
       <c r="AH3">
-        <v>559.1900000000001</v>
+        <v>568.3200000000001</v>
       </c>
       <c r="AI3">
         <v>606.01</v>
@@ -1105,7 +1133,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>44.18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>863</v>
+        <v>873</v>
       </c>
       <c r="D4">
-        <v>0.7</v>
+        <v>1.16</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1128,46 +1156,46 @@
         <v>857</v>
       </c>
       <c r="G4">
-        <v>-30.54</v>
+        <v>-29.73</v>
       </c>
       <c r="H4">
-        <v>0.7</v>
+        <v>1.87</v>
       </c>
       <c r="I4">
-        <v>-0.23</v>
+        <v>1.07</v>
       </c>
       <c r="J4">
-        <v>-7.63</v>
+        <v>-6.23</v>
       </c>
       <c r="K4">
-        <v>-15.39</v>
+        <v>-13.5</v>
       </c>
       <c r="L4">
-        <v>-30.92</v>
+        <v>-29.18</v>
       </c>
       <c r="M4">
-        <v>-3.94</v>
+        <v>-3.47</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P4">
-        <v>863.74</v>
+        <v>865.58</v>
       </c>
       <c r="Q4">
-        <v>897.1900000000001</v>
+        <v>894.34</v>
       </c>
       <c r="R4">
-        <v>984.36</v>
+        <v>980.3099999999999</v>
       </c>
       <c r="S4">
-        <v>1075.38</v>
+        <v>1074.07</v>
       </c>
       <c r="T4">
-        <v>-19.75</v>
+        <v>-18.72</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1182,34 +1210,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>27.59</v>
+        <v>33.25</v>
       </c>
       <c r="Z4">
-        <v>-34.83</v>
+        <v>-32.71</v>
       </c>
       <c r="AA4">
-        <v>-35.94</v>
+        <v>-35.29</v>
       </c>
       <c r="AB4">
-        <v>1.11</v>
+        <v>2.59</v>
       </c>
       <c r="AC4">
-        <v>41.08</v>
+        <v>62.15</v>
       </c>
       <c r="AD4">
-        <v>36.25</v>
+        <v>46.32</v>
       </c>
       <c r="AE4">
-        <v>19.97</v>
+        <v>19.47</v>
       </c>
       <c r="AF4">
-        <v>-7.89</v>
+        <v>-43.72</v>
       </c>
       <c r="AG4">
-        <v>957.49</v>
+        <v>953.49</v>
       </c>
       <c r="AH4">
-        <v>836.89</v>
+        <v>835.1900000000001</v>
       </c>
       <c r="AI4">
         <v>924.5700000000001</v>
@@ -1218,7 +1246,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>67.54000000000001</v>
+        <v>65.54000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1136.5</v>
+        <v>1127.3</v>
       </c>
       <c r="D5">
-        <v>2.94</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,46 +1269,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-19.83</v>
+        <v>-20.48</v>
       </c>
       <c r="H5">
-        <v>51.74</v>
+        <v>50.51</v>
       </c>
       <c r="I5">
-        <v>-0.66</v>
+        <v>-0.54</v>
       </c>
       <c r="J5">
-        <v>-7.07</v>
+        <v>-8.34</v>
       </c>
       <c r="K5">
-        <v>8.01</v>
+        <v>1.45</v>
       </c>
       <c r="L5">
-        <v>-5.9</v>
+        <v>-6.89</v>
       </c>
       <c r="M5">
-        <v>15.42</v>
+        <v>15.57</v>
       </c>
       <c r="N5">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="O5">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="P5">
-        <v>1124.6</v>
+        <v>1123.38</v>
       </c>
       <c r="Q5">
-        <v>1157.43</v>
+        <v>1152.9</v>
       </c>
       <c r="R5">
-        <v>1249.51</v>
+        <v>1247.73</v>
       </c>
       <c r="S5">
-        <v>1069.49</v>
+        <v>1069.87</v>
       </c>
       <c r="T5">
-        <v>6.27</v>
+        <v>5.37</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1295,34 +1323,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>41.23</v>
+        <v>39.61</v>
       </c>
       <c r="Z5">
-        <v>-31.76</v>
+        <v>-30.62</v>
       </c>
       <c r="AA5">
-        <v>-31.73</v>
+        <v>-31.51</v>
       </c>
       <c r="AB5">
-        <v>-0.03</v>
+        <v>0.89</v>
       </c>
       <c r="AC5">
-        <v>59.1</v>
+        <v>68.45</v>
       </c>
       <c r="AD5">
-        <v>49.51</v>
+        <v>55.83</v>
       </c>
       <c r="AE5">
-        <v>41.63</v>
+        <v>40.3</v>
       </c>
       <c r="AF5">
-        <v>289.45</v>
+        <v>-70.06999999999999</v>
       </c>
       <c r="AG5">
-        <v>1225.16</v>
+        <v>1215.5</v>
       </c>
       <c r="AH5">
-        <v>1089.7</v>
+        <v>1090.29</v>
       </c>
       <c r="AI5">
         <v>1228.34</v>
@@ -1331,7 +1359,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>25.14</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1665.3</v>
+        <v>1678.2</v>
       </c>
       <c r="D6">
-        <v>0.36</v>
+        <v>0.77</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,46 +1382,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-28.23</v>
+        <v>-27.67</v>
       </c>
       <c r="H6">
-        <v>13.19</v>
+        <v>14.06</v>
       </c>
       <c r="I6">
-        <v>-12.66</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="J6">
-        <v>-18.92</v>
+        <v>-15.98</v>
       </c>
       <c r="K6">
-        <v>-6.88</v>
+        <v>-7.29</v>
       </c>
       <c r="L6">
-        <v>-16.44</v>
+        <v>-16.04</v>
       </c>
       <c r="M6">
-        <v>0.3</v>
+        <v>0.59</v>
       </c>
       <c r="N6">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O6">
         <v>33</v>
       </c>
       <c r="P6">
-        <v>1760.34</v>
+        <v>1724.56</v>
       </c>
       <c r="Q6">
-        <v>1943.11</v>
+        <v>1926.65</v>
       </c>
       <c r="R6">
-        <v>2023.96</v>
+        <v>2017.94</v>
       </c>
       <c r="S6">
-        <v>1856.51</v>
+        <v>1854.33</v>
       </c>
       <c r="T6">
-        <v>-10.3</v>
+        <v>-9.5</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1408,43 +1436,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>22.7</v>
+        <v>24.71</v>
       </c>
       <c r="Z6">
-        <v>-79.8</v>
+        <v>-87.27</v>
       </c>
       <c r="AA6">
-        <v>-43.42</v>
+        <v>-52.19</v>
       </c>
       <c r="AB6">
-        <v>-36.37</v>
+        <v>-35.08</v>
       </c>
       <c r="AC6">
-        <v>0.93</v>
+        <v>4.54</v>
       </c>
       <c r="AD6">
-        <v>2.84</v>
+        <v>3.09</v>
       </c>
       <c r="AE6">
-        <v>67.01000000000001</v>
+        <v>64.91</v>
       </c>
       <c r="AF6">
-        <v>10.13</v>
+        <v>-19.95</v>
       </c>
       <c r="AG6">
-        <v>2191.43</v>
+        <v>2199.48</v>
       </c>
       <c r="AH6">
-        <v>1694.79</v>
+        <v>1653.83</v>
       </c>
       <c r="AI6">
-        <v>1876.67</v>
+        <v>1871.22</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>41.7</v>
+        <v>45.89</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1605,12 +1633,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1618,734 +1681,751 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
+        <v>11.45</v>
+      </c>
+      <c r="D7" s="6">
+        <v>28.96</v>
+      </c>
+      <c r="E7" s="7">
+        <v>17.51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>11.52</v>
+      </c>
+      <c r="D8" s="6">
+        <v>11.02</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-7.63</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-6.23</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-7.07</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-8.34</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-18.92</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-15.98</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-0.13</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-0.77</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-3.9</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-3.12</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-0.23</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1.07</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-0.66</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-0.54</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-12.66</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="E16" s="7">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-22.84</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-11.22</v>
+      </c>
+      <c r="E17" s="7">
+        <v>11.62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-12.01</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-10.97</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-30.92</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-29.18</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-5.9</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-6.89</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-16.44</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-16.04</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-16.15</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-4.87</v>
+      </c>
+      <c r="E22" s="7">
+        <v>11.28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>12.81</v>
+      </c>
+      <c r="D23" s="6">
         <v>13.43</v>
       </c>
-      <c r="D7" s="5">
-        <v>11.45</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="E23" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-15.39</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-13.5</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>8.01</v>
+      </c>
+      <c r="D25" s="6">
+        <v>1.45</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-6.56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-6.88</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-7.29</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-27.95</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-17.81</v>
+      </c>
+      <c r="E27" s="7">
+        <v>10.14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>11.16</v>
-      </c>
-      <c r="D8" s="5">
-        <v>11.52</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-12.15</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-11.3</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-8.27</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-7.63</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-30.54</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-29.73</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-11.86</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-7.07</v>
-      </c>
-      <c r="E10" s="7">
-        <v>4.79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-19.83</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-20.48</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-16.62</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-18.92</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-28.23</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-27.67</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>21.97</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-0.13</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-22.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6">
+        <v>661.95</v>
+      </c>
+      <c r="D32" s="6">
+        <v>755.15</v>
+      </c>
+      <c r="E32" s="7">
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-3.04</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-3.9</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>647.35</v>
+      </c>
+      <c r="D33" s="6">
+        <v>653.6</v>
+      </c>
+      <c r="E33" s="7">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-0.57</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-0.23</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>863</v>
+      </c>
+      <c r="D34" s="6">
+        <v>873</v>
+      </c>
+      <c r="E34" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-4.81</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-0.66</v>
-      </c>
-      <c r="E15" s="7">
-        <v>4.15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1136.5</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1127.3</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-9.199999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-13.68</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-12.66</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>1665.3</v>
+      </c>
+      <c r="D36" s="6">
+        <v>1678.2</v>
+      </c>
+      <c r="E36" s="7">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-20.97</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-22.84</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="6">
+        <v>40</v>
+      </c>
+      <c r="D37" s="6">
+        <v>79</v>
+      </c>
+      <c r="E37" s="7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="6">
+        <v>79</v>
+      </c>
+      <c r="D38" s="6">
+        <v>60</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="6">
+        <v>60</v>
+      </c>
+      <c r="D39" s="6">
+        <v>40</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>55.17</v>
+      </c>
+      <c r="D40" s="6">
+        <v>66.28</v>
+      </c>
+      <c r="E40" s="7">
+        <v>11.11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-12.87</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-12.01</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>57.19</v>
+      </c>
+      <c r="D41" s="6">
+        <v>58.98</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-30.84</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-30.92</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>27.59</v>
+      </c>
+      <c r="D42" s="6">
+        <v>33.25</v>
+      </c>
+      <c r="E42" s="7">
+        <v>5.66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-8.51</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-5.9</v>
-      </c>
-      <c r="E20" s="7">
-        <v>2.61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>41.23</v>
+      </c>
+      <c r="D43" s="6">
+        <v>39.61</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-16.58</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-16.44</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="6">
+        <v>22.7</v>
+      </c>
+      <c r="D44" s="6">
+        <v>24.71</v>
+      </c>
+      <c r="E44" s="7">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-14.71</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-16.15</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-90.94</v>
+      </c>
+      <c r="D45" s="6">
+        <v>164.41</v>
+      </c>
+      <c r="E45" s="7">
+        <v>255.35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5">
-        <v>12.13</v>
-      </c>
-      <c r="D23" s="5">
-        <v>12.81</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-87.90000000000001</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-88.45999999999999</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-17.16</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-15.39</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-7.89</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-43.72</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-35.83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>4.04</v>
-      </c>
-      <c r="D25" s="5">
-        <v>8.01</v>
-      </c>
-      <c r="E25" s="7">
-        <v>3.97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="6">
+        <v>289.45</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-70.06999999999999</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-359.52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-7.53</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-6.88</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-26.67</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-27.95</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-12.42</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-12.15</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-31.4</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-30.54</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-22.13</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-19.83</v>
-      </c>
-      <c r="E30" s="7">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-28.49</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-28.23</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>673.7</v>
-      </c>
-      <c r="D32" s="5">
-        <v>661.95</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-11.75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>645.3</v>
-      </c>
-      <c r="D33" s="5">
-        <v>647.35</v>
-      </c>
-      <c r="E33" s="7">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>857</v>
-      </c>
-      <c r="D34" s="5">
-        <v>863</v>
-      </c>
-      <c r="E34" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5">
-        <v>1104</v>
-      </c>
-      <c r="D35" s="5">
-        <v>1136.5</v>
-      </c>
-      <c r="E35" s="7">
-        <v>32.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
-        <v>1659.3</v>
-      </c>
-      <c r="D36" s="5">
-        <v>1665.3</v>
-      </c>
-      <c r="E36" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="5">
-        <v>60</v>
-      </c>
-      <c r="D37" s="5">
-        <v>40</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="5">
-        <v>40</v>
-      </c>
-      <c r="D38" s="5">
-        <v>60</v>
-      </c>
-      <c r="E38" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>57.38</v>
-      </c>
-      <c r="D39" s="5">
-        <v>55.17</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>56.61</v>
-      </c>
-      <c r="D40" s="5">
-        <v>57.19</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>24</v>
-      </c>
-      <c r="D41" s="5">
-        <v>27.59</v>
-      </c>
-      <c r="E41" s="7">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="5">
-        <v>32.11</v>
-      </c>
-      <c r="D42" s="5">
-        <v>41.23</v>
-      </c>
-      <c r="E42" s="7">
-        <v>9.119999999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>21.8</v>
-      </c>
-      <c r="D43" s="5">
-        <v>22.7</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="B49" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="5">
-        <v>-87.48</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-90.94</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-80.19</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-87.90000000000001</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-7.71</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-26.13</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-7.89</v>
-      </c>
-      <c r="E46" s="7">
-        <v>18.24</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-57.09</v>
-      </c>
-      <c r="D47" s="5">
-        <v>289.45</v>
-      </c>
-      <c r="E47" s="7">
-        <v>346.54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="5">
-        <v>57.13</v>
-      </c>
-      <c r="D48" s="5">
+      <c r="C49" s="6">
         <v>10.13</v>
       </c>
-      <c r="E48" s="6">
-        <v>-47</v>
+      <c r="D49" s="6">
+        <v>-19.95</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-30.08</v>
       </c>
     </row>
   </sheetData>
@@ -2371,60 +2451,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="11">
+        <v>57.92</v>
+      </c>
+      <c r="C2" s="12">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11">
+        <v>44.6</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="10">
-        <v>49.92</v>
-      </c>
-      <c r="C2" s="11">
-        <v>5</v>
-      </c>
-      <c r="D2" s="10">
-        <v>40.8</v>
-      </c>
-      <c r="E2" s="10">
-        <v>40</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-2.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-3.5</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>1.9</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-2.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2526,37 +2606,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.1542</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.009599999999999999</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.003</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0394</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1371</v>
+      <c r="A2" s="14">
+        <v>0.1557</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0076</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0059</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0347</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1087</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,34 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>27.6 → 33.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>27.6</t>
-  </si>
-  <si>
-    <t>33.2</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -279,14 +252,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -319,13 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,15 +368,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -918,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>755.15</v>
+        <v>726.7</v>
       </c>
       <c r="D2">
-        <v>14.08</v>
+        <v>-3.77</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -930,46 +902,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-17.81</v>
+        <v>-20.9</v>
       </c>
       <c r="H2">
-        <v>44.71</v>
+        <v>39.25</v>
       </c>
       <c r="I2">
-        <v>-0.77</v>
+        <v>1.52</v>
       </c>
       <c r="J2">
-        <v>28.96</v>
+        <v>20.35</v>
       </c>
       <c r="K2">
-        <v>-4.87</v>
+        <v>-8.9</v>
       </c>
       <c r="L2">
-        <v>-11.22</v>
+        <v>-13.53</v>
       </c>
       <c r="M2">
-        <v>-10.87</v>
+        <v>-11.19</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="P2">
-        <v>701.28</v>
+        <v>703.46</v>
       </c>
       <c r="Q2">
-        <v>623.02</v>
+        <v>629.26</v>
       </c>
       <c r="R2">
-        <v>636.22</v>
+        <v>637.02</v>
       </c>
       <c r="S2">
-        <v>669.6900000000001</v>
+        <v>669.23</v>
       </c>
       <c r="T2">
-        <v>12.76</v>
+        <v>8.59</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -984,34 +956,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>66.28</v>
+        <v>61.29</v>
       </c>
       <c r="Z2">
-        <v>23.05</v>
+        <v>26.27</v>
       </c>
       <c r="AA2">
-        <v>6.08</v>
+        <v>10.12</v>
       </c>
       <c r="AB2">
-        <v>16.96</v>
+        <v>16.15</v>
       </c>
       <c r="AC2">
-        <v>67.05</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="AD2">
-        <v>67.76000000000001</v>
+        <v>67.09</v>
       </c>
       <c r="AE2">
-        <v>43.59</v>
+        <v>44.06</v>
       </c>
       <c r="AF2">
-        <v>164.41</v>
+        <v>-75.89</v>
       </c>
       <c r="AG2">
-        <v>757.11</v>
+        <v>770.63</v>
       </c>
       <c r="AH2">
-        <v>488.93</v>
+        <v>487.9</v>
       </c>
       <c r="AI2">
         <v>626.27</v>
@@ -1020,7 +992,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>53.65</v>
+        <v>53.69</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,58 +1003,58 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>653.6</v>
+        <v>661.6</v>
       </c>
       <c r="D3">
-        <v>0.97</v>
+        <v>1.22</v>
       </c>
       <c r="E3">
-        <v>736.85</v>
+        <v>734.85</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-11.3</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="H3">
-        <v>27.41</v>
+        <v>28.97</v>
       </c>
       <c r="I3">
-        <v>-3.12</v>
+        <v>-1.7</v>
       </c>
       <c r="J3">
-        <v>11.02</v>
+        <v>15.39</v>
       </c>
       <c r="K3">
-        <v>13.43</v>
+        <v>15.07</v>
       </c>
       <c r="L3">
-        <v>-10.97</v>
+        <v>-10.21</v>
       </c>
       <c r="M3">
-        <v>0.76</v>
+        <v>1.58</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P3">
-        <v>659.03</v>
+        <v>656.74</v>
       </c>
       <c r="Q3">
-        <v>637.0700000000001</v>
+        <v>641.0700000000001</v>
       </c>
       <c r="R3">
-        <v>594.21</v>
+        <v>596.21</v>
       </c>
       <c r="S3">
-        <v>582.45</v>
+        <v>582.71</v>
       </c>
       <c r="T3">
-        <v>12.22</v>
+        <v>13.54</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1097,34 +1069,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>58.98</v>
+        <v>61.22</v>
       </c>
       <c r="Z3">
-        <v>21.18</v>
+        <v>20.44</v>
       </c>
       <c r="AA3">
-        <v>22.81</v>
+        <v>22.33</v>
       </c>
       <c r="AB3">
-        <v>-1.63</v>
+        <v>-1.89</v>
       </c>
       <c r="AC3">
-        <v>5.42</v>
+        <v>13.9</v>
       </c>
       <c r="AD3">
-        <v>24.04</v>
+        <v>13.6</v>
       </c>
       <c r="AE3">
-        <v>22.59</v>
+        <v>22.71</v>
       </c>
       <c r="AF3">
-        <v>-88.45999999999999</v>
+        <v>-84.13</v>
       </c>
       <c r="AG3">
-        <v>705.83</v>
+        <v>705.42</v>
       </c>
       <c r="AH3">
-        <v>568.3200000000001</v>
+        <v>576.73</v>
       </c>
       <c r="AI3">
         <v>606.01</v>
@@ -1133,7 +1105,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>39</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1116,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="D4">
-        <v>1.16</v>
+        <v>0.8</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1156,46 +1128,46 @@
         <v>857</v>
       </c>
       <c r="G4">
-        <v>-29.73</v>
+        <v>-29.17</v>
       </c>
       <c r="H4">
-        <v>1.87</v>
+        <v>2.68</v>
       </c>
       <c r="I4">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="J4">
-        <v>-6.23</v>
+        <v>-5.38</v>
       </c>
       <c r="K4">
-        <v>-13.5</v>
+        <v>-12.05</v>
       </c>
       <c r="L4">
-        <v>-29.18</v>
+        <v>-29.06</v>
       </c>
       <c r="M4">
-        <v>-3.47</v>
+        <v>-3.13</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P4">
-        <v>865.58</v>
+        <v>867.6</v>
       </c>
       <c r="Q4">
-        <v>894.34</v>
+        <v>890.99</v>
       </c>
       <c r="R4">
-        <v>980.3099999999999</v>
+        <v>976.16</v>
       </c>
       <c r="S4">
-        <v>1074.07</v>
+        <v>1072.87</v>
       </c>
       <c r="T4">
-        <v>-18.72</v>
+        <v>-17.98</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1210,34 +1182,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>33.25</v>
+        <v>36.97</v>
       </c>
       <c r="Z4">
-        <v>-32.71</v>
+        <v>-30.12</v>
       </c>
       <c r="AA4">
-        <v>-35.29</v>
+        <v>-34.26</v>
       </c>
       <c r="AB4">
-        <v>2.59</v>
+        <v>4.14</v>
       </c>
       <c r="AC4">
-        <v>62.15</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AD4">
-        <v>46.32</v>
+        <v>63.54</v>
       </c>
       <c r="AE4">
-        <v>19.47</v>
+        <v>19.19</v>
       </c>
       <c r="AF4">
-        <v>-43.72</v>
+        <v>-8.67</v>
       </c>
       <c r="AG4">
-        <v>953.49</v>
+        <v>944.9400000000001</v>
       </c>
       <c r="AH4">
-        <v>835.1900000000001</v>
+        <v>837.04</v>
       </c>
       <c r="AI4">
         <v>924.5700000000001</v>
@@ -1246,7 +1218,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>65.54000000000001</v>
+        <v>58.57</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1127.3</v>
+        <v>1107.4</v>
       </c>
       <c r="D5">
-        <v>-0.8100000000000001</v>
+        <v>-1.77</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1269,46 +1241,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-20.48</v>
+        <v>-21.89</v>
       </c>
       <c r="H5">
-        <v>50.51</v>
+        <v>47.85</v>
       </c>
       <c r="I5">
-        <v>-0.54</v>
+        <v>-1.33</v>
       </c>
       <c r="J5">
-        <v>-8.34</v>
+        <v>-9.08</v>
       </c>
       <c r="K5">
-        <v>1.45</v>
+        <v>-0.45</v>
       </c>
       <c r="L5">
-        <v>-6.89</v>
+        <v>-10.94</v>
       </c>
       <c r="M5">
-        <v>15.57</v>
+        <v>14.84</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="P5">
-        <v>1123.38</v>
+        <v>1120.4</v>
       </c>
       <c r="Q5">
-        <v>1152.9</v>
+        <v>1147.1</v>
       </c>
       <c r="R5">
-        <v>1247.73</v>
+        <v>1245.49</v>
       </c>
       <c r="S5">
-        <v>1069.87</v>
+        <v>1070.15</v>
       </c>
       <c r="T5">
-        <v>5.37</v>
+        <v>3.48</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1323,34 +1295,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>39.61</v>
+        <v>36.29</v>
       </c>
       <c r="Z5">
-        <v>-30.62</v>
+        <v>-30.96</v>
       </c>
       <c r="AA5">
-        <v>-31.51</v>
+        <v>-31.4</v>
       </c>
       <c r="AB5">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="AC5">
-        <v>68.45</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="AD5">
-        <v>55.83</v>
+        <v>67.84</v>
       </c>
       <c r="AE5">
-        <v>40.3</v>
+        <v>40.09</v>
       </c>
       <c r="AF5">
-        <v>-70.06999999999999</v>
+        <v>-6.96</v>
       </c>
       <c r="AG5">
-        <v>1215.5</v>
+        <v>1203.37</v>
       </c>
       <c r="AH5">
-        <v>1090.29</v>
+        <v>1090.82</v>
       </c>
       <c r="AI5">
         <v>1228.34</v>
@@ -1359,7 +1331,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>23.7</v>
+        <v>22.33</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,7 +1342,7 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1678.2</v>
+        <v>1691.1</v>
       </c>
       <c r="D6">
         <v>0.77</v>
@@ -1382,46 +1354,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-27.67</v>
+        <v>-27.12</v>
       </c>
       <c r="H6">
-        <v>14.06</v>
+        <v>14.94</v>
       </c>
       <c r="I6">
-        <v>-9.630000000000001</v>
+        <v>-9.66</v>
       </c>
       <c r="J6">
-        <v>-15.98</v>
+        <v>-15.75</v>
       </c>
       <c r="K6">
-        <v>-7.29</v>
+        <v>-5.84</v>
       </c>
       <c r="L6">
-        <v>-16.04</v>
+        <v>-16.96</v>
       </c>
       <c r="M6">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P6">
-        <v>1724.56</v>
+        <v>1688.38</v>
       </c>
       <c r="Q6">
-        <v>1926.65</v>
+        <v>1910.21</v>
       </c>
       <c r="R6">
-        <v>2017.94</v>
+        <v>2011.16</v>
       </c>
       <c r="S6">
-        <v>1854.33</v>
+        <v>1852.3</v>
       </c>
       <c r="T6">
-        <v>-9.5</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1436,34 +1408,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>24.71</v>
+        <v>26.77</v>
       </c>
       <c r="Z6">
-        <v>-87.27</v>
+        <v>-91.09999999999999</v>
       </c>
       <c r="AA6">
-        <v>-52.19</v>
+        <v>-59.97</v>
       </c>
       <c r="AB6">
-        <v>-35.08</v>
+        <v>-31.12</v>
       </c>
       <c r="AC6">
-        <v>4.54</v>
+        <v>11.11</v>
       </c>
       <c r="AD6">
-        <v>3.09</v>
+        <v>5.53</v>
       </c>
       <c r="AE6">
-        <v>64.91</v>
+        <v>63.35</v>
       </c>
       <c r="AF6">
-        <v>-19.95</v>
+        <v>-6.66</v>
       </c>
       <c r="AG6">
-        <v>2199.48</v>
+        <v>2198.55</v>
       </c>
       <c r="AH6">
-        <v>1653.83</v>
+        <v>1621.87</v>
       </c>
       <c r="AI6">
         <v>1871.22</v>
@@ -1472,7 +1444,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>45.89</v>
+        <v>47.1</v>
       </c>
     </row>
   </sheetData>
@@ -1613,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1633,47 +1605,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1681,751 +1618,700 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>11.45</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>28.96</v>
       </c>
-      <c r="E7" s="7">
-        <v>17.51</v>
+      <c r="D7" s="5">
+        <v>20.35</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-8.609999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>11.52</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>11.02</v>
       </c>
-      <c r="E8" s="8">
-        <v>-0.5</v>
+      <c r="D8" s="5">
+        <v>15.39</v>
+      </c>
+      <c r="E8" s="7">
+        <v>4.37</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-7.63</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-6.23</v>
       </c>
+      <c r="D9" s="5">
+        <v>-5.38</v>
+      </c>
       <c r="E9" s="7">
-        <v>1.4</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-7.07</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-8.34</v>
       </c>
-      <c r="E10" s="8">
-        <v>-1.27</v>
+      <c r="D10" s="5">
+        <v>-9.08</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-18.92</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-15.98</v>
       </c>
+      <c r="D11" s="5">
+        <v>-15.75</v>
+      </c>
       <c r="E11" s="7">
-        <v>2.94</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-0.13</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-0.77</v>
       </c>
-      <c r="E12" s="8">
-        <v>-0.64</v>
+      <c r="D12" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.29</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
-        <v>-3.9</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-3.12</v>
       </c>
+      <c r="D13" s="5">
+        <v>-1.7</v>
+      </c>
       <c r="E13" s="7">
-        <v>0.78</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>-0.23</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>1.07</v>
       </c>
+      <c r="D14" s="5">
+        <v>1.16</v>
+      </c>
       <c r="E14" s="7">
-        <v>1.3</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-0.66</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-0.54</v>
       </c>
-      <c r="E15" s="7">
+      <c r="D15" s="5">
+        <v>-1.33</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-9.66</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-11.22</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-13.53</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-10.97</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-10.21</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-29.18</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-29.06</v>
+      </c>
+      <c r="E19" s="7">
         <v>0.12</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-6.89</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-10.94</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-4.05</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-16.04</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-16.96</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-4.87</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-8.9</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-4.03</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>13.43</v>
+      </c>
+      <c r="D23" s="5">
+        <v>15.07</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-13.5</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-12.05</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>1.45</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-0.45</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-7.29</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-5.84</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-17.81</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-20.9</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-11.3</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-29.73</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-29.17</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-20.48</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-21.89</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-1.41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-27.67</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-27.12</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>755.15</v>
+      </c>
+      <c r="D32" s="5">
+        <v>726.7</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-28.45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>653.6</v>
+      </c>
+      <c r="D33" s="5">
+        <v>661.6</v>
+      </c>
+      <c r="E33" s="7">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-12.66</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="E16" s="7">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-22.84</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-11.22</v>
-      </c>
-      <c r="E17" s="7">
-        <v>11.62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-12.01</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-10.97</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-30.92</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-29.18</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>873</v>
+      </c>
+      <c r="D34" s="5">
+        <v>880</v>
+      </c>
+      <c r="E34" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-5.9</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-6.89</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1127.3</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1107.4</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-19.9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-16.44</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-16.04</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-16.15</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-4.87</v>
-      </c>
-      <c r="E22" s="7">
-        <v>11.28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>12.81</v>
-      </c>
-      <c r="D23" s="6">
-        <v>13.43</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-15.39</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-13.5</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>8.01</v>
-      </c>
-      <c r="D25" s="6">
-        <v>1.45</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-6.56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-6.88</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-7.29</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-27.95</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-17.81</v>
-      </c>
-      <c r="E27" s="7">
-        <v>10.14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-12.15</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-11.3</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-30.54</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-29.73</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-19.83</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-20.48</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-28.23</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-27.67</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
+      <c r="B36" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="6">
-        <v>661.95</v>
-      </c>
-      <c r="D32" s="6">
-        <v>755.15</v>
-      </c>
-      <c r="E32" s="7">
-        <v>93.2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>647.35</v>
-      </c>
-      <c r="D33" s="6">
-        <v>653.6</v>
-      </c>
-      <c r="E33" s="7">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>863</v>
-      </c>
-      <c r="D34" s="6">
-        <v>873</v>
-      </c>
-      <c r="E34" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1136.5</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1127.3</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-9.199999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>1665.3</v>
-      </c>
-      <c r="D36" s="6">
+      <c r="C36" s="5">
         <v>1678.2</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1691.1</v>
       </c>
       <c r="E36" s="7">
         <v>12.9</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="6">
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>66.28</v>
+      </c>
+      <c r="D37" s="5">
+        <v>61.29</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-4.99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>58.98</v>
+      </c>
+      <c r="D38" s="5">
+        <v>61.22</v>
+      </c>
+      <c r="E38" s="7">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>33.25</v>
+      </c>
+      <c r="D39" s="5">
+        <v>36.97</v>
+      </c>
+      <c r="E39" s="7">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="6">
-        <v>79</v>
-      </c>
-      <c r="E37" s="7">
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>39.61</v>
+      </c>
+      <c r="D40" s="5">
+        <v>36.29</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-3.32</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>24.71</v>
+      </c>
+      <c r="D41" s="5">
+        <v>26.77</v>
+      </c>
+      <c r="E41" s="7">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>164.41</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-75.89</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-240.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-88.45999999999999</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-84.13</v>
+      </c>
+      <c r="E43" s="7">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-43.72</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-8.67</v>
+      </c>
+      <c r="E44" s="7">
+        <v>35.05</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="6">
-        <v>79</v>
-      </c>
-      <c r="D38" s="6">
-        <v>60</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-70.06999999999999</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-6.96</v>
+      </c>
+      <c r="E45" s="7">
+        <v>63.11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="6">
-        <v>60</v>
-      </c>
-      <c r="D39" s="6">
-        <v>40</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>55.17</v>
-      </c>
-      <c r="D40" s="6">
-        <v>66.28</v>
-      </c>
-      <c r="E40" s="7">
-        <v>11.11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>57.19</v>
-      </c>
-      <c r="D41" s="6">
-        <v>58.98</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>27.59</v>
-      </c>
-      <c r="D42" s="6">
-        <v>33.25</v>
-      </c>
-      <c r="E42" s="7">
-        <v>5.66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>41.23</v>
-      </c>
-      <c r="D43" s="6">
-        <v>39.61</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="6">
-        <v>22.7</v>
-      </c>
-      <c r="D44" s="6">
-        <v>24.71</v>
-      </c>
-      <c r="E44" s="7">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="6">
-        <v>-90.94</v>
-      </c>
-      <c r="D45" s="6">
-        <v>164.41</v>
-      </c>
-      <c r="E45" s="7">
-        <v>255.35</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-87.90000000000001</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-88.45999999999999</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-7.89</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-43.72</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-35.83</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>289.45</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-70.06999999999999</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-359.52</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="6">
-        <v>10.13</v>
-      </c>
-      <c r="D49" s="6">
+      <c r="C46" s="5">
         <v>-19.95</v>
       </c>
-      <c r="E49" s="8">
-        <v>-30.08</v>
+      <c r="D46" s="5">
+        <v>-6.66</v>
+      </c>
+      <c r="E46" s="7">
+        <v>13.29</v>
       </c>
     </row>
   </sheetData>
@@ -2451,60 +2337,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>57.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>44.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>44.5</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>1.9</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-2.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>1.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-2.4</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2606,37 +2492,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1557</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0076</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0059</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0347</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1087</v>
+      <c r="A2" s="13">
+        <v>0.1484</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0158</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.0313</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1119</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -890,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>726.7</v>
+        <v>719.45</v>
       </c>
       <c r="D2">
-        <v>-3.77</v>
+        <v>-1</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,25 +902,25 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-20.9</v>
+        <v>-21.69</v>
       </c>
       <c r="H2">
-        <v>39.25</v>
+        <v>37.87</v>
       </c>
       <c r="I2">
-        <v>1.52</v>
+        <v>2.81</v>
       </c>
       <c r="J2">
-        <v>20.35</v>
+        <v>19.55</v>
       </c>
       <c r="K2">
-        <v>-8.9</v>
+        <v>-7.47</v>
       </c>
       <c r="L2">
-        <v>-13.53</v>
+        <v>-13.99</v>
       </c>
       <c r="M2">
-        <v>-11.19</v>
+        <v>-11.45</v>
       </c>
       <c r="N2">
         <v>79</v>
@@ -929,19 +929,19 @@
         <v>52</v>
       </c>
       <c r="P2">
-        <v>703.46</v>
+        <v>707.39</v>
       </c>
       <c r="Q2">
-        <v>629.26</v>
+        <v>635.14</v>
       </c>
       <c r="R2">
-        <v>637.02</v>
+        <v>637.62</v>
       </c>
       <c r="S2">
-        <v>669.23</v>
+        <v>668.84</v>
       </c>
       <c r="T2">
-        <v>8.59</v>
+        <v>7.57</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -956,34 +956,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>61.29</v>
+        <v>60.04</v>
       </c>
       <c r="Z2">
-        <v>26.27</v>
+        <v>27.92</v>
       </c>
       <c r="AA2">
-        <v>10.12</v>
+        <v>13.68</v>
       </c>
       <c r="AB2">
-        <v>16.15</v>
+        <v>14.24</v>
       </c>
       <c r="AC2">
-        <v>69.54000000000001</v>
+        <v>72.39</v>
       </c>
       <c r="AD2">
-        <v>67.09</v>
+        <v>69.66</v>
       </c>
       <c r="AE2">
-        <v>44.06</v>
+        <v>42.04</v>
       </c>
       <c r="AF2">
-        <v>-75.89</v>
+        <v>-94.55</v>
       </c>
       <c r="AG2">
-        <v>770.63</v>
+        <v>781.41</v>
       </c>
       <c r="AH2">
-        <v>487.9</v>
+        <v>488.88</v>
       </c>
       <c r="AI2">
         <v>626.27</v>
@@ -992,7 +992,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>53.69</v>
+        <v>53.19</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,10 +1003,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>661.6</v>
+        <v>660.65</v>
       </c>
       <c r="D3">
-        <v>1.22</v>
+        <v>-0.14</v>
       </c>
       <c r="E3">
         <v>734.85</v>
@@ -1015,25 +1015,25 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-9.970000000000001</v>
+        <v>-10.1</v>
       </c>
       <c r="H3">
-        <v>28.97</v>
+        <v>28.78</v>
       </c>
       <c r="I3">
-        <v>-1.7</v>
+        <v>-2.25</v>
       </c>
       <c r="J3">
-        <v>15.39</v>
+        <v>13.58</v>
       </c>
       <c r="K3">
-        <v>15.07</v>
+        <v>14.49</v>
       </c>
       <c r="L3">
-        <v>-10.21</v>
+        <v>-9.69</v>
       </c>
       <c r="M3">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1042,19 +1042,19 @@
         <v>68</v>
       </c>
       <c r="P3">
-        <v>656.74</v>
+        <v>653.7</v>
       </c>
       <c r="Q3">
-        <v>641.0700000000001</v>
+        <v>645.38</v>
       </c>
       <c r="R3">
-        <v>596.21</v>
+        <v>598.1799999999999</v>
       </c>
       <c r="S3">
-        <v>582.71</v>
+        <v>583.03</v>
       </c>
       <c r="T3">
-        <v>13.54</v>
+        <v>13.31</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1069,34 +1069,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>61.22</v>
+        <v>60.8</v>
       </c>
       <c r="Z3">
-        <v>20.44</v>
+        <v>19.56</v>
       </c>
       <c r="AA3">
-        <v>22.33</v>
+        <v>21.78</v>
       </c>
       <c r="AB3">
-        <v>-1.89</v>
+        <v>-2.22</v>
       </c>
       <c r="AC3">
-        <v>13.9</v>
+        <v>20.54</v>
       </c>
       <c r="AD3">
-        <v>13.6</v>
+        <v>13.29</v>
       </c>
       <c r="AE3">
-        <v>22.71</v>
+        <v>22.7</v>
       </c>
       <c r="AF3">
-        <v>-84.13</v>
+        <v>-81.18000000000001</v>
       </c>
       <c r="AG3">
-        <v>705.42</v>
+        <v>702.05</v>
       </c>
       <c r="AH3">
-        <v>576.73</v>
+        <v>588.71</v>
       </c>
       <c r="AI3">
         <v>606.01</v>
@@ -1105,7 +1105,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>36.99</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,10 +1116,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>880</v>
+        <v>867.5</v>
       </c>
       <c r="D4">
-        <v>0.8</v>
+        <v>-1.42</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1128,46 +1128,46 @@
         <v>857</v>
       </c>
       <c r="G4">
-        <v>-29.17</v>
+        <v>-30.18</v>
       </c>
       <c r="H4">
-        <v>2.68</v>
+        <v>1.23</v>
       </c>
       <c r="I4">
-        <v>1.16</v>
+        <v>0.29</v>
       </c>
       <c r="J4">
-        <v>-5.38</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="K4">
-        <v>-12.05</v>
+        <v>-14.91</v>
       </c>
       <c r="L4">
-        <v>-29.06</v>
+        <v>-28.47</v>
       </c>
       <c r="M4">
-        <v>-3.13</v>
+        <v>-3.41</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P4">
-        <v>867.6</v>
+        <v>868.1</v>
       </c>
       <c r="Q4">
-        <v>890.99</v>
+        <v>887.72</v>
       </c>
       <c r="R4">
-        <v>976.16</v>
+        <v>971.75</v>
       </c>
       <c r="S4">
-        <v>1072.87</v>
+        <v>1071.6</v>
       </c>
       <c r="T4">
-        <v>-17.98</v>
+        <v>-19.05</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1182,34 +1182,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>36.97</v>
+        <v>33.39</v>
       </c>
       <c r="Z4">
-        <v>-30.12</v>
+        <v>-28.74</v>
       </c>
       <c r="AA4">
-        <v>-34.26</v>
+        <v>-33.15</v>
       </c>
       <c r="AB4">
-        <v>4.14</v>
+        <v>4.41</v>
       </c>
       <c r="AC4">
-        <v>87.40000000000001</v>
+        <v>92.19</v>
       </c>
       <c r="AD4">
-        <v>63.54</v>
+        <v>80.58</v>
       </c>
       <c r="AE4">
-        <v>19.19</v>
+        <v>19.6</v>
       </c>
       <c r="AF4">
-        <v>-8.67</v>
+        <v>-37.22</v>
       </c>
       <c r="AG4">
-        <v>944.9400000000001</v>
+        <v>938.8099999999999</v>
       </c>
       <c r="AH4">
-        <v>837.04</v>
+        <v>836.62</v>
       </c>
       <c r="AI4">
         <v>924.5700000000001</v>
@@ -1218,7 +1218,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>58.57</v>
+        <v>50.95</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1107.4</v>
+        <v>1101.7</v>
       </c>
       <c r="D5">
-        <v>-1.77</v>
+        <v>-0.51</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,46 +1241,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-21.89</v>
+        <v>-22.29</v>
       </c>
       <c r="H5">
-        <v>47.85</v>
+        <v>47.09</v>
       </c>
       <c r="I5">
-        <v>-1.33</v>
+        <v>-2.23</v>
       </c>
       <c r="J5">
-        <v>-9.08</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="K5">
-        <v>-0.45</v>
+        <v>-1.23</v>
       </c>
       <c r="L5">
-        <v>-10.94</v>
+        <v>-9.83</v>
       </c>
       <c r="M5">
-        <v>14.84</v>
+        <v>14.71</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P5">
-        <v>1120.4</v>
+        <v>1115.38</v>
       </c>
       <c r="Q5">
-        <v>1147.1</v>
+        <v>1140.68</v>
       </c>
       <c r="R5">
-        <v>1245.49</v>
+        <v>1239.17</v>
       </c>
       <c r="S5">
-        <v>1070.15</v>
+        <v>1070.43</v>
       </c>
       <c r="T5">
-        <v>3.48</v>
+        <v>2.92</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1295,43 +1295,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>36.29</v>
+        <v>35.37</v>
       </c>
       <c r="Z5">
-        <v>-30.96</v>
+        <v>-31.33</v>
       </c>
       <c r="AA5">
-        <v>-31.4</v>
+        <v>-31.39</v>
       </c>
       <c r="AB5">
-        <v>0.44</v>
+        <v>0.05</v>
       </c>
       <c r="AC5">
-        <v>75.98999999999999</v>
+        <v>54.55</v>
       </c>
       <c r="AD5">
-        <v>67.84</v>
+        <v>66.33</v>
       </c>
       <c r="AE5">
-        <v>40.09</v>
+        <v>38.44</v>
       </c>
       <c r="AF5">
-        <v>-6.96</v>
+        <v>-74.36</v>
       </c>
       <c r="AG5">
-        <v>1203.37</v>
+        <v>1185.18</v>
       </c>
       <c r="AH5">
-        <v>1090.82</v>
+        <v>1096.18</v>
       </c>
       <c r="AI5">
-        <v>1228.34</v>
+        <v>1222.72</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>22.33</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1691.1</v>
+        <v>1696.9</v>
       </c>
       <c r="D6">
-        <v>0.77</v>
+        <v>0.34</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,46 +1354,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-27.12</v>
+        <v>-26.87</v>
       </c>
       <c r="H6">
-        <v>14.94</v>
+        <v>15.33</v>
       </c>
       <c r="I6">
-        <v>-9.66</v>
+        <v>-2.92</v>
       </c>
       <c r="J6">
-        <v>-15.75</v>
+        <v>-16</v>
       </c>
       <c r="K6">
-        <v>-5.84</v>
+        <v>-5.67</v>
       </c>
       <c r="L6">
-        <v>-16.96</v>
+        <v>-17.67</v>
       </c>
       <c r="M6">
-        <v>0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P6">
-        <v>1688.38</v>
+        <v>1678.16</v>
       </c>
       <c r="Q6">
-        <v>1910.21</v>
+        <v>1893.3</v>
       </c>
       <c r="R6">
-        <v>2011.16</v>
+        <v>2002.44</v>
       </c>
       <c r="S6">
-        <v>1852.3</v>
+        <v>1850.3</v>
       </c>
       <c r="T6">
-        <v>-8.699999999999999</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1408,34 +1408,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>26.77</v>
+        <v>27.72</v>
       </c>
       <c r="Z6">
-        <v>-91.09999999999999</v>
+        <v>-92.59999999999999</v>
       </c>
       <c r="AA6">
-        <v>-59.97</v>
+        <v>-66.5</v>
       </c>
       <c r="AB6">
-        <v>-31.12</v>
+        <v>-26.1</v>
       </c>
       <c r="AC6">
-        <v>11.11</v>
+        <v>18.15</v>
       </c>
       <c r="AD6">
-        <v>5.53</v>
+        <v>11.26</v>
       </c>
       <c r="AE6">
-        <v>63.35</v>
+        <v>60.95</v>
       </c>
       <c r="AF6">
-        <v>-6.66</v>
+        <v>-44.43</v>
       </c>
       <c r="AG6">
-        <v>2198.55</v>
+        <v>2190.35</v>
       </c>
       <c r="AH6">
-        <v>1621.87</v>
+        <v>1596.26</v>
       </c>
       <c r="AI6">
         <v>1871.22</v>
@@ -1444,7 +1444,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>47.1</v>
+        <v>48.15</v>
       </c>
     </row>
   </sheetData>
@@ -1642,13 +1642,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>28.96</v>
+        <v>20.35</v>
       </c>
       <c r="D7" s="5">
-        <v>20.35</v>
+        <v>19.55</v>
       </c>
       <c r="E7" s="6">
-        <v>-8.609999999999999</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1659,13 +1659,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>11.02</v>
+        <v>15.39</v>
       </c>
       <c r="D8" s="5">
-        <v>15.39</v>
-      </c>
-      <c r="E8" s="7">
-        <v>4.37</v>
+        <v>13.58</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1676,13 +1676,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-6.23</v>
+        <v>-5.38</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.38</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.85</v>
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-3.01</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1693,13 +1693,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-8.34</v>
+        <v>-9.08</v>
       </c>
       <c r="D10" s="5">
-        <v>-9.08</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="E10" s="6">
-        <v>-0.74</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1710,13 +1710,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-15.98</v>
+        <v>-15.75</v>
       </c>
       <c r="D11" s="5">
-        <v>-15.75</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.23</v>
+        <v>-16</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1727,13 +1727,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-0.77</v>
+        <v>1.52</v>
       </c>
       <c r="D12" s="5">
-        <v>1.52</v>
+        <v>2.81</v>
       </c>
       <c r="E12" s="7">
-        <v>2.29</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1744,13 +1744,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-3.12</v>
+        <v>-1.7</v>
       </c>
       <c r="D13" s="5">
-        <v>-1.7</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.42</v>
+        <v>-2.25</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1761,13 +1761,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="D14" s="5">
-        <v>1.16</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.09</v>
+        <v>0.29</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1778,13 +1778,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-0.54</v>
+        <v>-1.33</v>
       </c>
       <c r="D15" s="5">
-        <v>-1.33</v>
+        <v>-2.23</v>
       </c>
       <c r="E15" s="6">
-        <v>-0.79</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1795,13 +1795,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-9.630000000000001</v>
+        <v>-9.66</v>
       </c>
       <c r="D16" s="5">
-        <v>-9.66</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-0.03</v>
+        <v>-2.92</v>
+      </c>
+      <c r="E16" s="7">
+        <v>6.74</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1812,13 +1812,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>-11.22</v>
+        <v>-13.53</v>
       </c>
       <c r="D17" s="5">
-        <v>-13.53</v>
+        <v>-13.99</v>
       </c>
       <c r="E17" s="6">
-        <v>-2.31</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1829,13 +1829,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-10.97</v>
+        <v>-10.21</v>
       </c>
       <c r="D18" s="5">
-        <v>-10.21</v>
+        <v>-9.69</v>
       </c>
       <c r="E18" s="7">
-        <v>0.76</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1846,13 +1846,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-29.18</v>
+        <v>-29.06</v>
       </c>
       <c r="D19" s="5">
-        <v>-29.06</v>
+        <v>-28.47</v>
       </c>
       <c r="E19" s="7">
-        <v>0.12</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1863,13 +1863,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-6.89</v>
+        <v>-10.94</v>
       </c>
       <c r="D20" s="5">
-        <v>-10.94</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-4.05</v>
+        <v>-9.83</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.11</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1880,13 +1880,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-16.04</v>
+        <v>-16.96</v>
       </c>
       <c r="D21" s="5">
-        <v>-16.96</v>
+        <v>-17.67</v>
       </c>
       <c r="E21" s="6">
-        <v>-0.92</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1897,13 +1897,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-4.87</v>
+        <v>-8.9</v>
       </c>
       <c r="D22" s="5">
-        <v>-8.9</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-4.03</v>
+        <v>-7.47</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.43</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1914,13 +1914,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>13.43</v>
+        <v>15.07</v>
       </c>
       <c r="D23" s="5">
-        <v>15.07</v>
-      </c>
-      <c r="E23" s="7">
-        <v>1.64</v>
+        <v>14.49</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1931,13 +1931,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-13.5</v>
+        <v>-12.05</v>
       </c>
       <c r="D24" s="5">
-        <v>-12.05</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.45</v>
+        <v>-14.91</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-2.86</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1948,13 +1948,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>1.45</v>
+        <v>-0.45</v>
       </c>
       <c r="D25" s="5">
-        <v>-0.45</v>
+        <v>-1.23</v>
       </c>
       <c r="E25" s="6">
-        <v>-1.9</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1965,13 +1965,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-7.29</v>
+        <v>-5.84</v>
       </c>
       <c r="D26" s="5">
-        <v>-5.84</v>
+        <v>-5.67</v>
       </c>
       <c r="E26" s="7">
-        <v>1.45</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1982,13 +1982,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-17.81</v>
+        <v>-20.9</v>
       </c>
       <c r="D27" s="5">
-        <v>-20.9</v>
+        <v>-21.69</v>
       </c>
       <c r="E27" s="6">
-        <v>-3.09</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1999,13 +1999,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-11.3</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="D28" s="5">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.33</v>
+        <v>-10.1</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2016,13 +2016,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-29.73</v>
+        <v>-29.17</v>
       </c>
       <c r="D29" s="5">
-        <v>-29.17</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.5600000000000001</v>
+        <v>-30.18</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2033,13 +2033,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-20.48</v>
+        <v>-21.89</v>
       </c>
       <c r="D30" s="5">
-        <v>-21.89</v>
+        <v>-22.29</v>
       </c>
       <c r="E30" s="6">
-        <v>-1.41</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2050,13 +2050,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-27.67</v>
+        <v>-27.12</v>
       </c>
       <c r="D31" s="5">
-        <v>-27.12</v>
+        <v>-26.87</v>
       </c>
       <c r="E31" s="7">
-        <v>0.55</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2067,13 +2067,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>755.15</v>
+        <v>726.7</v>
       </c>
       <c r="D32" s="5">
-        <v>726.7</v>
+        <v>719.45</v>
       </c>
       <c r="E32" s="6">
-        <v>-28.45</v>
+        <v>-7.25</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2084,13 +2084,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>653.6</v>
+        <v>661.6</v>
       </c>
       <c r="D33" s="5">
-        <v>661.6</v>
-      </c>
-      <c r="E33" s="7">
-        <v>8</v>
+        <v>660.65</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2101,13 +2101,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="D34" s="5">
-        <v>880</v>
-      </c>
-      <c r="E34" s="7">
-        <v>7</v>
+        <v>867.5</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-12.5</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2118,13 +2118,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>1127.3</v>
+        <v>1107.4</v>
       </c>
       <c r="D35" s="5">
-        <v>1107.4</v>
+        <v>1101.7</v>
       </c>
       <c r="E35" s="6">
-        <v>-19.9</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2135,13 +2135,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>1678.2</v>
+        <v>1691.1</v>
       </c>
       <c r="D36" s="5">
-        <v>1691.1</v>
+        <v>1696.9</v>
       </c>
       <c r="E36" s="7">
-        <v>12.9</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="C37" s="5">
-        <v>66.28</v>
+        <v>61.29</v>
       </c>
       <c r="D37" s="5">
-        <v>61.29</v>
+        <v>60.04</v>
       </c>
       <c r="E37" s="6">
-        <v>-4.99</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2169,13 +2169,13 @@
         <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>58.98</v>
+        <v>61.22</v>
       </c>
       <c r="D38" s="5">
-        <v>61.22</v>
-      </c>
-      <c r="E38" s="7">
-        <v>2.24</v>
+        <v>60.8</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2186,13 +2186,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>33.25</v>
+        <v>36.97</v>
       </c>
       <c r="D39" s="5">
-        <v>36.97</v>
-      </c>
-      <c r="E39" s="7">
-        <v>3.72</v>
+        <v>33.39</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-3.58</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2203,13 +2203,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>39.61</v>
+        <v>36.29</v>
       </c>
       <c r="D40" s="5">
-        <v>36.29</v>
+        <v>35.37</v>
       </c>
       <c r="E40" s="6">
-        <v>-3.32</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2220,13 +2220,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>24.71</v>
+        <v>26.77</v>
       </c>
       <c r="D41" s="5">
-        <v>26.77</v>
+        <v>27.72</v>
       </c>
       <c r="E41" s="7">
-        <v>2.06</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2237,13 +2237,13 @@
         <v>31</v>
       </c>
       <c r="C42" s="5">
-        <v>164.41</v>
+        <v>-75.89</v>
       </c>
       <c r="D42" s="5">
-        <v>-75.89</v>
+        <v>-94.55</v>
       </c>
       <c r="E42" s="6">
-        <v>-240.3</v>
+        <v>-18.66</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2254,13 +2254,13 @@
         <v>31</v>
       </c>
       <c r="C43" s="5">
-        <v>-88.45999999999999</v>
+        <v>-84.13</v>
       </c>
       <c r="D43" s="5">
-        <v>-84.13</v>
+        <v>-81.18000000000001</v>
       </c>
       <c r="E43" s="7">
-        <v>4.33</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2271,13 +2271,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>-43.72</v>
+        <v>-8.67</v>
       </c>
       <c r="D44" s="5">
-        <v>-8.67</v>
-      </c>
-      <c r="E44" s="7">
-        <v>35.05</v>
+        <v>-37.22</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-28.55</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2288,13 +2288,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-70.06999999999999</v>
+        <v>-6.96</v>
       </c>
       <c r="D45" s="5">
-        <v>-6.96</v>
-      </c>
-      <c r="E45" s="7">
-        <v>63.11</v>
+        <v>-74.36</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-67.40000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2305,13 +2305,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>-19.95</v>
+        <v>-6.66</v>
       </c>
       <c r="D46" s="5">
-        <v>-6.66</v>
-      </c>
-      <c r="E46" s="7">
-        <v>13.29</v>
+        <v>-44.43</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-37.77</v>
       </c>
     </row>
   </sheetData>
@@ -2376,16 +2376,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>44.5</v>
+        <v>43.5</v>
       </c>
       <c r="E2" s="10">
         <v>60</v>
       </c>
       <c r="F2" s="10">
-        <v>1.1</v>
+        <v>-0.2</v>
       </c>
       <c r="G2" s="10">
-        <v>-2.4</v>
+        <v>-3</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2510,19 +2510,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.1484</v>
+        <v>0.1471</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0158</v>
+        <v>0.0173</v>
       </c>
       <c r="C2" s="13">
-        <v>0.005600000000000001</v>
+        <v>-0.0031</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.0313</v>
+        <v>-0.0341</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1119</v>
+        <v>-0.1145</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -151,12 +151,12 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>UP</t>
   </si>
   <si>
@@ -166,7 +166,28 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -252,14 +273,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +313,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,14 +389,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -750,7 +772,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -890,10 +913,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>719.45</v>
+        <v>794.5</v>
       </c>
       <c r="D2">
-        <v>-1</v>
+        <v>10.43</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,97 +925,97 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-21.69</v>
+        <v>-13.52</v>
       </c>
       <c r="H2">
-        <v>37.87</v>
+        <v>52.25</v>
       </c>
       <c r="I2">
-        <v>2.81</v>
+        <v>17.93</v>
       </c>
       <c r="J2">
-        <v>19.55</v>
+        <v>32.01</v>
       </c>
       <c r="K2">
-        <v>-7.47</v>
+        <v>3.4</v>
       </c>
       <c r="L2">
-        <v>-13.99</v>
+        <v>-6.1</v>
       </c>
       <c r="M2">
-        <v>-11.45</v>
+        <v>-9.76</v>
       </c>
       <c r="N2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O2">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="P2">
-        <v>707.39</v>
+        <v>731.55</v>
       </c>
       <c r="Q2">
-        <v>635.14</v>
+        <v>645.23</v>
       </c>
       <c r="R2">
-        <v>637.62</v>
+        <v>639.78</v>
       </c>
       <c r="S2">
-        <v>668.84</v>
+        <v>668.5599999999999</v>
       </c>
       <c r="T2">
-        <v>7.57</v>
+        <v>18.84</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>60.04</v>
+        <v>67.41</v>
       </c>
       <c r="Z2">
-        <v>27.92</v>
+        <v>34.88</v>
       </c>
       <c r="AA2">
-        <v>13.68</v>
+        <v>17.92</v>
       </c>
       <c r="AB2">
-        <v>14.24</v>
+        <v>16.96</v>
       </c>
       <c r="AC2">
-        <v>72.39</v>
+        <v>72.8</v>
       </c>
       <c r="AD2">
-        <v>69.66</v>
+        <v>71.58</v>
       </c>
       <c r="AE2">
-        <v>42.04</v>
+        <v>47.15</v>
       </c>
       <c r="AF2">
-        <v>-94.55</v>
+        <v>403.99</v>
       </c>
       <c r="AG2">
-        <v>781.41</v>
+        <v>806.26</v>
       </c>
       <c r="AH2">
-        <v>488.88</v>
+        <v>484.2</v>
       </c>
       <c r="AI2">
-        <v>626.27</v>
+        <v>627.79</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>53.19</v>
+        <v>55.1</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,10 +1026,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>660.65</v>
+        <v>653.9</v>
       </c>
       <c r="D3">
-        <v>-0.14</v>
+        <v>-1.02</v>
       </c>
       <c r="E3">
         <v>734.85</v>
@@ -1015,88 +1038,88 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-10.1</v>
+        <v>-11.02</v>
       </c>
       <c r="H3">
-        <v>28.78</v>
+        <v>27.47</v>
       </c>
       <c r="I3">
-        <v>-2.25</v>
+        <v>1.33</v>
       </c>
       <c r="J3">
-        <v>13.58</v>
+        <v>13.81</v>
       </c>
       <c r="K3">
-        <v>14.49</v>
+        <v>15.52</v>
       </c>
       <c r="L3">
-        <v>-9.69</v>
+        <v>-10.77</v>
       </c>
       <c r="M3">
-        <v>1.73</v>
+        <v>1.37</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P3">
-        <v>653.7</v>
+        <v>655.42</v>
       </c>
       <c r="Q3">
-        <v>645.38</v>
+        <v>649.4299999999999</v>
       </c>
       <c r="R3">
-        <v>598.1799999999999</v>
+        <v>599.95</v>
       </c>
       <c r="S3">
-        <v>583.03</v>
+        <v>583.35</v>
       </c>
       <c r="T3">
-        <v>13.31</v>
+        <v>12.09</v>
       </c>
       <c r="U3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X3">
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>60.8</v>
+        <v>57.73</v>
       </c>
       <c r="Z3">
-        <v>19.56</v>
+        <v>18.1</v>
       </c>
       <c r="AA3">
-        <v>21.78</v>
+        <v>21.04</v>
       </c>
       <c r="AB3">
-        <v>-2.22</v>
+        <v>-2.94</v>
       </c>
       <c r="AC3">
-        <v>20.54</v>
+        <v>18.24</v>
       </c>
       <c r="AD3">
-        <v>13.29</v>
+        <v>17.56</v>
       </c>
       <c r="AE3">
-        <v>22.7</v>
+        <v>22.32</v>
       </c>
       <c r="AF3">
-        <v>-81.18000000000001</v>
+        <v>-91.93000000000001</v>
       </c>
       <c r="AG3">
-        <v>702.05</v>
+        <v>694.6799999999999</v>
       </c>
       <c r="AH3">
-        <v>588.71</v>
+        <v>604.1900000000001</v>
       </c>
       <c r="AI3">
         <v>606.01</v>
@@ -1105,7 +1128,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>36.57</v>
+        <v>34.45</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,10 +1139,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>867.5</v>
+        <v>873.6</v>
       </c>
       <c r="D4">
-        <v>-1.42</v>
+        <v>0.7</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1128,88 +1151,88 @@
         <v>857</v>
       </c>
       <c r="G4">
-        <v>-30.18</v>
+        <v>-29.68</v>
       </c>
       <c r="H4">
-        <v>1.23</v>
+        <v>1.94</v>
       </c>
       <c r="I4">
-        <v>0.29</v>
+        <v>1.94</v>
       </c>
       <c r="J4">
-        <v>-8.390000000000001</v>
+        <v>-6.37</v>
       </c>
       <c r="K4">
-        <v>-14.91</v>
+        <v>-14.41</v>
       </c>
       <c r="L4">
-        <v>-28.47</v>
+        <v>-28.77</v>
       </c>
       <c r="M4">
-        <v>-3.41</v>
+        <v>-2.81</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P4">
-        <v>868.1</v>
+        <v>871.42</v>
       </c>
       <c r="Q4">
-        <v>887.72</v>
+        <v>884.95</v>
       </c>
       <c r="R4">
-        <v>971.75</v>
+        <v>967.84</v>
       </c>
       <c r="S4">
-        <v>1071.6</v>
+        <v>1070.42</v>
       </c>
       <c r="T4">
-        <v>-19.05</v>
+        <v>-18.39</v>
       </c>
       <c r="U4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X4">
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>33.39</v>
+        <v>36.62</v>
       </c>
       <c r="Z4">
-        <v>-28.74</v>
+        <v>-26.85</v>
       </c>
       <c r="AA4">
-        <v>-33.15</v>
+        <v>-31.89</v>
       </c>
       <c r="AB4">
-        <v>4.41</v>
+        <v>5.05</v>
       </c>
       <c r="AC4">
-        <v>92.19</v>
+        <v>91.42</v>
       </c>
       <c r="AD4">
-        <v>80.58</v>
+        <v>90.34</v>
       </c>
       <c r="AE4">
-        <v>19.6</v>
+        <v>19.24</v>
       </c>
       <c r="AF4">
-        <v>-37.22</v>
+        <v>-67.92</v>
       </c>
       <c r="AG4">
-        <v>938.8099999999999</v>
+        <v>932.52</v>
       </c>
       <c r="AH4">
-        <v>836.62</v>
+        <v>837.38</v>
       </c>
       <c r="AI4">
         <v>924.5700000000001</v>
@@ -1218,7 +1241,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>50.95</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1252,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1101.7</v>
+        <v>1099.6</v>
       </c>
       <c r="D5">
-        <v>-0.51</v>
+        <v>-0.19</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,97 +1264,97 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-22.29</v>
+        <v>-22.44</v>
       </c>
       <c r="H5">
-        <v>47.09</v>
+        <v>46.81</v>
       </c>
       <c r="I5">
-        <v>-2.23</v>
+        <v>-0.4</v>
       </c>
       <c r="J5">
-        <v>-9.949999999999999</v>
+        <v>-10.6</v>
       </c>
       <c r="K5">
-        <v>-1.23</v>
+        <v>-2.78</v>
       </c>
       <c r="L5">
-        <v>-9.83</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="M5">
-        <v>14.71</v>
+        <v>14.15</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P5">
-        <v>1115.38</v>
+        <v>1114.5</v>
       </c>
       <c r="Q5">
-        <v>1140.68</v>
+        <v>1136.44</v>
       </c>
       <c r="R5">
-        <v>1239.17</v>
+        <v>1233.52</v>
       </c>
       <c r="S5">
-        <v>1070.43</v>
+        <v>1070.74</v>
       </c>
       <c r="T5">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="U5" t="s">
+        <v>44</v>
+      </c>
+      <c r="V5" t="s">
         <v>43</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
         <v>44</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
       </c>
       <c r="X5">
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>35.37</v>
+        <v>35.02</v>
       </c>
       <c r="Z5">
-        <v>-31.33</v>
+        <v>-31.43</v>
       </c>
       <c r="AA5">
         <v>-31.39</v>
       </c>
       <c r="AB5">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="AC5">
-        <v>54.55</v>
+        <v>37.77</v>
       </c>
       <c r="AD5">
-        <v>66.33</v>
+        <v>56.1</v>
       </c>
       <c r="AE5">
-        <v>38.44</v>
+        <v>37.15</v>
       </c>
       <c r="AF5">
-        <v>-74.36</v>
+        <v>-69.73</v>
       </c>
       <c r="AG5">
-        <v>1185.18</v>
+        <v>1179.51</v>
       </c>
       <c r="AH5">
-        <v>1096.18</v>
+        <v>1093.36</v>
       </c>
       <c r="AI5">
-        <v>1222.72</v>
+        <v>1212.25</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>21.15</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1365,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1696.9</v>
+        <v>1699.5</v>
       </c>
       <c r="D6">
-        <v>0.34</v>
+        <v>0.15</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,88 +1377,88 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-26.87</v>
+        <v>-26.76</v>
       </c>
       <c r="H6">
-        <v>15.33</v>
+        <v>15.51</v>
       </c>
       <c r="I6">
-        <v>-2.92</v>
+        <v>2.42</v>
       </c>
       <c r="J6">
-        <v>-16</v>
+        <v>-16.49</v>
       </c>
       <c r="K6">
-        <v>-5.67</v>
+        <v>-5.04</v>
       </c>
       <c r="L6">
-        <v>-17.67</v>
+        <v>-18.35</v>
       </c>
       <c r="M6">
-        <v>-0.31</v>
+        <v>-2.72</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P6">
-        <v>1678.16</v>
+        <v>1686.2</v>
       </c>
       <c r="Q6">
-        <v>1893.3</v>
+        <v>1876.28</v>
       </c>
       <c r="R6">
-        <v>2002.44</v>
+        <v>1993.18</v>
       </c>
       <c r="S6">
-        <v>1850.3</v>
+        <v>1848.46</v>
       </c>
       <c r="T6">
-        <v>-8.289999999999999</v>
+        <v>-8.06</v>
       </c>
       <c r="U6" t="s">
+        <v>44</v>
+      </c>
+      <c r="V6" t="s">
         <v>43</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
         <v>44</v>
-      </c>
-      <c r="W6" t="s">
-        <v>43</v>
       </c>
       <c r="X6">
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>27.72</v>
+        <v>28.18</v>
       </c>
       <c r="Z6">
-        <v>-92.59999999999999</v>
+        <v>-92.51000000000001</v>
       </c>
       <c r="AA6">
-        <v>-66.5</v>
+        <v>-71.7</v>
       </c>
       <c r="AB6">
-        <v>-26.1</v>
+        <v>-20.81</v>
       </c>
       <c r="AC6">
-        <v>18.15</v>
+        <v>23.13</v>
       </c>
       <c r="AD6">
-        <v>11.26</v>
+        <v>17.46</v>
       </c>
       <c r="AE6">
-        <v>60.95</v>
+        <v>59.58</v>
       </c>
       <c r="AF6">
-        <v>-44.43</v>
+        <v>-34.51</v>
       </c>
       <c r="AG6">
-        <v>2190.35</v>
+        <v>2176.95</v>
       </c>
       <c r="AH6">
-        <v>1596.26</v>
+        <v>1575.62</v>
       </c>
       <c r="AI6">
         <v>1871.22</v>
@@ -1444,7 +1467,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>48.15</v>
+        <v>47.9</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1608,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1605,12 +1628,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1618,700 +1676,734 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>20.35</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>19.55</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.8</v>
+      <c r="D7" s="6">
+        <v>32.01</v>
+      </c>
+      <c r="E7" s="7">
+        <v>12.46</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>15.39</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>13.58</v>
       </c>
-      <c r="E8" s="6">
-        <v>-1.81</v>
+      <c r="D8" s="6">
+        <v>13.81</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.23</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-5.38</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-8.390000000000001</v>
       </c>
-      <c r="E9" s="6">
-        <v>-3.01</v>
+      <c r="D9" s="6">
+        <v>-6.37</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2.02</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-9.08</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-9.949999999999999</v>
       </c>
-      <c r="E10" s="6">
-        <v>-0.87</v>
+      <c r="D10" s="6">
+        <v>-10.6</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-15.75</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-16</v>
       </c>
-      <c r="E11" s="6">
-        <v>-0.25</v>
+      <c r="D11" s="6">
+        <v>-16.49</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>1.52</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>2.81</v>
       </c>
+      <c r="D12" s="6">
+        <v>17.93</v>
+      </c>
       <c r="E12" s="7">
-        <v>1.29</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-1.7</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-2.25</v>
       </c>
-      <c r="E13" s="6">
-        <v>-0.55</v>
+      <c r="D13" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="E13" s="7">
+        <v>3.58</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>1.16</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>0.29</v>
       </c>
-      <c r="E14" s="6">
-        <v>-0.87</v>
+      <c r="D14" s="6">
+        <v>1.94</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.65</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-1.33</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-2.23</v>
       </c>
-      <c r="E15" s="6">
-        <v>-0.9</v>
+      <c r="D15" s="6">
+        <v>-0.4</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.83</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-9.66</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-2.92</v>
       </c>
+      <c r="D16" s="6">
+        <v>2.42</v>
+      </c>
       <c r="E16" s="7">
-        <v>6.74</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>-13.53</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-13.99</v>
       </c>
-      <c r="E17" s="6">
-        <v>-0.46</v>
+      <c r="D17" s="6">
+        <v>-6.1</v>
+      </c>
+      <c r="E17" s="7">
+        <v>7.89</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>-10.21</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-9.69</v>
       </c>
-      <c r="E18" s="7">
-        <v>0.52</v>
+      <c r="D18" s="6">
+        <v>-10.77</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-29.06</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-28.47</v>
       </c>
-      <c r="E19" s="7">
-        <v>0.59</v>
+      <c r="D19" s="6">
+        <v>-28.77</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>-10.94</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-9.83</v>
       </c>
+      <c r="D20" s="6">
+        <v>-9.699999999999999</v>
+      </c>
       <c r="E20" s="7">
-        <v>1.11</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-16.96</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-17.67</v>
       </c>
-      <c r="E21" s="6">
-        <v>-0.71</v>
+      <c r="D21" s="6">
+        <v>-18.35</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>-8.9</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>-7.47</v>
       </c>
+      <c r="D22" s="6">
+        <v>3.4</v>
+      </c>
       <c r="E22" s="7">
-        <v>1.43</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="5">
-        <v>15.07</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>14.49</v>
       </c>
-      <c r="E23" s="6">
-        <v>-0.58</v>
+      <c r="D23" s="6">
+        <v>15.52</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.03</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="5">
-        <v>-12.05</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>-14.91</v>
       </c>
-      <c r="E24" s="6">
-        <v>-2.86</v>
+      <c r="D24" s="6">
+        <v>-14.41</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
-        <v>-0.45</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C25" s="6">
         <v>-1.23</v>
       </c>
-      <c r="E25" s="6">
-        <v>-0.78</v>
+      <c r="D25" s="6">
+        <v>-2.78</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="5">
-        <v>-5.84</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C26" s="6">
         <v>-5.67</v>
       </c>
+      <c r="D26" s="6">
+        <v>-5.04</v>
+      </c>
       <c r="E26" s="7">
-        <v>0.17</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="5">
-        <v>-20.9</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="6">
         <v>-21.69</v>
       </c>
-      <c r="E27" s="6">
-        <v>-0.79</v>
+      <c r="D27" s="6">
+        <v>-13.52</v>
+      </c>
+      <c r="E27" s="7">
+        <v>8.17</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="5">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C28" s="6">
         <v>-10.1</v>
       </c>
-      <c r="E28" s="6">
-        <v>-0.13</v>
+      <c r="D28" s="6">
+        <v>-11.02</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="5">
-        <v>-29.17</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C29" s="6">
         <v>-30.18</v>
       </c>
-      <c r="E29" s="6">
-        <v>-1.01</v>
+      <c r="D29" s="6">
+        <v>-29.68</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.5</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="5">
-        <v>-21.89</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-22.29</v>
       </c>
-      <c r="E30" s="6">
-        <v>-0.4</v>
+      <c r="D30" s="6">
+        <v>-22.44</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="5">
-        <v>-27.12</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C31" s="6">
         <v>-26.87</v>
       </c>
+      <c r="D31" s="6">
+        <v>-26.76</v>
+      </c>
       <c r="E31" s="7">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="5">
-        <v>726.7</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C32" s="6">
         <v>719.45</v>
       </c>
-      <c r="E32" s="6">
-        <v>-7.25</v>
+      <c r="D32" s="6">
+        <v>794.5</v>
+      </c>
+      <c r="E32" s="7">
+        <v>75.05</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="5">
-        <v>661.6</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C33" s="6">
         <v>660.65</v>
       </c>
-      <c r="E33" s="6">
-        <v>-0.95</v>
+      <c r="D33" s="6">
+        <v>653.9</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-6.75</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="5">
-        <v>880</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C34" s="6">
         <v>867.5</v>
       </c>
-      <c r="E34" s="6">
-        <v>-12.5</v>
+      <c r="D34" s="6">
+        <v>873.6</v>
+      </c>
+      <c r="E34" s="7">
+        <v>6.1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="5">
-        <v>1107.4</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C35" s="6">
         <v>1101.7</v>
       </c>
-      <c r="E35" s="6">
-        <v>-5.7</v>
+      <c r="D35" s="6">
+        <v>1099.6</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="5">
-        <v>1691.1</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="C36" s="6">
         <v>1696.9</v>
       </c>
+      <c r="D36" s="6">
+        <v>1699.5</v>
+      </c>
       <c r="E36" s="7">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="6">
+        <v>79</v>
+      </c>
+      <c r="D37" s="6">
+        <v>99</v>
+      </c>
+      <c r="E37" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="6">
+        <v>99</v>
+      </c>
+      <c r="D38" s="6">
+        <v>79</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="5">
-        <v>61.29</v>
-      </c>
-      <c r="D37" s="5">
+      <c r="C39" s="6">
         <v>60.04</v>
       </c>
-      <c r="E37" s="6">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="D39" s="6">
+        <v>67.41</v>
+      </c>
+      <c r="E39" s="7">
+        <v>7.37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="5">
-        <v>61.22</v>
-      </c>
-      <c r="D38" s="5">
+      <c r="C40" s="6">
         <v>60.8</v>
       </c>
-      <c r="E38" s="6">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="D40" s="6">
+        <v>57.73</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-3.07</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="5">
-        <v>36.97</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="C41" s="6">
         <v>33.39</v>
       </c>
-      <c r="E39" s="6">
-        <v>-3.58</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="D41" s="6">
+        <v>36.62</v>
+      </c>
+      <c r="E41" s="7">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="5">
-        <v>36.29</v>
-      </c>
-      <c r="D40" s="5">
+      <c r="C42" s="6">
         <v>35.37</v>
       </c>
-      <c r="E40" s="6">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="D42" s="6">
+        <v>35.02</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="5">
-        <v>26.77</v>
-      </c>
-      <c r="D41" s="5">
+      <c r="C43" s="6">
         <v>27.72</v>
       </c>
-      <c r="E41" s="7">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="D43" s="6">
+        <v>28.18</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="5">
-        <v>-75.89</v>
-      </c>
-      <c r="D42" s="5">
+      <c r="C44" s="6">
         <v>-94.55</v>
       </c>
-      <c r="E42" s="6">
-        <v>-18.66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="D44" s="6">
+        <v>403.99</v>
+      </c>
+      <c r="E44" s="7">
+        <v>498.54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="5">
-        <v>-84.13</v>
-      </c>
-      <c r="D43" s="5">
+      <c r="C45" s="6">
         <v>-81.18000000000001</v>
       </c>
-      <c r="E43" s="7">
-        <v>2.95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="D45" s="6">
+        <v>-91.93000000000001</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-10.75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="5">
-        <v>-8.67</v>
-      </c>
-      <c r="D44" s="5">
+      <c r="C46" s="6">
         <v>-37.22</v>
       </c>
-      <c r="E44" s="6">
-        <v>-28.55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="D46" s="6">
+        <v>-67.92</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-30.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B47" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="5">
-        <v>-6.96</v>
-      </c>
-      <c r="D45" s="5">
+      <c r="C47" s="6">
         <v>-74.36</v>
       </c>
-      <c r="E45" s="6">
-        <v>-67.40000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="D47" s="6">
+        <v>-69.73</v>
+      </c>
+      <c r="E47" s="7">
+        <v>4.63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C46" s="5">
-        <v>-6.66</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C48" s="6">
         <v>-44.43</v>
       </c>
-      <c r="E46" s="6">
-        <v>-37.77</v>
+      <c r="D48" s="6">
+        <v>-34.51</v>
+      </c>
+      <c r="E48" s="7">
+        <v>9.92</v>
       </c>
     </row>
   </sheetData>
@@ -2337,60 +2429,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="11">
+        <v>57.92</v>
+      </c>
+      <c r="C2" s="12">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11">
+        <v>45</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="10">
-        <v>57.92</v>
-      </c>
-      <c r="C2" s="11">
-        <v>5</v>
-      </c>
-      <c r="D2" s="10">
-        <v>43.5</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-0.2</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-3</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-0.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2492,37 +2584,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.1471</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0173</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0031</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0341</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1145</v>
+      <c r="A2" s="14">
+        <v>0.1415</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0137</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0272</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0281</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.09759999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,28 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +252,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,15 +368,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -772,8 +750,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -913,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>794.5</v>
+        <v>757.45</v>
       </c>
       <c r="D2">
-        <v>10.43</v>
+        <v>-4.66</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -925,46 +902,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-13.52</v>
+        <v>-17.56</v>
       </c>
       <c r="H2">
-        <v>52.25</v>
+        <v>45.15</v>
       </c>
       <c r="I2">
-        <v>17.93</v>
+        <v>14.43</v>
       </c>
       <c r="J2">
-        <v>32.01</v>
+        <v>27.8</v>
       </c>
       <c r="K2">
-        <v>3.4</v>
+        <v>0.74</v>
       </c>
       <c r="L2">
-        <v>-6.1</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="M2">
-        <v>-9.76</v>
+        <v>-10.67</v>
       </c>
       <c r="N2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O2">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="P2">
-        <v>731.55</v>
+        <v>750.65</v>
       </c>
       <c r="Q2">
-        <v>645.23</v>
+        <v>653.24</v>
       </c>
       <c r="R2">
-        <v>639.78</v>
+        <v>641.28</v>
       </c>
       <c r="S2">
-        <v>668.5599999999999</v>
+        <v>668.27</v>
       </c>
       <c r="T2">
-        <v>18.84</v>
+        <v>13.35</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -979,43 +956,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>67.41</v>
+        <v>61.39</v>
       </c>
       <c r="Z2">
-        <v>34.88</v>
+        <v>36.98</v>
       </c>
       <c r="AA2">
-        <v>17.92</v>
+        <v>21.73</v>
       </c>
       <c r="AB2">
-        <v>16.96</v>
+        <v>15.25</v>
       </c>
       <c r="AC2">
-        <v>72.8</v>
+        <v>72.37</v>
       </c>
       <c r="AD2">
-        <v>71.58</v>
+        <v>72.52</v>
       </c>
       <c r="AE2">
-        <v>47.15</v>
+        <v>46.95</v>
       </c>
       <c r="AF2">
-        <v>403.99</v>
+        <v>-35.04</v>
       </c>
       <c r="AG2">
-        <v>806.26</v>
+        <v>820.0599999999999</v>
       </c>
       <c r="AH2">
-        <v>484.2</v>
+        <v>486.43</v>
       </c>
       <c r="AI2">
-        <v>627.79</v>
+        <v>628.4</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>55.1</v>
+        <v>56.75</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1026,10 +1003,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>653.9</v>
+        <v>670.05</v>
       </c>
       <c r="D3">
-        <v>-1.02</v>
+        <v>2.47</v>
       </c>
       <c r="E3">
         <v>734.85</v>
@@ -1038,46 +1015,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-11.02</v>
+        <v>-8.82</v>
       </c>
       <c r="H3">
-        <v>27.47</v>
+        <v>30.61</v>
       </c>
       <c r="I3">
-        <v>1.33</v>
+        <v>3.51</v>
       </c>
       <c r="J3">
-        <v>13.81</v>
+        <v>16.99</v>
       </c>
       <c r="K3">
-        <v>15.52</v>
+        <v>18.46</v>
       </c>
       <c r="L3">
-        <v>-10.77</v>
+        <v>-7.57</v>
       </c>
       <c r="M3">
-        <v>1.37</v>
+        <v>1.98</v>
       </c>
       <c r="N3">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O3">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P3">
-        <v>655.42</v>
+        <v>659.96</v>
       </c>
       <c r="Q3">
-        <v>649.4299999999999</v>
+        <v>652.4299999999999</v>
       </c>
       <c r="R3">
-        <v>599.95</v>
+        <v>602.13</v>
       </c>
       <c r="S3">
-        <v>583.35</v>
+        <v>583.76</v>
       </c>
       <c r="T3">
-        <v>12.09</v>
+        <v>14.78</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1092,34 +1069,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>57.73</v>
+        <v>62.59</v>
       </c>
       <c r="Z3">
-        <v>18.1</v>
+        <v>18.04</v>
       </c>
       <c r="AA3">
-        <v>21.04</v>
+        <v>20.44</v>
       </c>
       <c r="AB3">
-        <v>-2.94</v>
+        <v>-2.4</v>
       </c>
       <c r="AC3">
-        <v>18.24</v>
+        <v>24.94</v>
       </c>
       <c r="AD3">
-        <v>17.56</v>
+        <v>21.24</v>
       </c>
       <c r="AE3">
-        <v>22.32</v>
+        <v>22.22</v>
       </c>
       <c r="AF3">
-        <v>-91.93000000000001</v>
+        <v>-82.68000000000001</v>
       </c>
       <c r="AG3">
-        <v>694.6799999999999</v>
+        <v>694.54</v>
       </c>
       <c r="AH3">
-        <v>604.1900000000001</v>
+        <v>610.33</v>
       </c>
       <c r="AI3">
         <v>606.01</v>
@@ -1128,7 +1105,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>34.45</v>
+        <v>33.76</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1139,7 +1116,7 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>873.6</v>
+        <v>879.75</v>
       </c>
       <c r="D4">
         <v>0.7</v>
@@ -1151,46 +1128,46 @@
         <v>857</v>
       </c>
       <c r="G4">
-        <v>-29.68</v>
+        <v>-29.19</v>
       </c>
       <c r="H4">
-        <v>1.94</v>
+        <v>2.65</v>
       </c>
       <c r="I4">
         <v>1.94</v>
       </c>
       <c r="J4">
-        <v>-6.37</v>
+        <v>-5.29</v>
       </c>
       <c r="K4">
-        <v>-14.41</v>
+        <v>-13.79</v>
       </c>
       <c r="L4">
-        <v>-28.77</v>
+        <v>-27.98</v>
       </c>
       <c r="M4">
-        <v>-2.81</v>
+        <v>-2.74</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P4">
-        <v>871.42</v>
+        <v>874.77</v>
       </c>
       <c r="Q4">
-        <v>884.95</v>
+        <v>882.48</v>
       </c>
       <c r="R4">
-        <v>967.84</v>
+        <v>964.21</v>
       </c>
       <c r="S4">
-        <v>1070.42</v>
+        <v>1069.21</v>
       </c>
       <c r="T4">
-        <v>-18.39</v>
+        <v>-17.72</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1205,34 +1182,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>36.62</v>
+        <v>39.78</v>
       </c>
       <c r="Z4">
-        <v>-26.85</v>
+        <v>-24.57</v>
       </c>
       <c r="AA4">
-        <v>-31.89</v>
+        <v>-30.43</v>
       </c>
       <c r="AB4">
-        <v>5.05</v>
+        <v>5.86</v>
       </c>
       <c r="AC4">
         <v>91.42</v>
       </c>
       <c r="AD4">
-        <v>90.34</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="AE4">
-        <v>19.24</v>
+        <v>18.74</v>
       </c>
       <c r="AF4">
-        <v>-67.92</v>
+        <v>-64.58</v>
       </c>
       <c r="AG4">
-        <v>932.52</v>
+        <v>925.27</v>
       </c>
       <c r="AH4">
-        <v>837.38</v>
+        <v>839.6900000000001</v>
       </c>
       <c r="AI4">
         <v>924.5700000000001</v>
@@ -1241,7 +1218,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>44.69</v>
+        <v>40.09</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1252,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1099.6</v>
+        <v>1106</v>
       </c>
       <c r="D5">
-        <v>-0.19</v>
+        <v>0.58</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1264,46 +1241,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-22.44</v>
+        <v>-21.99</v>
       </c>
       <c r="H5">
-        <v>46.81</v>
+        <v>47.66</v>
       </c>
       <c r="I5">
-        <v>-0.4</v>
+        <v>-2.68</v>
       </c>
       <c r="J5">
-        <v>-10.6</v>
+        <v>-6.63</v>
       </c>
       <c r="K5">
-        <v>-2.78</v>
+        <v>-4.05</v>
       </c>
       <c r="L5">
-        <v>-9.699999999999999</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="M5">
-        <v>14.15</v>
+        <v>13.44</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P5">
-        <v>1114.5</v>
+        <v>1108.4</v>
       </c>
       <c r="Q5">
-        <v>1136.44</v>
+        <v>1133.44</v>
       </c>
       <c r="R5">
-        <v>1233.52</v>
+        <v>1228.9</v>
       </c>
       <c r="S5">
-        <v>1070.74</v>
+        <v>1071.27</v>
       </c>
       <c r="T5">
-        <v>2.7</v>
+        <v>3.24</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1318,34 +1295,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>35.02</v>
+        <v>37.07</v>
       </c>
       <c r="Z5">
-        <v>-31.43</v>
+        <v>-30.64</v>
       </c>
       <c r="AA5">
-        <v>-31.39</v>
+        <v>-31.24</v>
       </c>
       <c r="AB5">
-        <v>-0.04</v>
+        <v>0.6</v>
       </c>
       <c r="AC5">
-        <v>37.77</v>
+        <v>40.63</v>
       </c>
       <c r="AD5">
-        <v>56.1</v>
+        <v>44.32</v>
       </c>
       <c r="AE5">
-        <v>37.15</v>
+        <v>36.09</v>
       </c>
       <c r="AF5">
-        <v>-69.73</v>
+        <v>-69.90000000000001</v>
       </c>
       <c r="AG5">
-        <v>1179.51</v>
+        <v>1176.22</v>
       </c>
       <c r="AH5">
-        <v>1093.36</v>
+        <v>1090.66</v>
       </c>
       <c r="AI5">
         <v>1212.25</v>
@@ -1354,7 +1331,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>21.11</v>
+        <v>20.01</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1365,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1699.5</v>
+        <v>1707.6</v>
       </c>
       <c r="D6">
-        <v>0.15</v>
+        <v>0.48</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1377,46 +1354,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-26.76</v>
+        <v>-26.41</v>
       </c>
       <c r="H6">
-        <v>15.51</v>
+        <v>16.06</v>
       </c>
       <c r="I6">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="J6">
-        <v>-16.49</v>
+        <v>-16.29</v>
       </c>
       <c r="K6">
-        <v>-5.04</v>
+        <v>-6.21</v>
       </c>
       <c r="L6">
-        <v>-18.35</v>
+        <v>-18.2</v>
       </c>
       <c r="M6">
-        <v>-2.72</v>
+        <v>-4.94</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="P6">
-        <v>1686.2</v>
+        <v>1694.66</v>
       </c>
       <c r="Q6">
-        <v>1876.28</v>
+        <v>1859.21</v>
       </c>
       <c r="R6">
-        <v>1993.18</v>
+        <v>1985.18</v>
       </c>
       <c r="S6">
-        <v>1848.46</v>
+        <v>1846.6</v>
       </c>
       <c r="T6">
-        <v>-8.06</v>
+        <v>-7.53</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1431,34 +1408,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>28.18</v>
+        <v>29.65</v>
       </c>
       <c r="Z6">
-        <v>-92.51000000000001</v>
+        <v>-90.73999999999999</v>
       </c>
       <c r="AA6">
-        <v>-71.7</v>
+        <v>-75.51000000000001</v>
       </c>
       <c r="AB6">
-        <v>-20.81</v>
+        <v>-15.23</v>
       </c>
       <c r="AC6">
-        <v>23.13</v>
+        <v>27.13</v>
       </c>
       <c r="AD6">
-        <v>17.46</v>
+        <v>22.8</v>
       </c>
       <c r="AE6">
-        <v>59.58</v>
+        <v>56.79</v>
       </c>
       <c r="AF6">
-        <v>-34.51</v>
+        <v>-58.02</v>
       </c>
       <c r="AG6">
-        <v>2176.95</v>
+        <v>2157.35</v>
       </c>
       <c r="AH6">
-        <v>1575.62</v>
+        <v>1561.08</v>
       </c>
       <c r="AI6">
         <v>1871.22</v>
@@ -1467,7 +1444,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>47.9</v>
+        <v>47.68</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1628,47 +1605,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1676,543 +1618,543 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>19.55</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>32.01</v>
       </c>
-      <c r="E7" s="7">
-        <v>12.46</v>
+      <c r="D7" s="5">
+        <v>27.8</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-4.21</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>13.58</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>13.81</v>
       </c>
+      <c r="D8" s="5">
+        <v>16.99</v>
+      </c>
       <c r="E8" s="7">
-        <v>0.23</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-6.37</v>
       </c>
+      <c r="D9" s="5">
+        <v>-5.29</v>
+      </c>
       <c r="E9" s="7">
-        <v>2.02</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-9.949999999999999</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-10.6</v>
       </c>
-      <c r="E10" s="8">
-        <v>-0.65</v>
+      <c r="D10" s="5">
+        <v>-6.63</v>
+      </c>
+      <c r="E10" s="7">
+        <v>3.97</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-16</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-16.49</v>
       </c>
-      <c r="E11" s="8">
-        <v>-0.49</v>
+      <c r="D11" s="5">
+        <v>-16.29</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.2</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>2.81</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>17.93</v>
       </c>
-      <c r="E12" s="7">
-        <v>15.12</v>
+      <c r="D12" s="5">
+        <v>14.43</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-3.5</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
-        <v>-2.25</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>1.33</v>
       </c>
+      <c r="D13" s="5">
+        <v>3.51</v>
+      </c>
       <c r="E13" s="7">
-        <v>3.58</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-0.4</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-2.68</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-2.28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2.42</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2.54</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-6.1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-9.369999999999999</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-3.27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-10.77</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-7.57</v>
+      </c>
+      <c r="E17" s="7">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.29</v>
-      </c>
-      <c r="D14" s="6">
-        <v>1.94</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-28.77</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-27.98</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2.23</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-0.4</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-9.140000000000001</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-2.92</v>
-      </c>
-      <c r="D16" s="6">
-        <v>2.42</v>
-      </c>
-      <c r="E16" s="7">
-        <v>5.34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-18.35</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-18.2</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-13.99</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-6.1</v>
-      </c>
-      <c r="E17" s="7">
-        <v>7.89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0.74</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-9.69</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-10.77</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>15.52</v>
+      </c>
+      <c r="D22" s="5">
+        <v>18.46</v>
+      </c>
+      <c r="E22" s="7">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-28.47</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-28.77</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-14.41</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-13.79</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-9.83</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-2.78</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-4.05</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-17.67</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-18.35</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-5.04</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-6.21</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-7.47</v>
-      </c>
-      <c r="D22" s="6">
-        <v>3.4</v>
-      </c>
-      <c r="E22" s="7">
-        <v>10.87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-13.52</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-17.56</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-4.04</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>14.49</v>
-      </c>
-      <c r="D23" s="6">
-        <v>15.52</v>
-      </c>
-      <c r="E23" s="7">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-11.02</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-8.82</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-14.91</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-14.41</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-29.68</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-29.19</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-1.23</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-2.78</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-22.44</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-21.99</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-5.67</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-5.04</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-26.76</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-26.41</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-21.69</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-13.52</v>
-      </c>
-      <c r="E27" s="7">
-        <v>8.17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="5">
+        <v>794.5</v>
+      </c>
+      <c r="D31" s="5">
+        <v>757.45</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-37.05</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-10.1</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-11.02</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>653.9</v>
+      </c>
+      <c r="D32" s="5">
+        <v>670.05</v>
+      </c>
+      <c r="E32" s="7">
+        <v>16.15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-30.18</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-29.68</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>873.6</v>
+      </c>
+      <c r="D33" s="5">
+        <v>879.75</v>
+      </c>
+      <c r="E33" s="7">
+        <v>6.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-22.29</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-22.44</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>1099.6</v>
+      </c>
+      <c r="D34" s="5">
+        <v>1106</v>
+      </c>
+      <c r="E34" s="7">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-26.87</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-26.76</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1699.5</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1707.6</v>
+      </c>
+      <c r="E35" s="7">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>719.45</v>
-      </c>
-      <c r="D32" s="6">
-        <v>794.5</v>
-      </c>
-      <c r="E32" s="7">
-        <v>75.05</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="5">
+        <v>99</v>
+      </c>
+      <c r="D36" s="5">
+        <v>79</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>660.65</v>
-      </c>
-      <c r="D33" s="6">
-        <v>653.9</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-6.75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>867.5</v>
-      </c>
-      <c r="D34" s="6">
-        <v>873.6</v>
-      </c>
-      <c r="E34" s="7">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1101.7</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1099.6</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>1696.9</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1699.5</v>
-      </c>
-      <c r="E36" s="7">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="5">
         <v>79</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="5">
         <v>99</v>
       </c>
       <c r="E37" s="7">
@@ -2220,190 +2162,173 @@
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>67.41</v>
+      </c>
+      <c r="D38" s="5">
+        <v>61.39</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-6.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="6">
-        <v>99</v>
-      </c>
-      <c r="D38" s="6">
-        <v>79</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>57.73</v>
+      </c>
+      <c r="D39" s="5">
+        <v>62.59</v>
+      </c>
+      <c r="E39" s="7">
+        <v>4.86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>36.62</v>
+      </c>
+      <c r="D40" s="5">
+        <v>39.78</v>
+      </c>
+      <c r="E40" s="7">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>35.02</v>
+      </c>
+      <c r="D41" s="5">
+        <v>37.07</v>
+      </c>
+      <c r="E41" s="7">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="5">
+        <v>28.18</v>
+      </c>
+      <c r="D42" s="5">
+        <v>29.65</v>
+      </c>
+      <c r="E42" s="7">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>60.04</v>
-      </c>
-      <c r="D39" s="6">
-        <v>67.41</v>
-      </c>
-      <c r="E39" s="7">
-        <v>7.37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>403.99</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-35.04</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-439.03</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>60.8</v>
-      </c>
-      <c r="D40" s="6">
-        <v>57.73</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-3.07</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-91.93000000000001</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-82.68000000000001</v>
+      </c>
+      <c r="E44" s="7">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>33.39</v>
-      </c>
-      <c r="D41" s="6">
-        <v>36.62</v>
-      </c>
-      <c r="E41" s="7">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-67.92</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-64.58</v>
+      </c>
+      <c r="E45" s="7">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>35.37</v>
-      </c>
-      <c r="D42" s="6">
-        <v>35.02</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-69.73</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-69.90000000000001</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>27.72</v>
-      </c>
-      <c r="D43" s="6">
-        <v>28.18</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
+      <c r="B47" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="6">
-        <v>-94.55</v>
-      </c>
-      <c r="D44" s="6">
-        <v>403.99</v>
-      </c>
-      <c r="E44" s="7">
-        <v>498.54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-81.18000000000001</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-91.93000000000001</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-10.75</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-37.22</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-67.92</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-30.7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-74.36</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-69.73</v>
-      </c>
-      <c r="E47" s="7">
-        <v>4.63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-44.43</v>
-      </c>
-      <c r="D48" s="6">
+      <c r="C47" s="5">
         <v>-34.51</v>
       </c>
-      <c r="E48" s="7">
-        <v>9.92</v>
+      <c r="D47" s="5">
+        <v>-58.02</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-23.51</v>
       </c>
     </row>
   </sheetData>
@@ -2429,60 +2354,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>68</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>57.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>45</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>46.1</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>2.5</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-0.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2584,37 +2509,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1415</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0137</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0272</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0281</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.09759999999999999</v>
+      <c r="A2" s="13">
+        <v>0.1344</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0198</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0274</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.04940000000000001</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1067</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -890,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>757.45</v>
+        <v>728.8</v>
       </c>
       <c r="D2">
-        <v>-4.66</v>
+        <v>-3.78</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,46 +902,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-17.56</v>
+        <v>-20.67</v>
       </c>
       <c r="H2">
-        <v>45.15</v>
+        <v>39.66</v>
       </c>
       <c r="I2">
-        <v>14.43</v>
+        <v>-3.49</v>
       </c>
       <c r="J2">
-        <v>27.8</v>
+        <v>22.03</v>
       </c>
       <c r="K2">
-        <v>0.74</v>
+        <v>0.46</v>
       </c>
       <c r="L2">
-        <v>-9.369999999999999</v>
+        <v>-11.66</v>
       </c>
       <c r="M2">
-        <v>-10.67</v>
+        <v>-11.05</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="P2">
-        <v>750.65</v>
+        <v>745.38</v>
       </c>
       <c r="Q2">
-        <v>653.24</v>
+        <v>660.01</v>
       </c>
       <c r="R2">
-        <v>641.28</v>
+        <v>642.2</v>
       </c>
       <c r="S2">
-        <v>668.27</v>
+        <v>668.11</v>
       </c>
       <c r="T2">
-        <v>13.35</v>
+        <v>9.08</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -956,34 +956,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>61.39</v>
+        <v>57.15</v>
       </c>
       <c r="Z2">
-        <v>36.98</v>
+        <v>35.92</v>
       </c>
       <c r="AA2">
-        <v>21.73</v>
+        <v>24.57</v>
       </c>
       <c r="AB2">
-        <v>15.25</v>
+        <v>11.35</v>
       </c>
       <c r="AC2">
-        <v>72.37</v>
+        <v>70.13</v>
       </c>
       <c r="AD2">
-        <v>72.52</v>
+        <v>71.77</v>
       </c>
       <c r="AE2">
-        <v>46.95</v>
+        <v>46.2</v>
       </c>
       <c r="AF2">
-        <v>-35.04</v>
+        <v>-87.45</v>
       </c>
       <c r="AG2">
-        <v>820.0599999999999</v>
+        <v>827.59</v>
       </c>
       <c r="AH2">
-        <v>486.43</v>
+        <v>492.42</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -992,7 +992,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>56.75</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,10 +1003,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>670.05</v>
+        <v>676.05</v>
       </c>
       <c r="D3">
-        <v>2.47</v>
+        <v>0.9</v>
       </c>
       <c r="E3">
         <v>734.85</v>
@@ -1015,25 +1015,25 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-8.82</v>
+        <v>-8</v>
       </c>
       <c r="H3">
-        <v>30.61</v>
+        <v>31.78</v>
       </c>
       <c r="I3">
-        <v>3.51</v>
+        <v>3.43</v>
       </c>
       <c r="J3">
-        <v>16.99</v>
+        <v>10.81</v>
       </c>
       <c r="K3">
-        <v>18.46</v>
+        <v>20.28</v>
       </c>
       <c r="L3">
-        <v>-7.57</v>
+        <v>-7.56</v>
       </c>
       <c r="M3">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1042,19 +1042,19 @@
         <v>70</v>
       </c>
       <c r="P3">
-        <v>659.96</v>
+        <v>664.45</v>
       </c>
       <c r="Q3">
-        <v>652.4299999999999</v>
+        <v>654.95</v>
       </c>
       <c r="R3">
-        <v>602.13</v>
+        <v>604.12</v>
       </c>
       <c r="S3">
-        <v>583.76</v>
+        <v>584.23</v>
       </c>
       <c r="T3">
-        <v>14.78</v>
+        <v>15.72</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1069,43 +1069,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>62.59</v>
+        <v>64.23</v>
       </c>
       <c r="Z3">
-        <v>18.04</v>
+        <v>18.27</v>
       </c>
       <c r="AA3">
-        <v>20.44</v>
+        <v>20.01</v>
       </c>
       <c r="AB3">
-        <v>-2.4</v>
+        <v>-1.74</v>
       </c>
       <c r="AC3">
-        <v>24.94</v>
+        <v>36.59</v>
       </c>
       <c r="AD3">
-        <v>21.24</v>
+        <v>26.59</v>
       </c>
       <c r="AE3">
-        <v>22.22</v>
+        <v>22.91</v>
       </c>
       <c r="AF3">
-        <v>-82.68000000000001</v>
+        <v>-15.62</v>
       </c>
       <c r="AG3">
-        <v>694.54</v>
+        <v>696.34</v>
       </c>
       <c r="AH3">
-        <v>610.33</v>
+        <v>613.55</v>
       </c>
       <c r="AI3">
-        <v>606.01</v>
+        <v>613.74</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>33.76</v>
+        <v>35.76</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,10 +1116,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>879.75</v>
+        <v>875</v>
       </c>
       <c r="D4">
-        <v>0.7</v>
+        <v>-0.54</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1128,46 +1128,46 @@
         <v>857</v>
       </c>
       <c r="G4">
-        <v>-29.19</v>
+        <v>-29.57</v>
       </c>
       <c r="H4">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="I4">
-        <v>1.94</v>
+        <v>0.23</v>
       </c>
       <c r="J4">
-        <v>-5.29</v>
+        <v>-5.83</v>
       </c>
       <c r="K4">
-        <v>-13.79</v>
+        <v>-15.43</v>
       </c>
       <c r="L4">
-        <v>-27.98</v>
+        <v>-28.4</v>
       </c>
       <c r="M4">
-        <v>-2.74</v>
+        <v>-2.54</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P4">
-        <v>874.77</v>
+        <v>875.17</v>
       </c>
       <c r="Q4">
-        <v>882.48</v>
+        <v>880.09</v>
       </c>
       <c r="R4">
-        <v>964.21</v>
+        <v>960.65</v>
       </c>
       <c r="S4">
-        <v>1069.21</v>
+        <v>1067.95</v>
       </c>
       <c r="T4">
-        <v>-17.72</v>
+        <v>-18.07</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1182,34 +1182,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.78</v>
+        <v>38.19</v>
       </c>
       <c r="Z4">
-        <v>-24.57</v>
+        <v>-22.88</v>
       </c>
       <c r="AA4">
-        <v>-30.43</v>
+        <v>-28.92</v>
       </c>
       <c r="AB4">
-        <v>5.86</v>
+        <v>6.04</v>
       </c>
       <c r="AC4">
-        <v>91.42</v>
+        <v>96.3</v>
       </c>
       <c r="AD4">
-        <v>91.68000000000001</v>
+        <v>93.05</v>
       </c>
       <c r="AE4">
-        <v>18.74</v>
+        <v>18.36</v>
       </c>
       <c r="AF4">
-        <v>-64.58</v>
+        <v>-49.9</v>
       </c>
       <c r="AG4">
-        <v>925.27</v>
+        <v>918.51</v>
       </c>
       <c r="AH4">
-        <v>839.6900000000001</v>
+        <v>841.66</v>
       </c>
       <c r="AI4">
         <v>924.5700000000001</v>
@@ -1218,7 +1218,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>40.09</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1106</v>
+        <v>1099</v>
       </c>
       <c r="D5">
-        <v>0.58</v>
+        <v>-0.63</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,46 +1241,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-21.99</v>
+        <v>-22.48</v>
       </c>
       <c r="H5">
-        <v>47.66</v>
+        <v>46.73</v>
       </c>
       <c r="I5">
-        <v>-2.68</v>
+        <v>-2.51</v>
       </c>
       <c r="J5">
-        <v>-6.63</v>
+        <v>-5.74</v>
       </c>
       <c r="K5">
-        <v>-4.05</v>
+        <v>-5.32</v>
       </c>
       <c r="L5">
-        <v>-9.140000000000001</v>
+        <v>-6.52</v>
       </c>
       <c r="M5">
-        <v>13.44</v>
+        <v>13.72</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P5">
-        <v>1108.4</v>
+        <v>1102.74</v>
       </c>
       <c r="Q5">
-        <v>1133.44</v>
+        <v>1131.49</v>
       </c>
       <c r="R5">
-        <v>1228.9</v>
+        <v>1223.3</v>
       </c>
       <c r="S5">
-        <v>1071.27</v>
+        <v>1071.69</v>
       </c>
       <c r="T5">
-        <v>3.24</v>
+        <v>2.55</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1295,43 +1295,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>37.07</v>
+        <v>35.74</v>
       </c>
       <c r="Z5">
-        <v>-30.64</v>
+        <v>-30.23</v>
       </c>
       <c r="AA5">
-        <v>-31.24</v>
+        <v>-31.04</v>
       </c>
       <c r="AB5">
-        <v>0.6</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AC5">
-        <v>40.63</v>
+        <v>41.98</v>
       </c>
       <c r="AD5">
-        <v>44.32</v>
+        <v>40.13</v>
       </c>
       <c r="AE5">
-        <v>36.09</v>
+        <v>35.21</v>
       </c>
       <c r="AF5">
-        <v>-69.90000000000001</v>
+        <v>-65.78</v>
       </c>
       <c r="AG5">
-        <v>1176.22</v>
+        <v>1176.87</v>
       </c>
       <c r="AH5">
-        <v>1090.66</v>
+        <v>1086.11</v>
       </c>
       <c r="AI5">
-        <v>1212.25</v>
+        <v>1202.84</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>20.01</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1707.6</v>
+        <v>1671.2</v>
       </c>
       <c r="D6">
-        <v>0.48</v>
+        <v>-2.13</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,46 +1354,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-26.41</v>
+        <v>-27.97</v>
       </c>
       <c r="H6">
-        <v>16.06</v>
+        <v>13.59</v>
       </c>
       <c r="I6">
-        <v>2.54</v>
+        <v>-0.42</v>
       </c>
       <c r="J6">
-        <v>-16.29</v>
+        <v>-18.44</v>
       </c>
       <c r="K6">
-        <v>-6.21</v>
+        <v>-9.69</v>
       </c>
       <c r="L6">
-        <v>-18.2</v>
+        <v>-22.1</v>
       </c>
       <c r="M6">
-        <v>-4.94</v>
+        <v>-5.28</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P6">
-        <v>1694.66</v>
+        <v>1693.26</v>
       </c>
       <c r="Q6">
-        <v>1859.21</v>
+        <v>1841.02</v>
       </c>
       <c r="R6">
-        <v>1985.18</v>
+        <v>1976.52</v>
       </c>
       <c r="S6">
-        <v>1846.6</v>
+        <v>1844.54</v>
       </c>
       <c r="T6">
-        <v>-7.53</v>
+        <v>-9.4</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1408,43 +1408,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>29.65</v>
+        <v>26.97</v>
       </c>
       <c r="Z6">
-        <v>-90.73999999999999</v>
+        <v>-91.22</v>
       </c>
       <c r="AA6">
-        <v>-75.51000000000001</v>
+        <v>-78.65000000000001</v>
       </c>
       <c r="AB6">
-        <v>-15.23</v>
+        <v>-12.57</v>
       </c>
       <c r="AC6">
-        <v>27.13</v>
+        <v>26.85</v>
       </c>
       <c r="AD6">
-        <v>22.8</v>
+        <v>25.7</v>
       </c>
       <c r="AE6">
-        <v>56.79</v>
+        <v>55.75</v>
       </c>
       <c r="AF6">
-        <v>-58.02</v>
+        <v>-34.51</v>
       </c>
       <c r="AG6">
-        <v>2157.35</v>
+        <v>2138.37</v>
       </c>
       <c r="AH6">
-        <v>1561.08</v>
+        <v>1543.67</v>
       </c>
       <c r="AI6">
-        <v>1871.22</v>
+        <v>1854.05</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>47.68</v>
+        <v>48.87</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1642,13 +1642,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>32.01</v>
+        <v>27.8</v>
       </c>
       <c r="D7" s="5">
-        <v>27.8</v>
+        <v>22.03</v>
       </c>
       <c r="E7" s="6">
-        <v>-4.21</v>
+        <v>-5.77</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1659,13 +1659,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>13.81</v>
+        <v>16.99</v>
       </c>
       <c r="D8" s="5">
-        <v>16.99</v>
-      </c>
-      <c r="E8" s="7">
-        <v>3.18</v>
+        <v>10.81</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-6.18</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1676,13 +1676,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-6.37</v>
+        <v>-5.29</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.29</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.08</v>
+        <v>-5.83</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1693,13 +1693,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-10.6</v>
+        <v>-6.63</v>
       </c>
       <c r="D10" s="5">
-        <v>-6.63</v>
+        <v>-5.74</v>
       </c>
       <c r="E10" s="7">
-        <v>3.97</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1710,13 +1710,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-16.49</v>
+        <v>-16.29</v>
       </c>
       <c r="D11" s="5">
-        <v>-16.29</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.2</v>
+        <v>-18.44</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1727,13 +1727,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>17.93</v>
+        <v>14.43</v>
       </c>
       <c r="D12" s="5">
-        <v>14.43</v>
+        <v>-3.49</v>
       </c>
       <c r="E12" s="6">
-        <v>-3.5</v>
+        <v>-17.92</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1744,591 +1744,574 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>1.33</v>
+        <v>3.51</v>
       </c>
       <c r="D13" s="5">
-        <v>3.51</v>
-      </c>
-      <c r="E13" s="7">
-        <v>2.18</v>
+        <v>3.43</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-0.4</v>
+        <v>1.94</v>
       </c>
       <c r="D14" s="5">
-        <v>-2.68</v>
+        <v>0.23</v>
       </c>
       <c r="E14" s="6">
-        <v>-2.28</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>2.42</v>
+        <v>-2.68</v>
       </c>
       <c r="D15" s="5">
-        <v>2.54</v>
+        <v>-2.51</v>
       </c>
       <c r="E15" s="7">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-6.1</v>
+        <v>2.54</v>
       </c>
       <c r="D16" s="5">
-        <v>-9.369999999999999</v>
+        <v>-0.42</v>
       </c>
       <c r="E16" s="6">
-        <v>-3.27</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>-10.77</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="D17" s="5">
-        <v>-7.57</v>
-      </c>
-      <c r="E17" s="7">
-        <v>3.2</v>
+        <v>-11.66</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-2.29</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-28.77</v>
+        <v>-7.57</v>
       </c>
       <c r="D18" s="5">
-        <v>-27.98</v>
+        <v>-7.56</v>
       </c>
       <c r="E18" s="7">
-        <v>0.79</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-9.699999999999999</v>
+        <v>-27.98</v>
       </c>
       <c r="D19" s="5">
-        <v>-9.140000000000001</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.5600000000000001</v>
+        <v>-28.4</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-18.35</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="D20" s="5">
-        <v>-18.2</v>
+        <v>-6.52</v>
       </c>
       <c r="E20" s="7">
-        <v>0.15</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>3.4</v>
+        <v>-18.2</v>
       </c>
       <c r="D21" s="5">
-        <v>0.74</v>
+        <v>-22.1</v>
       </c>
       <c r="E21" s="6">
-        <v>-2.66</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>15.52</v>
+        <v>0.74</v>
       </c>
       <c r="D22" s="5">
-        <v>18.46</v>
-      </c>
-      <c r="E22" s="7">
-        <v>2.94</v>
+        <v>0.46</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>-14.41</v>
+        <v>18.46</v>
       </c>
       <c r="D23" s="5">
-        <v>-13.79</v>
+        <v>20.28</v>
       </c>
       <c r="E23" s="7">
-        <v>0.62</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-2.78</v>
+        <v>-13.79</v>
       </c>
       <c r="D24" s="5">
-        <v>-4.05</v>
+        <v>-15.43</v>
       </c>
       <c r="E24" s="6">
-        <v>-1.27</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-5.04</v>
+        <v>-4.05</v>
       </c>
       <c r="D25" s="5">
-        <v>-6.21</v>
+        <v>-5.32</v>
       </c>
       <c r="E25" s="6">
-        <v>-1.17</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-13.52</v>
+        <v>-6.21</v>
       </c>
       <c r="D26" s="5">
-        <v>-17.56</v>
+        <v>-9.69</v>
       </c>
       <c r="E26" s="6">
-        <v>-4.04</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-11.02</v>
+        <v>-17.56</v>
       </c>
       <c r="D27" s="5">
-        <v>-8.82</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.2</v>
+        <v>-20.67</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-3.11</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-29.68</v>
+        <v>-8.82</v>
       </c>
       <c r="D28" s="5">
-        <v>-29.19</v>
+        <v>-8</v>
       </c>
       <c r="E28" s="7">
-        <v>0.49</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-22.44</v>
+        <v>-29.19</v>
       </c>
       <c r="D29" s="5">
-        <v>-21.99</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.45</v>
+        <v>-29.57</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-26.76</v>
+        <v>-21.99</v>
       </c>
       <c r="D30" s="5">
-        <v>-26.41</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.35</v>
+        <v>-22.48</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>794.5</v>
+        <v>-26.41</v>
       </c>
       <c r="D31" s="5">
-        <v>757.45</v>
+        <v>-27.97</v>
       </c>
       <c r="E31" s="6">
-        <v>-37.05</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>653.9</v>
+        <v>757.45</v>
       </c>
       <c r="D32" s="5">
-        <v>670.05</v>
-      </c>
-      <c r="E32" s="7">
-        <v>16.15</v>
+        <v>728.8</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-28.65</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>873.6</v>
+        <v>670.05</v>
       </c>
       <c r="D33" s="5">
-        <v>879.75</v>
+        <v>676.05</v>
       </c>
       <c r="E33" s="7">
-        <v>6.15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>1099.6</v>
+        <v>879.75</v>
       </c>
       <c r="D34" s="5">
-        <v>1106</v>
-      </c>
-      <c r="E34" s="7">
-        <v>6.4</v>
+        <v>875</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-4.75</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>1699.5</v>
+        <v>1106</v>
       </c>
       <c r="D35" s="5">
-        <v>1707.6</v>
-      </c>
-      <c r="E35" s="7">
-        <v>8.1</v>
+        <v>1099</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-7</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>99</v>
+        <v>1707.6</v>
       </c>
       <c r="D36" s="5">
-        <v>79</v>
+        <v>1671.2</v>
       </c>
       <c r="E36" s="6">
-        <v>-20</v>
+        <v>-36.4</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C37" s="5">
-        <v>79</v>
+        <v>61.39</v>
       </c>
       <c r="D37" s="5">
-        <v>99</v>
-      </c>
-      <c r="E37" s="7">
-        <v>20</v>
+        <v>57.15</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-4.24</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>67.41</v>
+        <v>62.59</v>
       </c>
       <c r="D38" s="5">
-        <v>61.39</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-6.02</v>
+        <v>64.23</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1.64</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>57.73</v>
+        <v>39.78</v>
       </c>
       <c r="D39" s="5">
-        <v>62.59</v>
-      </c>
-      <c r="E39" s="7">
-        <v>4.86</v>
+        <v>38.19</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>36.62</v>
+        <v>37.07</v>
       </c>
       <c r="D40" s="5">
-        <v>39.78</v>
-      </c>
-      <c r="E40" s="7">
-        <v>3.16</v>
+        <v>35.74</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>35.02</v>
+        <v>29.65</v>
       </c>
       <c r="D41" s="5">
-        <v>37.07</v>
-      </c>
-      <c r="E41" s="7">
-        <v>2.05</v>
+        <v>26.97</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C42" s="5">
-        <v>28.18</v>
+        <v>-35.04</v>
       </c>
       <c r="D42" s="5">
-        <v>29.65</v>
-      </c>
-      <c r="E42" s="7">
-        <v>1.47</v>
+        <v>-87.45</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-52.41</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C43" s="5">
-        <v>403.99</v>
+        <v>-82.68000000000001</v>
       </c>
       <c r="D43" s="5">
-        <v>-35.04</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-439.03</v>
+        <v>-15.62</v>
+      </c>
+      <c r="E43" s="7">
+        <v>67.06</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>-91.93000000000001</v>
+        <v>-64.58</v>
       </c>
       <c r="D44" s="5">
-        <v>-82.68000000000001</v>
+        <v>-49.9</v>
       </c>
       <c r="E44" s="7">
-        <v>9.25</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-67.92</v>
+        <v>-69.90000000000001</v>
       </c>
       <c r="D45" s="5">
-        <v>-64.58</v>
+        <v>-65.78</v>
       </c>
       <c r="E45" s="7">
-        <v>3.34</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>-69.73</v>
+        <v>-58.02</v>
       </c>
       <c r="D46" s="5">
-        <v>-69.90000000000001</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="5">
         <v>-34.51</v>
       </c>
-      <c r="D47" s="5">
-        <v>-58.02</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-23.51</v>
+      <c r="E46" s="7">
+        <v>23.51</v>
       </c>
     </row>
   </sheetData>
@@ -2393,16 +2376,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>46.1</v>
+        <v>44.5</v>
       </c>
       <c r="E2" s="10">
         <v>60</v>
       </c>
       <c r="F2" s="10">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="G2" s="10">
-        <v>-1</v>
+        <v>-1.9</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2527,19 +2510,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.1344</v>
+        <v>0.1372</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0198</v>
+        <v>0.0221</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0274</v>
+        <v>-0.0254</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.04940000000000001</v>
+        <v>-0.0528</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1067</v>
+        <v>-0.1105</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>27.0 → 32.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>27.0</t>
+  </si>
+  <si>
+    <t>32.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -252,14 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,14 +395,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -890,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>728.8</v>
+        <v>739</v>
       </c>
       <c r="D2">
-        <v>-3.78</v>
+        <v>1.4</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,46 +930,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-20.67</v>
+        <v>-19.56</v>
       </c>
       <c r="H2">
-        <v>39.66</v>
+        <v>41.61</v>
       </c>
       <c r="I2">
-        <v>-3.49</v>
+        <v>1.69</v>
       </c>
       <c r="J2">
-        <v>22.03</v>
+        <v>24.52</v>
       </c>
       <c r="K2">
-        <v>0.46</v>
+        <v>3.69</v>
       </c>
       <c r="L2">
-        <v>-11.66</v>
+        <v>-13.08</v>
       </c>
       <c r="M2">
-        <v>-11.05</v>
+        <v>-10.83</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>745.38</v>
+        <v>747.84</v>
       </c>
       <c r="Q2">
-        <v>660.01</v>
+        <v>667.66</v>
       </c>
       <c r="R2">
-        <v>642.2</v>
+        <v>642.97</v>
       </c>
       <c r="S2">
-        <v>668.11</v>
+        <v>668.24</v>
       </c>
       <c r="T2">
-        <v>9.08</v>
+        <v>10.59</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -956,34 +984,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>57.15</v>
+        <v>58.25</v>
       </c>
       <c r="Z2">
-        <v>35.92</v>
+        <v>35.49</v>
       </c>
       <c r="AA2">
-        <v>24.57</v>
+        <v>26.75</v>
       </c>
       <c r="AB2">
-        <v>11.35</v>
+        <v>8.74</v>
       </c>
       <c r="AC2">
-        <v>70.13</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="AD2">
-        <v>71.77</v>
+        <v>68.83</v>
       </c>
       <c r="AE2">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="AF2">
-        <v>-87.45</v>
+        <v>-78.51000000000001</v>
       </c>
       <c r="AG2">
-        <v>827.59</v>
+        <v>834.98</v>
       </c>
       <c r="AH2">
-        <v>492.42</v>
+        <v>500.34</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -992,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>55.47</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,58 +1031,58 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>676.05</v>
+        <v>657.8</v>
       </c>
       <c r="D3">
-        <v>0.9</v>
+        <v>-2.7</v>
       </c>
       <c r="E3">
-        <v>734.85</v>
+        <v>722.85</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H3">
-        <v>31.78</v>
+        <v>28.23</v>
       </c>
       <c r="I3">
-        <v>3.43</v>
+        <v>-0.57</v>
       </c>
       <c r="J3">
-        <v>10.81</v>
+        <v>5.12</v>
       </c>
       <c r="K3">
-        <v>20.28</v>
+        <v>17.96</v>
       </c>
       <c r="L3">
-        <v>-7.56</v>
+        <v>-10.49</v>
       </c>
       <c r="M3">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="P3">
-        <v>664.45</v>
+        <v>663.6900000000001</v>
       </c>
       <c r="Q3">
-        <v>654.95</v>
+        <v>657.1</v>
       </c>
       <c r="R3">
-        <v>604.12</v>
+        <v>605.84</v>
       </c>
       <c r="S3">
-        <v>584.23</v>
+        <v>584.64</v>
       </c>
       <c r="T3">
-        <v>15.72</v>
+        <v>12.51</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1069,34 +1097,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>64.23</v>
+        <v>56.15</v>
       </c>
       <c r="Z3">
-        <v>18.27</v>
+        <v>16.79</v>
       </c>
       <c r="AA3">
-        <v>20.01</v>
+        <v>19.36</v>
       </c>
       <c r="AB3">
-        <v>-1.74</v>
+        <v>-2.58</v>
       </c>
       <c r="AC3">
-        <v>36.59</v>
+        <v>34.53</v>
       </c>
       <c r="AD3">
-        <v>26.59</v>
+        <v>32.02</v>
       </c>
       <c r="AE3">
-        <v>22.91</v>
+        <v>23.18</v>
       </c>
       <c r="AF3">
-        <v>-15.62</v>
+        <v>-86.38</v>
       </c>
       <c r="AG3">
-        <v>696.34</v>
+        <v>693.92</v>
       </c>
       <c r="AH3">
-        <v>613.55</v>
+        <v>620.28</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1105,7 +1133,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>35.76</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="D4">
-        <v>-0.54</v>
+        <v>0.57</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1128,46 +1156,46 @@
         <v>857</v>
       </c>
       <c r="G4">
-        <v>-29.57</v>
+        <v>-29.17</v>
       </c>
       <c r="H4">
-        <v>2.1</v>
+        <v>2.68</v>
       </c>
       <c r="I4">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>-5.83</v>
+        <v>-4.64</v>
       </c>
       <c r="K4">
-        <v>-15.43</v>
+        <v>-13.89</v>
       </c>
       <c r="L4">
-        <v>-28.4</v>
+        <v>-27.6</v>
       </c>
       <c r="M4">
-        <v>-2.54</v>
+        <v>-2.37</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P4">
         <v>875.17</v>
       </c>
       <c r="Q4">
-        <v>880.09</v>
+        <v>877.9400000000001</v>
       </c>
       <c r="R4">
-        <v>960.65</v>
+        <v>957.1</v>
       </c>
       <c r="S4">
-        <v>1067.95</v>
+        <v>1066.8</v>
       </c>
       <c r="T4">
-        <v>-18.07</v>
+        <v>-17.51</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1182,34 +1210,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.19</v>
+        <v>40.86</v>
       </c>
       <c r="Z4">
-        <v>-22.88</v>
+        <v>-20.9</v>
       </c>
       <c r="AA4">
-        <v>-28.92</v>
+        <v>-27.31</v>
       </c>
       <c r="AB4">
-        <v>6.04</v>
+        <v>6.41</v>
       </c>
       <c r="AC4">
-        <v>96.3</v>
+        <v>97.08</v>
       </c>
       <c r="AD4">
-        <v>93.05</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="AE4">
-        <v>18.36</v>
+        <v>17.7</v>
       </c>
       <c r="AF4">
-        <v>-49.9</v>
+        <v>-79.17</v>
       </c>
       <c r="AG4">
-        <v>918.51</v>
+        <v>910.64</v>
       </c>
       <c r="AH4">
-        <v>841.66</v>
+        <v>845.24</v>
       </c>
       <c r="AI4">
         <v>924.5700000000001</v>
@@ -1218,7 +1246,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>36.5</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1099</v>
+        <v>1105.3</v>
       </c>
       <c r="D5">
-        <v>-0.63</v>
+        <v>0.57</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,46 +1269,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-22.48</v>
+        <v>-22.04</v>
       </c>
       <c r="H5">
-        <v>46.73</v>
+        <v>47.57</v>
       </c>
       <c r="I5">
-        <v>-2.51</v>
+        <v>-0.19</v>
       </c>
       <c r="J5">
-        <v>-5.74</v>
+        <v>-2.87</v>
       </c>
       <c r="K5">
-        <v>-5.32</v>
+        <v>-4.18</v>
       </c>
       <c r="L5">
-        <v>-6.52</v>
+        <v>-6.16</v>
       </c>
       <c r="M5">
-        <v>13.72</v>
+        <v>13.88</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P5">
-        <v>1102.74</v>
+        <v>1102.32</v>
       </c>
       <c r="Q5">
-        <v>1131.49</v>
+        <v>1129.23</v>
       </c>
       <c r="R5">
-        <v>1223.3</v>
+        <v>1218.62</v>
       </c>
       <c r="S5">
-        <v>1071.69</v>
+        <v>1072.15</v>
       </c>
       <c r="T5">
-        <v>2.55</v>
+        <v>3.09</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1295,34 +1323,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>35.74</v>
+        <v>37.89</v>
       </c>
       <c r="Z5">
-        <v>-30.23</v>
+        <v>-29.06</v>
       </c>
       <c r="AA5">
-        <v>-31.04</v>
+        <v>-30.65</v>
       </c>
       <c r="AB5">
-        <v>0.8100000000000001</v>
+        <v>1.58</v>
       </c>
       <c r="AC5">
-        <v>41.98</v>
+        <v>52.49</v>
       </c>
       <c r="AD5">
-        <v>40.13</v>
+        <v>45.03</v>
       </c>
       <c r="AE5">
-        <v>35.21</v>
+        <v>36.67</v>
       </c>
       <c r="AF5">
-        <v>-65.78</v>
+        <v>166.39</v>
       </c>
       <c r="AG5">
-        <v>1176.87</v>
+        <v>1175.12</v>
       </c>
       <c r="AH5">
-        <v>1086.11</v>
+        <v>1083.34</v>
       </c>
       <c r="AI5">
         <v>1202.84</v>
@@ -1331,7 +1359,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>20.3</v>
+        <v>19.95</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1671.2</v>
+        <v>1700.1</v>
       </c>
       <c r="D6">
-        <v>-2.13</v>
+        <v>1.73</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,46 +1382,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-27.97</v>
+        <v>-26.73</v>
       </c>
       <c r="H6">
-        <v>13.59</v>
+        <v>15.55</v>
       </c>
       <c r="I6">
-        <v>-0.42</v>
+        <v>0.53</v>
       </c>
       <c r="J6">
-        <v>-18.44</v>
+        <v>-16.46</v>
       </c>
       <c r="K6">
-        <v>-9.69</v>
+        <v>-7.1</v>
       </c>
       <c r="L6">
-        <v>-22.1</v>
+        <v>-19.19</v>
       </c>
       <c r="M6">
-        <v>-5.28</v>
+        <v>-5.75</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P6">
-        <v>1693.26</v>
+        <v>1695.06</v>
       </c>
       <c r="Q6">
-        <v>1841.02</v>
+        <v>1822.55</v>
       </c>
       <c r="R6">
-        <v>1976.52</v>
+        <v>1968.71</v>
       </c>
       <c r="S6">
-        <v>1844.54</v>
+        <v>1843.16</v>
       </c>
       <c r="T6">
-        <v>-9.4</v>
+        <v>-7.76</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1408,43 +1436,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>26.97</v>
+        <v>32.21</v>
       </c>
       <c r="Z6">
-        <v>-91.22</v>
+        <v>-88.26000000000001</v>
       </c>
       <c r="AA6">
-        <v>-78.65000000000001</v>
+        <v>-80.56999999999999</v>
       </c>
       <c r="AB6">
-        <v>-12.57</v>
+        <v>-7.68</v>
       </c>
       <c r="AC6">
-        <v>26.85</v>
+        <v>39.99</v>
       </c>
       <c r="AD6">
-        <v>25.7</v>
+        <v>31.33</v>
       </c>
       <c r="AE6">
-        <v>55.75</v>
+        <v>54.2</v>
       </c>
       <c r="AF6">
-        <v>-34.51</v>
+        <v>-63.03</v>
       </c>
       <c r="AG6">
-        <v>2138.37</v>
+        <v>2105.72</v>
       </c>
       <c r="AH6">
-        <v>1543.67</v>
+        <v>1539.39</v>
       </c>
       <c r="AI6">
-        <v>1854.05</v>
+        <v>1845.66</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>48.87</v>
+        <v>49.9</v>
       </c>
     </row>
   </sheetData>
@@ -1605,12 +1633,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1618,700 +1681,700 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>27.8</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>22.03</v>
       </c>
-      <c r="E7" s="6">
-        <v>-5.77</v>
+      <c r="D7" s="6">
+        <v>24.52</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2.49</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>16.99</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>10.81</v>
       </c>
-      <c r="E8" s="6">
-        <v>-6.18</v>
+      <c r="D8" s="6">
+        <v>5.12</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-5.69</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-5.29</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-5.83</v>
       </c>
-      <c r="E9" s="6">
-        <v>-0.54</v>
+      <c r="D9" s="6">
+        <v>-4.64</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.19</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-6.63</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-5.74</v>
       </c>
+      <c r="D10" s="6">
+        <v>-2.87</v>
+      </c>
       <c r="E10" s="7">
-        <v>0.89</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-16.29</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-18.44</v>
       </c>
-      <c r="E11" s="6">
-        <v>-2.15</v>
+      <c r="D11" s="6">
+        <v>-16.46</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.98</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>14.43</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-3.49</v>
       </c>
-      <c r="E12" s="6">
-        <v>-17.92</v>
+      <c r="D12" s="6">
+        <v>1.69</v>
+      </c>
+      <c r="E12" s="7">
+        <v>5.18</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>3.51</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>3.43</v>
       </c>
-      <c r="E13" s="6">
-        <v>-0.08</v>
+      <c r="D13" s="6">
+        <v>-0.57</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-4</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>1.94</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>0.23</v>
       </c>
-      <c r="E14" s="6">
-        <v>-1.71</v>
+      <c r="D14" s="6">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-2.68</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-2.51</v>
       </c>
+      <c r="D15" s="6">
+        <v>-0.19</v>
+      </c>
       <c r="E15" s="7">
-        <v>0.17</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>2.54</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-0.42</v>
       </c>
-      <c r="E16" s="6">
-        <v>-2.96</v>
+      <c r="D16" s="6">
+        <v>0.53</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.95</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>-9.369999999999999</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-11.66</v>
       </c>
-      <c r="E17" s="6">
-        <v>-2.29</v>
+      <c r="D17" s="6">
+        <v>-13.08</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>-7.57</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-7.56</v>
       </c>
-      <c r="E18" s="7">
-        <v>0.01</v>
+      <c r="D18" s="6">
+        <v>-10.49</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-2.93</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-27.98</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-28.4</v>
       </c>
-      <c r="E19" s="6">
-        <v>-0.42</v>
+      <c r="D19" s="6">
+        <v>-27.6</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.8</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>-9.140000000000001</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-6.52</v>
       </c>
+      <c r="D20" s="6">
+        <v>-6.16</v>
+      </c>
       <c r="E20" s="7">
-        <v>2.62</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-18.2</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-22.1</v>
       </c>
-      <c r="E21" s="6">
-        <v>-3.9</v>
+      <c r="D21" s="6">
+        <v>-19.19</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2.91</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>0.74</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>0.46</v>
       </c>
-      <c r="E22" s="6">
-        <v>-0.28</v>
+      <c r="D22" s="6">
+        <v>3.69</v>
+      </c>
+      <c r="E22" s="7">
+        <v>3.23</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="5">
-        <v>18.46</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>20.28</v>
       </c>
-      <c r="E23" s="7">
-        <v>1.82</v>
+      <c r="D23" s="6">
+        <v>17.96</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-2.32</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="5">
-        <v>-13.79</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>-15.43</v>
       </c>
-      <c r="E24" s="6">
-        <v>-1.64</v>
+      <c r="D24" s="6">
+        <v>-13.89</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.54</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
-        <v>-4.05</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C25" s="6">
         <v>-5.32</v>
       </c>
-      <c r="E25" s="6">
-        <v>-1.27</v>
+      <c r="D25" s="6">
+        <v>-4.18</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.14</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="5">
-        <v>-6.21</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C26" s="6">
         <v>-9.69</v>
       </c>
-      <c r="E26" s="6">
-        <v>-3.48</v>
+      <c r="D26" s="6">
+        <v>-7.1</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.59</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="5">
-        <v>-17.56</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="6">
         <v>-20.67</v>
       </c>
-      <c r="E27" s="6">
-        <v>-3.11</v>
+      <c r="D27" s="6">
+        <v>-19.56</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.11</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="5">
-        <v>-8.82</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C28" s="6">
         <v>-8</v>
       </c>
-      <c r="E28" s="7">
-        <v>0.82</v>
+      <c r="D28" s="6">
+        <v>-9</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="5">
-        <v>-29.19</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C29" s="6">
         <v>-29.57</v>
       </c>
-      <c r="E29" s="6">
-        <v>-0.38</v>
+      <c r="D29" s="6">
+        <v>-29.17</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="5">
-        <v>-21.99</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-22.48</v>
       </c>
-      <c r="E30" s="6">
-        <v>-0.49</v>
+      <c r="D30" s="6">
+        <v>-22.04</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.44</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="5">
-        <v>-26.41</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C31" s="6">
         <v>-27.97</v>
       </c>
-      <c r="E31" s="6">
-        <v>-1.56</v>
+      <c r="D31" s="6">
+        <v>-26.73</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.24</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="5">
-        <v>757.45</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C32" s="6">
         <v>728.8</v>
       </c>
-      <c r="E32" s="6">
-        <v>-28.65</v>
+      <c r="D32" s="6">
+        <v>739</v>
+      </c>
+      <c r="E32" s="7">
+        <v>10.2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="5">
-        <v>670.05</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C33" s="6">
         <v>676.05</v>
       </c>
-      <c r="E33" s="7">
-        <v>6</v>
+      <c r="D33" s="6">
+        <v>657.8</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-18.25</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="5">
-        <v>879.75</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C34" s="6">
         <v>875</v>
       </c>
-      <c r="E34" s="6">
-        <v>-4.75</v>
+      <c r="D34" s="6">
+        <v>880</v>
+      </c>
+      <c r="E34" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="5">
-        <v>1106</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C35" s="6">
         <v>1099</v>
       </c>
-      <c r="E35" s="6">
-        <v>-7</v>
+      <c r="D35" s="6">
+        <v>1105.3</v>
+      </c>
+      <c r="E35" s="7">
+        <v>6.3</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="5">
-        <v>1707.6</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="C36" s="6">
         <v>1671.2</v>
       </c>
-      <c r="E36" s="6">
-        <v>-36.4</v>
+      <c r="D36" s="6">
+        <v>1700.1</v>
+      </c>
+      <c r="E36" s="7">
+        <v>28.9</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="5">
-        <v>61.39</v>
-      </c>
-      <c r="D37" s="5">
+      <c r="C37" s="6">
         <v>57.15</v>
       </c>
-      <c r="E37" s="6">
-        <v>-4.24</v>
+      <c r="D37" s="6">
+        <v>58.25</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.1</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="5">
-        <v>62.59</v>
-      </c>
-      <c r="D38" s="5">
+      <c r="C38" s="6">
         <v>64.23</v>
       </c>
-      <c r="E38" s="7">
-        <v>1.64</v>
+      <c r="D38" s="6">
+        <v>56.15</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-8.08</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="5">
-        <v>39.78</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="C39" s="6">
         <v>38.19</v>
       </c>
-      <c r="E39" s="6">
-        <v>-1.59</v>
+      <c r="D39" s="6">
+        <v>40.86</v>
+      </c>
+      <c r="E39" s="7">
+        <v>2.67</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="5">
-        <v>37.07</v>
-      </c>
-      <c r="D40" s="5">
+      <c r="C40" s="6">
         <v>35.74</v>
       </c>
-      <c r="E40" s="6">
-        <v>-1.33</v>
+      <c r="D40" s="6">
+        <v>37.89</v>
+      </c>
+      <c r="E40" s="7">
+        <v>2.15</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="5">
-        <v>29.65</v>
-      </c>
-      <c r="D41" s="5">
+      <c r="C41" s="6">
         <v>26.97</v>
       </c>
-      <c r="E41" s="6">
-        <v>-2.68</v>
+      <c r="D41" s="6">
+        <v>32.21</v>
+      </c>
+      <c r="E41" s="7">
+        <v>5.24</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="5">
-        <v>-35.04</v>
-      </c>
-      <c r="D42" s="5">
+      <c r="C42" s="6">
         <v>-87.45</v>
       </c>
-      <c r="E42" s="6">
-        <v>-52.41</v>
+      <c r="D42" s="6">
+        <v>-78.51000000000001</v>
+      </c>
+      <c r="E42" s="7">
+        <v>8.94</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="5">
-        <v>-82.68000000000001</v>
-      </c>
-      <c r="D43" s="5">
+      <c r="C43" s="6">
         <v>-15.62</v>
       </c>
-      <c r="E43" s="7">
-        <v>67.06</v>
+      <c r="D43" s="6">
+        <v>-86.38</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-70.76000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="5">
-        <v>-64.58</v>
-      </c>
-      <c r="D44" s="5">
+      <c r="C44" s="6">
         <v>-49.9</v>
       </c>
-      <c r="E44" s="7">
-        <v>14.68</v>
+      <c r="D44" s="6">
+        <v>-79.17</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-29.27</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="5">
-        <v>-69.90000000000001</v>
-      </c>
-      <c r="D45" s="5">
+      <c r="C45" s="6">
         <v>-65.78</v>
       </c>
+      <c r="D45" s="6">
+        <v>166.39</v>
+      </c>
       <c r="E45" s="7">
-        <v>4.12</v>
+        <v>232.17</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C46" s="5">
-        <v>-58.02</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C46" s="6">
         <v>-34.51</v>
       </c>
-      <c r="E46" s="7">
-        <v>23.51</v>
+      <c r="D46" s="6">
+        <v>-63.03</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-28.52</v>
       </c>
     </row>
   </sheetData>
@@ -2337,60 +2400,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="11">
+        <v>57.92</v>
+      </c>
+      <c r="C2" s="12">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11">
+        <v>45.1</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="10">
-        <v>57.92</v>
-      </c>
-      <c r="C2" s="11">
-        <v>5</v>
-      </c>
-      <c r="D2" s="10">
-        <v>44.5</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-1.9</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>1.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-0.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2492,37 +2555,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.1372</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0221</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0254</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0528</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1105</v>
+      <c r="A2" s="14">
+        <v>0.1388</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0194</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0237</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0575</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1083</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,34 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>27.0 → 32.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>27.0</t>
-  </si>
-  <si>
-    <t>32.2</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -279,14 +252,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -319,13 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,15 +368,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -918,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>739</v>
+        <v>711.8</v>
       </c>
       <c r="D2">
-        <v>1.4</v>
+        <v>-3.68</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -930,46 +902,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-19.56</v>
+        <v>-22.53</v>
       </c>
       <c r="H2">
-        <v>41.61</v>
+        <v>36.4</v>
       </c>
       <c r="I2">
-        <v>1.69</v>
+        <v>-1.06</v>
       </c>
       <c r="J2">
-        <v>24.52</v>
+        <v>21.49</v>
       </c>
       <c r="K2">
-        <v>3.69</v>
+        <v>0.08</v>
       </c>
       <c r="L2">
-        <v>-13.08</v>
+        <v>-14.23</v>
       </c>
       <c r="M2">
-        <v>-10.83</v>
+        <v>-11.27</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P2">
-        <v>747.84</v>
+        <v>746.3099999999999</v>
       </c>
       <c r="Q2">
-        <v>667.66</v>
+        <v>674.1799999999999</v>
       </c>
       <c r="R2">
-        <v>642.97</v>
+        <v>643.4</v>
       </c>
       <c r="S2">
-        <v>668.24</v>
+        <v>668.05</v>
       </c>
       <c r="T2">
-        <v>10.59</v>
+        <v>6.55</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -984,34 +956,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>58.25</v>
+        <v>54.23</v>
       </c>
       <c r="Z2">
-        <v>35.49</v>
+        <v>32.58</v>
       </c>
       <c r="AA2">
-        <v>26.75</v>
+        <v>27.92</v>
       </c>
       <c r="AB2">
-        <v>8.74</v>
+        <v>4.66</v>
       </c>
       <c r="AC2">
-        <v>64.01000000000001</v>
+        <v>41.02</v>
       </c>
       <c r="AD2">
-        <v>68.83</v>
+        <v>58.39</v>
       </c>
       <c r="AE2">
-        <v>46.5</v>
+        <v>45.6</v>
       </c>
       <c r="AF2">
-        <v>-78.51000000000001</v>
+        <v>-94.81</v>
       </c>
       <c r="AG2">
-        <v>834.98</v>
+        <v>837.47</v>
       </c>
       <c r="AH2">
-        <v>500.34</v>
+        <v>510.89</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -1020,7 +992,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>54.71</v>
+        <v>52.94</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,37 +1003,37 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>657.8</v>
+        <v>642.5</v>
       </c>
       <c r="D3">
-        <v>-2.7</v>
+        <v>-2.33</v>
       </c>
       <c r="E3">
-        <v>722.85</v>
+        <v>715.8</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-9</v>
+        <v>-10.24</v>
       </c>
       <c r="H3">
-        <v>28.23</v>
+        <v>25.24</v>
       </c>
       <c r="I3">
-        <v>-0.57</v>
+        <v>-2.75</v>
       </c>
       <c r="J3">
-        <v>5.12</v>
+        <v>4.51</v>
       </c>
       <c r="K3">
-        <v>17.96</v>
+        <v>15.45</v>
       </c>
       <c r="L3">
-        <v>-10.49</v>
+        <v>-11.12</v>
       </c>
       <c r="M3">
-        <v>1.94</v>
+        <v>1.32</v>
       </c>
       <c r="N3">
         <v>99</v>
@@ -1070,19 +1042,19 @@
         <v>66</v>
       </c>
       <c r="P3">
-        <v>663.6900000000001</v>
+        <v>660.0599999999999</v>
       </c>
       <c r="Q3">
-        <v>657.1</v>
+        <v>658.76</v>
       </c>
       <c r="R3">
-        <v>605.84</v>
+        <v>607.33</v>
       </c>
       <c r="S3">
-        <v>584.64</v>
+        <v>584.87</v>
       </c>
       <c r="T3">
-        <v>12.51</v>
+        <v>9.85</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1097,34 +1069,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>56.15</v>
+        <v>50.42</v>
       </c>
       <c r="Z3">
-        <v>16.79</v>
+        <v>14.21</v>
       </c>
       <c r="AA3">
-        <v>19.36</v>
+        <v>18.33</v>
       </c>
       <c r="AB3">
-        <v>-2.58</v>
+        <v>-4.12</v>
       </c>
       <c r="AC3">
-        <v>34.53</v>
+        <v>19.35</v>
       </c>
       <c r="AD3">
-        <v>32.02</v>
+        <v>30.16</v>
       </c>
       <c r="AE3">
-        <v>23.18</v>
+        <v>23.13</v>
       </c>
       <c r="AF3">
-        <v>-86.38</v>
+        <v>-87.56</v>
       </c>
       <c r="AG3">
-        <v>693.92</v>
+        <v>688.89</v>
       </c>
       <c r="AH3">
-        <v>620.28</v>
+        <v>628.63</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1133,7 +1105,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>34.48</v>
+        <v>30.83</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1116,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>880</v>
+        <v>868</v>
       </c>
       <c r="D4">
-        <v>0.57</v>
+        <v>-1.36</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1156,46 +1128,46 @@
         <v>857</v>
       </c>
       <c r="G4">
-        <v>-29.17</v>
+        <v>-30.14</v>
       </c>
       <c r="H4">
-        <v>2.68</v>
+        <v>1.28</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="J4">
-        <v>-4.64</v>
+        <v>-5.96</v>
       </c>
       <c r="K4">
-        <v>-13.89</v>
+        <v>-14.06</v>
       </c>
       <c r="L4">
-        <v>-27.6</v>
+        <v>-26.19</v>
       </c>
       <c r="M4">
-        <v>-2.37</v>
+        <v>-2.91</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>875.17</v>
+        <v>875.27</v>
       </c>
       <c r="Q4">
-        <v>877.9400000000001</v>
+        <v>875.59</v>
       </c>
       <c r="R4">
-        <v>957.1</v>
+        <v>953.02</v>
       </c>
       <c r="S4">
-        <v>1066.8</v>
+        <v>1065.55</v>
       </c>
       <c r="T4">
-        <v>-17.51</v>
+        <v>-18.54</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1210,43 +1182,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>40.86</v>
+        <v>36.76</v>
       </c>
       <c r="Z4">
-        <v>-20.9</v>
+        <v>-20.07</v>
       </c>
       <c r="AA4">
-        <v>-27.31</v>
+        <v>-25.86</v>
       </c>
       <c r="AB4">
-        <v>6.41</v>
+        <v>5.8</v>
       </c>
       <c r="AC4">
-        <v>97.08</v>
+        <v>89.36</v>
       </c>
       <c r="AD4">
-        <v>94.93000000000001</v>
+        <v>94.25</v>
       </c>
       <c r="AE4">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="AF4">
-        <v>-79.17</v>
+        <v>-12.49</v>
       </c>
       <c r="AG4">
-        <v>910.64</v>
+        <v>903.47</v>
       </c>
       <c r="AH4">
-        <v>845.24</v>
+        <v>847.7</v>
       </c>
       <c r="AI4">
-        <v>924.5700000000001</v>
+        <v>921.8200000000001</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>33.38</v>
+        <v>32.21</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1105.3</v>
+        <v>1076.1</v>
       </c>
       <c r="D5">
-        <v>0.57</v>
+        <v>-2.64</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1269,46 +1241,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-22.04</v>
+        <v>-24.1</v>
       </c>
       <c r="H5">
-        <v>47.57</v>
+        <v>43.67</v>
       </c>
       <c r="I5">
-        <v>-0.19</v>
+        <v>-2.32</v>
       </c>
       <c r="J5">
-        <v>-2.87</v>
+        <v>-6.47</v>
       </c>
       <c r="K5">
-        <v>-4.18</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L5">
-        <v>-6.16</v>
+        <v>-8.82</v>
       </c>
       <c r="M5">
-        <v>13.88</v>
+        <v>13.7</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="P5">
-        <v>1102.32</v>
+        <v>1097.2</v>
       </c>
       <c r="Q5">
-        <v>1129.23</v>
+        <v>1124.66</v>
       </c>
       <c r="R5">
-        <v>1218.62</v>
+        <v>1213.44</v>
       </c>
       <c r="S5">
-        <v>1072.15</v>
+        <v>1072.44</v>
       </c>
       <c r="T5">
-        <v>3.09</v>
+        <v>0.34</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1323,43 +1295,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>37.89</v>
+        <v>32.46</v>
       </c>
       <c r="Z5">
-        <v>-29.06</v>
+        <v>-30.15</v>
       </c>
       <c r="AA5">
-        <v>-30.65</v>
+        <v>-30.55</v>
       </c>
       <c r="AB5">
-        <v>1.58</v>
+        <v>0.4</v>
       </c>
       <c r="AC5">
-        <v>52.49</v>
+        <v>35.66</v>
       </c>
       <c r="AD5">
-        <v>45.03</v>
+        <v>43.38</v>
       </c>
       <c r="AE5">
-        <v>36.67</v>
+        <v>37.43</v>
       </c>
       <c r="AF5">
-        <v>166.39</v>
+        <v>17.53</v>
       </c>
       <c r="AG5">
-        <v>1175.12</v>
+        <v>1172.66</v>
       </c>
       <c r="AH5">
-        <v>1083.34</v>
+        <v>1076.66</v>
       </c>
       <c r="AI5">
-        <v>1202.84</v>
+        <v>1196.23</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>19.95</v>
+        <v>18.62</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1700.1</v>
+        <v>1669.8</v>
       </c>
       <c r="D6">
-        <v>1.73</v>
+        <v>-1.78</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1382,25 +1354,25 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-26.73</v>
+        <v>-28.04</v>
       </c>
       <c r="H6">
-        <v>15.55</v>
+        <v>13.49</v>
       </c>
       <c r="I6">
-        <v>0.53</v>
+        <v>-1.6</v>
       </c>
       <c r="J6">
-        <v>-16.46</v>
+        <v>-19.31</v>
       </c>
       <c r="K6">
-        <v>-7.1</v>
+        <v>-10.54</v>
       </c>
       <c r="L6">
-        <v>-19.19</v>
+        <v>-20.63</v>
       </c>
       <c r="M6">
-        <v>-5.75</v>
+        <v>-5.66</v>
       </c>
       <c r="N6">
         <v>40</v>
@@ -1409,19 +1381,19 @@
         <v>31</v>
       </c>
       <c r="P6">
-        <v>1695.06</v>
+        <v>1689.64</v>
       </c>
       <c r="Q6">
-        <v>1822.55</v>
+        <v>1804.59</v>
       </c>
       <c r="R6">
-        <v>1968.71</v>
+        <v>1960.07</v>
       </c>
       <c r="S6">
-        <v>1843.16</v>
+        <v>1841.3</v>
       </c>
       <c r="T6">
-        <v>-7.76</v>
+        <v>-9.31</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1436,34 +1408,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>32.21</v>
+        <v>29.8</v>
       </c>
       <c r="Z6">
-        <v>-88.26000000000001</v>
+        <v>-87.34</v>
       </c>
       <c r="AA6">
-        <v>-80.56999999999999</v>
+        <v>-81.93000000000001</v>
       </c>
       <c r="AB6">
-        <v>-7.68</v>
+        <v>-5.42</v>
       </c>
       <c r="AC6">
-        <v>39.99</v>
+        <v>47.81</v>
       </c>
       <c r="AD6">
-        <v>31.33</v>
+        <v>38.22</v>
       </c>
       <c r="AE6">
-        <v>54.2</v>
+        <v>53.26</v>
       </c>
       <c r="AF6">
-        <v>-63.03</v>
+        <v>-41.25</v>
       </c>
       <c r="AG6">
-        <v>2105.72</v>
+        <v>2078.01</v>
       </c>
       <c r="AH6">
-        <v>1539.39</v>
+        <v>1531.17</v>
       </c>
       <c r="AI6">
         <v>1845.66</v>
@@ -1472,7 +1444,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>49.9</v>
+        <v>49.65</v>
       </c>
     </row>
   </sheetData>
@@ -1633,47 +1605,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1681,700 +1618,700 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>22.03</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>24.52</v>
       </c>
-      <c r="E7" s="7">
-        <v>2.49</v>
+      <c r="D7" s="5">
+        <v>21.49</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-3.03</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>10.81</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>5.12</v>
       </c>
-      <c r="E8" s="8">
-        <v>-5.69</v>
+      <c r="D8" s="5">
+        <v>4.51</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-5.83</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-4.64</v>
       </c>
-      <c r="E9" s="7">
-        <v>1.19</v>
+      <c r="D9" s="5">
+        <v>-5.96</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-5.74</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-2.87</v>
       </c>
-      <c r="E10" s="7">
-        <v>2.87</v>
+      <c r="D10" s="5">
+        <v>-6.47</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-3.6</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-18.44</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-16.46</v>
       </c>
-      <c r="E11" s="7">
-        <v>1.98</v>
+      <c r="D11" s="5">
+        <v>-19.31</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-2.85</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-3.49</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>1.69</v>
       </c>
-      <c r="E12" s="7">
-        <v>5.18</v>
+      <c r="D12" s="5">
+        <v>-1.06</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
-        <v>3.43</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-0.57</v>
       </c>
-      <c r="E13" s="8">
-        <v>-4</v>
+      <c r="D13" s="5">
+        <v>-2.75</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-2.18</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>0.23</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>0</v>
       </c>
-      <c r="E14" s="8">
-        <v>-0.23</v>
+      <c r="D14" s="5">
+        <v>0.06</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.06</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
+        <v>-0.19</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-2.32</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-2.13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-1.6</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-2.13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-13.08</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-14.23</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-10.49</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-11.12</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-27.6</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-26.19</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-6.16</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-8.82</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-19.19</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-20.63</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-3.61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>17.96</v>
+      </c>
+      <c r="D23" s="5">
+        <v>15.45</v>
+      </c>
+      <c r="E23" s="6">
         <v>-2.51</v>
       </c>
-      <c r="D15" s="6">
-        <v>-0.19</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-13.89</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-14.06</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-4.18</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-4.21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-0.42</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0.53</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-7.1</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-10.54</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-3.44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-11.66</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-13.08</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-19.56</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-22.53</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-2.97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-7.56</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-10.49</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-2.93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-9</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-10.24</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-28.4</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-27.6</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-29.17</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-30.14</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-6.52</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-6.16</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-22.04</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-24.1</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-2.06</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-22.1</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-19.19</v>
-      </c>
-      <c r="E21" s="7">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-26.73</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-28.04</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.46</v>
-      </c>
-      <c r="D22" s="6">
-        <v>3.69</v>
-      </c>
-      <c r="E22" s="7">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>739</v>
+      </c>
+      <c r="D32" s="5">
+        <v>711.8</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-27.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>20.28</v>
-      </c>
-      <c r="D23" s="6">
-        <v>17.96</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-2.32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>657.8</v>
+      </c>
+      <c r="D33" s="5">
+        <v>642.5</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-15.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-15.43</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-13.89</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>880</v>
+      </c>
+      <c r="D34" s="5">
+        <v>868</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-5.32</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-4.18</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1105.3</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1076.1</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-29.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-9.69</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-7.1</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1700.1</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1669.8</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-30.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-20.67</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-19.56</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>58.25</v>
+      </c>
+      <c r="D37" s="5">
+        <v>54.23</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-4.02</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-8</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-9</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>56.15</v>
+      </c>
+      <c r="D38" s="5">
+        <v>50.42</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-5.73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-29.57</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-29.17</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>40.86</v>
+      </c>
+      <c r="D39" s="5">
+        <v>36.76</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-4.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-22.48</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-22.04</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>37.89</v>
+      </c>
+      <c r="D40" s="5">
+        <v>32.46</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-5.43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-27.97</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-26.73</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>32.21</v>
+      </c>
+      <c r="D41" s="5">
+        <v>29.8</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>728.8</v>
-      </c>
-      <c r="D32" s="6">
-        <v>739</v>
-      </c>
-      <c r="E32" s="7">
-        <v>10.2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-78.51000000000001</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-94.81</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-16.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>676.05</v>
-      </c>
-      <c r="D33" s="6">
-        <v>657.8</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-18.25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-86.38</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-87.56</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>875</v>
-      </c>
-      <c r="D34" s="6">
-        <v>880</v>
-      </c>
-      <c r="E34" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-79.17</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-12.49</v>
+      </c>
+      <c r="E44" s="7">
+        <v>66.68000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1099</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1105.3</v>
-      </c>
-      <c r="E35" s="7">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>166.39</v>
+      </c>
+      <c r="D45" s="5">
+        <v>17.53</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-148.86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>1671.2</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1700.1</v>
-      </c>
-      <c r="E36" s="7">
-        <v>28.9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="6">
-        <v>57.15</v>
-      </c>
-      <c r="D37" s="6">
-        <v>58.25</v>
-      </c>
-      <c r="E37" s="7">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>64.23</v>
-      </c>
-      <c r="D38" s="6">
-        <v>56.15</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-8.08</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>38.19</v>
-      </c>
-      <c r="D39" s="6">
-        <v>40.86</v>
-      </c>
-      <c r="E39" s="7">
-        <v>2.67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>35.74</v>
-      </c>
-      <c r="D40" s="6">
-        <v>37.89</v>
-      </c>
-      <c r="E40" s="7">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>26.97</v>
-      </c>
-      <c r="D41" s="6">
-        <v>32.21</v>
-      </c>
-      <c r="E41" s="7">
-        <v>5.24</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="6">
-        <v>-87.45</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-78.51000000000001</v>
-      </c>
-      <c r="E42" s="7">
-        <v>8.94</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-15.62</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-86.38</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-70.76000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-49.9</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-79.17</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-29.27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-65.78</v>
-      </c>
-      <c r="D45" s="6">
-        <v>166.39</v>
-      </c>
-      <c r="E45" s="7">
-        <v>232.17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-34.51</v>
-      </c>
-      <c r="D46" s="6">
+      <c r="C46" s="5">
         <v>-63.03</v>
       </c>
-      <c r="E46" s="8">
-        <v>-28.52</v>
+      <c r="D46" s="5">
+        <v>-41.25</v>
+      </c>
+      <c r="E46" s="7">
+        <v>21.78</v>
       </c>
     </row>
   </sheetData>
@@ -2400,60 +2337,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>57.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>45.1</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>40.7</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>1.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-0.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-1.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-3.5</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2555,37 +2492,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1388</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0194</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0237</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0575</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1083</v>
+      <c r="A2" s="13">
+        <v>0.137</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0132</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0291</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.0566</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1127</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.4 → 46.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.4</t>
+  </si>
+  <si>
+    <t>46.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -368,14 +395,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -890,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>711.8</v>
+        <v>696.25</v>
       </c>
       <c r="D2">
-        <v>-3.68</v>
+        <v>-2.18</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,46 +930,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-22.53</v>
+        <v>-24.22</v>
       </c>
       <c r="H2">
-        <v>36.4</v>
+        <v>33.42</v>
       </c>
       <c r="I2">
-        <v>-1.06</v>
+        <v>-12.37</v>
       </c>
       <c r="J2">
-        <v>21.49</v>
+        <v>19.74</v>
       </c>
       <c r="K2">
-        <v>0.08</v>
+        <v>-2.44</v>
       </c>
       <c r="L2">
-        <v>-14.23</v>
+        <v>-15.06</v>
       </c>
       <c r="M2">
-        <v>-11.27</v>
+        <v>-11.56</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="P2">
-        <v>746.3099999999999</v>
+        <v>726.66</v>
       </c>
       <c r="Q2">
-        <v>674.1799999999999</v>
+        <v>680.96</v>
       </c>
       <c r="R2">
-        <v>643.4</v>
+        <v>643.6</v>
       </c>
       <c r="S2">
-        <v>668.05</v>
+        <v>667.9400000000001</v>
       </c>
       <c r="T2">
-        <v>6.55</v>
+        <v>4.24</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -956,34 +984,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>54.23</v>
+        <v>52.02</v>
       </c>
       <c r="Z2">
-        <v>32.58</v>
+        <v>28.69</v>
       </c>
       <c r="AA2">
-        <v>27.92</v>
+        <v>28.07</v>
       </c>
       <c r="AB2">
-        <v>4.66</v>
+        <v>0.62</v>
       </c>
       <c r="AC2">
-        <v>41.02</v>
+        <v>20.88</v>
       </c>
       <c r="AD2">
-        <v>58.39</v>
+        <v>41.97</v>
       </c>
       <c r="AE2">
-        <v>45.6</v>
+        <v>44.38</v>
       </c>
       <c r="AF2">
-        <v>-94.81</v>
+        <v>-94.39</v>
       </c>
       <c r="AG2">
-        <v>837.47</v>
+        <v>835.4299999999999</v>
       </c>
       <c r="AH2">
-        <v>510.89</v>
+        <v>526.49</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -992,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>52.94</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,10 +1031,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>642.5</v>
+        <v>631.7</v>
       </c>
       <c r="D3">
-        <v>-2.33</v>
+        <v>-1.68</v>
       </c>
       <c r="E3">
         <v>715.8</v>
@@ -1015,46 +1043,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-10.24</v>
+        <v>-11.75</v>
       </c>
       <c r="H3">
-        <v>25.24</v>
+        <v>23.14</v>
       </c>
       <c r="I3">
-        <v>-2.75</v>
+        <v>-3.4</v>
       </c>
       <c r="J3">
-        <v>4.51</v>
+        <v>3.68</v>
       </c>
       <c r="K3">
-        <v>15.45</v>
+        <v>14.55</v>
       </c>
       <c r="L3">
-        <v>-11.12</v>
+        <v>-11.64</v>
       </c>
       <c r="M3">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P3">
-        <v>660.0599999999999</v>
+        <v>655.62</v>
       </c>
       <c r="Q3">
-        <v>658.76</v>
+        <v>659.58</v>
       </c>
       <c r="R3">
-        <v>607.33</v>
+        <v>608.53</v>
       </c>
       <c r="S3">
-        <v>584.87</v>
+        <v>585.03</v>
       </c>
       <c r="T3">
-        <v>9.85</v>
+        <v>7.98</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1069,34 +1097,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>50.42</v>
+        <v>46.79</v>
       </c>
       <c r="Z3">
-        <v>14.21</v>
+        <v>11.17</v>
       </c>
       <c r="AA3">
-        <v>18.33</v>
+        <v>16.9</v>
       </c>
       <c r="AB3">
-        <v>-4.12</v>
+        <v>-5.73</v>
       </c>
       <c r="AC3">
-        <v>19.35</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>30.16</v>
+        <v>17.96</v>
       </c>
       <c r="AE3">
-        <v>23.13</v>
+        <v>22.65</v>
       </c>
       <c r="AF3">
-        <v>-87.56</v>
+        <v>-88.76000000000001</v>
       </c>
       <c r="AG3">
-        <v>688.89</v>
+        <v>685.3</v>
       </c>
       <c r="AH3">
-        <v>628.63</v>
+        <v>633.86</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1105,7 +1133,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>30.83</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,58 +1144,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>868</v>
+        <v>855</v>
       </c>
       <c r="D4">
-        <v>-1.36</v>
+        <v>-1.5</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
       </c>
       <c r="F4">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="G4">
-        <v>-30.14</v>
+        <v>-31.18</v>
       </c>
       <c r="H4">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.06</v>
+        <v>-2.13</v>
       </c>
       <c r="J4">
-        <v>-5.96</v>
+        <v>-6.56</v>
       </c>
       <c r="K4">
-        <v>-14.06</v>
+        <v>-18.07</v>
       </c>
       <c r="L4">
-        <v>-26.19</v>
+        <v>-26.92</v>
       </c>
       <c r="M4">
-        <v>-2.91</v>
+        <v>-2.62</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P4">
-        <v>875.27</v>
+        <v>871.55</v>
       </c>
       <c r="Q4">
-        <v>875.59</v>
+        <v>873.27</v>
       </c>
       <c r="R4">
-        <v>953.02</v>
+        <v>948.8200000000001</v>
       </c>
       <c r="S4">
-        <v>1065.55</v>
+        <v>1064.22</v>
       </c>
       <c r="T4">
-        <v>-18.54</v>
+        <v>-19.66</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1182,43 +1210,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>36.76</v>
+        <v>32.9</v>
       </c>
       <c r="Z4">
-        <v>-20.07</v>
+        <v>-20.22</v>
       </c>
       <c r="AA4">
-        <v>-25.86</v>
+        <v>-24.74</v>
       </c>
       <c r="AB4">
-        <v>5.8</v>
+        <v>4.51</v>
       </c>
       <c r="AC4">
-        <v>89.36</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="AD4">
-        <v>94.25</v>
+        <v>87.92</v>
       </c>
       <c r="AE4">
-        <v>17.9</v>
+        <v>18.05</v>
       </c>
       <c r="AF4">
-        <v>-12.49</v>
+        <v>0.13</v>
       </c>
       <c r="AG4">
-        <v>903.47</v>
+        <v>899.83</v>
       </c>
       <c r="AH4">
-        <v>847.7</v>
+        <v>846.72</v>
       </c>
       <c r="AI4">
-        <v>921.8200000000001</v>
+        <v>914.15</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>32.21</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1076.1</v>
+        <v>1055.7</v>
       </c>
       <c r="D5">
-        <v>-2.64</v>
+        <v>-1.9</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,46 +1269,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-24.1</v>
+        <v>-25.53</v>
       </c>
       <c r="H5">
-        <v>43.67</v>
+        <v>40.95</v>
       </c>
       <c r="I5">
-        <v>-2.32</v>
+        <v>-3.99</v>
       </c>
       <c r="J5">
-        <v>-6.47</v>
+        <v>-9.58</v>
       </c>
       <c r="K5">
-        <v>-8.390000000000001</v>
+        <v>-11.83</v>
       </c>
       <c r="L5">
-        <v>-8.82</v>
+        <v>-11.36</v>
       </c>
       <c r="M5">
-        <v>13.7</v>
+        <v>12.96</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="P5">
-        <v>1097.2</v>
+        <v>1088.42</v>
       </c>
       <c r="Q5">
-        <v>1124.66</v>
+        <v>1120.72</v>
       </c>
       <c r="R5">
-        <v>1213.44</v>
+        <v>1207.26</v>
       </c>
       <c r="S5">
-        <v>1072.44</v>
+        <v>1072.56</v>
       </c>
       <c r="T5">
-        <v>0.34</v>
+        <v>-1.57</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1292,46 +1320,46 @@
         <v>44</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>32.46</v>
+        <v>29.3</v>
       </c>
       <c r="Z5">
-        <v>-30.15</v>
+        <v>-32.28</v>
       </c>
       <c r="AA5">
-        <v>-30.55</v>
+        <v>-30.89</v>
       </c>
       <c r="AB5">
-        <v>0.4</v>
+        <v>-1.39</v>
       </c>
       <c r="AC5">
-        <v>35.66</v>
+        <v>22.4</v>
       </c>
       <c r="AD5">
-        <v>43.38</v>
+        <v>36.85</v>
       </c>
       <c r="AE5">
-        <v>37.43</v>
+        <v>36.55</v>
       </c>
       <c r="AF5">
-        <v>17.53</v>
+        <v>-62.55</v>
       </c>
       <c r="AG5">
-        <v>1172.66</v>
+        <v>1177.46</v>
       </c>
       <c r="AH5">
-        <v>1076.66</v>
+        <v>1063.98</v>
       </c>
       <c r="AI5">
-        <v>1196.23</v>
+        <v>1172.54</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>18.62</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1669.8</v>
+        <v>1634.4</v>
       </c>
       <c r="D6">
-        <v>-1.78</v>
+        <v>-2.12</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,46 +1382,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-28.04</v>
+        <v>-29.56</v>
       </c>
       <c r="H6">
-        <v>13.49</v>
+        <v>11.09</v>
       </c>
       <c r="I6">
-        <v>-1.6</v>
+        <v>-3.83</v>
       </c>
       <c r="J6">
-        <v>-19.31</v>
+        <v>-19.45</v>
       </c>
       <c r="K6">
-        <v>-10.54</v>
+        <v>-16.6</v>
       </c>
       <c r="L6">
-        <v>-20.63</v>
+        <v>-19.05</v>
       </c>
       <c r="M6">
-        <v>-5.66</v>
+        <v>-6.68</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="P6">
-        <v>1689.64</v>
+        <v>1676.62</v>
       </c>
       <c r="Q6">
-        <v>1804.59</v>
+        <v>1785.57</v>
       </c>
       <c r="R6">
-        <v>1960.07</v>
+        <v>1950.38</v>
       </c>
       <c r="S6">
-        <v>1841.3</v>
+        <v>1839.4</v>
       </c>
       <c r="T6">
-        <v>-9.31</v>
+        <v>-11.14</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1408,43 +1436,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>29.8</v>
+        <v>27.23</v>
       </c>
       <c r="Z6">
-        <v>-87.34</v>
+        <v>-88.45999999999999</v>
       </c>
       <c r="AA6">
-        <v>-81.93000000000001</v>
+        <v>-83.23</v>
       </c>
       <c r="AB6">
-        <v>-5.42</v>
+        <v>-5.23</v>
       </c>
       <c r="AC6">
-        <v>47.81</v>
+        <v>54.33</v>
       </c>
       <c r="AD6">
-        <v>38.22</v>
+        <v>47.38</v>
       </c>
       <c r="AE6">
-        <v>53.26</v>
+        <v>52.09</v>
       </c>
       <c r="AF6">
-        <v>-41.25</v>
+        <v>-39.97</v>
       </c>
       <c r="AG6">
-        <v>2078.01</v>
+        <v>2050.22</v>
       </c>
       <c r="AH6">
-        <v>1531.17</v>
+        <v>1520.93</v>
       </c>
       <c r="AI6">
-        <v>1845.66</v>
+        <v>1809.12</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>49.65</v>
+        <v>50.86</v>
       </c>
     </row>
   </sheetData>
@@ -1605,12 +1633,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1618,700 +1681,700 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>24.52</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>21.49</v>
       </c>
-      <c r="E7" s="6">
-        <v>-3.03</v>
+      <c r="D7" s="6">
+        <v>19.74</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>5.12</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>4.51</v>
       </c>
-      <c r="E8" s="6">
-        <v>-0.61</v>
+      <c r="D8" s="6">
+        <v>3.68</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-4.64</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-5.96</v>
       </c>
-      <c r="E9" s="6">
-        <v>-1.32</v>
+      <c r="D9" s="6">
+        <v>-6.56</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-2.87</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-6.47</v>
       </c>
-      <c r="E10" s="6">
-        <v>-3.6</v>
+      <c r="D10" s="6">
+        <v>-9.58</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-3.11</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-16.46</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-19.31</v>
       </c>
-      <c r="E11" s="6">
-        <v>-2.85</v>
+      <c r="D11" s="6">
+        <v>-19.45</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>1.69</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-1.06</v>
       </c>
-      <c r="E12" s="6">
+      <c r="D12" s="6">
+        <v>-12.37</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-11.31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
         <v>-2.75</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-3.4</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-2.13</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-2.32</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-3.99</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-1.6</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-3.83</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-14.23</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-15.06</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-0.57</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-2.75</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-2.18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-11.12</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-11.64</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>0</v>
-      </c>
-      <c r="D14" s="5">
-        <v>0.06</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-26.19</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-26.92</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-0.19</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-2.32</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-8.82</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-11.36</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-2.54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0.53</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-1.6</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-20.63</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-19.05</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-13.08</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-14.23</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-2.44</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-10.49</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-11.12</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>15.45</v>
+      </c>
+      <c r="D23" s="6">
+        <v>14.55</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-27.6</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-26.19</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-14.06</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-18.07</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-4.01</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-6.16</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-8.82</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-11.83</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-3.44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-19.19</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-20.63</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-10.54</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-16.6</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-6.06</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5">
-        <v>3.69</v>
-      </c>
-      <c r="D22" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-3.61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-22.53</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-24.22</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5">
-        <v>17.96</v>
-      </c>
-      <c r="D23" s="5">
-        <v>15.45</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-2.51</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-10.24</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-11.75</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-13.89</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-14.06</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-30.14</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-31.18</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-4.18</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-4.21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-24.1</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-25.53</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-7.1</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-10.54</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-28.04</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-29.56</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-19.56</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-22.53</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-2.97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6">
+        <v>711.8</v>
+      </c>
+      <c r="D32" s="6">
+        <v>696.25</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-15.55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-9</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-10.24</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>642.5</v>
+      </c>
+      <c r="D33" s="6">
+        <v>631.7</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-10.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-29.17</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-30.14</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>868</v>
+      </c>
+      <c r="D34" s="6">
+        <v>855</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-22.04</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-24.1</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1076.1</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1055.7</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-20.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-26.73</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-28.04</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>1669.8</v>
+      </c>
+      <c r="D36" s="6">
+        <v>1634.4</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-35.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>739</v>
-      </c>
-      <c r="D32" s="5">
-        <v>711.8</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-27.2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="6">
+        <v>54.23</v>
+      </c>
+      <c r="D37" s="6">
+        <v>52.02</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-2.21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>657.8</v>
-      </c>
-      <c r="D33" s="5">
-        <v>642.5</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-15.3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="6">
+        <v>50.42</v>
+      </c>
+      <c r="D38" s="6">
+        <v>46.79</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-3.63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>880</v>
-      </c>
-      <c r="D34" s="5">
-        <v>868</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>36.76</v>
+      </c>
+      <c r="D39" s="6">
+        <v>32.9</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-3.86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5">
-        <v>1105.3</v>
-      </c>
-      <c r="D35" s="5">
-        <v>1076.1</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-29.2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>32.46</v>
+      </c>
+      <c r="D40" s="6">
+        <v>29.3</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-3.16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
-        <v>1700.1</v>
-      </c>
-      <c r="D36" s="5">
-        <v>1669.8</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-30.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>29.8</v>
+      </c>
+      <c r="D41" s="6">
+        <v>27.23</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-2.57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="5">
-        <v>58.25</v>
-      </c>
-      <c r="D37" s="5">
-        <v>54.23</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-4.02</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-94.81</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-94.39</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="5">
-        <v>56.15</v>
-      </c>
-      <c r="D38" s="5">
-        <v>50.42</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-5.73</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-87.56</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-88.76000000000001</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>40.86</v>
-      </c>
-      <c r="D39" s="5">
-        <v>36.76</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-4.1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-12.49</v>
+      </c>
+      <c r="D44" s="6">
+        <v>0.13</v>
+      </c>
+      <c r="E44" s="8">
+        <v>12.62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>37.89</v>
-      </c>
-      <c r="D40" s="5">
-        <v>32.46</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-5.43</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>17.53</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-62.55</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-80.08</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>32.21</v>
-      </c>
-      <c r="D41" s="5">
-        <v>29.8</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="5">
-        <v>-78.51000000000001</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-94.81</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-16.3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-86.38</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-87.56</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-79.17</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-12.49</v>
-      </c>
-      <c r="E44" s="7">
-        <v>66.68000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>166.39</v>
-      </c>
-      <c r="D45" s="5">
-        <v>17.53</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-148.86</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-63.03</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C46" s="6">
         <v>-41.25</v>
       </c>
-      <c r="E46" s="7">
-        <v>21.78</v>
+      <c r="D46" s="6">
+        <v>-39.97</v>
+      </c>
+      <c r="E46" s="8">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
@@ -2337,60 +2400,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
-        <v>57.92</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="11">
+        <v>49.92</v>
+      </c>
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>40.7</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-1.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-3.5</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D2" s="11">
+        <v>37.6</v>
+      </c>
+      <c r="E2" s="11">
+        <v>40</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-2.4</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-6.9</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2492,37 +2555,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.137</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0132</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0291</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0566</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1127</v>
+      <c r="A2" s="14">
+        <v>0.1296</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.012</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0262</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0668</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1156</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,34 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.4 → 46.8</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.4</t>
-  </si>
-  <si>
-    <t>46.8</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -279,14 +252,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -319,13 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,15 +368,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -778,7 +750,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -918,10 +891,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>696.25</v>
+        <v>722.75</v>
       </c>
       <c r="D2">
-        <v>-2.18</v>
+        <v>3.81</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -930,46 +903,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-24.22</v>
+        <v>-21.33</v>
       </c>
       <c r="H2">
-        <v>33.42</v>
+        <v>38.5</v>
       </c>
       <c r="I2">
-        <v>-12.37</v>
+        <v>-4.58</v>
       </c>
       <c r="J2">
-        <v>19.74</v>
+        <v>28.9</v>
       </c>
       <c r="K2">
-        <v>-2.44</v>
+        <v>0.11</v>
       </c>
       <c r="L2">
-        <v>-15.06</v>
+        <v>-12.83</v>
       </c>
       <c r="M2">
-        <v>-11.56</v>
+        <v>-10.88</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="P2">
-        <v>726.66</v>
+        <v>719.72</v>
       </c>
       <c r="Q2">
-        <v>680.96</v>
+        <v>688.98</v>
       </c>
       <c r="R2">
-        <v>643.6</v>
+        <v>644.49</v>
       </c>
       <c r="S2">
-        <v>667.9400000000001</v>
+        <v>667.98</v>
       </c>
       <c r="T2">
-        <v>4.24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -984,34 +957,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>52.02</v>
+        <v>55.36</v>
       </c>
       <c r="Z2">
-        <v>28.69</v>
+        <v>27.43</v>
       </c>
       <c r="AA2">
-        <v>28.07</v>
+        <v>27.94</v>
       </c>
       <c r="AB2">
-        <v>0.62</v>
+        <v>-0.52</v>
       </c>
       <c r="AC2">
-        <v>20.88</v>
+        <v>7.24</v>
       </c>
       <c r="AD2">
-        <v>41.97</v>
+        <v>23.05</v>
       </c>
       <c r="AE2">
-        <v>44.38</v>
+        <v>47.75</v>
       </c>
       <c r="AF2">
-        <v>-94.39</v>
+        <v>104.2</v>
       </c>
       <c r="AG2">
-        <v>835.4299999999999</v>
+        <v>833.88</v>
       </c>
       <c r="AH2">
-        <v>526.49</v>
+        <v>544.0700000000001</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -1020,7 +993,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>49.51</v>
+        <v>49.46</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,10 +1004,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>631.7</v>
+        <v>623.55</v>
       </c>
       <c r="D3">
-        <v>-1.68</v>
+        <v>-1.29</v>
       </c>
       <c r="E3">
         <v>715.8</v>
@@ -1043,46 +1016,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-11.75</v>
+        <v>-12.89</v>
       </c>
       <c r="H3">
-        <v>23.14</v>
+        <v>21.55</v>
       </c>
       <c r="I3">
-        <v>-3.4</v>
+        <v>-6.94</v>
       </c>
       <c r="J3">
-        <v>3.68</v>
+        <v>1.34</v>
       </c>
       <c r="K3">
-        <v>14.55</v>
+        <v>12.5</v>
       </c>
       <c r="L3">
-        <v>-11.64</v>
+        <v>-9.33</v>
       </c>
       <c r="M3">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="P3">
-        <v>655.62</v>
+        <v>646.3200000000001</v>
       </c>
       <c r="Q3">
-        <v>659.58</v>
+        <v>658.04</v>
       </c>
       <c r="R3">
-        <v>608.53</v>
+        <v>609.49</v>
       </c>
       <c r="S3">
-        <v>585.03</v>
+        <v>585.1900000000001</v>
       </c>
       <c r="T3">
-        <v>7.98</v>
+        <v>6.55</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1097,34 +1070,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>46.79</v>
+        <v>44.21</v>
       </c>
       <c r="Z3">
-        <v>11.17</v>
+        <v>8.01</v>
       </c>
       <c r="AA3">
-        <v>16.9</v>
+        <v>15.12</v>
       </c>
       <c r="AB3">
-        <v>-5.73</v>
+        <v>-7.11</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>17.96</v>
+        <v>6.45</v>
       </c>
       <c r="AE3">
-        <v>22.65</v>
+        <v>22.5</v>
       </c>
       <c r="AF3">
-        <v>-88.76000000000001</v>
+        <v>-86.73999999999999</v>
       </c>
       <c r="AG3">
-        <v>685.3</v>
+        <v>688.36</v>
       </c>
       <c r="AH3">
-        <v>633.86</v>
+        <v>627.72</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1133,7 +1106,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>27.88</v>
+        <v>26.16</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,58 +1117,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="D4">
-        <v>-1.5</v>
+        <v>-0.58</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
       </c>
       <c r="F4">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="G4">
-        <v>-31.18</v>
+        <v>-31.58</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-2.13</v>
+        <v>-3.38</v>
       </c>
       <c r="J4">
-        <v>-6.56</v>
+        <v>-5.69</v>
       </c>
       <c r="K4">
-        <v>-18.07</v>
+        <v>-21.09</v>
       </c>
       <c r="L4">
-        <v>-26.92</v>
+        <v>-27.54</v>
       </c>
       <c r="M4">
-        <v>-2.62</v>
+        <v>-2.88</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P4">
-        <v>871.55</v>
+        <v>865.6</v>
       </c>
       <c r="Q4">
-        <v>873.27</v>
+        <v>870.52</v>
       </c>
       <c r="R4">
-        <v>948.8200000000001</v>
+        <v>944.74</v>
       </c>
       <c r="S4">
-        <v>1064.22</v>
+        <v>1062.78</v>
       </c>
       <c r="T4">
-        <v>-19.66</v>
+        <v>-20.02</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1210,43 +1183,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>32.9</v>
+        <v>31.53</v>
       </c>
       <c r="Z4">
-        <v>-20.22</v>
+        <v>-20.51</v>
       </c>
       <c r="AA4">
-        <v>-24.74</v>
+        <v>-23.89</v>
       </c>
       <c r="AB4">
-        <v>4.51</v>
+        <v>3.38</v>
       </c>
       <c r="AC4">
-        <v>77.31999999999999</v>
+        <v>58.88</v>
       </c>
       <c r="AD4">
-        <v>87.92</v>
+        <v>75.19</v>
       </c>
       <c r="AE4">
-        <v>18.05</v>
+        <v>17.47</v>
       </c>
       <c r="AF4">
-        <v>0.13</v>
+        <v>18.41</v>
       </c>
       <c r="AG4">
-        <v>899.83</v>
+        <v>894.51</v>
       </c>
       <c r="AH4">
-        <v>846.72</v>
+        <v>846.54</v>
       </c>
       <c r="AI4">
-        <v>914.15</v>
+        <v>905.39</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>33.54</v>
+        <v>35.11</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1230,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1055.7</v>
+        <v>1039.4</v>
       </c>
       <c r="D5">
-        <v>-1.9</v>
+        <v>-1.54</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1269,46 +1242,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-25.53</v>
+        <v>-26.68</v>
       </c>
       <c r="H5">
-        <v>40.95</v>
+        <v>38.77</v>
       </c>
       <c r="I5">
-        <v>-3.99</v>
+        <v>-6.02</v>
       </c>
       <c r="J5">
-        <v>-9.58</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="K5">
-        <v>-11.83</v>
+        <v>-14.23</v>
       </c>
       <c r="L5">
-        <v>-11.36</v>
+        <v>-14.28</v>
       </c>
       <c r="M5">
-        <v>12.96</v>
+        <v>12.41</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P5">
-        <v>1088.42</v>
+        <v>1075.1</v>
       </c>
       <c r="Q5">
-        <v>1120.72</v>
+        <v>1115.05</v>
       </c>
       <c r="R5">
-        <v>1207.26</v>
+        <v>1200.44</v>
       </c>
       <c r="S5">
-        <v>1072.56</v>
+        <v>1072.69</v>
       </c>
       <c r="T5">
-        <v>-1.57</v>
+        <v>-3.1</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1323,43 +1296,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>29.3</v>
+        <v>27.04</v>
       </c>
       <c r="Z5">
-        <v>-32.28</v>
+        <v>-34.88</v>
       </c>
       <c r="AA5">
-        <v>-30.89</v>
+        <v>-31.69</v>
       </c>
       <c r="AB5">
-        <v>-1.39</v>
+        <v>-3.19</v>
       </c>
       <c r="AC5">
-        <v>22.4</v>
+        <v>1.27</v>
       </c>
       <c r="AD5">
-        <v>36.85</v>
+        <v>19.78</v>
       </c>
       <c r="AE5">
-        <v>36.55</v>
+        <v>36.29</v>
       </c>
       <c r="AF5">
-        <v>-62.55</v>
+        <v>-65.20999999999999</v>
       </c>
       <c r="AG5">
-        <v>1177.46</v>
+        <v>1180.3</v>
       </c>
       <c r="AH5">
-        <v>1063.98</v>
+        <v>1049.79</v>
       </c>
       <c r="AI5">
-        <v>1172.54</v>
+        <v>1161.38</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>18.39</v>
+        <v>19.59</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1343,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1634.4</v>
+        <v>1628.5</v>
       </c>
       <c r="D6">
-        <v>-2.12</v>
+        <v>-0.36</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1382,46 +1355,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-29.56</v>
+        <v>-29.82</v>
       </c>
       <c r="H6">
-        <v>11.09</v>
+        <v>10.68</v>
       </c>
       <c r="I6">
-        <v>-3.83</v>
+        <v>-4.63</v>
       </c>
       <c r="J6">
-        <v>-19.45</v>
+        <v>-19.17</v>
       </c>
       <c r="K6">
-        <v>-16.6</v>
+        <v>-17.28</v>
       </c>
       <c r="L6">
-        <v>-19.05</v>
+        <v>-17.23</v>
       </c>
       <c r="M6">
-        <v>-6.68</v>
+        <v>-6.77</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P6">
-        <v>1676.62</v>
+        <v>1660.8</v>
       </c>
       <c r="Q6">
-        <v>1785.57</v>
+        <v>1768.1</v>
       </c>
       <c r="R6">
-        <v>1950.38</v>
+        <v>1939.66</v>
       </c>
       <c r="S6">
-        <v>1839.4</v>
+        <v>1837.36</v>
       </c>
       <c r="T6">
-        <v>-11.14</v>
+        <v>-11.37</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1436,43 +1409,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>27.23</v>
+        <v>26.81</v>
       </c>
       <c r="Z6">
-        <v>-88.45999999999999</v>
+        <v>-88.79000000000001</v>
       </c>
       <c r="AA6">
-        <v>-83.23</v>
+        <v>-84.34</v>
       </c>
       <c r="AB6">
-        <v>-5.23</v>
+        <v>-4.45</v>
       </c>
       <c r="AC6">
-        <v>54.33</v>
+        <v>45.74</v>
       </c>
       <c r="AD6">
-        <v>47.38</v>
+        <v>49.29</v>
       </c>
       <c r="AE6">
-        <v>52.09</v>
+        <v>50.96</v>
       </c>
       <c r="AF6">
-        <v>-39.97</v>
+        <v>20.92</v>
       </c>
       <c r="AG6">
-        <v>2050.22</v>
+        <v>2025.3</v>
       </c>
       <c r="AH6">
-        <v>1520.93</v>
+        <v>1510.9</v>
       </c>
       <c r="AI6">
-        <v>1809.12</v>
+        <v>1794.37</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>50.86</v>
+        <v>52.32</v>
       </c>
     </row>
   </sheetData>
@@ -1633,47 +1606,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1681,700 +1619,700 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>21.49</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>19.74</v>
       </c>
-      <c r="E7" s="7">
-        <v>-1.75</v>
+      <c r="D7" s="5">
+        <v>28.9</v>
+      </c>
+      <c r="E7" s="6">
+        <v>9.16</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>4.51</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>3.68</v>
       </c>
+      <c r="D8" s="5">
+        <v>1.34</v>
+      </c>
       <c r="E8" s="7">
-        <v>-0.83</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-5.96</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-6.56</v>
       </c>
-      <c r="E9" s="7">
-        <v>-0.6</v>
+      <c r="D9" s="5">
+        <v>-5.69</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.87</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-6.47</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-9.58</v>
       </c>
-      <c r="E10" s="7">
-        <v>-3.11</v>
+      <c r="D10" s="5">
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.2</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-19.31</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-19.45</v>
       </c>
-      <c r="E11" s="7">
-        <v>-0.14</v>
+      <c r="D11" s="5">
+        <v>-19.17</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.28</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>-1.06</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-12.37</v>
       </c>
-      <c r="E12" s="7">
-        <v>-11.31</v>
+      <c r="D12" s="5">
+        <v>-4.58</v>
+      </c>
+      <c r="E12" s="6">
+        <v>7.79</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
-        <v>-2.75</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-3.4</v>
       </c>
+      <c r="D13" s="5">
+        <v>-6.94</v>
+      </c>
       <c r="E13" s="7">
-        <v>-0.65</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>0.06</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-2.13</v>
       </c>
+      <c r="D14" s="5">
+        <v>-3.38</v>
+      </c>
       <c r="E14" s="7">
-        <v>-2.19</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-2.32</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-3.99</v>
       </c>
+      <c r="D15" s="5">
+        <v>-6.02</v>
+      </c>
       <c r="E15" s="7">
-        <v>-1.67</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-1.6</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-3.83</v>
       </c>
+      <c r="D16" s="5">
+        <v>-4.63</v>
+      </c>
       <c r="E16" s="7">
-        <v>-2.23</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
+        <v>-15.06</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-12.83</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-11.64</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-9.33</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-26.92</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-27.54</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-11.36</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-14.28</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-2.92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-19.05</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-17.23</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-2.44</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="E22" s="6">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>14.55</v>
+      </c>
+      <c r="D23" s="5">
+        <v>12.5</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-2.05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-18.07</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-21.09</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-3.02</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-11.83</v>
+      </c>
+      <c r="D25" s="5">
         <v>-14.23</v>
       </c>
-      <c r="D17" s="6">
-        <v>-15.06</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="E25" s="7">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-16.6</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-17.28</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-24.22</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-21.33</v>
+      </c>
+      <c r="E27" s="6">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-11.12</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-11.64</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-11.75</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-12.89</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-26.19</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-26.92</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-31.18</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-31.58</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-8.82</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-11.36</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-2.54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-25.53</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-26.68</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-20.63</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-19.05</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-29.56</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-29.82</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.08</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-2.44</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2.52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>696.25</v>
+      </c>
+      <c r="D32" s="5">
+        <v>722.75</v>
+      </c>
+      <c r="E32" s="6">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>15.45</v>
-      </c>
-      <c r="D23" s="6">
-        <v>14.55</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>631.7</v>
+      </c>
+      <c r="D33" s="5">
+        <v>623.55</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-8.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-14.06</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-18.07</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-4.01</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>855</v>
+      </c>
+      <c r="D34" s="5">
+        <v>850</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-11.83</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1055.7</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1039.4</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-16.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-10.54</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-16.6</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-6.06</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1634.4</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1628.5</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-5.9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-22.53</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-24.22</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>52.02</v>
+      </c>
+      <c r="D37" s="5">
+        <v>55.36</v>
+      </c>
+      <c r="E37" s="6">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-10.24</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-11.75</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>46.79</v>
+      </c>
+      <c r="D38" s="5">
+        <v>44.21</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-2.58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-30.14</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-31.18</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>32.9</v>
+      </c>
+      <c r="D39" s="5">
+        <v>31.53</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-24.1</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-25.53</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>29.3</v>
+      </c>
+      <c r="D40" s="5">
+        <v>27.04</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-2.26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-28.04</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-29.56</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>27.23</v>
+      </c>
+      <c r="D41" s="5">
+        <v>26.81</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>711.8</v>
-      </c>
-      <c r="D32" s="6">
-        <v>696.25</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-15.55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-94.39</v>
+      </c>
+      <c r="D42" s="5">
+        <v>104.2</v>
+      </c>
+      <c r="E42" s="6">
+        <v>198.59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>642.5</v>
-      </c>
-      <c r="D33" s="6">
-        <v>631.7</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-10.8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-88.76000000000001</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-86.73999999999999</v>
+      </c>
+      <c r="E43" s="6">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>868</v>
-      </c>
-      <c r="D34" s="6">
-        <v>855</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="D44" s="5">
+        <v>18.41</v>
+      </c>
+      <c r="E44" s="6">
+        <v>18.28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1076.1</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1055.7</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-20.4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-62.55</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-65.20999999999999</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>1669.8</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1634.4</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-35.4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="6">
-        <v>54.23</v>
-      </c>
-      <c r="D37" s="6">
-        <v>52.02</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>50.42</v>
-      </c>
-      <c r="D38" s="6">
-        <v>46.79</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-3.63</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>36.76</v>
-      </c>
-      <c r="D39" s="6">
-        <v>32.9</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-3.86</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>32.46</v>
-      </c>
-      <c r="D40" s="6">
-        <v>29.3</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-3.16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>29.8</v>
-      </c>
-      <c r="D41" s="6">
-        <v>27.23</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-2.57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="6">
-        <v>-94.81</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-94.39</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-87.56</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-88.76000000000001</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-12.49</v>
-      </c>
-      <c r="D44" s="6">
-        <v>0.13</v>
-      </c>
-      <c r="E44" s="8">
-        <v>12.62</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>17.53</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-62.55</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-80.08</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-41.25</v>
-      </c>
-      <c r="D46" s="6">
+      <c r="C46" s="5">
         <v>-39.97</v>
       </c>
-      <c r="E46" s="8">
-        <v>1.28</v>
+      <c r="D46" s="5">
+        <v>20.92</v>
+      </c>
+      <c r="E46" s="6">
+        <v>60.89</v>
       </c>
     </row>
   </sheetData>
@@ -2400,60 +2338,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>49.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>37.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>37</v>
+      </c>
+      <c r="E2" s="10">
         <v>40</v>
       </c>
-      <c r="F2" s="11">
-        <v>-2.4</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-6.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-0.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-8</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2555,37 +2493,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1296</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.012</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0262</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0668</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1156</v>
+      <c r="A2" s="13">
+        <v>0.1241</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0075</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0288</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.0677</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1088</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -252,14 +252,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -750,8 +750,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -891,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>722.75</v>
+        <v>708.6</v>
       </c>
       <c r="D2">
-        <v>3.81</v>
+        <v>-1.96</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -903,46 +902,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-21.33</v>
+        <v>-22.87</v>
       </c>
       <c r="H2">
-        <v>38.5</v>
+        <v>35.79</v>
       </c>
       <c r="I2">
-        <v>-4.58</v>
+        <v>-2.77</v>
       </c>
       <c r="J2">
-        <v>28.9</v>
+        <v>26</v>
       </c>
       <c r="K2">
-        <v>0.11</v>
+        <v>-0.18</v>
       </c>
       <c r="L2">
-        <v>-12.83</v>
+        <v>-13.5</v>
       </c>
       <c r="M2">
-        <v>-10.88</v>
+        <v>-11.19</v>
       </c>
       <c r="N2">
         <v>79</v>
       </c>
       <c r="O2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>719.72</v>
+        <v>715.6799999999999</v>
       </c>
       <c r="Q2">
-        <v>688.98</v>
+        <v>695.78</v>
       </c>
       <c r="R2">
-        <v>644.49</v>
+        <v>645.21</v>
       </c>
       <c r="S2">
-        <v>667.98</v>
+        <v>668.01</v>
       </c>
       <c r="T2">
-        <v>8.199999999999999</v>
+        <v>6.08</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -957,34 +956,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>55.36</v>
+        <v>53.23</v>
       </c>
       <c r="Z2">
-        <v>27.43</v>
+        <v>25</v>
       </c>
       <c r="AA2">
-        <v>27.94</v>
+        <v>27.35</v>
       </c>
       <c r="AB2">
-        <v>-0.52</v>
+        <v>-2.36</v>
       </c>
       <c r="AC2">
-        <v>7.24</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AD2">
-        <v>23.05</v>
+        <v>12.66</v>
       </c>
       <c r="AE2">
-        <v>47.75</v>
+        <v>47.24</v>
       </c>
       <c r="AF2">
-        <v>104.2</v>
+        <v>-87.93000000000001</v>
       </c>
       <c r="AG2">
-        <v>833.88</v>
+        <v>830.0599999999999</v>
       </c>
       <c r="AH2">
-        <v>544.0700000000001</v>
+        <v>561.5</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -993,7 +992,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>49.46</v>
+        <v>48.15</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1004,58 +1003,58 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>623.55</v>
+        <v>631.9</v>
       </c>
       <c r="D3">
-        <v>-1.29</v>
+        <v>1.34</v>
       </c>
       <c r="E3">
-        <v>715.8</v>
+        <v>713</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-12.89</v>
+        <v>-11.37</v>
       </c>
       <c r="H3">
-        <v>21.55</v>
+        <v>23.18</v>
       </c>
       <c r="I3">
-        <v>-6.94</v>
+        <v>-6.53</v>
       </c>
       <c r="J3">
-        <v>1.34</v>
+        <v>-3.44</v>
       </c>
       <c r="K3">
-        <v>12.5</v>
+        <v>12.94</v>
       </c>
       <c r="L3">
-        <v>-9.33</v>
+        <v>-11.72</v>
       </c>
       <c r="M3">
-        <v>0.75</v>
+        <v>1.3</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P3">
-        <v>646.3200000000001</v>
+        <v>637.49</v>
       </c>
       <c r="Q3">
-        <v>658.04</v>
+        <v>656.12</v>
       </c>
       <c r="R3">
-        <v>609.49</v>
+        <v>610.74</v>
       </c>
       <c r="S3">
-        <v>585.1900000000001</v>
+        <v>585.4</v>
       </c>
       <c r="T3">
-        <v>6.55</v>
+        <v>7.94</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1070,34 +1069,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>44.21</v>
+        <v>47.41</v>
       </c>
       <c r="Z3">
-        <v>8.01</v>
+        <v>6.11</v>
       </c>
       <c r="AA3">
-        <v>15.12</v>
+        <v>13.32</v>
       </c>
       <c r="AB3">
-        <v>-7.11</v>
+        <v>-7.21</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="AD3">
-        <v>6.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
-        <v>22.5</v>
+        <v>21.96</v>
       </c>
       <c r="AF3">
-        <v>-86.73999999999999</v>
+        <v>-83.84999999999999</v>
       </c>
       <c r="AG3">
-        <v>688.36</v>
+        <v>688</v>
       </c>
       <c r="AH3">
-        <v>627.72</v>
+        <v>624.24</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1106,7 +1105,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>26.16</v>
+        <v>24.81</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1117,58 +1116,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="D4">
-        <v>-0.58</v>
+        <v>-1.18</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
       </c>
       <c r="F4">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="G4">
-        <v>-31.58</v>
+        <v>-32.39</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-3.38</v>
+        <v>-4</v>
       </c>
       <c r="J4">
-        <v>-5.69</v>
+        <v>-7.18</v>
       </c>
       <c r="K4">
-        <v>-21.09</v>
+        <v>-22</v>
       </c>
       <c r="L4">
-        <v>-27.54</v>
+        <v>-26.84</v>
       </c>
       <c r="M4">
-        <v>-2.88</v>
+        <v>-2.93</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P4">
-        <v>865.6</v>
+        <v>858.6</v>
       </c>
       <c r="Q4">
-        <v>870.52</v>
+        <v>867.27</v>
       </c>
       <c r="R4">
-        <v>944.74</v>
+        <v>940.16</v>
       </c>
       <c r="S4">
-        <v>1062.78</v>
+        <v>1061.27</v>
       </c>
       <c r="T4">
-        <v>-20.02</v>
+        <v>-20.85</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1183,43 +1182,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.53</v>
+        <v>28.94</v>
       </c>
       <c r="Z4">
-        <v>-20.51</v>
+        <v>-21.3</v>
       </c>
       <c r="AA4">
-        <v>-23.89</v>
+        <v>-23.37</v>
       </c>
       <c r="AB4">
-        <v>3.38</v>
+        <v>2.07</v>
       </c>
       <c r="AC4">
-        <v>58.88</v>
+        <v>43.01</v>
       </c>
       <c r="AD4">
-        <v>75.19</v>
+        <v>59.74</v>
       </c>
       <c r="AE4">
-        <v>17.47</v>
+        <v>17.22</v>
       </c>
       <c r="AF4">
-        <v>18.41</v>
+        <v>-40.21</v>
       </c>
       <c r="AG4">
-        <v>894.51</v>
+        <v>889.11</v>
       </c>
       <c r="AH4">
-        <v>846.54</v>
+        <v>845.4400000000001</v>
       </c>
       <c r="AI4">
-        <v>905.39</v>
+        <v>896.67</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>35.11</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1230,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1039.4</v>
+        <v>1019.6</v>
       </c>
       <c r="D5">
-        <v>-1.54</v>
+        <v>-1.9</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1242,46 +1241,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-26.68</v>
+        <v>-28.08</v>
       </c>
       <c r="H5">
-        <v>38.77</v>
+        <v>36.13</v>
       </c>
       <c r="I5">
-        <v>-6.02</v>
+        <v>-7.22</v>
       </c>
       <c r="J5">
-        <v>-8.380000000000001</v>
+        <v>-11.56</v>
       </c>
       <c r="K5">
-        <v>-14.23</v>
+        <v>-15.72</v>
       </c>
       <c r="L5">
-        <v>-14.28</v>
+        <v>-14.68</v>
       </c>
       <c r="M5">
-        <v>12.41</v>
+        <v>12.54</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P5">
-        <v>1075.1</v>
+        <v>1059.22</v>
       </c>
       <c r="Q5">
-        <v>1115.05</v>
+        <v>1109.09</v>
       </c>
       <c r="R5">
-        <v>1200.44</v>
+        <v>1193.73</v>
       </c>
       <c r="S5">
-        <v>1072.69</v>
+        <v>1072.71</v>
       </c>
       <c r="T5">
-        <v>-3.1</v>
+        <v>-4.95</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1296,43 +1295,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>27.04</v>
+        <v>24.55</v>
       </c>
       <c r="Z5">
-        <v>-34.88</v>
+        <v>-38.1</v>
       </c>
       <c r="AA5">
-        <v>-31.69</v>
+        <v>-32.97</v>
       </c>
       <c r="AB5">
-        <v>-3.19</v>
+        <v>-5.13</v>
       </c>
       <c r="AC5">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>19.78</v>
+        <v>7.89</v>
       </c>
       <c r="AE5">
-        <v>36.29</v>
+        <v>37.69</v>
       </c>
       <c r="AF5">
-        <v>-65.20999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="AG5">
-        <v>1180.3</v>
+        <v>1185.94</v>
       </c>
       <c r="AH5">
-        <v>1049.79</v>
+        <v>1032.23</v>
       </c>
       <c r="AI5">
-        <v>1161.38</v>
+        <v>1126.16</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>19.59</v>
+        <v>23.82</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1343,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1628.5</v>
+        <v>1595.8</v>
       </c>
       <c r="D6">
-        <v>-0.36</v>
+        <v>-2.01</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1355,46 +1354,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-29.82</v>
+        <v>-31.22</v>
       </c>
       <c r="H6">
-        <v>10.68</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="I6">
-        <v>-4.63</v>
+        <v>-4.51</v>
       </c>
       <c r="J6">
-        <v>-19.17</v>
+        <v>-19.32</v>
       </c>
       <c r="K6">
-        <v>-17.28</v>
+        <v>-20.07</v>
       </c>
       <c r="L6">
-        <v>-17.23</v>
+        <v>-18.48</v>
       </c>
       <c r="M6">
-        <v>-6.77</v>
+        <v>-6.5</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P6">
-        <v>1660.8</v>
+        <v>1645.72</v>
       </c>
       <c r="Q6">
-        <v>1768.1</v>
+        <v>1749.35</v>
       </c>
       <c r="R6">
-        <v>1939.66</v>
+        <v>1929.96</v>
       </c>
       <c r="S6">
-        <v>1837.36</v>
+        <v>1834.97</v>
       </c>
       <c r="T6">
-        <v>-11.37</v>
+        <v>-13.03</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1409,43 +1408,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>26.81</v>
+        <v>24.58</v>
       </c>
       <c r="Z6">
-        <v>-88.79000000000001</v>
+        <v>-90.65000000000001</v>
       </c>
       <c r="AA6">
-        <v>-84.34</v>
+        <v>-85.61</v>
       </c>
       <c r="AB6">
-        <v>-4.45</v>
+        <v>-5.05</v>
       </c>
       <c r="AC6">
-        <v>45.74</v>
+        <v>36.25</v>
       </c>
       <c r="AD6">
-        <v>49.29</v>
+        <v>45.44</v>
       </c>
       <c r="AE6">
-        <v>50.96</v>
+        <v>52.05</v>
       </c>
       <c r="AF6">
-        <v>20.92</v>
+        <v>-28.57</v>
       </c>
       <c r="AG6">
-        <v>2025.3</v>
+        <v>1998.91</v>
       </c>
       <c r="AH6">
-        <v>1510.9</v>
+        <v>1499.8</v>
       </c>
       <c r="AI6">
-        <v>1794.37</v>
+        <v>1755.91</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>52.32</v>
+        <v>55.14</v>
       </c>
     </row>
   </sheetData>
@@ -1643,13 +1642,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>19.74</v>
+        <v>28.9</v>
       </c>
       <c r="D7" s="5">
-        <v>28.9</v>
+        <v>26</v>
       </c>
       <c r="E7" s="6">
-        <v>9.16</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1660,13 +1659,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>3.68</v>
+        <v>1.34</v>
       </c>
       <c r="D8" s="5">
-        <v>1.34</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-2.34</v>
+        <v>-3.44</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-4.78</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1677,13 +1676,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-6.56</v>
+        <v>-5.69</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.69</v>
+        <v>-7.18</v>
       </c>
       <c r="E9" s="6">
-        <v>0.87</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1694,13 +1693,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-9.58</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="D10" s="5">
-        <v>-8.380000000000001</v>
+        <v>-11.56</v>
       </c>
       <c r="E10" s="6">
-        <v>1.2</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1711,13 +1710,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-19.45</v>
+        <v>-19.17</v>
       </c>
       <c r="D11" s="5">
-        <v>-19.17</v>
+        <v>-19.32</v>
       </c>
       <c r="E11" s="6">
-        <v>0.28</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1728,13 +1727,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-12.37</v>
+        <v>-4.58</v>
       </c>
       <c r="D12" s="5">
-        <v>-4.58</v>
-      </c>
-      <c r="E12" s="6">
-        <v>7.79</v>
+        <v>-2.77</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.81</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1745,13 +1744,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-3.4</v>
+        <v>-6.94</v>
       </c>
       <c r="D13" s="5">
-        <v>-6.94</v>
+        <v>-6.53</v>
       </c>
       <c r="E13" s="7">
-        <v>-3.54</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1762,13 +1761,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-2.13</v>
+        <v>-3.38</v>
       </c>
       <c r="D14" s="5">
-        <v>-3.38</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.25</v>
+        <v>-4</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1779,13 +1778,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-3.99</v>
+        <v>-6.02</v>
       </c>
       <c r="D15" s="5">
-        <v>-6.02</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.03</v>
+        <v>-7.22</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1796,13 +1795,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-3.83</v>
+        <v>-4.63</v>
       </c>
       <c r="D16" s="5">
-        <v>-4.63</v>
+        <v>-4.51</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.8</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1813,13 +1812,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>-15.06</v>
+        <v>-12.83</v>
       </c>
       <c r="D17" s="5">
-        <v>-12.83</v>
+        <v>-13.5</v>
       </c>
       <c r="E17" s="6">
-        <v>2.23</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1830,13 +1829,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-11.64</v>
+        <v>-9.33</v>
       </c>
       <c r="D18" s="5">
-        <v>-9.33</v>
+        <v>-11.72</v>
       </c>
       <c r="E18" s="6">
-        <v>2.31</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1847,13 +1846,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-26.92</v>
+        <v>-27.54</v>
       </c>
       <c r="D19" s="5">
-        <v>-27.54</v>
+        <v>-26.84</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.62</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1864,13 +1863,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-11.36</v>
+        <v>-14.28</v>
       </c>
       <c r="D20" s="5">
-        <v>-14.28</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-2.92</v>
+        <v>-14.68</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1881,13 +1880,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-19.05</v>
+        <v>-17.23</v>
       </c>
       <c r="D21" s="5">
-        <v>-17.23</v>
+        <v>-18.48</v>
       </c>
       <c r="E21" s="6">
-        <v>1.82</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1898,13 +1897,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-2.44</v>
+        <v>0.11</v>
       </c>
       <c r="D22" s="5">
-        <v>0.11</v>
+        <v>-0.18</v>
       </c>
       <c r="E22" s="6">
-        <v>2.55</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1915,13 +1914,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>14.55</v>
+        <v>12.5</v>
       </c>
       <c r="D23" s="5">
-        <v>12.5</v>
+        <v>12.94</v>
       </c>
       <c r="E23" s="7">
-        <v>-2.05</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1932,13 +1931,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-18.07</v>
+        <v>-21.09</v>
       </c>
       <c r="D24" s="5">
-        <v>-21.09</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-3.02</v>
+        <v>-22</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1949,13 +1948,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-11.83</v>
+        <v>-14.23</v>
       </c>
       <c r="D25" s="5">
-        <v>-14.23</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.4</v>
+        <v>-15.72</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1966,13 +1965,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-16.6</v>
+        <v>-17.28</v>
       </c>
       <c r="D26" s="5">
-        <v>-17.28</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.68</v>
+        <v>-20.07</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-2.79</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1983,13 +1982,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-24.22</v>
+        <v>-21.33</v>
       </c>
       <c r="D27" s="5">
-        <v>-21.33</v>
+        <v>-22.87</v>
       </c>
       <c r="E27" s="6">
-        <v>2.89</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2000,13 +1999,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-11.75</v>
+        <v>-12.89</v>
       </c>
       <c r="D28" s="5">
-        <v>-12.89</v>
+        <v>-11.37</v>
       </c>
       <c r="E28" s="7">
-        <v>-1.14</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2017,13 +2016,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-31.18</v>
+        <v>-31.58</v>
       </c>
       <c r="D29" s="5">
-        <v>-31.58</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.4</v>
+        <v>-32.39</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2034,13 +2033,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-25.53</v>
+        <v>-26.68</v>
       </c>
       <c r="D30" s="5">
-        <v>-26.68</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.15</v>
+        <v>-28.08</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2051,13 +2050,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-29.56</v>
+        <v>-29.82</v>
       </c>
       <c r="D31" s="5">
-        <v>-29.82</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.26</v>
+        <v>-31.22</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2068,13 +2067,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>696.25</v>
+        <v>722.75</v>
       </c>
       <c r="D32" s="5">
-        <v>722.75</v>
+        <v>708.6</v>
       </c>
       <c r="E32" s="6">
-        <v>26.5</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2085,13 +2084,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>631.7</v>
+        <v>623.55</v>
       </c>
       <c r="D33" s="5">
-        <v>623.55</v>
+        <v>631.9</v>
       </c>
       <c r="E33" s="7">
-        <v>-8.15</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2102,13 +2101,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="D34" s="5">
-        <v>850</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-5</v>
+        <v>840</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-10</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2119,13 +2118,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>1055.7</v>
+        <v>1039.4</v>
       </c>
       <c r="D35" s="5">
-        <v>1039.4</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-16.3</v>
+        <v>1019.6</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-19.8</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2136,13 +2135,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>1634.4</v>
+        <v>1628.5</v>
       </c>
       <c r="D36" s="5">
-        <v>1628.5</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-5.9</v>
+        <v>1595.8</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-32.7</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2153,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="C37" s="5">
-        <v>52.02</v>
+        <v>55.36</v>
       </c>
       <c r="D37" s="5">
-        <v>55.36</v>
+        <v>53.23</v>
       </c>
       <c r="E37" s="6">
-        <v>3.34</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2170,13 +2169,13 @@
         <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>46.79</v>
+        <v>44.21</v>
       </c>
       <c r="D38" s="5">
-        <v>44.21</v>
+        <v>47.41</v>
       </c>
       <c r="E38" s="7">
-        <v>-2.58</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2187,13 +2186,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>32.9</v>
+        <v>31.53</v>
       </c>
       <c r="D39" s="5">
-        <v>31.53</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.37</v>
+        <v>28.94</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-2.59</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2204,13 +2203,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>29.3</v>
+        <v>27.04</v>
       </c>
       <c r="D40" s="5">
-        <v>27.04</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-2.26</v>
+        <v>24.55</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2221,13 +2220,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>27.23</v>
+        <v>26.81</v>
       </c>
       <c r="D41" s="5">
-        <v>26.81</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.42</v>
+        <v>24.58</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-2.23</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2238,13 +2237,13 @@
         <v>31</v>
       </c>
       <c r="C42" s="5">
-        <v>-94.39</v>
+        <v>104.2</v>
       </c>
       <c r="D42" s="5">
-        <v>104.2</v>
+        <v>-87.93000000000001</v>
       </c>
       <c r="E42" s="6">
-        <v>198.59</v>
+        <v>-192.13</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2255,13 +2254,13 @@
         <v>31</v>
       </c>
       <c r="C43" s="5">
-        <v>-88.76000000000001</v>
+        <v>-86.73999999999999</v>
       </c>
       <c r="D43" s="5">
-        <v>-86.73999999999999</v>
-      </c>
-      <c r="E43" s="6">
-        <v>2.02</v>
+        <v>-83.84999999999999</v>
+      </c>
+      <c r="E43" s="7">
+        <v>2.89</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2272,13 +2271,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>0.13</v>
+        <v>18.41</v>
       </c>
       <c r="D44" s="5">
-        <v>18.41</v>
+        <v>-40.21</v>
       </c>
       <c r="E44" s="6">
-        <v>18.28</v>
+        <v>-58.62</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2289,13 +2288,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-62.55</v>
+        <v>-65.20999999999999</v>
       </c>
       <c r="D45" s="5">
-        <v>-65.20999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="E45" s="7">
-        <v>-2.66</v>
+        <v>65.34999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2306,13 +2305,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>-39.97</v>
+        <v>20.92</v>
       </c>
       <c r="D46" s="5">
-        <v>20.92</v>
+        <v>-28.57</v>
       </c>
       <c r="E46" s="6">
-        <v>60.89</v>
+        <v>-49.49</v>
       </c>
     </row>
   </sheetData>
@@ -2377,16 +2376,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>37</v>
+        <v>35.7</v>
       </c>
       <c r="E2" s="10">
         <v>40</v>
       </c>
       <c r="F2" s="10">
-        <v>-0.6</v>
+        <v>-3.1</v>
       </c>
       <c r="G2" s="10">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2511,19 +2510,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.1241</v>
+        <v>0.1254</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0075</v>
+        <v>0.013</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0288</v>
+        <v>-0.0293</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.0677</v>
+        <v>-0.065</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1088</v>
+        <v>-0.1119</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,46 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>47.4 → 50.7</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>47.4</t>
+  </si>
+  <si>
+    <t>50.7</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>24.6 → 31.6</t>
+  </si>
+  <si>
+    <t>24.6</t>
+  </si>
+  <si>
+    <t>31.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -252,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,17 +407,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -890,10 +930,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>708.6</v>
+        <v>712.7</v>
       </c>
       <c r="D2">
-        <v>-1.96</v>
+        <v>0.58</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,46 +942,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-22.87</v>
+        <v>-22.43</v>
       </c>
       <c r="H2">
-        <v>35.79</v>
+        <v>36.57</v>
       </c>
       <c r="I2">
-        <v>-2.77</v>
+        <v>-3.56</v>
       </c>
       <c r="J2">
-        <v>26</v>
+        <v>24.48</v>
       </c>
       <c r="K2">
-        <v>-0.18</v>
+        <v>1.9</v>
       </c>
       <c r="L2">
-        <v>-13.5</v>
+        <v>-12.27</v>
       </c>
       <c r="M2">
-        <v>-11.19</v>
+        <v>-11.3</v>
       </c>
       <c r="N2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P2">
-        <v>715.6799999999999</v>
+        <v>710.42</v>
       </c>
       <c r="Q2">
-        <v>695.78</v>
+        <v>702.75</v>
       </c>
       <c r="R2">
-        <v>645.21</v>
+        <v>646.15</v>
       </c>
       <c r="S2">
-        <v>668.01</v>
+        <v>668.02</v>
       </c>
       <c r="T2">
-        <v>6.08</v>
+        <v>6.69</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -956,34 +996,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>53.23</v>
+        <v>53.78</v>
       </c>
       <c r="Z2">
-        <v>25</v>
+        <v>23.14</v>
       </c>
       <c r="AA2">
-        <v>27.35</v>
+        <v>26.51</v>
       </c>
       <c r="AB2">
-        <v>-2.36</v>
+        <v>-3.37</v>
       </c>
       <c r="AC2">
-        <v>9.859999999999999</v>
+        <v>13.68</v>
       </c>
       <c r="AD2">
-        <v>12.66</v>
+        <v>10.26</v>
       </c>
       <c r="AE2">
-        <v>47.24</v>
+        <v>45.42</v>
       </c>
       <c r="AF2">
-        <v>-87.93000000000001</v>
+        <v>-94.8</v>
       </c>
       <c r="AG2">
-        <v>830.0599999999999</v>
+        <v>824.1</v>
       </c>
       <c r="AH2">
-        <v>561.5</v>
+        <v>581.4</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -992,7 +1032,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>48.15</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,58 +1043,58 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>631.9</v>
+        <v>640.9</v>
       </c>
       <c r="D3">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="E3">
-        <v>713</v>
+        <v>695.3</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-11.37</v>
+        <v>-7.82</v>
       </c>
       <c r="H3">
-        <v>23.18</v>
+        <v>24.93</v>
       </c>
       <c r="I3">
-        <v>-6.53</v>
+        <v>-2.57</v>
       </c>
       <c r="J3">
-        <v>-3.44</v>
+        <v>-4.38</v>
       </c>
       <c r="K3">
-        <v>12.94</v>
+        <v>12.81</v>
       </c>
       <c r="L3">
-        <v>-11.72</v>
+        <v>-10.11</v>
       </c>
       <c r="M3">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P3">
-        <v>637.49</v>
+        <v>634.11</v>
       </c>
       <c r="Q3">
-        <v>656.12</v>
+        <v>655.22</v>
       </c>
       <c r="R3">
-        <v>610.74</v>
+        <v>612.34</v>
       </c>
       <c r="S3">
-        <v>585.4</v>
+        <v>585.6799999999999</v>
       </c>
       <c r="T3">
-        <v>7.94</v>
+        <v>9.43</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1069,34 +1109,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>47.41</v>
+        <v>50.7</v>
       </c>
       <c r="Z3">
-        <v>6.11</v>
+        <v>5.27</v>
       </c>
       <c r="AA3">
-        <v>13.32</v>
+        <v>11.71</v>
       </c>
       <c r="AB3">
-        <v>-7.21</v>
+        <v>-6.44</v>
       </c>
       <c r="AC3">
-        <v>4.21</v>
+        <v>15.02</v>
       </c>
       <c r="AD3">
-        <v>1.4</v>
+        <v>6.41</v>
       </c>
       <c r="AE3">
-        <v>21.96</v>
+        <v>22.16</v>
       </c>
       <c r="AF3">
-        <v>-83.84999999999999</v>
+        <v>-34.73</v>
       </c>
       <c r="AG3">
-        <v>688</v>
+        <v>687.77</v>
       </c>
       <c r="AH3">
-        <v>624.24</v>
+        <v>622.66</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1105,7 +1145,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>24.81</v>
+        <v>22.54</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,58 +1156,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="D4">
-        <v>-1.18</v>
+        <v>-0.36</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
       </c>
       <c r="F4">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="G4">
-        <v>-32.39</v>
+        <v>-32.63</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-4</v>
+        <v>-4.89</v>
       </c>
       <c r="J4">
-        <v>-7.18</v>
+        <v>-7.51</v>
       </c>
       <c r="K4">
-        <v>-22</v>
+        <v>-23.95</v>
       </c>
       <c r="L4">
-        <v>-26.84</v>
+        <v>-27.94</v>
       </c>
       <c r="M4">
-        <v>-2.93</v>
+        <v>-3.41</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P4">
-        <v>858.6</v>
+        <v>850</v>
       </c>
       <c r="Q4">
-        <v>867.27</v>
+        <v>865.12</v>
       </c>
       <c r="R4">
-        <v>940.16</v>
+        <v>935.73</v>
       </c>
       <c r="S4">
-        <v>1061.27</v>
+        <v>1059.68</v>
       </c>
       <c r="T4">
-        <v>-20.85</v>
+        <v>-21.01</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1182,43 +1222,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>28.94</v>
+        <v>28.19</v>
       </c>
       <c r="Z4">
-        <v>-21.3</v>
+        <v>-21.92</v>
       </c>
       <c r="AA4">
-        <v>-23.37</v>
+        <v>-23.08</v>
       </c>
       <c r="AB4">
-        <v>2.07</v>
+        <v>1.16</v>
       </c>
       <c r="AC4">
-        <v>43.01</v>
+        <v>32.92</v>
       </c>
       <c r="AD4">
-        <v>59.74</v>
+        <v>44.94</v>
       </c>
       <c r="AE4">
-        <v>17.22</v>
+        <v>17.06</v>
       </c>
       <c r="AF4">
-        <v>-40.21</v>
+        <v>-44.03</v>
       </c>
       <c r="AG4">
-        <v>889.11</v>
+        <v>889.9400000000001</v>
       </c>
       <c r="AH4">
-        <v>845.4400000000001</v>
+        <v>840.3</v>
       </c>
       <c r="AI4">
-        <v>896.67</v>
+        <v>891.26</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>38.2</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1269,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1019.6</v>
+        <v>1040.2</v>
       </c>
       <c r="D5">
-        <v>-1.9</v>
+        <v>2.02</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,46 +1281,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-28.08</v>
+        <v>-26.63</v>
       </c>
       <c r="H5">
-        <v>36.13</v>
+        <v>38.88</v>
       </c>
       <c r="I5">
-        <v>-7.22</v>
+        <v>-5.89</v>
       </c>
       <c r="J5">
-        <v>-11.56</v>
+        <v>-8.66</v>
       </c>
       <c r="K5">
-        <v>-15.72</v>
+        <v>-13.97</v>
       </c>
       <c r="L5">
-        <v>-14.68</v>
+        <v>-12.95</v>
       </c>
       <c r="M5">
-        <v>12.54</v>
+        <v>12.98</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P5">
-        <v>1059.22</v>
+        <v>1046.2</v>
       </c>
       <c r="Q5">
-        <v>1109.09</v>
+        <v>1103.38</v>
       </c>
       <c r="R5">
-        <v>1193.73</v>
+        <v>1187.63</v>
       </c>
       <c r="S5">
-        <v>1072.71</v>
+        <v>1072.81</v>
       </c>
       <c r="T5">
-        <v>-4.95</v>
+        <v>-3.04</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1295,34 +1335,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>24.55</v>
+        <v>31.59</v>
       </c>
       <c r="Z5">
-        <v>-38.1</v>
+        <v>-38.55</v>
       </c>
       <c r="AA5">
-        <v>-32.97</v>
+        <v>-34.09</v>
       </c>
       <c r="AB5">
-        <v>-5.13</v>
+        <v>-4.46</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>14.07</v>
       </c>
       <c r="AD5">
-        <v>7.89</v>
+        <v>5.11</v>
       </c>
       <c r="AE5">
-        <v>37.69</v>
+        <v>37.6</v>
       </c>
       <c r="AF5">
-        <v>0.14</v>
+        <v>-37.08</v>
       </c>
       <c r="AG5">
-        <v>1185.94</v>
+        <v>1183</v>
       </c>
       <c r="AH5">
-        <v>1032.23</v>
+        <v>1023.76</v>
       </c>
       <c r="AI5">
         <v>1126.16</v>
@@ -1331,7 +1371,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>23.82</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1382,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1595.8</v>
+        <v>1599.9</v>
       </c>
       <c r="D6">
-        <v>-2.01</v>
+        <v>0.26</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,25 +1394,25 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-31.22</v>
+        <v>-31.05</v>
       </c>
       <c r="H6">
-        <v>8.460000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="I6">
-        <v>-4.51</v>
+        <v>-5.89</v>
       </c>
       <c r="J6">
-        <v>-19.32</v>
+        <v>-18.82</v>
       </c>
       <c r="K6">
-        <v>-20.07</v>
+        <v>-21.82</v>
       </c>
       <c r="L6">
-        <v>-18.48</v>
+        <v>-19.88</v>
       </c>
       <c r="M6">
-        <v>-6.5</v>
+        <v>-6.88</v>
       </c>
       <c r="N6">
         <v>40</v>
@@ -1381,19 +1421,19 @@
         <v>20</v>
       </c>
       <c r="P6">
-        <v>1645.72</v>
+        <v>1625.68</v>
       </c>
       <c r="Q6">
-        <v>1749.35</v>
+        <v>1729.28</v>
       </c>
       <c r="R6">
-        <v>1929.96</v>
+        <v>1921.14</v>
       </c>
       <c r="S6">
-        <v>1834.97</v>
+        <v>1832.63</v>
       </c>
       <c r="T6">
-        <v>-13.03</v>
+        <v>-12.7</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1408,43 +1448,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>24.58</v>
+        <v>25.42</v>
       </c>
       <c r="Z6">
-        <v>-90.65000000000001</v>
+        <v>-90.75</v>
       </c>
       <c r="AA6">
-        <v>-85.61</v>
+        <v>-86.63</v>
       </c>
       <c r="AB6">
-        <v>-5.05</v>
+        <v>-4.11</v>
       </c>
       <c r="AC6">
-        <v>36.25</v>
+        <v>33.61</v>
       </c>
       <c r="AD6">
-        <v>45.44</v>
+        <v>38.53</v>
       </c>
       <c r="AE6">
-        <v>52.05</v>
+        <v>51.1</v>
       </c>
       <c r="AF6">
-        <v>-28.57</v>
+        <v>-27.48</v>
       </c>
       <c r="AG6">
-        <v>1998.91</v>
+        <v>1957.09</v>
       </c>
       <c r="AH6">
-        <v>1499.8</v>
+        <v>1501.46</v>
       </c>
       <c r="AI6">
-        <v>1755.91</v>
+        <v>1750.65</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>55.14</v>
+        <v>57.59</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1625,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1605,719 +1645,808 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>28.9</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>26</v>
       </c>
-      <c r="E7" s="6">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>24.48</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>1.34</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-3.44</v>
       </c>
-      <c r="E8" s="6">
-        <v>-4.78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-4.38</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-5.69</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-7.18</v>
       </c>
-      <c r="E9" s="6">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-7.51</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-8.380000000000001</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-11.56</v>
       </c>
-      <c r="E10" s="6">
-        <v>-3.18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-8.66</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-19.17</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-19.32</v>
       </c>
-      <c r="E11" s="6">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-18.82</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-4.58</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>-2.77</v>
       </c>
-      <c r="E12" s="7">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-3.56</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-6.94</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>-6.53</v>
       </c>
-      <c r="E13" s="7">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>-2.57</v>
+      </c>
+      <c r="E14" s="8">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-3.38</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>-4</v>
       </c>
-      <c r="E14" s="6">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-4.89</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-6.02</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-7.22</v>
       </c>
-      <c r="E15" s="6">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-5.89</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-4.63</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>-4.51</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-5.89</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>-12.83</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>-13.5</v>
       </c>
-      <c r="E17" s="6">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>-12.27</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>-9.33</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="6">
         <v>-11.72</v>
       </c>
-      <c r="E18" s="6">
-        <v>-2.39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="6">
+        <v>-10.11</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-27.54</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="6">
         <v>-26.84</v>
       </c>
-      <c r="E19" s="7">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-27.94</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>-14.28</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="6">
         <v>-14.68</v>
       </c>
-      <c r="E20" s="6">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="6">
+        <v>-12.95</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-17.23</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="6">
         <v>-18.48</v>
       </c>
-      <c r="E21" s="6">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="6">
+        <v>-19.88</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>0.11</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="6">
         <v>-0.18</v>
       </c>
-      <c r="E22" s="6">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="6">
+        <v>1.9</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="5">
-        <v>12.5</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="6">
         <v>12.94</v>
       </c>
-      <c r="E23" s="7">
+      <c r="D24" s="6">
+        <v>12.81</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-22</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-23.95</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-15.72</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-13.97</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-20.07</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-21.82</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-22.87</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-22.43</v>
+      </c>
+      <c r="E28" s="8">
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-11.37</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-7.82</v>
+      </c>
+      <c r="E29" s="8">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-21.09</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-22</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-32.39</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-32.63</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-14.23</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-15.72</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-28.08</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-26.63</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-17.28</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-20.07</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-2.79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-31.22</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-31.05</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-21.33</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-22.87</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>708.6</v>
+      </c>
+      <c r="D33" s="6">
+        <v>712.7</v>
+      </c>
+      <c r="E33" s="8">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-12.89</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-11.37</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>631.9</v>
+      </c>
+      <c r="D34" s="6">
+        <v>640.9</v>
+      </c>
+      <c r="E34" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-31.58</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-32.39</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>840</v>
+      </c>
+      <c r="D35" s="6">
+        <v>837</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-26.68</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-28.08</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>1019.6</v>
+      </c>
+      <c r="D36" s="6">
+        <v>1040.2</v>
+      </c>
+      <c r="E36" s="8">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-29.82</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-31.22</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6">
+        <v>1595.8</v>
+      </c>
+      <c r="D37" s="6">
+        <v>1599.9</v>
+      </c>
+      <c r="E37" s="8">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>722.75</v>
-      </c>
-      <c r="D32" s="5">
-        <v>708.6</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-14.15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="6">
+        <v>79</v>
+      </c>
+      <c r="D38" s="6">
+        <v>99</v>
+      </c>
+      <c r="E38" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>623.55</v>
-      </c>
-      <c r="D33" s="5">
-        <v>631.9</v>
-      </c>
-      <c r="E33" s="7">
-        <v>8.35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="6">
+        <v>99</v>
+      </c>
+      <c r="D39" s="6">
+        <v>79</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>53.23</v>
+      </c>
+      <c r="D40" s="6">
+        <v>53.78</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>47.41</v>
+      </c>
+      <c r="D41" s="6">
+        <v>50.7</v>
+      </c>
+      <c r="E41" s="8">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>850</v>
-      </c>
-      <c r="D34" s="5">
-        <v>840</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>28.94</v>
+      </c>
+      <c r="D42" s="6">
+        <v>28.19</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5">
-        <v>1039.4</v>
-      </c>
-      <c r="D35" s="5">
-        <v>1019.6</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-19.8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>24.55</v>
+      </c>
+      <c r="D43" s="6">
+        <v>31.59</v>
+      </c>
+      <c r="E43" s="8">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
-        <v>1628.5</v>
-      </c>
-      <c r="D36" s="5">
-        <v>1595.8</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-32.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="6">
+        <v>24.58</v>
+      </c>
+      <c r="D44" s="6">
+        <v>25.42</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="5">
-        <v>55.36</v>
-      </c>
-      <c r="D37" s="5">
-        <v>53.23</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-87.93000000000001</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-94.8</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-6.87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="5">
-        <v>44.21</v>
-      </c>
-      <c r="D38" s="5">
-        <v>47.41</v>
-      </c>
-      <c r="E38" s="7">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-83.84999999999999</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-34.73</v>
+      </c>
+      <c r="E46" s="8">
+        <v>49.12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>31.53</v>
-      </c>
-      <c r="D39" s="5">
-        <v>28.94</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-2.59</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-40.21</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-44.03</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-3.82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>27.04</v>
-      </c>
-      <c r="D40" s="5">
-        <v>24.55</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-2.49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.14</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-37.08</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-37.22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>26.81</v>
-      </c>
-      <c r="D41" s="5">
-        <v>24.58</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-2.23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
+      <c r="B49" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="5">
-        <v>104.2</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-87.93000000000001</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-192.13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-86.73999999999999</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-83.84999999999999</v>
-      </c>
-      <c r="E43" s="7">
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="5">
-        <v>18.41</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-40.21</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-58.62</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-65.20999999999999</v>
-      </c>
-      <c r="D45" s="5">
-        <v>0.14</v>
-      </c>
-      <c r="E45" s="7">
-        <v>65.34999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>20.92</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C49" s="6">
         <v>-28.57</v>
       </c>
-      <c r="E46" s="6">
-        <v>-49.49</v>
+      <c r="D49" s="6">
+        <v>-27.48</v>
+      </c>
+      <c r="E49" s="8">
+        <v>1.09</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2337,60 +2466,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>49.92</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>35.7</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>37.9</v>
+      </c>
+      <c r="E2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="10">
-        <v>-3.1</v>
-      </c>
-      <c r="G2" s="10">
+      <c r="F2" s="11">
+        <v>-3</v>
+      </c>
+      <c r="G2" s="11">
         <v>-9</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2492,37 +2621,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.1254</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.013</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0293</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.065</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1119</v>
+      <c r="A2" s="14">
+        <v>0.1298</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0173</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0341</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0688</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.113</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,31 +181,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>47.4 → 50.7</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.2 → 46.0</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>47.4</t>
-  </si>
-  <si>
-    <t>50.7</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>24.6 → 31.6</t>
-  </si>
-  <si>
-    <t>24.6</t>
-  </si>
-  <si>
-    <t>31.6</t>
+    <t>28.2</t>
+  </si>
+  <si>
+    <t>46.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -930,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>712.7</v>
+        <v>704.7</v>
       </c>
       <c r="D2">
-        <v>0.58</v>
+        <v>-1.12</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -942,46 +930,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-22.43</v>
+        <v>-23.3</v>
       </c>
       <c r="H2">
-        <v>36.57</v>
+        <v>35.04</v>
       </c>
       <c r="I2">
-        <v>-3.56</v>
+        <v>-1</v>
       </c>
       <c r="J2">
-        <v>24.48</v>
+        <v>22.93</v>
       </c>
       <c r="K2">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="L2">
-        <v>-12.27</v>
+        <v>-12.43</v>
       </c>
       <c r="M2">
-        <v>-11.3</v>
+        <v>-11.22</v>
       </c>
       <c r="N2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O2">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="P2">
-        <v>710.42</v>
+        <v>709</v>
       </c>
       <c r="Q2">
-        <v>702.75</v>
+        <v>710.26</v>
       </c>
       <c r="R2">
-        <v>646.15</v>
+        <v>647.0599999999999</v>
       </c>
       <c r="S2">
-        <v>668.02</v>
+        <v>667.9400000000001</v>
       </c>
       <c r="T2">
-        <v>6.69</v>
+        <v>5.5</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -996,34 +984,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>53.78</v>
+        <v>52.47</v>
       </c>
       <c r="Z2">
-        <v>23.14</v>
+        <v>20.78</v>
       </c>
       <c r="AA2">
-        <v>26.51</v>
+        <v>25.36</v>
       </c>
       <c r="AB2">
-        <v>-3.37</v>
+        <v>-4.59</v>
       </c>
       <c r="AC2">
-        <v>13.68</v>
+        <v>7.43</v>
       </c>
       <c r="AD2">
-        <v>10.26</v>
+        <v>10.32</v>
       </c>
       <c r="AE2">
-        <v>45.42</v>
+        <v>45.1</v>
       </c>
       <c r="AF2">
-        <v>-94.8</v>
+        <v>-87.55</v>
       </c>
       <c r="AG2">
-        <v>824.1</v>
+        <v>809.5599999999999</v>
       </c>
       <c r="AH2">
-        <v>581.4</v>
+        <v>610.97</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -1032,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>47.02</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1031,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>640.9</v>
+        <v>648.1</v>
       </c>
       <c r="D3">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="E3">
         <v>695.3</v>
@@ -1055,46 +1043,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-7.82</v>
+        <v>-6.79</v>
       </c>
       <c r="H3">
-        <v>24.93</v>
+        <v>26.34</v>
       </c>
       <c r="I3">
-        <v>-2.57</v>
+        <v>0.87</v>
       </c>
       <c r="J3">
-        <v>-4.38</v>
+        <v>-1.65</v>
       </c>
       <c r="K3">
-        <v>12.81</v>
+        <v>15.53</v>
       </c>
       <c r="L3">
-        <v>-10.11</v>
+        <v>-6.1</v>
       </c>
       <c r="M3">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="N3">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O3">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P3">
-        <v>634.11</v>
+        <v>635.23</v>
       </c>
       <c r="Q3">
-        <v>655.22</v>
+        <v>655.38</v>
       </c>
       <c r="R3">
-        <v>612.34</v>
+        <v>613.83</v>
       </c>
       <c r="S3">
-        <v>585.6799999999999</v>
+        <v>586.02</v>
       </c>
       <c r="T3">
-        <v>9.43</v>
+        <v>10.59</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1109,34 +1097,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>50.7</v>
+        <v>53.22</v>
       </c>
       <c r="Z3">
-        <v>5.27</v>
+        <v>5.12</v>
       </c>
       <c r="AA3">
-        <v>11.71</v>
+        <v>10.39</v>
       </c>
       <c r="AB3">
-        <v>-6.44</v>
+        <v>-5.27</v>
       </c>
       <c r="AC3">
-        <v>15.02</v>
+        <v>30.02</v>
       </c>
       <c r="AD3">
-        <v>6.41</v>
+        <v>16.42</v>
       </c>
       <c r="AE3">
-        <v>22.16</v>
+        <v>21.65</v>
       </c>
       <c r="AF3">
-        <v>-34.73</v>
+        <v>-28.92</v>
       </c>
       <c r="AG3">
-        <v>687.77</v>
+        <v>687.75</v>
       </c>
       <c r="AH3">
-        <v>622.66</v>
+        <v>623.01</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1145,7 +1133,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>22.54</v>
+        <v>20.56</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>837</v>
+        <v>872.5</v>
       </c>
       <c r="D4">
-        <v>-0.36</v>
+        <v>4.24</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1168,46 +1156,46 @@
         <v>837</v>
       </c>
       <c r="G4">
-        <v>-32.63</v>
+        <v>-29.77</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="I4">
-        <v>-4.89</v>
+        <v>0.52</v>
       </c>
       <c r="J4">
-        <v>-7.51</v>
+        <v>-0.85</v>
       </c>
       <c r="K4">
-        <v>-23.95</v>
+        <v>-20.48</v>
       </c>
       <c r="L4">
-        <v>-27.94</v>
+        <v>-24.2</v>
       </c>
       <c r="M4">
-        <v>-3.41</v>
+        <v>-2.14</v>
       </c>
       <c r="N4">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="O4">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>850</v>
+        <v>850.9</v>
       </c>
       <c r="Q4">
-        <v>865.12</v>
+        <v>864.85</v>
       </c>
       <c r="R4">
-        <v>935.73</v>
+        <v>931.99</v>
       </c>
       <c r="S4">
-        <v>1059.68</v>
+        <v>1058.18</v>
       </c>
       <c r="T4">
-        <v>-21.01</v>
+        <v>-17.55</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1222,34 +1210,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>28.19</v>
+        <v>46.01</v>
       </c>
       <c r="Z4">
-        <v>-21.92</v>
+        <v>-19.32</v>
       </c>
       <c r="AA4">
-        <v>-23.08</v>
+        <v>-22.33</v>
       </c>
       <c r="AB4">
-        <v>1.16</v>
+        <v>3.01</v>
       </c>
       <c r="AC4">
-        <v>32.92</v>
+        <v>51.36</v>
       </c>
       <c r="AD4">
-        <v>44.94</v>
+        <v>42.43</v>
       </c>
       <c r="AE4">
-        <v>17.06</v>
+        <v>18.38</v>
       </c>
       <c r="AF4">
-        <v>-44.03</v>
+        <v>0.42</v>
       </c>
       <c r="AG4">
-        <v>889.9400000000001</v>
+        <v>889.1900000000001</v>
       </c>
       <c r="AH4">
-        <v>840.3</v>
+        <v>840.51</v>
       </c>
       <c r="AI4">
         <v>891.26</v>
@@ -1258,7 +1246,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>41.6</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1040.2</v>
+        <v>1045</v>
       </c>
       <c r="D5">
-        <v>2.02</v>
+        <v>0.46</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1281,46 +1269,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-26.63</v>
+        <v>-26.29</v>
       </c>
       <c r="H5">
-        <v>38.88</v>
+        <v>39.52</v>
       </c>
       <c r="I5">
-        <v>-5.89</v>
+        <v>-2.89</v>
       </c>
       <c r="J5">
-        <v>-8.66</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="K5">
-        <v>-13.97</v>
+        <v>-13.84</v>
       </c>
       <c r="L5">
-        <v>-12.95</v>
+        <v>-13.04</v>
       </c>
       <c r="M5">
-        <v>12.98</v>
+        <v>12.99</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P5">
-        <v>1046.2</v>
+        <v>1039.98</v>
       </c>
       <c r="Q5">
-        <v>1103.38</v>
+        <v>1097.46</v>
       </c>
       <c r="R5">
-        <v>1187.63</v>
+        <v>1181.88</v>
       </c>
       <c r="S5">
-        <v>1072.81</v>
+        <v>1072.96</v>
       </c>
       <c r="T5">
-        <v>-3.04</v>
+        <v>-2.61</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1335,34 +1323,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>31.59</v>
+        <v>33.16</v>
       </c>
       <c r="Z5">
-        <v>-38.55</v>
+        <v>-38.08</v>
       </c>
       <c r="AA5">
-        <v>-34.09</v>
+        <v>-34.89</v>
       </c>
       <c r="AB5">
-        <v>-4.46</v>
+        <v>-3.19</v>
       </c>
       <c r="AC5">
-        <v>14.07</v>
+        <v>31.26</v>
       </c>
       <c r="AD5">
-        <v>5.11</v>
+        <v>15.11</v>
       </c>
       <c r="AE5">
-        <v>37.6</v>
+        <v>37.17</v>
       </c>
       <c r="AF5">
-        <v>-37.08</v>
+        <v>-51.95</v>
       </c>
       <c r="AG5">
-        <v>1183</v>
+        <v>1175.86</v>
       </c>
       <c r="AH5">
-        <v>1023.76</v>
+        <v>1019.05</v>
       </c>
       <c r="AI5">
         <v>1126.16</v>
@@ -1371,7 +1359,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>26.75</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1599.9</v>
+        <v>1610</v>
       </c>
       <c r="D6">
-        <v>0.26</v>
+        <v>0.63</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1394,46 +1382,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-31.05</v>
+        <v>-30.61</v>
       </c>
       <c r="H6">
-        <v>8.74</v>
+        <v>9.43</v>
       </c>
       <c r="I6">
-        <v>-5.89</v>
+        <v>-3.58</v>
       </c>
       <c r="J6">
-        <v>-18.82</v>
+        <v>-19.56</v>
       </c>
       <c r="K6">
-        <v>-21.82</v>
+        <v>-21.2</v>
       </c>
       <c r="L6">
-        <v>-19.88</v>
+        <v>-18.22</v>
       </c>
       <c r="M6">
-        <v>-6.88</v>
+        <v>-6.78</v>
       </c>
       <c r="N6">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="O6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P6">
-        <v>1625.68</v>
+        <v>1613.72</v>
       </c>
       <c r="Q6">
-        <v>1729.28</v>
+        <v>1710.68</v>
       </c>
       <c r="R6">
-        <v>1921.14</v>
+        <v>1912.76</v>
       </c>
       <c r="S6">
-        <v>1832.63</v>
+        <v>1830.56</v>
       </c>
       <c r="T6">
-        <v>-12.7</v>
+        <v>-12.05</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1448,34 +1436,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>25.42</v>
+        <v>27.56</v>
       </c>
       <c r="Z6">
-        <v>-90.75</v>
+        <v>-88.98</v>
       </c>
       <c r="AA6">
-        <v>-86.63</v>
+        <v>-87.09999999999999</v>
       </c>
       <c r="AB6">
-        <v>-4.11</v>
+        <v>-1.88</v>
       </c>
       <c r="AC6">
-        <v>33.61</v>
+        <v>37.49</v>
       </c>
       <c r="AD6">
-        <v>38.53</v>
+        <v>35.79</v>
       </c>
       <c r="AE6">
-        <v>51.1</v>
+        <v>50.04</v>
       </c>
       <c r="AF6">
-        <v>-27.48</v>
+        <v>-46.17</v>
       </c>
       <c r="AG6">
-        <v>1957.09</v>
+        <v>1910.66</v>
       </c>
       <c r="AH6">
-        <v>1501.46</v>
+        <v>1510.69</v>
       </c>
       <c r="AI6">
         <v>1750.65</v>
@@ -1484,7 +1472,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>57.59</v>
+        <v>59.17</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1665,7 +1653,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1683,565 +1671,562 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>66</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>24.48</v>
+      </c>
+      <c r="D7" s="6">
+        <v>22.93</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>26</v>
+        <v>-4.38</v>
       </c>
       <c r="D8" s="6">
-        <v>24.48</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.52</v>
+        <v>-1.65</v>
+      </c>
+      <c r="E8" s="8">
+        <v>2.73</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-3.44</v>
+        <v>-7.51</v>
       </c>
       <c r="D9" s="6">
-        <v>-4.38</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.9399999999999999</v>
+        <v>-0.85</v>
+      </c>
+      <c r="E9" s="8">
+        <v>6.66</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-7.18</v>
+        <v>-8.66</v>
       </c>
       <c r="D10" s="6">
-        <v>-7.51</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.33</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-11.56</v>
+        <v>-18.82</v>
       </c>
       <c r="D11" s="6">
-        <v>-8.66</v>
-      </c>
-      <c r="E11" s="8">
-        <v>2.9</v>
+        <v>-19.56</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-19.32</v>
+        <v>-3.56</v>
       </c>
       <c r="D12" s="6">
-        <v>-18.82</v>
+        <v>-1</v>
       </c>
       <c r="E12" s="8">
-        <v>0.5</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-2.77</v>
+        <v>-2.57</v>
       </c>
       <c r="D13" s="6">
-        <v>-3.56</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.79</v>
+        <v>0.87</v>
+      </c>
+      <c r="E13" s="8">
+        <v>3.44</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-6.53</v>
+        <v>-4.89</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.57</v>
+        <v>0.52</v>
       </c>
       <c r="E14" s="8">
-        <v>3.96</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-4</v>
+        <v>-5.89</v>
       </c>
       <c r="D15" s="6">
-        <v>-4.89</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.89</v>
+        <v>-2.89</v>
+      </c>
+      <c r="E15" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-7.22</v>
+        <v>-5.89</v>
       </c>
       <c r="D16" s="6">
-        <v>-5.89</v>
+        <v>-3.58</v>
       </c>
       <c r="E16" s="8">
-        <v>1.33</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.51</v>
+        <v>-12.27</v>
       </c>
       <c r="D17" s="6">
-        <v>-5.89</v>
+        <v>-12.43</v>
       </c>
       <c r="E17" s="7">
-        <v>-1.38</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>-13.5</v>
+        <v>-10.11</v>
       </c>
       <c r="D18" s="6">
-        <v>-12.27</v>
+        <v>-6.1</v>
       </c>
       <c r="E18" s="8">
-        <v>1.23</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-11.72</v>
+        <v>-27.94</v>
       </c>
       <c r="D19" s="6">
-        <v>-10.11</v>
+        <v>-24.2</v>
       </c>
       <c r="E19" s="8">
-        <v>1.61</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-26.84</v>
+        <v>-12.95</v>
       </c>
       <c r="D20" s="6">
-        <v>-27.94</v>
+        <v>-13.04</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.1</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-14.68</v>
+        <v>-19.88</v>
       </c>
       <c r="D21" s="6">
-        <v>-12.95</v>
+        <v>-18.22</v>
       </c>
       <c r="E21" s="8">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-18.48</v>
+        <v>1.9</v>
       </c>
       <c r="D22" s="6">
-        <v>-19.88</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.4</v>
+        <v>2.55</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.65</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-0.18</v>
+        <v>12.81</v>
       </c>
       <c r="D23" s="6">
-        <v>1.9</v>
+        <v>15.53</v>
       </c>
       <c r="E23" s="8">
-        <v>2.08</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>12.94</v>
+        <v>-23.95</v>
       </c>
       <c r="D24" s="6">
-        <v>12.81</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.13</v>
+        <v>-20.48</v>
+      </c>
+      <c r="E24" s="8">
+        <v>3.47</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-22</v>
+        <v>-13.97</v>
       </c>
       <c r="D25" s="6">
-        <v>-23.95</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.95</v>
+        <v>-13.84</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.13</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-15.72</v>
+        <v>-21.82</v>
       </c>
       <c r="D26" s="6">
-        <v>-13.97</v>
+        <v>-21.2</v>
       </c>
       <c r="E26" s="8">
-        <v>1.75</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-20.07</v>
+        <v>-22.43</v>
       </c>
       <c r="D27" s="6">
-        <v>-21.82</v>
+        <v>-23.3</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.75</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-22.87</v>
+        <v>-7.82</v>
       </c>
       <c r="D28" s="6">
-        <v>-22.43</v>
+        <v>-6.79</v>
       </c>
       <c r="E28" s="8">
-        <v>0.44</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-11.37</v>
+        <v>-32.63</v>
       </c>
       <c r="D29" s="6">
-        <v>-7.82</v>
+        <v>-29.77</v>
       </c>
       <c r="E29" s="8">
-        <v>3.55</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-32.39</v>
+        <v>-26.63</v>
       </c>
       <c r="D30" s="6">
-        <v>-32.63</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.24</v>
+        <v>-26.29</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.34</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-28.08</v>
+        <v>-31.05</v>
       </c>
       <c r="D31" s="6">
-        <v>-26.63</v>
+        <v>-30.61</v>
       </c>
       <c r="E31" s="8">
-        <v>1.45</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>-31.22</v>
+        <v>712.7</v>
       </c>
       <c r="D32" s="6">
-        <v>-31.05</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.17</v>
+        <v>704.7</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-8</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>708.6</v>
+        <v>640.9</v>
       </c>
       <c r="D33" s="6">
-        <v>712.7</v>
+        <v>648.1</v>
       </c>
       <c r="E33" s="8">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>631.9</v>
+        <v>837</v>
       </c>
       <c r="D34" s="6">
-        <v>640.9</v>
+        <v>872.5</v>
       </c>
       <c r="E34" s="8">
-        <v>9</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>840</v>
+        <v>1040.2</v>
       </c>
       <c r="D35" s="6">
-        <v>837</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-3</v>
+        <v>1045</v>
+      </c>
+      <c r="E35" s="8">
+        <v>4.8</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>1019.6</v>
+        <v>1599.9</v>
       </c>
       <c r="D36" s="6">
-        <v>1040.2</v>
+        <v>1610</v>
       </c>
       <c r="E36" s="8">
-        <v>20.6</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C37" s="6">
-        <v>1595.8</v>
+        <v>99</v>
       </c>
       <c r="D37" s="6">
-        <v>1599.9</v>
-      </c>
-      <c r="E37" s="8">
-        <v>4.1</v>
+        <v>79</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>13</v>
@@ -2258,195 +2243,212 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C39" s="6">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="D39" s="6">
-        <v>79</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-20</v>
+        <v>40</v>
+      </c>
+      <c r="E39" s="8">
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C40" s="6">
-        <v>53.23</v>
+        <v>40</v>
       </c>
       <c r="D40" s="6">
-        <v>53.78</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.55</v>
+        <v>21</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-19</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>47.41</v>
+        <v>53.78</v>
       </c>
       <c r="D41" s="6">
-        <v>50.7</v>
-      </c>
-      <c r="E41" s="8">
-        <v>3.29</v>
+        <v>52.47</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C42" s="6">
-        <v>28.94</v>
+        <v>50.7</v>
       </c>
       <c r="D42" s="6">
-        <v>28.19</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.75</v>
+        <v>53.22</v>
+      </c>
+      <c r="E42" s="8">
+        <v>2.52</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C43" s="6">
-        <v>24.55</v>
+        <v>28.19</v>
       </c>
       <c r="D43" s="6">
-        <v>31.59</v>
+        <v>46.01</v>
       </c>
       <c r="E43" s="8">
-        <v>7.04</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C44" s="6">
-        <v>24.58</v>
+        <v>31.59</v>
       </c>
       <c r="D44" s="6">
-        <v>25.42</v>
+        <v>33.16</v>
       </c>
       <c r="E44" s="8">
-        <v>0.84</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C45" s="6">
-        <v>-87.93000000000001</v>
+        <v>25.42</v>
       </c>
       <c r="D45" s="6">
-        <v>-94.8</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-6.87</v>
+        <v>27.56</v>
+      </c>
+      <c r="E45" s="8">
+        <v>2.14</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>-83.84999999999999</v>
+        <v>-94.8</v>
       </c>
       <c r="D46" s="6">
-        <v>-34.73</v>
+        <v>-87.55</v>
       </c>
       <c r="E46" s="8">
-        <v>49.12</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C47" s="6">
-        <v>-40.21</v>
+        <v>-34.73</v>
       </c>
       <c r="D47" s="6">
-        <v>-44.03</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-3.82</v>
+        <v>-28.92</v>
+      </c>
+      <c r="E47" s="8">
+        <v>5.81</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C48" s="6">
-        <v>0.14</v>
+        <v>-44.03</v>
       </c>
       <c r="D48" s="6">
-        <v>-37.08</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-37.22</v>
+        <v>0.42</v>
+      </c>
+      <c r="E48" s="8">
+        <v>44.45</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C49" s="6">
-        <v>-28.57</v>
+        <v>-37.08</v>
       </c>
       <c r="D49" s="6">
+        <v>-51.95</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-14.87</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="6">
         <v>-27.48</v>
       </c>
-      <c r="E49" s="8">
-        <v>1.09</v>
+      <c r="D50" s="6">
+        <v>-46.17</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-18.69</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2470,28 +2472,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2505,16 +2507,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>37.9</v>
+        <v>42.5</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-3</v>
+        <v>-1.7</v>
       </c>
       <c r="G2" s="11">
-        <v>-9</v>
+        <v>-7.5</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2639,19 +2641,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.1298</v>
+        <v>0.1299</v>
       </c>
       <c r="B2" s="14">
-        <v>0.0173</v>
+        <v>0.0189</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0341</v>
+        <v>-0.0214</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.0688</v>
+        <v>-0.0678</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.113</v>
+        <v>-0.1122</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,19 +181,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.2 → 46.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>28.2</t>
-  </si>
-  <si>
-    <t>46.0</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>53.2 → 50.0</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>53.2</t>
+  </si>
+  <si>
+    <t>50.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -279,14 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -319,13 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -918,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>704.7</v>
+        <v>748.2</v>
       </c>
       <c r="D2">
-        <v>-1.12</v>
+        <v>6.17</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -930,46 +930,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-23.3</v>
+        <v>-18.56</v>
       </c>
       <c r="H2">
-        <v>35.04</v>
+        <v>43.37</v>
       </c>
       <c r="I2">
-        <v>-1</v>
+        <v>7.46</v>
       </c>
       <c r="J2">
-        <v>22.93</v>
+        <v>34.94</v>
       </c>
       <c r="K2">
-        <v>2.55</v>
+        <v>11.65</v>
       </c>
       <c r="L2">
-        <v>-12.43</v>
+        <v>-6.76</v>
       </c>
       <c r="M2">
-        <v>-11.22</v>
+        <v>-10.12</v>
       </c>
       <c r="N2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O2">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P2">
-        <v>709</v>
+        <v>719.39</v>
       </c>
       <c r="Q2">
-        <v>710.26</v>
+        <v>720.0599999999999</v>
       </c>
       <c r="R2">
-        <v>647.0599999999999</v>
+        <v>648.73</v>
       </c>
       <c r="S2">
-        <v>667.9400000000001</v>
+        <v>668.09</v>
       </c>
       <c r="T2">
-        <v>5.5</v>
+        <v>11.99</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -984,34 +984,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>52.47</v>
+        <v>58.4</v>
       </c>
       <c r="Z2">
-        <v>20.78</v>
+        <v>22.16</v>
       </c>
       <c r="AA2">
-        <v>25.36</v>
+        <v>24.72</v>
       </c>
       <c r="AB2">
-        <v>-4.59</v>
+        <v>-2.56</v>
       </c>
       <c r="AC2">
-        <v>7.43</v>
+        <v>18.64</v>
       </c>
       <c r="AD2">
-        <v>10.32</v>
+        <v>13.25</v>
       </c>
       <c r="AE2">
-        <v>45.1</v>
+        <v>46.81</v>
       </c>
       <c r="AF2">
-        <v>-87.55</v>
+        <v>-30.25</v>
       </c>
       <c r="AG2">
-        <v>809.5599999999999</v>
+        <v>787.2</v>
       </c>
       <c r="AH2">
-        <v>610.97</v>
+        <v>652.91</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -1020,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>44.5</v>
+        <v>44.54</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,58 +1031,58 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>648.1</v>
+        <v>639.6</v>
       </c>
       <c r="D3">
-        <v>1.12</v>
+        <v>-1.31</v>
       </c>
       <c r="E3">
-        <v>695.3</v>
+        <v>690.45</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-6.79</v>
+        <v>-7.36</v>
       </c>
       <c r="H3">
-        <v>26.34</v>
+        <v>24.68</v>
       </c>
       <c r="I3">
-        <v>0.87</v>
+        <v>1.25</v>
       </c>
       <c r="J3">
-        <v>-1.65</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="K3">
-        <v>15.53</v>
+        <v>15.57</v>
       </c>
       <c r="L3">
-        <v>-6.1</v>
+        <v>-8.01</v>
       </c>
       <c r="M3">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P3">
-        <v>635.23</v>
+        <v>636.8099999999999</v>
       </c>
       <c r="Q3">
-        <v>655.38</v>
+        <v>654.08</v>
       </c>
       <c r="R3">
-        <v>613.83</v>
+        <v>615.13</v>
       </c>
       <c r="S3">
-        <v>586.02</v>
+        <v>586.35</v>
       </c>
       <c r="T3">
-        <v>10.59</v>
+        <v>9.08</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1097,34 +1097,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>53.22</v>
+        <v>49.97</v>
       </c>
       <c r="Z3">
-        <v>5.12</v>
+        <v>4.27</v>
       </c>
       <c r="AA3">
-        <v>10.39</v>
+        <v>9.17</v>
       </c>
       <c r="AB3">
-        <v>-5.27</v>
+        <v>-4.9</v>
       </c>
       <c r="AC3">
-        <v>30.02</v>
+        <v>35.41</v>
       </c>
       <c r="AD3">
-        <v>16.42</v>
+        <v>26.82</v>
       </c>
       <c r="AE3">
-        <v>21.65</v>
+        <v>21.83</v>
       </c>
       <c r="AF3">
-        <v>-28.92</v>
+        <v>31.16</v>
       </c>
       <c r="AG3">
-        <v>687.75</v>
+        <v>686.8200000000001</v>
       </c>
       <c r="AH3">
-        <v>623.01</v>
+        <v>621.35</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1133,7 +1133,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>20.56</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>872.5</v>
+        <v>865.55</v>
       </c>
       <c r="D4">
-        <v>4.24</v>
+        <v>-0.8</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1156,25 +1156,25 @@
         <v>837</v>
       </c>
       <c r="G4">
-        <v>-29.77</v>
+        <v>-30.33</v>
       </c>
       <c r="H4">
-        <v>4.24</v>
+        <v>3.41</v>
       </c>
       <c r="I4">
-        <v>0.52</v>
+        <v>1.23</v>
       </c>
       <c r="J4">
-        <v>-0.85</v>
+        <v>-1.42</v>
       </c>
       <c r="K4">
-        <v>-20.48</v>
+        <v>-19.5</v>
       </c>
       <c r="L4">
-        <v>-24.2</v>
+        <v>-23.61</v>
       </c>
       <c r="M4">
-        <v>-2.14</v>
+        <v>-2.51</v>
       </c>
       <c r="N4">
         <v>40</v>
@@ -1183,19 +1183,19 @@
         <v>25</v>
       </c>
       <c r="P4">
-        <v>850.9</v>
+        <v>853.01</v>
       </c>
       <c r="Q4">
-        <v>864.85</v>
+        <v>865.03</v>
       </c>
       <c r="R4">
-        <v>931.99</v>
+        <v>927.83</v>
       </c>
       <c r="S4">
-        <v>1058.18</v>
+        <v>1056.67</v>
       </c>
       <c r="T4">
-        <v>-17.55</v>
+        <v>-18.09</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1210,34 +1210,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>46.01</v>
+        <v>43.72</v>
       </c>
       <c r="Z4">
-        <v>-19.32</v>
+        <v>-17.62</v>
       </c>
       <c r="AA4">
-        <v>-22.33</v>
+        <v>-21.39</v>
       </c>
       <c r="AB4">
-        <v>3.01</v>
+        <v>3.77</v>
       </c>
       <c r="AC4">
-        <v>51.36</v>
+        <v>70.66</v>
       </c>
       <c r="AD4">
-        <v>42.43</v>
+        <v>51.65</v>
       </c>
       <c r="AE4">
-        <v>18.38</v>
+        <v>18.57</v>
       </c>
       <c r="AF4">
-        <v>0.42</v>
+        <v>19.74</v>
       </c>
       <c r="AG4">
-        <v>889.1900000000001</v>
+        <v>889.33</v>
       </c>
       <c r="AH4">
-        <v>840.51</v>
+        <v>840.73</v>
       </c>
       <c r="AI4">
         <v>891.26</v>
@@ -1246,7 +1246,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>36.44</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1045</v>
+        <v>1029</v>
       </c>
       <c r="D5">
-        <v>0.46</v>
+        <v>-1.53</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1269,25 +1269,25 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-26.29</v>
+        <v>-27.42</v>
       </c>
       <c r="H5">
-        <v>39.52</v>
+        <v>37.38</v>
       </c>
       <c r="I5">
-        <v>-2.89</v>
+        <v>-2.53</v>
       </c>
       <c r="J5">
-        <v>-9.470000000000001</v>
+        <v>-11.56</v>
       </c>
       <c r="K5">
-        <v>-13.84</v>
+        <v>-15.41</v>
       </c>
       <c r="L5">
-        <v>-13.04</v>
+        <v>-13.43</v>
       </c>
       <c r="M5">
-        <v>12.99</v>
+        <v>12.3</v>
       </c>
       <c r="N5">
         <v>60</v>
@@ -1296,19 +1296,19 @@
         <v>39</v>
       </c>
       <c r="P5">
-        <v>1039.98</v>
+        <v>1034.64</v>
       </c>
       <c r="Q5">
-        <v>1097.46</v>
+        <v>1090.92</v>
       </c>
       <c r="R5">
-        <v>1181.88</v>
+        <v>1175.8</v>
       </c>
       <c r="S5">
-        <v>1072.96</v>
+        <v>1073.05</v>
       </c>
       <c r="T5">
-        <v>-2.61</v>
+        <v>-4.1</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1323,34 +1323,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>33.16</v>
+        <v>30.64</v>
       </c>
       <c r="Z5">
-        <v>-38.08</v>
+        <v>-38.55</v>
       </c>
       <c r="AA5">
-        <v>-34.89</v>
+        <v>-35.62</v>
       </c>
       <c r="AB5">
-        <v>-3.19</v>
+        <v>-2.93</v>
       </c>
       <c r="AC5">
-        <v>31.26</v>
+        <v>44.74</v>
       </c>
       <c r="AD5">
-        <v>15.11</v>
+        <v>30.02</v>
       </c>
       <c r="AE5">
-        <v>37.17</v>
+        <v>36.23</v>
       </c>
       <c r="AF5">
-        <v>-51.95</v>
+        <v>-81.38</v>
       </c>
       <c r="AG5">
-        <v>1175.86</v>
+        <v>1169.25</v>
       </c>
       <c r="AH5">
-        <v>1019.05</v>
+        <v>1012.58</v>
       </c>
       <c r="AI5">
         <v>1126.16</v>
@@ -1359,7 +1359,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>28.08</v>
+        <v>29.24</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1610</v>
+        <v>1580.2</v>
       </c>
       <c r="D6">
-        <v>0.63</v>
+        <v>-1.85</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1382,46 +1382,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-30.61</v>
+        <v>-31.9</v>
       </c>
       <c r="H6">
-        <v>9.43</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
-        <v>-3.58</v>
+        <v>-3.32</v>
       </c>
       <c r="J6">
-        <v>-19.56</v>
+        <v>-20.27</v>
       </c>
       <c r="K6">
-        <v>-21.2</v>
+        <v>-20.17</v>
       </c>
       <c r="L6">
-        <v>-18.22</v>
+        <v>-22.17</v>
       </c>
       <c r="M6">
-        <v>-6.78</v>
+        <v>-8.6</v>
       </c>
       <c r="N6">
         <v>21</v>
       </c>
       <c r="O6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P6">
-        <v>1613.72</v>
+        <v>1602.88</v>
       </c>
       <c r="Q6">
-        <v>1710.68</v>
+        <v>1693.58</v>
       </c>
       <c r="R6">
-        <v>1912.76</v>
+        <v>1902.79</v>
       </c>
       <c r="S6">
-        <v>1830.56</v>
+        <v>1828.39</v>
       </c>
       <c r="T6">
-        <v>-12.05</v>
+        <v>-13.57</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1436,43 +1436,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>27.56</v>
+        <v>25.26</v>
       </c>
       <c r="Z6">
-        <v>-88.98</v>
+        <v>-88.95999999999999</v>
       </c>
       <c r="AA6">
-        <v>-87.09999999999999</v>
+        <v>-87.48</v>
       </c>
       <c r="AB6">
-        <v>-1.88</v>
+        <v>-1.49</v>
       </c>
       <c r="AC6">
-        <v>37.49</v>
+        <v>31.55</v>
       </c>
       <c r="AD6">
-        <v>35.79</v>
+        <v>34.22</v>
       </c>
       <c r="AE6">
-        <v>50.04</v>
+        <v>49.32</v>
       </c>
       <c r="AF6">
-        <v>-46.17</v>
+        <v>-69.65000000000001</v>
       </c>
       <c r="AG6">
-        <v>1910.66</v>
+        <v>1875.03</v>
       </c>
       <c r="AH6">
-        <v>1510.69</v>
+        <v>1512.12</v>
       </c>
       <c r="AI6">
-        <v>1750.65</v>
+        <v>1735.4</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>59.17</v>
+        <v>60.95</v>
       </c>
     </row>
   </sheetData>
@@ -1613,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1705,13 +1705,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>24.48</v>
+        <v>22.93</v>
       </c>
       <c r="D7" s="6">
-        <v>22.93</v>
+        <v>34.94</v>
       </c>
       <c r="E7" s="7">
-        <v>-1.55</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1722,13 +1722,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-4.38</v>
+        <v>-1.65</v>
       </c>
       <c r="D8" s="6">
-        <v>-1.65</v>
-      </c>
-      <c r="E8" s="8">
-        <v>2.73</v>
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.84</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1739,13 +1739,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-7.51</v>
+        <v>-0.85</v>
       </c>
       <c r="D9" s="6">
-        <v>-0.85</v>
+        <v>-1.42</v>
       </c>
       <c r="E9" s="8">
-        <v>6.66</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1756,13 +1756,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-8.66</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="D10" s="6">
-        <v>-9.470000000000001</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.8100000000000001</v>
+        <v>-11.56</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-2.09</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1773,13 +1773,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-18.82</v>
+        <v>-19.56</v>
       </c>
       <c r="D11" s="6">
-        <v>-19.56</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.74</v>
+        <v>-20.27</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1790,13 +1790,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-3.56</v>
+        <v>-1</v>
       </c>
       <c r="D12" s="6">
-        <v>-1</v>
-      </c>
-      <c r="E12" s="8">
-        <v>2.56</v>
+        <v>7.46</v>
+      </c>
+      <c r="E12" s="7">
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1807,13 +1807,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-2.57</v>
+        <v>0.87</v>
       </c>
       <c r="D13" s="6">
-        <v>0.87</v>
-      </c>
-      <c r="E13" s="8">
-        <v>3.44</v>
+        <v>1.25</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.38</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1824,13 +1824,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.89</v>
+        <v>0.52</v>
       </c>
       <c r="D14" s="6">
-        <v>0.52</v>
-      </c>
-      <c r="E14" s="8">
-        <v>5.41</v>
+        <v>1.23</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.71</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1841,13 +1841,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-5.89</v>
+        <v>-2.89</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.89</v>
-      </c>
-      <c r="E15" s="8">
-        <v>3</v>
+        <v>-2.53</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.36</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1858,13 +1858,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-5.89</v>
+        <v>-3.58</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.58</v>
-      </c>
-      <c r="E16" s="8">
-        <v>2.31</v>
+        <v>-3.32</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.26</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1875,13 +1875,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>-12.27</v>
+        <v>-12.43</v>
       </c>
       <c r="D17" s="6">
-        <v>-12.43</v>
+        <v>-6.76</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.16</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1892,13 +1892,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>-10.11</v>
+        <v>-6.1</v>
       </c>
       <c r="D18" s="6">
-        <v>-6.1</v>
+        <v>-8.01</v>
       </c>
       <c r="E18" s="8">
-        <v>4.01</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1909,13 +1909,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-27.94</v>
+        <v>-24.2</v>
       </c>
       <c r="D19" s="6">
-        <v>-24.2</v>
-      </c>
-      <c r="E19" s="8">
-        <v>3.74</v>
+        <v>-23.61</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.59</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1926,13 +1926,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-12.95</v>
+        <v>-13.04</v>
       </c>
       <c r="D20" s="6">
-        <v>-13.04</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.09</v>
+        <v>-13.43</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1943,13 +1943,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-19.88</v>
+        <v>-18.22</v>
       </c>
       <c r="D21" s="6">
-        <v>-18.22</v>
+        <v>-22.17</v>
       </c>
       <c r="E21" s="8">
-        <v>1.66</v>
+        <v>-3.95</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1960,13 +1960,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="D22" s="6">
-        <v>2.55</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.65</v>
+        <v>11.65</v>
+      </c>
+      <c r="E22" s="7">
+        <v>9.1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1977,13 +1977,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>12.81</v>
+        <v>15.53</v>
       </c>
       <c r="D23" s="6">
-        <v>15.53</v>
-      </c>
-      <c r="E23" s="8">
-        <v>2.72</v>
+        <v>15.57</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.04</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1994,13 +1994,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-23.95</v>
+        <v>-20.48</v>
       </c>
       <c r="D24" s="6">
-        <v>-20.48</v>
-      </c>
-      <c r="E24" s="8">
-        <v>3.47</v>
+        <v>-19.5</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.98</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2011,13 +2011,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-13.97</v>
+        <v>-13.84</v>
       </c>
       <c r="D25" s="6">
-        <v>-13.84</v>
+        <v>-15.41</v>
       </c>
       <c r="E25" s="8">
-        <v>0.13</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2028,13 +2028,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-21.82</v>
+        <v>-21.2</v>
       </c>
       <c r="D26" s="6">
-        <v>-21.2</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.62</v>
+        <v>-20.17</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.03</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2045,13 +2045,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-22.43</v>
+        <v>-23.3</v>
       </c>
       <c r="D27" s="6">
-        <v>-23.3</v>
+        <v>-18.56</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.87</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2062,13 +2062,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-7.82</v>
+        <v>-6.79</v>
       </c>
       <c r="D28" s="6">
-        <v>-6.79</v>
+        <v>-7.36</v>
       </c>
       <c r="E28" s="8">
-        <v>1.03</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2079,13 +2079,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-32.63</v>
+        <v>-29.77</v>
       </c>
       <c r="D29" s="6">
-        <v>-29.77</v>
+        <v>-30.33</v>
       </c>
       <c r="E29" s="8">
-        <v>2.86</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2096,13 +2096,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-26.63</v>
+        <v>-26.29</v>
       </c>
       <c r="D30" s="6">
-        <v>-26.29</v>
+        <v>-27.42</v>
       </c>
       <c r="E30" s="8">
-        <v>0.34</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2113,13 +2113,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-31.05</v>
+        <v>-30.61</v>
       </c>
       <c r="D31" s="6">
-        <v>-30.61</v>
+        <v>-31.9</v>
       </c>
       <c r="E31" s="8">
-        <v>0.44</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2130,13 +2130,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>712.7</v>
+        <v>704.7</v>
       </c>
       <c r="D32" s="6">
-        <v>704.7</v>
+        <v>748.2</v>
       </c>
       <c r="E32" s="7">
-        <v>-8</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2147,13 +2147,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>640.9</v>
+        <v>648.1</v>
       </c>
       <c r="D33" s="6">
-        <v>648.1</v>
+        <v>639.6</v>
       </c>
       <c r="E33" s="8">
-        <v>7.2</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2164,13 +2164,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>837</v>
+        <v>872.5</v>
       </c>
       <c r="D34" s="6">
-        <v>872.5</v>
+        <v>865.55</v>
       </c>
       <c r="E34" s="8">
-        <v>35.5</v>
+        <v>-6.95</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2181,13 +2181,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>1040.2</v>
+        <v>1045</v>
       </c>
       <c r="D35" s="6">
-        <v>1045</v>
+        <v>1029</v>
       </c>
       <c r="E35" s="8">
-        <v>4.8</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2198,13 +2198,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>1599.9</v>
+        <v>1610</v>
       </c>
       <c r="D36" s="6">
-        <v>1610</v>
+        <v>1580.2</v>
       </c>
       <c r="E36" s="8">
-        <v>10.1</v>
+        <v>-29.8</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2215,13 +2215,13 @@
         <v>13</v>
       </c>
       <c r="C37" s="6">
+        <v>79</v>
+      </c>
+      <c r="D37" s="6">
         <v>99</v>
       </c>
-      <c r="D37" s="6">
-        <v>79</v>
-      </c>
       <c r="E37" s="7">
-        <v>-20</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2232,217 +2232,183 @@
         <v>13</v>
       </c>
       <c r="C38" s="6">
+        <v>99</v>
+      </c>
+      <c r="D38" s="6">
         <v>79</v>
       </c>
-      <c r="D38" s="6">
-        <v>99</v>
-      </c>
       <c r="E38" s="8">
-        <v>20</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>21</v>
+        <v>52.47</v>
       </c>
       <c r="D39" s="6">
-        <v>40</v>
-      </c>
-      <c r="E39" s="8">
-        <v>19</v>
+        <v>58.4</v>
+      </c>
+      <c r="E39" s="7">
+        <v>5.93</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>40</v>
+        <v>53.22</v>
       </c>
       <c r="D40" s="6">
-        <v>21</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-19</v>
+        <v>49.97</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-3.25</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>53.78</v>
+        <v>46.01</v>
       </c>
       <c r="D41" s="6">
-        <v>52.47</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.31</v>
+        <v>43.72</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-2.29</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C42" s="6">
-        <v>50.7</v>
+        <v>33.16</v>
       </c>
       <c r="D42" s="6">
-        <v>53.22</v>
+        <v>30.64</v>
       </c>
       <c r="E42" s="8">
-        <v>2.52</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C43" s="6">
-        <v>28.19</v>
+        <v>27.56</v>
       </c>
       <c r="D43" s="6">
-        <v>46.01</v>
+        <v>25.26</v>
       </c>
       <c r="E43" s="8">
-        <v>17.82</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>31.59</v>
+        <v>-87.55</v>
       </c>
       <c r="D44" s="6">
-        <v>33.16</v>
-      </c>
-      <c r="E44" s="8">
-        <v>1.57</v>
+        <v>-30.25</v>
+      </c>
+      <c r="E44" s="7">
+        <v>57.3</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>25.42</v>
+        <v>-28.92</v>
       </c>
       <c r="D45" s="6">
-        <v>27.56</v>
-      </c>
-      <c r="E45" s="8">
-        <v>2.14</v>
+        <v>31.16</v>
+      </c>
+      <c r="E45" s="7">
+        <v>60.08</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>-94.8</v>
+        <v>0.42</v>
       </c>
       <c r="D46" s="6">
-        <v>-87.55</v>
-      </c>
-      <c r="E46" s="8">
-        <v>7.25</v>
+        <v>19.74</v>
+      </c>
+      <c r="E46" s="7">
+        <v>19.32</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C47" s="6">
-        <v>-34.73</v>
+        <v>-51.95</v>
       </c>
       <c r="D47" s="6">
-        <v>-28.92</v>
+        <v>-81.38</v>
       </c>
       <c r="E47" s="8">
-        <v>5.81</v>
+        <v>-29.43</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C48" s="6">
-        <v>-44.03</v>
+        <v>-46.17</v>
       </c>
       <c r="D48" s="6">
-        <v>0.42</v>
+        <v>-69.65000000000001</v>
       </c>
       <c r="E48" s="8">
-        <v>44.45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-37.08</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-51.95</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-14.87</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-27.48</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-46.17</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-18.69</v>
+        <v>-23.48</v>
       </c>
     </row>
   </sheetData>
@@ -2507,16 +2473,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>42.5</v>
+        <v>41.6</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-1.7</v>
+        <v>0.2</v>
       </c>
       <c r="G2" s="11">
-        <v>-7.5</v>
+        <v>-5.6</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2641,19 +2607,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.1299</v>
+        <v>0.123</v>
       </c>
       <c r="B2" s="14">
-        <v>0.0189</v>
+        <v>0.0159</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0214</v>
+        <v>-0.0251</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.0678</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1122</v>
+        <v>-0.1012</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -184,16 +184,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>53.2 → 50.0</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.2</t>
+    <t>50.0 → 50.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>50.0</t>
+  </si>
+  <si>
+    <t>50.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -279,14 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -319,13 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -918,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>748.2</v>
+        <v>714.75</v>
       </c>
       <c r="D2">
-        <v>6.17</v>
+        <v>-4.47</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -930,46 +930,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-18.56</v>
+        <v>-22.2</v>
       </c>
       <c r="H2">
-        <v>43.37</v>
+        <v>36.96</v>
       </c>
       <c r="I2">
-        <v>7.46</v>
+        <v>-1.11</v>
       </c>
       <c r="J2">
-        <v>34.94</v>
+        <v>29.4</v>
       </c>
       <c r="K2">
-        <v>11.65</v>
+        <v>4.09</v>
       </c>
       <c r="L2">
-        <v>-6.76</v>
+        <v>-10.17</v>
       </c>
       <c r="M2">
-        <v>-10.12</v>
+        <v>-10.83</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="P2">
-        <v>719.39</v>
+        <v>717.79</v>
       </c>
       <c r="Q2">
-        <v>720.0599999999999</v>
+        <v>722.65</v>
       </c>
       <c r="R2">
-        <v>648.73</v>
+        <v>650.04</v>
       </c>
       <c r="S2">
-        <v>668.09</v>
+        <v>668.11</v>
       </c>
       <c r="T2">
-        <v>11.99</v>
+        <v>6.98</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -984,34 +984,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>58.4</v>
+        <v>52.93</v>
       </c>
       <c r="Z2">
-        <v>22.16</v>
+        <v>20.32</v>
       </c>
       <c r="AA2">
-        <v>24.72</v>
+        <v>23.84</v>
       </c>
       <c r="AB2">
-        <v>-2.56</v>
+        <v>-3.52</v>
       </c>
       <c r="AC2">
-        <v>18.64</v>
+        <v>16.8</v>
       </c>
       <c r="AD2">
-        <v>13.25</v>
+        <v>14.29</v>
       </c>
       <c r="AE2">
-        <v>46.81</v>
+        <v>46.19</v>
       </c>
       <c r="AF2">
-        <v>-30.25</v>
+        <v>-94.28</v>
       </c>
       <c r="AG2">
-        <v>787.2</v>
+        <v>784.26</v>
       </c>
       <c r="AH2">
-        <v>652.91</v>
+        <v>661.04</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -1020,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>44.54</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,58 +1031,58 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>639.6</v>
+        <v>639.95</v>
       </c>
       <c r="D3">
-        <v>-1.31</v>
+        <v>0.05</v>
       </c>
       <c r="E3">
-        <v>690.45</v>
+        <v>676.05</v>
       </c>
       <c r="F3">
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-7.36</v>
+        <v>-5.34</v>
       </c>
       <c r="H3">
-        <v>24.68</v>
+        <v>24.75</v>
       </c>
       <c r="I3">
-        <v>1.25</v>
+        <v>2.63</v>
       </c>
       <c r="J3">
-        <v>-0.8100000000000001</v>
+        <v>-3.84</v>
       </c>
       <c r="K3">
-        <v>15.57</v>
+        <v>13.87</v>
       </c>
       <c r="L3">
-        <v>-8.01</v>
+        <v>-7.31</v>
       </c>
       <c r="M3">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="N3">
         <v>79</v>
       </c>
       <c r="O3">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P3">
-        <v>636.8099999999999</v>
+        <v>640.09</v>
       </c>
       <c r="Q3">
-        <v>654.08</v>
+        <v>652.4</v>
       </c>
       <c r="R3">
-        <v>615.13</v>
+        <v>616.39</v>
       </c>
       <c r="S3">
-        <v>586.35</v>
+        <v>586.73</v>
       </c>
       <c r="T3">
-        <v>9.08</v>
+        <v>9.07</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1097,34 +1097,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>49.97</v>
+        <v>50.11</v>
       </c>
       <c r="Z3">
-        <v>4.27</v>
+        <v>3.59</v>
       </c>
       <c r="AA3">
-        <v>9.17</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AB3">
-        <v>-4.9</v>
+        <v>-4.47</v>
       </c>
       <c r="AC3">
-        <v>35.41</v>
+        <v>34.43</v>
       </c>
       <c r="AD3">
-        <v>26.82</v>
+        <v>33.29</v>
       </c>
       <c r="AE3">
-        <v>21.83</v>
+        <v>21.82</v>
       </c>
       <c r="AF3">
-        <v>31.16</v>
+        <v>50.32</v>
       </c>
       <c r="AG3">
-        <v>686.8200000000001</v>
+        <v>684.36</v>
       </c>
       <c r="AH3">
-        <v>621.35</v>
+        <v>620.4400000000001</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1133,7 +1133,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>18.49</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>865.55</v>
+        <v>865</v>
       </c>
       <c r="D4">
-        <v>-0.8</v>
+        <v>-0.06</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1156,46 +1156,46 @@
         <v>837</v>
       </c>
       <c r="G4">
-        <v>-30.33</v>
+        <v>-30.38</v>
       </c>
       <c r="H4">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="I4">
-        <v>1.23</v>
+        <v>1.76</v>
       </c>
       <c r="J4">
-        <v>-1.42</v>
+        <v>0.36</v>
       </c>
       <c r="K4">
-        <v>-19.5</v>
+        <v>-20.45</v>
       </c>
       <c r="L4">
-        <v>-23.61</v>
+        <v>-23.68</v>
       </c>
       <c r="M4">
-        <v>-2.51</v>
+        <v>-2.34</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>853.01</v>
+        <v>856.01</v>
       </c>
       <c r="Q4">
         <v>865.03</v>
       </c>
       <c r="R4">
-        <v>927.83</v>
+        <v>923.79</v>
       </c>
       <c r="S4">
-        <v>1056.67</v>
+        <v>1055.11</v>
       </c>
       <c r="T4">
-        <v>-18.09</v>
+        <v>-18.02</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1210,28 +1210,28 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>43.72</v>
+        <v>43.54</v>
       </c>
       <c r="Z4">
-        <v>-17.62</v>
+        <v>-16.13</v>
       </c>
       <c r="AA4">
-        <v>-21.39</v>
+        <v>-20.34</v>
       </c>
       <c r="AB4">
-        <v>3.77</v>
+        <v>4.21</v>
       </c>
       <c r="AC4">
-        <v>70.66</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AD4">
-        <v>51.65</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="AE4">
-        <v>18.57</v>
+        <v>18.19</v>
       </c>
       <c r="AF4">
-        <v>19.74</v>
+        <v>-19.92</v>
       </c>
       <c r="AG4">
         <v>889.33</v>
@@ -1246,7 +1246,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>32.5</v>
+        <v>29.08</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1029</v>
+        <v>1002.4</v>
       </c>
       <c r="D5">
-        <v>-1.53</v>
+        <v>-2.59</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1269,46 +1269,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-27.42</v>
+        <v>-29.29</v>
       </c>
       <c r="H5">
-        <v>37.38</v>
+        <v>33.83</v>
       </c>
       <c r="I5">
-        <v>-2.53</v>
+        <v>-3.56</v>
       </c>
       <c r="J5">
-        <v>-11.56</v>
+        <v>-13.57</v>
       </c>
       <c r="K5">
-        <v>-15.41</v>
+        <v>-17.78</v>
       </c>
       <c r="L5">
-        <v>-13.43</v>
+        <v>-13.68</v>
       </c>
       <c r="M5">
-        <v>12.3</v>
+        <v>11.25</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="P5">
-        <v>1034.64</v>
+        <v>1027.24</v>
       </c>
       <c r="Q5">
-        <v>1090.92</v>
+        <v>1083.84</v>
       </c>
       <c r="R5">
-        <v>1175.8</v>
+        <v>1169.67</v>
       </c>
       <c r="S5">
-        <v>1073.05</v>
+        <v>1073.01</v>
       </c>
       <c r="T5">
-        <v>-4.1</v>
+        <v>-6.58</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1323,43 +1323,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>30.64</v>
+        <v>26.98</v>
       </c>
       <c r="Z5">
-        <v>-38.55</v>
+        <v>-40.6</v>
       </c>
       <c r="AA5">
-        <v>-35.62</v>
+        <v>-36.62</v>
       </c>
       <c r="AB5">
-        <v>-2.93</v>
+        <v>-3.99</v>
       </c>
       <c r="AC5">
-        <v>44.74</v>
+        <v>36.72</v>
       </c>
       <c r="AD5">
-        <v>30.02</v>
+        <v>37.57</v>
       </c>
       <c r="AE5">
-        <v>36.23</v>
+        <v>38.52</v>
       </c>
       <c r="AF5">
-        <v>-81.38</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="AG5">
-        <v>1169.25</v>
+        <v>1167.39</v>
       </c>
       <c r="AH5">
-        <v>1012.58</v>
+        <v>1000.28</v>
       </c>
       <c r="AI5">
-        <v>1126.16</v>
+        <v>1124.27</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>29.24</v>
+        <v>33.14</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1580.2</v>
+        <v>1534</v>
       </c>
       <c r="D6">
-        <v>-1.85</v>
+        <v>-2.92</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1382,46 +1382,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-31.9</v>
+        <v>-33.89</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>4.26</v>
       </c>
       <c r="I6">
-        <v>-3.32</v>
+        <v>-5.8</v>
       </c>
       <c r="J6">
-        <v>-20.27</v>
+        <v>-20.2</v>
       </c>
       <c r="K6">
-        <v>-20.17</v>
+        <v>-24.43</v>
       </c>
       <c r="L6">
-        <v>-22.17</v>
+        <v>-24.55</v>
       </c>
       <c r="M6">
-        <v>-8.6</v>
+        <v>-8.25</v>
       </c>
       <c r="N6">
         <v>21</v>
       </c>
       <c r="O6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P6">
-        <v>1602.88</v>
+        <v>1583.98</v>
       </c>
       <c r="Q6">
-        <v>1693.58</v>
+        <v>1674.95</v>
       </c>
       <c r="R6">
-        <v>1902.79</v>
+        <v>1890.74</v>
       </c>
       <c r="S6">
-        <v>1828.39</v>
+        <v>1826.06</v>
       </c>
       <c r="T6">
-        <v>-13.57</v>
+        <v>-15.99</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1436,43 +1436,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>25.26</v>
+        <v>22.16</v>
       </c>
       <c r="Z6">
-        <v>-88.95999999999999</v>
+        <v>-91.62</v>
       </c>
       <c r="AA6">
-        <v>-87.48</v>
+        <v>-88.3</v>
       </c>
       <c r="AB6">
-        <v>-1.49</v>
+        <v>-3.32</v>
       </c>
       <c r="AC6">
-        <v>31.55</v>
+        <v>19.97</v>
       </c>
       <c r="AD6">
-        <v>34.22</v>
+        <v>29.67</v>
       </c>
       <c r="AE6">
-        <v>49.32</v>
+        <v>49.39</v>
       </c>
       <c r="AF6">
-        <v>-69.65000000000001</v>
+        <v>35.57</v>
       </c>
       <c r="AG6">
-        <v>1875.03</v>
+        <v>1840.09</v>
       </c>
       <c r="AH6">
-        <v>1512.12</v>
+        <v>1509.8</v>
       </c>
       <c r="AI6">
-        <v>1735.4</v>
+        <v>1703.38</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>60.95</v>
+        <v>63.42</v>
       </c>
     </row>
   </sheetData>
@@ -1613,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1705,13 +1705,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>22.93</v>
+        <v>34.94</v>
       </c>
       <c r="D7" s="6">
-        <v>34.94</v>
+        <v>29.4</v>
       </c>
       <c r="E7" s="7">
-        <v>12.01</v>
+        <v>-5.54</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1722,13 +1722,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-1.65</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="D8" s="6">
-        <v>-0.8100000000000001</v>
+        <v>-3.84</v>
       </c>
       <c r="E8" s="7">
-        <v>0.84</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1739,13 +1739,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-0.85</v>
+        <v>-1.42</v>
       </c>
       <c r="D9" s="6">
-        <v>-1.42</v>
+        <v>0.36</v>
       </c>
       <c r="E9" s="8">
-        <v>-0.57</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1756,13 +1756,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-9.470000000000001</v>
+        <v>-11.56</v>
       </c>
       <c r="D10" s="6">
-        <v>-11.56</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-2.09</v>
+        <v>-13.57</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.01</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1773,13 +1773,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-19.56</v>
+        <v>-20.27</v>
       </c>
       <c r="D11" s="6">
-        <v>-20.27</v>
+        <v>-20.2</v>
       </c>
       <c r="E11" s="8">
-        <v>-0.71</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1790,13 +1790,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-1</v>
+        <v>7.46</v>
       </c>
       <c r="D12" s="6">
-        <v>7.46</v>
+        <v>-1.11</v>
       </c>
       <c r="E12" s="7">
-        <v>8.460000000000001</v>
+        <v>-8.57</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1807,13 +1807,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>0.87</v>
+        <v>1.25</v>
       </c>
       <c r="D13" s="6">
-        <v>1.25</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.38</v>
+        <v>2.63</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.38</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1824,13 +1824,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>0.52</v>
+        <v>1.23</v>
       </c>
       <c r="D14" s="6">
-        <v>1.23</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.71</v>
+        <v>1.76</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.53</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1841,13 +1841,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-2.89</v>
+        <v>-2.53</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.53</v>
+        <v>-3.56</v>
       </c>
       <c r="E15" s="7">
-        <v>0.36</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1858,13 +1858,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.58</v>
+        <v>-3.32</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.32</v>
+        <v>-5.8</v>
       </c>
       <c r="E16" s="7">
-        <v>0.26</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1875,13 +1875,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>-12.43</v>
+        <v>-6.76</v>
       </c>
       <c r="D17" s="6">
-        <v>-6.76</v>
+        <v>-10.17</v>
       </c>
       <c r="E17" s="7">
-        <v>5.67</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1892,13 +1892,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>-6.1</v>
+        <v>-8.01</v>
       </c>
       <c r="D18" s="6">
-        <v>-8.01</v>
+        <v>-7.31</v>
       </c>
       <c r="E18" s="8">
-        <v>-1.91</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1909,13 +1909,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-24.2</v>
+        <v>-23.61</v>
       </c>
       <c r="D19" s="6">
-        <v>-23.61</v>
+        <v>-23.68</v>
       </c>
       <c r="E19" s="7">
-        <v>0.59</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1926,13 +1926,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-13.04</v>
+        <v>-13.43</v>
       </c>
       <c r="D20" s="6">
-        <v>-13.43</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.39</v>
+        <v>-13.68</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1943,13 +1943,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-18.22</v>
+        <v>-22.17</v>
       </c>
       <c r="D21" s="6">
-        <v>-22.17</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-3.95</v>
+        <v>-24.55</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-2.38</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1960,13 +1960,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>2.55</v>
+        <v>11.65</v>
       </c>
       <c r="D22" s="6">
-        <v>11.65</v>
+        <v>4.09</v>
       </c>
       <c r="E22" s="7">
-        <v>9.1</v>
+        <v>-7.56</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1977,13 +1977,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>15.53</v>
+        <v>15.57</v>
       </c>
       <c r="D23" s="6">
-        <v>15.57</v>
+        <v>13.87</v>
       </c>
       <c r="E23" s="7">
-        <v>0.04</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1994,13 +1994,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-20.48</v>
+        <v>-19.5</v>
       </c>
       <c r="D24" s="6">
-        <v>-19.5</v>
+        <v>-20.45</v>
       </c>
       <c r="E24" s="7">
-        <v>0.98</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2011,13 +2011,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-13.84</v>
+        <v>-15.41</v>
       </c>
       <c r="D25" s="6">
-        <v>-15.41</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.57</v>
+        <v>-17.78</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.37</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2028,13 +2028,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-21.2</v>
+        <v>-20.17</v>
       </c>
       <c r="D26" s="6">
-        <v>-20.17</v>
+        <v>-24.43</v>
       </c>
       <c r="E26" s="7">
-        <v>1.03</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2045,13 +2045,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-23.3</v>
+        <v>-18.56</v>
       </c>
       <c r="D27" s="6">
-        <v>-18.56</v>
+        <v>-22.2</v>
       </c>
       <c r="E27" s="7">
-        <v>4.74</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2062,13 +2062,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-6.79</v>
+        <v>-7.36</v>
       </c>
       <c r="D28" s="6">
-        <v>-7.36</v>
+        <v>-5.34</v>
       </c>
       <c r="E28" s="8">
-        <v>-0.57</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2079,13 +2079,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-29.77</v>
+        <v>-30.33</v>
       </c>
       <c r="D29" s="6">
-        <v>-30.33</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.5600000000000001</v>
+        <v>-30.38</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2096,13 +2096,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-26.29</v>
+        <v>-27.42</v>
       </c>
       <c r="D30" s="6">
-        <v>-27.42</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.13</v>
+        <v>-29.29</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2113,13 +2113,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-30.61</v>
+        <v>-31.9</v>
       </c>
       <c r="D31" s="6">
-        <v>-31.9</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.29</v>
+        <v>-33.89</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.99</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2130,13 +2130,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>704.7</v>
+        <v>748.2</v>
       </c>
       <c r="D32" s="6">
-        <v>748.2</v>
+        <v>714.75</v>
       </c>
       <c r="E32" s="7">
-        <v>43.5</v>
+        <v>-33.45</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2147,13 +2147,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>648.1</v>
+        <v>639.6</v>
       </c>
       <c r="D33" s="6">
-        <v>639.6</v>
+        <v>639.95</v>
       </c>
       <c r="E33" s="8">
-        <v>-8.5</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2164,13 +2164,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>872.5</v>
+        <v>865.55</v>
       </c>
       <c r="D34" s="6">
-        <v>865.55</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-6.95</v>
+        <v>865</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2181,13 +2181,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>1045</v>
+        <v>1029</v>
       </c>
       <c r="D35" s="6">
-        <v>1029</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-16</v>
+        <v>1002.4</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-26.6</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2198,13 +2198,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>1610</v>
+        <v>1580.2</v>
       </c>
       <c r="D36" s="6">
-        <v>1580.2</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-29.8</v>
+        <v>1534</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-46.2</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2212,16 +2212,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C37" s="6">
-        <v>79</v>
+        <v>58.4</v>
       </c>
       <c r="D37" s="6">
-        <v>99</v>
+        <v>52.93</v>
       </c>
       <c r="E37" s="7">
-        <v>20</v>
+        <v>-5.47</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2229,186 +2229,152 @@
         <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C38" s="6">
-        <v>99</v>
+        <v>49.97</v>
       </c>
       <c r="D38" s="6">
-        <v>79</v>
+        <v>50.11</v>
       </c>
       <c r="E38" s="8">
-        <v>-20</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>52.47</v>
+        <v>43.72</v>
       </c>
       <c r="D39" s="6">
-        <v>58.4</v>
+        <v>43.54</v>
       </c>
       <c r="E39" s="7">
-        <v>5.93</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>53.22</v>
+        <v>30.64</v>
       </c>
       <c r="D40" s="6">
-        <v>49.97</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-3.25</v>
+        <v>26.98</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-3.66</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>46.01</v>
+        <v>25.26</v>
       </c>
       <c r="D41" s="6">
-        <v>43.72</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-2.29</v>
+        <v>22.16</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C42" s="6">
-        <v>33.16</v>
+        <v>-30.25</v>
       </c>
       <c r="D42" s="6">
-        <v>30.64</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-2.52</v>
+        <v>-94.28</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-64.03</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C43" s="6">
-        <v>27.56</v>
+        <v>31.16</v>
       </c>
       <c r="D43" s="6">
-        <v>25.26</v>
+        <v>50.32</v>
       </c>
       <c r="E43" s="8">
-        <v>-2.3</v>
+        <v>19.16</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>-87.55</v>
+        <v>19.74</v>
       </c>
       <c r="D44" s="6">
-        <v>-30.25</v>
+        <v>-19.92</v>
       </c>
       <c r="E44" s="7">
-        <v>57.3</v>
+        <v>-39.66</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>-28.92</v>
+        <v>-81.38</v>
       </c>
       <c r="D45" s="6">
-        <v>31.16</v>
-      </c>
-      <c r="E45" s="7">
-        <v>60.08</v>
+        <v>68.48999999999999</v>
+      </c>
+      <c r="E45" s="8">
+        <v>149.87</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>0.42</v>
+        <v>-69.65000000000001</v>
       </c>
       <c r="D46" s="6">
-        <v>19.74</v>
-      </c>
-      <c r="E46" s="7">
-        <v>19.32</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-51.95</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-81.38</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-29.43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-46.17</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-69.65000000000001</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-23.48</v>
+        <v>35.57</v>
+      </c>
+      <c r="E46" s="8">
+        <v>105.22</v>
       </c>
     </row>
   </sheetData>
@@ -2473,16 +2439,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>41.6</v>
+        <v>39.1</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>0.2</v>
+        <v>-1.6</v>
       </c>
       <c r="G2" s="11">
-        <v>-5.6</v>
+        <v>-8.9</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2607,19 +2573,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.123</v>
+        <v>0.1125</v>
       </c>
       <c r="B2" s="14">
-        <v>0.0159</v>
+        <v>0.0172</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0251</v>
+        <v>-0.0234</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.08599999999999999</v>
+        <v>-0.0825</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1012</v>
+        <v>-0.1083</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,49 +166,13 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.0 → 50.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>50.0</t>
-  </si>
-  <si>
-    <t>50.1</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Delta</t>
+    <t>No numeric changes detected since last run.</t>
   </si>
   <si>
     <t>Rank</t>
@@ -239,13 +203,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,22 +239,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,24 +256,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,34 +325,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1613,7 +1536,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1633,47 +1556,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1682,699 +1570,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>34.94</v>
-      </c>
-      <c r="D7" s="6">
-        <v>29.4</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-5.54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-3.84</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-3.03</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-1.42</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0.36</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-11.56</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-13.57</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-2.01</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-20.27</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-20.2</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>7.46</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-1.11</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-8.57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1.25</v>
-      </c>
-      <c r="D13" s="6">
-        <v>2.63</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>1.23</v>
-      </c>
-      <c r="D14" s="6">
-        <v>1.76</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2.53</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-3.56</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-3.32</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-5.8</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-6.76</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-10.17</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-3.41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-8.01</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-7.31</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-23.61</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-23.68</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-13.43</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-13.68</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-22.17</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-24.55</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-2.38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>11.65</v>
-      </c>
-      <c r="D22" s="6">
-        <v>4.09</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-7.56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>15.57</v>
-      </c>
-      <c r="D23" s="6">
-        <v>13.87</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-19.5</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-20.45</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-15.41</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-17.78</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-20.17</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-24.43</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-4.26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-18.56</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-22.2</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-3.64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-7.36</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-5.34</v>
-      </c>
-      <c r="E28" s="8">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-30.33</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-30.38</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-27.42</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-29.29</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-31.9</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-33.89</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.99</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>748.2</v>
-      </c>
-      <c r="D32" s="6">
-        <v>714.75</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-33.45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>639.6</v>
-      </c>
-      <c r="D33" s="6">
-        <v>639.95</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>865.55</v>
-      </c>
-      <c r="D34" s="6">
-        <v>865</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1029</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1002.4</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-26.6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>1580.2</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1534</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-46.2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="6">
-        <v>58.4</v>
-      </c>
-      <c r="D37" s="6">
-        <v>52.93</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-5.47</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>49.97</v>
-      </c>
-      <c r="D38" s="6">
-        <v>50.11</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>43.72</v>
-      </c>
-      <c r="D39" s="6">
-        <v>43.54</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>30.64</v>
-      </c>
-      <c r="D40" s="6">
-        <v>26.98</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-3.66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>25.26</v>
-      </c>
-      <c r="D41" s="6">
-        <v>22.16</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-30.25</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-94.28</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-64.03</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="6">
-        <v>31.16</v>
-      </c>
-      <c r="D43" s="6">
-        <v>50.32</v>
-      </c>
-      <c r="E43" s="8">
-        <v>19.16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>19.74</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-19.92</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-39.66</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-81.38</v>
-      </c>
-      <c r="D45" s="6">
-        <v>68.48999999999999</v>
-      </c>
-      <c r="E45" s="8">
-        <v>149.87</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-69.65000000000001</v>
-      </c>
-      <c r="D46" s="6">
-        <v>35.57</v>
-      </c>
-      <c r="E46" s="8">
-        <v>105.22</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2400,60 +1596,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
+      <c r="B1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="6">
         <v>49.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="7">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="6">
         <v>39.1</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="6">
         <v>40</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="6">
         <v>-1.6</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="6">
         <v>-8.9</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="6">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="6">
         <v>20</v>
       </c>
     </row>
@@ -2555,36 +1751,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
+      <c r="A2" s="9">
         <v>0.1125</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="9">
         <v>0.0172</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="9">
         <v>-0.0234</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="9">
         <v>-0.0825</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="9">
         <v>-0.1083</v>
       </c>
     </row>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,13 +166,49 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.1 → 45.7</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.1</t>
+  </si>
+  <si>
+    <t>45.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -203,11 +239,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,8 +277,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,6 +308,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -325,27 +395,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -841,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>714.75</v>
+        <v>729.3</v>
       </c>
       <c r="D2">
-        <v>-4.47</v>
+        <v>2.04</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -853,46 +930,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-22.2</v>
+        <v>-20.62</v>
       </c>
       <c r="H2">
-        <v>36.96</v>
+        <v>39.75</v>
       </c>
       <c r="I2">
-        <v>-1.11</v>
+        <v>2.92</v>
       </c>
       <c r="J2">
-        <v>29.4</v>
+        <v>10.03</v>
       </c>
       <c r="K2">
-        <v>4.09</v>
+        <v>5.82</v>
       </c>
       <c r="L2">
-        <v>-10.17</v>
+        <v>-8.69</v>
       </c>
       <c r="M2">
-        <v>-10.83</v>
+        <v>-10.56</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="P2">
-        <v>717.79</v>
+        <v>721.9299999999999</v>
       </c>
       <c r="Q2">
-        <v>722.65</v>
+        <v>721.0700000000001</v>
       </c>
       <c r="R2">
-        <v>650.04</v>
+        <v>651.77</v>
       </c>
       <c r="S2">
-        <v>668.11</v>
+        <v>668.16</v>
       </c>
       <c r="T2">
-        <v>6.98</v>
+        <v>9.15</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -907,34 +984,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>52.93</v>
+        <v>54.91</v>
       </c>
       <c r="Z2">
-        <v>20.32</v>
+        <v>19.81</v>
       </c>
       <c r="AA2">
-        <v>23.84</v>
+        <v>23.04</v>
       </c>
       <c r="AB2">
-        <v>-3.52</v>
+        <v>-3.22</v>
       </c>
       <c r="AC2">
-        <v>16.8</v>
+        <v>22.08</v>
       </c>
       <c r="AD2">
-        <v>14.29</v>
+        <v>19.18</v>
       </c>
       <c r="AE2">
-        <v>46.19</v>
+        <v>45.74</v>
       </c>
       <c r="AF2">
-        <v>-94.28</v>
+        <v>-94.44</v>
       </c>
       <c r="AG2">
-        <v>784.26</v>
+        <v>780.1</v>
       </c>
       <c r="AH2">
-        <v>661.04</v>
+        <v>662.03</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -943,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>44.07</v>
+        <v>42.55</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -954,10 +1031,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>639.95</v>
+        <v>628.45</v>
       </c>
       <c r="D3">
-        <v>0.05</v>
+        <v>-1.8</v>
       </c>
       <c r="E3">
         <v>676.05</v>
@@ -966,46 +1043,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-5.34</v>
+        <v>-7.04</v>
       </c>
       <c r="H3">
-        <v>24.75</v>
+        <v>22.5</v>
       </c>
       <c r="I3">
-        <v>2.63</v>
+        <v>-0.55</v>
       </c>
       <c r="J3">
-        <v>-3.84</v>
+        <v>-6.7</v>
       </c>
       <c r="K3">
-        <v>13.87</v>
+        <v>11.79</v>
       </c>
       <c r="L3">
-        <v>-7.31</v>
+        <v>-6.83</v>
       </c>
       <c r="M3">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="N3">
         <v>79</v>
       </c>
       <c r="O3">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P3">
-        <v>640.09</v>
+        <v>639.4</v>
       </c>
       <c r="Q3">
-        <v>652.4</v>
+        <v>650.09</v>
       </c>
       <c r="R3">
-        <v>616.39</v>
+        <v>617.75</v>
       </c>
       <c r="S3">
-        <v>586.73</v>
+        <v>587.02</v>
       </c>
       <c r="T3">
-        <v>9.07</v>
+        <v>7.06</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1020,34 +1097,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>50.11</v>
+        <v>45.74</v>
       </c>
       <c r="Z3">
-        <v>3.59</v>
+        <v>2.09</v>
       </c>
       <c r="AA3">
-        <v>8.050000000000001</v>
+        <v>6.86</v>
       </c>
       <c r="AB3">
-        <v>-4.47</v>
+        <v>-4.77</v>
       </c>
       <c r="AC3">
-        <v>34.43</v>
+        <v>21.97</v>
       </c>
       <c r="AD3">
-        <v>33.29</v>
+        <v>30.6</v>
       </c>
       <c r="AE3">
-        <v>21.82</v>
+        <v>21.84</v>
       </c>
       <c r="AF3">
-        <v>50.32</v>
+        <v>-52.18</v>
       </c>
       <c r="AG3">
-        <v>684.36</v>
+        <v>681.96</v>
       </c>
       <c r="AH3">
-        <v>620.4400000000001</v>
+        <v>618.22</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1056,7 +1133,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>16.8</v>
+        <v>16.07</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1067,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>865</v>
+        <v>860.5</v>
       </c>
       <c r="D4">
-        <v>-0.06</v>
+        <v>-0.52</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1079,46 +1156,46 @@
         <v>837</v>
       </c>
       <c r="G4">
-        <v>-30.38</v>
+        <v>-30.74</v>
       </c>
       <c r="H4">
-        <v>3.35</v>
+        <v>2.81</v>
       </c>
       <c r="I4">
-        <v>1.76</v>
+        <v>2.44</v>
       </c>
       <c r="J4">
-        <v>0.36</v>
+        <v>-0.52</v>
       </c>
       <c r="K4">
-        <v>-20.45</v>
+        <v>-20.94</v>
       </c>
       <c r="L4">
-        <v>-23.68</v>
+        <v>-23.99</v>
       </c>
       <c r="M4">
-        <v>-2.34</v>
+        <v>-2.54</v>
       </c>
       <c r="N4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P4">
-        <v>856.01</v>
+        <v>860.11</v>
       </c>
       <c r="Q4">
-        <v>865.03</v>
+        <v>864.86</v>
       </c>
       <c r="R4">
-        <v>923.79</v>
+        <v>919.47</v>
       </c>
       <c r="S4">
-        <v>1055.11</v>
+        <v>1053.54</v>
       </c>
       <c r="T4">
-        <v>-18.02</v>
+        <v>-18.32</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1133,34 +1210,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>43.54</v>
+        <v>41.98</v>
       </c>
       <c r="Z4">
-        <v>-16.13</v>
+        <v>-15.14</v>
       </c>
       <c r="AA4">
-        <v>-20.34</v>
+        <v>-19.3</v>
       </c>
       <c r="AB4">
-        <v>4.21</v>
+        <v>4.16</v>
       </c>
       <c r="AC4">
-        <v>91.09999999999999</v>
+        <v>83.55</v>
       </c>
       <c r="AD4">
-        <v>71.04000000000001</v>
+        <v>81.77</v>
       </c>
       <c r="AE4">
-        <v>18.19</v>
+        <v>18.02</v>
       </c>
       <c r="AF4">
-        <v>-19.92</v>
+        <v>-39.91</v>
       </c>
       <c r="AG4">
-        <v>889.33</v>
+        <v>889.24</v>
       </c>
       <c r="AH4">
-        <v>840.73</v>
+        <v>840.49</v>
       </c>
       <c r="AI4">
         <v>891.26</v>
@@ -1169,7 +1246,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>29.08</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1180,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1002.4</v>
+        <v>985.4</v>
       </c>
       <c r="D5">
-        <v>-2.59</v>
+        <v>-1.7</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1192,46 +1269,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-29.29</v>
+        <v>-30.49</v>
       </c>
       <c r="H5">
-        <v>33.83</v>
+        <v>31.56</v>
       </c>
       <c r="I5">
-        <v>-3.56</v>
+        <v>-3.35</v>
       </c>
       <c r="J5">
-        <v>-13.57</v>
+        <v>-13.86</v>
       </c>
       <c r="K5">
-        <v>-17.78</v>
+        <v>-30.49</v>
       </c>
       <c r="L5">
-        <v>-13.68</v>
+        <v>-12.52</v>
       </c>
       <c r="M5">
-        <v>11.25</v>
+        <v>11.26</v>
       </c>
       <c r="N5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O5">
         <v>29</v>
       </c>
       <c r="P5">
-        <v>1027.24</v>
+        <v>1020.4</v>
       </c>
       <c r="Q5">
-        <v>1083.84</v>
+        <v>1076.44</v>
       </c>
       <c r="R5">
-        <v>1169.67</v>
+        <v>1163.51</v>
       </c>
       <c r="S5">
-        <v>1073.01</v>
+        <v>1072.97</v>
       </c>
       <c r="T5">
-        <v>-6.58</v>
+        <v>-8.16</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1246,43 +1323,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>26.98</v>
+        <v>24.92</v>
       </c>
       <c r="Z5">
-        <v>-40.6</v>
+        <v>-43.1</v>
       </c>
       <c r="AA5">
-        <v>-36.62</v>
+        <v>-37.91</v>
       </c>
       <c r="AB5">
-        <v>-3.99</v>
+        <v>-5.19</v>
       </c>
       <c r="AC5">
-        <v>36.72</v>
+        <v>20.45</v>
       </c>
       <c r="AD5">
-        <v>37.57</v>
+        <v>33.97</v>
       </c>
       <c r="AE5">
-        <v>38.52</v>
+        <v>37.39</v>
       </c>
       <c r="AF5">
-        <v>68.48999999999999</v>
+        <v>-40.42</v>
       </c>
       <c r="AG5">
         <v>1167.39</v>
       </c>
       <c r="AH5">
-        <v>1000.28</v>
+        <v>985.48</v>
       </c>
       <c r="AI5">
-        <v>1124.27</v>
+        <v>1105.66</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>33.14</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1293,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1534</v>
+        <v>1550</v>
       </c>
       <c r="D6">
-        <v>-2.92</v>
+        <v>1.04</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1305,46 +1382,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-33.89</v>
+        <v>-33.2</v>
       </c>
       <c r="H6">
-        <v>4.26</v>
+        <v>5.35</v>
       </c>
       <c r="I6">
-        <v>-5.8</v>
+        <v>-2.87</v>
       </c>
       <c r="J6">
-        <v>-20.2</v>
+        <v>-18.7</v>
       </c>
       <c r="K6">
-        <v>-24.43</v>
+        <v>-27.33</v>
       </c>
       <c r="L6">
-        <v>-24.55</v>
+        <v>-24.63</v>
       </c>
       <c r="M6">
-        <v>-8.25</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="N6">
         <v>21</v>
       </c>
       <c r="O6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P6">
-        <v>1583.98</v>
+        <v>1574.82</v>
       </c>
       <c r="Q6">
-        <v>1674.95</v>
+        <v>1659.59</v>
       </c>
       <c r="R6">
-        <v>1890.74</v>
+        <v>1878.62</v>
       </c>
       <c r="S6">
-        <v>1826.06</v>
+        <v>1823.58</v>
       </c>
       <c r="T6">
-        <v>-15.99</v>
+        <v>-15</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1359,43 +1436,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>22.16</v>
+        <v>25.56</v>
       </c>
       <c r="Z6">
-        <v>-91.62</v>
+        <v>-91.38</v>
       </c>
       <c r="AA6">
-        <v>-88.3</v>
+        <v>-88.92</v>
       </c>
       <c r="AB6">
-        <v>-3.32</v>
+        <v>-2.46</v>
       </c>
       <c r="AC6">
-        <v>19.97</v>
+        <v>14.23</v>
       </c>
       <c r="AD6">
-        <v>29.67</v>
+        <v>21.92</v>
       </c>
       <c r="AE6">
-        <v>49.39</v>
+        <v>47.87</v>
       </c>
       <c r="AF6">
-        <v>35.57</v>
+        <v>-54.2</v>
       </c>
       <c r="AG6">
-        <v>1840.09</v>
+        <v>1809.86</v>
       </c>
       <c r="AH6">
-        <v>1509.8</v>
+        <v>1509.32</v>
       </c>
       <c r="AI6">
-        <v>1703.38</v>
+        <v>1690.77</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>63.42</v>
+        <v>65.55</v>
       </c>
     </row>
   </sheetData>
@@ -1536,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1556,12 +1633,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1570,7 +1682,733 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>29.4</v>
+      </c>
+      <c r="D7" s="6">
+        <v>10.03</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-19.37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-3.84</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-6.7</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.36</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-0.52</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-13.57</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-13.86</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-20.2</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-18.7</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-1.11</v>
+      </c>
+      <c r="D12" s="6">
+        <v>2.92</v>
+      </c>
+      <c r="E12" s="8">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
+        <v>2.63</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-0.55</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-3.18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1.76</v>
+      </c>
+      <c r="D14" s="6">
+        <v>2.44</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-3.56</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-3.35</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-5.8</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-2.87</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-10.17</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-8.69</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-7.31</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-6.83</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-23.68</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-23.99</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-13.68</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-12.52</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-24.55</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-24.63</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6">
+        <v>4.09</v>
+      </c>
+      <c r="D22" s="6">
+        <v>5.82</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>13.87</v>
+      </c>
+      <c r="D23" s="6">
+        <v>11.79</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-2.08</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-20.45</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-20.94</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-17.78</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-30.49</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-12.71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-24.43</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-27.33</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-22.2</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-20.62</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-5.34</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-7.04</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-30.38</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-30.74</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-29.29</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-30.49</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-33.89</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-33.2</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6">
+        <v>714.75</v>
+      </c>
+      <c r="D32" s="6">
+        <v>729.3</v>
+      </c>
+      <c r="E32" s="8">
+        <v>14.55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>639.95</v>
+      </c>
+      <c r="D33" s="6">
+        <v>628.45</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-11.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>865</v>
+      </c>
+      <c r="D34" s="6">
+        <v>860.5</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1002.4</v>
+      </c>
+      <c r="D35" s="6">
+        <v>985.4</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>1534</v>
+      </c>
+      <c r="D36" s="6">
+        <v>1550</v>
+      </c>
+      <c r="E36" s="8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="6">
+        <v>40</v>
+      </c>
+      <c r="D37" s="6">
+        <v>60</v>
+      </c>
+      <c r="E37" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="6">
+        <v>60</v>
+      </c>
+      <c r="D38" s="6">
+        <v>40</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>52.93</v>
+      </c>
+      <c r="D39" s="6">
+        <v>54.91</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>50.11</v>
+      </c>
+      <c r="D40" s="6">
+        <v>45.74</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-4.37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>43.54</v>
+      </c>
+      <c r="D41" s="6">
+        <v>41.98</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>26.98</v>
+      </c>
+      <c r="D42" s="6">
+        <v>24.92</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-2.06</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>22.16</v>
+      </c>
+      <c r="D43" s="6">
+        <v>25.56</v>
+      </c>
+      <c r="E43" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-94.28</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-94.44</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>50.32</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-52.18</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-102.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-19.92</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-39.91</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-19.99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>68.48999999999999</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-40.42</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-108.91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="6">
+        <v>35.57</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-54.2</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-89.77</v>
       </c>
     </row>
   </sheetData>
@@ -1596,60 +2434,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>58</v>
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="11">
         <v>49.92</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="6">
-        <v>39.1</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="D2" s="11">
+        <v>38.6</v>
+      </c>
+      <c r="E2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="6">
-        <v>-1.6</v>
-      </c>
-      <c r="G2" s="6">
-        <v>-8.9</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="F2" s="11">
+        <v>-6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-12.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -1751,37 +2589,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="9">
-        <v>0.1125</v>
-      </c>
-      <c r="B2" s="9">
-        <v>0.0172</v>
-      </c>
-      <c r="C2" s="9">
-        <v>-0.0234</v>
-      </c>
-      <c r="D2" s="9">
-        <v>-0.0825</v>
-      </c>
-      <c r="E2" s="9">
-        <v>-0.1083</v>
+      <c r="A2" s="14">
+        <v>0.1126</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0141</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0254</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0814</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1056</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,34 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.1 → 45.7</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>45.7</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -395,15 +368,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -918,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>729.3</v>
+        <v>730.85</v>
       </c>
       <c r="D2">
-        <v>2.04</v>
+        <v>0.21</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -930,46 +902,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-20.62</v>
+        <v>-20.45</v>
       </c>
       <c r="H2">
-        <v>39.75</v>
+        <v>40.05</v>
       </c>
       <c r="I2">
-        <v>2.92</v>
+        <v>2.55</v>
       </c>
       <c r="J2">
-        <v>10.03</v>
+        <v>-3.96</v>
       </c>
       <c r="K2">
-        <v>5.82</v>
+        <v>6.44</v>
       </c>
       <c r="L2">
-        <v>-8.69</v>
+        <v>-7.75</v>
       </c>
       <c r="M2">
-        <v>-10.56</v>
+        <v>-10.74</v>
       </c>
       <c r="N2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P2">
-        <v>721.9299999999999</v>
+        <v>725.5599999999999</v>
       </c>
       <c r="Q2">
-        <v>721.0700000000001</v>
+        <v>721.8200000000001</v>
       </c>
       <c r="R2">
-        <v>651.77</v>
+        <v>653.85</v>
       </c>
       <c r="S2">
-        <v>668.16</v>
+        <v>668.21</v>
       </c>
       <c r="T2">
-        <v>9.15</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -984,34 +956,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>54.91</v>
+        <v>55.13</v>
       </c>
       <c r="Z2">
-        <v>19.81</v>
+        <v>19.31</v>
       </c>
       <c r="AA2">
-        <v>23.04</v>
+        <v>22.29</v>
       </c>
       <c r="AB2">
-        <v>-3.22</v>
+        <v>-2.98</v>
       </c>
       <c r="AC2">
-        <v>22.08</v>
+        <v>14.99</v>
       </c>
       <c r="AD2">
-        <v>19.18</v>
+        <v>17.96</v>
       </c>
       <c r="AE2">
-        <v>45.74</v>
+        <v>44.33</v>
       </c>
       <c r="AF2">
-        <v>-94.44</v>
+        <v>-95.84</v>
       </c>
       <c r="AG2">
-        <v>780.1</v>
+        <v>780.95</v>
       </c>
       <c r="AH2">
-        <v>662.03</v>
+        <v>662.6900000000001</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -1020,7 +992,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>42.55</v>
+        <v>41.23</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,10 +1003,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>628.45</v>
+        <v>630</v>
       </c>
       <c r="D3">
-        <v>-1.8</v>
+        <v>0.25</v>
       </c>
       <c r="E3">
         <v>676.05</v>
@@ -1043,46 +1015,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-7.04</v>
+        <v>-6.81</v>
       </c>
       <c r="H3">
-        <v>22.5</v>
+        <v>22.81</v>
       </c>
       <c r="I3">
-        <v>-0.55</v>
+        <v>-1.7</v>
       </c>
       <c r="J3">
-        <v>-6.7</v>
+        <v>-6.62</v>
       </c>
       <c r="K3">
-        <v>11.79</v>
+        <v>11.43</v>
       </c>
       <c r="L3">
-        <v>-6.83</v>
+        <v>-6.54</v>
       </c>
       <c r="M3">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="N3">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O3">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P3">
-        <v>639.4</v>
+        <v>637.22</v>
       </c>
       <c r="Q3">
-        <v>650.09</v>
+        <v>647.9400000000001</v>
       </c>
       <c r="R3">
-        <v>617.75</v>
+        <v>619.16</v>
       </c>
       <c r="S3">
-        <v>587.02</v>
+        <v>587.3200000000001</v>
       </c>
       <c r="T3">
-        <v>7.06</v>
+        <v>7.27</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1097,34 +1069,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>45.74</v>
+        <v>46.42</v>
       </c>
       <c r="Z3">
-        <v>2.09</v>
+        <v>1.02</v>
       </c>
       <c r="AA3">
-        <v>6.86</v>
+        <v>5.69</v>
       </c>
       <c r="AB3">
-        <v>-4.77</v>
+        <v>-4.67</v>
       </c>
       <c r="AC3">
-        <v>21.97</v>
+        <v>16.06</v>
       </c>
       <c r="AD3">
-        <v>30.6</v>
+        <v>24.15</v>
       </c>
       <c r="AE3">
-        <v>21.84</v>
+        <v>20.99</v>
       </c>
       <c r="AF3">
-        <v>-52.18</v>
+        <v>-69.26000000000001</v>
       </c>
       <c r="AG3">
-        <v>681.96</v>
+        <v>679.09</v>
       </c>
       <c r="AH3">
-        <v>618.22</v>
+        <v>616.79</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1133,7 +1105,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>16.07</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1116,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>860.5</v>
+        <v>852.05</v>
       </c>
       <c r="D4">
-        <v>-0.52</v>
+        <v>-0.98</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1156,46 +1128,46 @@
         <v>837</v>
       </c>
       <c r="G4">
-        <v>-30.74</v>
+        <v>-31.42</v>
       </c>
       <c r="H4">
-        <v>2.81</v>
+        <v>1.8</v>
       </c>
       <c r="I4">
-        <v>2.44</v>
+        <v>1.8</v>
       </c>
       <c r="J4">
-        <v>-0.52</v>
+        <v>-1.36</v>
       </c>
       <c r="K4">
-        <v>-20.94</v>
+        <v>-20.27</v>
       </c>
       <c r="L4">
-        <v>-23.99</v>
+        <v>-25.07</v>
       </c>
       <c r="M4">
-        <v>-2.54</v>
+        <v>-2.77</v>
       </c>
       <c r="N4">
         <v>60</v>
       </c>
       <c r="O4">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P4">
-        <v>860.11</v>
+        <v>863.12</v>
       </c>
       <c r="Q4">
-        <v>864.86</v>
+        <v>863.97</v>
       </c>
       <c r="R4">
-        <v>919.47</v>
+        <v>915.0700000000001</v>
       </c>
       <c r="S4">
-        <v>1053.54</v>
+        <v>1051.93</v>
       </c>
       <c r="T4">
-        <v>-18.32</v>
+        <v>-19</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1210,34 +1182,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>41.98</v>
+        <v>39.14</v>
       </c>
       <c r="Z4">
-        <v>-15.14</v>
+        <v>-14.86</v>
       </c>
       <c r="AA4">
-        <v>-19.3</v>
+        <v>-18.41</v>
       </c>
       <c r="AB4">
-        <v>4.16</v>
+        <v>3.55</v>
       </c>
       <c r="AC4">
-        <v>83.55</v>
+        <v>74.98</v>
       </c>
       <c r="AD4">
-        <v>81.77</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="AE4">
-        <v>18.02</v>
+        <v>18.66</v>
       </c>
       <c r="AF4">
-        <v>-39.91</v>
+        <v>-65.83</v>
       </c>
       <c r="AG4">
-        <v>889.24</v>
+        <v>888.88</v>
       </c>
       <c r="AH4">
-        <v>840.49</v>
+        <v>839.0700000000001</v>
       </c>
       <c r="AI4">
         <v>891.26</v>
@@ -1246,7 +1218,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>25.3</v>
+        <v>26.16</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>985.4</v>
+        <v>985.8</v>
       </c>
       <c r="D5">
-        <v>-1.7</v>
+        <v>0.04</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1269,22 +1241,22 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-30.49</v>
+        <v>-30.46</v>
       </c>
       <c r="H5">
-        <v>31.56</v>
+        <v>31.62</v>
       </c>
       <c r="I5">
-        <v>-3.35</v>
+        <v>-5.23</v>
       </c>
       <c r="J5">
-        <v>-13.86</v>
+        <v>-13.02</v>
       </c>
       <c r="K5">
-        <v>-30.49</v>
+        <v>-28.69</v>
       </c>
       <c r="L5">
-        <v>-12.52</v>
+        <v>-10.87</v>
       </c>
       <c r="M5">
         <v>11.26</v>
@@ -1293,22 +1265,22 @@
         <v>40</v>
       </c>
       <c r="O5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P5">
-        <v>1020.4</v>
+        <v>1009.52</v>
       </c>
       <c r="Q5">
-        <v>1076.44</v>
+        <v>1069.61</v>
       </c>
       <c r="R5">
-        <v>1163.51</v>
+        <v>1157.04</v>
       </c>
       <c r="S5">
-        <v>1072.97</v>
+        <v>1072.92</v>
       </c>
       <c r="T5">
-        <v>-8.16</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1323,43 +1295,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>24.92</v>
+        <v>25.07</v>
       </c>
       <c r="Z5">
-        <v>-43.1</v>
+        <v>-44.54</v>
       </c>
       <c r="AA5">
-        <v>-37.91</v>
+        <v>-39.24</v>
       </c>
       <c r="AB5">
-        <v>-5.19</v>
+        <v>-5.3</v>
       </c>
       <c r="AC5">
-        <v>20.45</v>
+        <v>8.26</v>
       </c>
       <c r="AD5">
-        <v>33.97</v>
+        <v>21.81</v>
       </c>
       <c r="AE5">
-        <v>37.39</v>
+        <v>36.82</v>
       </c>
       <c r="AF5">
-        <v>-40.42</v>
+        <v>-71.04000000000001</v>
       </c>
       <c r="AG5">
-        <v>1167.39</v>
+        <v>1166.38</v>
       </c>
       <c r="AH5">
-        <v>985.48</v>
+        <v>972.84</v>
       </c>
       <c r="AI5">
-        <v>1105.66</v>
+        <v>1105.62</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>36.52</v>
+        <v>38.52</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1550</v>
+        <v>1544.5</v>
       </c>
       <c r="D6">
-        <v>1.04</v>
+        <v>-0.35</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1382,25 +1354,25 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-33.2</v>
+        <v>-33.44</v>
       </c>
       <c r="H6">
-        <v>5.35</v>
+        <v>4.98</v>
       </c>
       <c r="I6">
-        <v>-2.87</v>
+        <v>-3.46</v>
       </c>
       <c r="J6">
-        <v>-18.7</v>
+        <v>-16.83</v>
       </c>
       <c r="K6">
-        <v>-27.33</v>
+        <v>-28.58</v>
       </c>
       <c r="L6">
-        <v>-24.63</v>
+        <v>-25.51</v>
       </c>
       <c r="M6">
-        <v>-8.140000000000001</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="N6">
         <v>21</v>
@@ -1409,19 +1381,19 @@
         <v>15</v>
       </c>
       <c r="P6">
-        <v>1574.82</v>
+        <v>1563.74</v>
       </c>
       <c r="Q6">
-        <v>1659.59</v>
+        <v>1643.22</v>
       </c>
       <c r="R6">
-        <v>1878.62</v>
+        <v>1867.29</v>
       </c>
       <c r="S6">
-        <v>1823.58</v>
+        <v>1821.15</v>
       </c>
       <c r="T6">
-        <v>-15</v>
+        <v>-15.19</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1436,34 +1408,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>25.56</v>
+        <v>25.16</v>
       </c>
       <c r="Z6">
-        <v>-91.38</v>
+        <v>-90.59</v>
       </c>
       <c r="AA6">
-        <v>-88.92</v>
+        <v>-89.25</v>
       </c>
       <c r="AB6">
-        <v>-2.46</v>
+        <v>-1.34</v>
       </c>
       <c r="AC6">
-        <v>14.23</v>
+        <v>21.19</v>
       </c>
       <c r="AD6">
-        <v>21.92</v>
+        <v>18.46</v>
       </c>
       <c r="AE6">
-        <v>47.87</v>
+        <v>46.8</v>
       </c>
       <c r="AF6">
-        <v>-54.2</v>
+        <v>-53.87</v>
       </c>
       <c r="AG6">
-        <v>1809.86</v>
+        <v>1764.63</v>
       </c>
       <c r="AH6">
-        <v>1509.32</v>
+        <v>1521.8</v>
       </c>
       <c r="AI6">
         <v>1690.77</v>
@@ -1472,7 +1444,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>65.55</v>
+        <v>65.95</v>
       </c>
     </row>
   </sheetData>
@@ -1633,47 +1605,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1681,734 +1618,734 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>29.4</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>10.03</v>
       </c>
-      <c r="E7" s="7">
-        <v>-19.37</v>
+      <c r="D7" s="5">
+        <v>-3.96</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-13.99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-3.84</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-6.7</v>
       </c>
+      <c r="D8" s="5">
+        <v>-6.62</v>
+      </c>
       <c r="E8" s="7">
-        <v>-2.86</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>0.36</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-0.52</v>
       </c>
-      <c r="E9" s="7">
+      <c r="D9" s="5">
+        <v>-1.36</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-13.86</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-13.02</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-18.7</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-16.83</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2.92</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2.55</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-0.55</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-1.7</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-3.35</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-5.23</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-2.87</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-3.46</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-8.69</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-7.75</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-6.83</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-6.54</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-23.99</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-25.07</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-12.52</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-10.87</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-24.63</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-25.51</v>
+      </c>
+      <c r="E21" s="6">
         <v>-0.88</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>5.82</v>
+      </c>
+      <c r="D22" s="5">
+        <v>6.44</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>11.79</v>
+      </c>
+      <c r="D23" s="5">
+        <v>11.43</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-20.94</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-20.27</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-13.57</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-13.86</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-30.49</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-28.69</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-20.2</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-18.7</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-27.33</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-28.58</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-1.11</v>
-      </c>
-      <c r="D12" s="6">
-        <v>2.92</v>
-      </c>
-      <c r="E12" s="8">
-        <v>4.03</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-20.62</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-20.45</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>2.63</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-0.55</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-3.18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-7.04</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-6.81</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>1.76</v>
-      </c>
-      <c r="D14" s="6">
-        <v>2.44</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-30.74</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-31.42</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-30.49</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-30.46</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-33.2</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-33.44</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>729.3</v>
+      </c>
+      <c r="D32" s="5">
+        <v>730.85</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>628.45</v>
+      </c>
+      <c r="D33" s="5">
+        <v>630</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>860.5</v>
+      </c>
+      <c r="D34" s="5">
+        <v>852.05</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-8.449999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>985.4</v>
+      </c>
+      <c r="D35" s="5">
+        <v>985.8</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1550</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1544.5</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="5">
+        <v>99</v>
+      </c>
+      <c r="D37" s="5">
+        <v>79</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="5">
+        <v>79</v>
+      </c>
+      <c r="D38" s="5">
+        <v>99</v>
+      </c>
+      <c r="E38" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>54.91</v>
+      </c>
+      <c r="D39" s="5">
+        <v>55.13</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>45.74</v>
+      </c>
+      <c r="D40" s="5">
+        <v>46.42</v>
+      </c>
+      <c r="E40" s="7">
         <v>0.68</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>41.98</v>
+      </c>
+      <c r="D41" s="5">
+        <v>39.14</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-2.84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-3.56</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-3.35</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="5">
+        <v>24.92</v>
+      </c>
+      <c r="D42" s="5">
+        <v>25.07</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-5.8</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-2.87</v>
-      </c>
-      <c r="E16" s="8">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>25.56</v>
+      </c>
+      <c r="D43" s="5">
+        <v>25.16</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-10.17</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-8.69</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-94.44</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-95.84</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-7.31</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-6.83</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-52.18</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-69.26000000000001</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-17.08</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-23.68</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-23.99</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-39.91</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-65.83</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-25.92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-13.68</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-12.52</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-40.42</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-71.04000000000001</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-30.62</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-24.55</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-24.63</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>4.09</v>
-      </c>
-      <c r="D22" s="6">
-        <v>5.82</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>13.87</v>
-      </c>
-      <c r="D23" s="6">
-        <v>11.79</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2.08</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-20.45</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-20.94</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-17.78</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-30.49</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-12.71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-24.43</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-27.33</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-22.2</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-20.62</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-5.34</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-7.04</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-30.38</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-30.74</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-29.29</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-30.49</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-33.89</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-33.2</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>714.75</v>
-      </c>
-      <c r="D32" s="6">
-        <v>729.3</v>
-      </c>
-      <c r="E32" s="8">
-        <v>14.55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>639.95</v>
-      </c>
-      <c r="D33" s="6">
-        <v>628.45</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-11.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>865</v>
-      </c>
-      <c r="D34" s="6">
-        <v>860.5</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-4.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1002.4</v>
-      </c>
-      <c r="D35" s="6">
-        <v>985.4</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>1534</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1550</v>
-      </c>
-      <c r="E36" s="8">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="6">
-        <v>40</v>
-      </c>
-      <c r="D37" s="6">
-        <v>60</v>
-      </c>
-      <c r="E37" s="8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="6">
-        <v>60</v>
-      </c>
-      <c r="D38" s="6">
-        <v>40</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>52.93</v>
-      </c>
-      <c r="D39" s="6">
-        <v>54.91</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>50.11</v>
-      </c>
-      <c r="D40" s="6">
-        <v>45.74</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-4.37</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>43.54</v>
-      </c>
-      <c r="D41" s="6">
-        <v>41.98</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>26.98</v>
-      </c>
-      <c r="D42" s="6">
-        <v>24.92</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>22.16</v>
-      </c>
-      <c r="D43" s="6">
-        <v>25.56</v>
-      </c>
-      <c r="E43" s="8">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
+      <c r="B48" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="6">
-        <v>-94.28</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-94.44</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>50.32</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-52.18</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-102.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-19.92</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-39.91</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-19.99</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>68.48999999999999</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-40.42</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-108.91</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>35.57</v>
-      </c>
-      <c r="D48" s="6">
+      <c r="C48" s="5">
         <v>-54.2</v>
       </c>
+      <c r="D48" s="5">
+        <v>-53.87</v>
+      </c>
       <c r="E48" s="7">
-        <v>-89.77</v>
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>
@@ -2434,60 +2371,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>49.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>38.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>38.2</v>
+      </c>
+      <c r="E2" s="10">
         <v>40</v>
       </c>
-      <c r="F2" s="11">
-        <v>-6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-12.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-8.4</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-11.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2589,37 +2526,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
+      <c r="A2" s="13">
         <v>0.1126</v>
       </c>
-      <c r="B2" s="14">
-        <v>0.0141</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0254</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0814</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1056</v>
+      <c r="B2" s="13">
+        <v>0.0149</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0277</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.08710000000000001</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1074</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>25.2 → 35.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>25.2</t>
+  </si>
+  <si>
+    <t>35.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -252,14 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,14 +395,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -890,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>730.85</v>
+        <v>725.4</v>
       </c>
       <c r="D2">
-        <v>0.21</v>
+        <v>-0.75</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,22 +930,22 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-20.45</v>
+        <v>-21.04</v>
       </c>
       <c r="H2">
-        <v>40.05</v>
+        <v>39.01</v>
       </c>
       <c r="I2">
-        <v>2.55</v>
+        <v>2.94</v>
       </c>
       <c r="J2">
-        <v>-3.96</v>
+        <v>1.34</v>
       </c>
       <c r="K2">
-        <v>6.44</v>
+        <v>6.29</v>
       </c>
       <c r="L2">
-        <v>-7.75</v>
+        <v>-7.4</v>
       </c>
       <c r="M2">
         <v>-10.74</v>
@@ -926,22 +954,22 @@
         <v>79</v>
       </c>
       <c r="O2">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="P2">
-        <v>725.5599999999999</v>
+        <v>729.7</v>
       </c>
       <c r="Q2">
-        <v>721.8200000000001</v>
+        <v>723.1</v>
       </c>
       <c r="R2">
-        <v>653.85</v>
+        <v>655.25</v>
       </c>
       <c r="S2">
-        <v>668.21</v>
+        <v>668.1900000000001</v>
       </c>
       <c r="T2">
-        <v>9.369999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -956,34 +984,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>55.13</v>
+        <v>54.15</v>
       </c>
       <c r="Z2">
-        <v>19.31</v>
+        <v>18.26</v>
       </c>
       <c r="AA2">
-        <v>22.29</v>
+        <v>21.49</v>
       </c>
       <c r="AB2">
-        <v>-2.98</v>
+        <v>-3.22</v>
       </c>
       <c r="AC2">
-        <v>14.99</v>
+        <v>20.57</v>
       </c>
       <c r="AD2">
-        <v>17.96</v>
+        <v>19.21</v>
       </c>
       <c r="AE2">
-        <v>44.33</v>
+        <v>42.96</v>
       </c>
       <c r="AF2">
-        <v>-95.84</v>
+        <v>-87.09999999999999</v>
       </c>
       <c r="AG2">
-        <v>780.95</v>
+        <v>781.33</v>
       </c>
       <c r="AH2">
-        <v>662.6900000000001</v>
+        <v>664.87</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -992,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>41.23</v>
+        <v>39.01</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,10 +1031,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>630</v>
+        <v>633.75</v>
       </c>
       <c r="D3">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="E3">
         <v>676.05</v>
@@ -1015,46 +1043,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-6.81</v>
+        <v>-6.26</v>
       </c>
       <c r="H3">
-        <v>22.81</v>
+        <v>23.54</v>
       </c>
       <c r="I3">
-        <v>-1.7</v>
+        <v>-2.21</v>
       </c>
       <c r="J3">
-        <v>-6.62</v>
+        <v>-5.84</v>
       </c>
       <c r="K3">
-        <v>11.43</v>
+        <v>12.95</v>
       </c>
       <c r="L3">
-        <v>-6.54</v>
+        <v>-5.66</v>
       </c>
       <c r="M3">
-        <v>1.49</v>
+        <v>0.72</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P3">
-        <v>637.22</v>
+        <v>634.35</v>
       </c>
       <c r="Q3">
-        <v>647.9400000000001</v>
+        <v>645.83</v>
       </c>
       <c r="R3">
-        <v>619.16</v>
+        <v>620.7</v>
       </c>
       <c r="S3">
-        <v>587.3200000000001</v>
+        <v>587.63</v>
       </c>
       <c r="T3">
-        <v>7.27</v>
+        <v>7.85</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1069,34 +1097,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>46.42</v>
+        <v>48.11</v>
       </c>
       <c r="Z3">
-        <v>1.02</v>
+        <v>0.46</v>
       </c>
       <c r="AA3">
-        <v>5.69</v>
+        <v>4.65</v>
       </c>
       <c r="AB3">
-        <v>-4.67</v>
+        <v>-4.18</v>
       </c>
       <c r="AC3">
-        <v>16.06</v>
+        <v>12.73</v>
       </c>
       <c r="AD3">
-        <v>24.15</v>
+        <v>16.92</v>
       </c>
       <c r="AE3">
-        <v>20.99</v>
+        <v>20.66</v>
       </c>
       <c r="AF3">
-        <v>-69.26000000000001</v>
+        <v>-73.93000000000001</v>
       </c>
       <c r="AG3">
-        <v>679.09</v>
+        <v>674.64</v>
       </c>
       <c r="AH3">
-        <v>616.79</v>
+        <v>617.03</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1105,7 +1133,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>15.43</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>852.05</v>
+        <v>868.75</v>
       </c>
       <c r="D4">
-        <v>-0.98</v>
+        <v>1.96</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1128,46 +1156,46 @@
         <v>837</v>
       </c>
       <c r="G4">
-        <v>-31.42</v>
+        <v>-30.07</v>
       </c>
       <c r="H4">
-        <v>1.8</v>
+        <v>3.79</v>
       </c>
       <c r="I4">
-        <v>1.8</v>
+        <v>-0.43</v>
       </c>
       <c r="J4">
-        <v>-1.36</v>
+        <v>-0.13</v>
       </c>
       <c r="K4">
-        <v>-20.27</v>
+        <v>-18.17</v>
       </c>
       <c r="L4">
-        <v>-25.07</v>
+        <v>-22.11</v>
       </c>
       <c r="M4">
-        <v>-2.77</v>
+        <v>-2.99</v>
       </c>
       <c r="N4">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P4">
-        <v>863.12</v>
+        <v>862.37</v>
       </c>
       <c r="Q4">
-        <v>863.97</v>
+        <v>864.16</v>
       </c>
       <c r="R4">
-        <v>915.0700000000001</v>
+        <v>911.04</v>
       </c>
       <c r="S4">
-        <v>1051.93</v>
+        <v>1050.34</v>
       </c>
       <c r="T4">
-        <v>-19</v>
+        <v>-17.29</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1182,34 +1210,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.14</v>
+        <v>46.79</v>
       </c>
       <c r="Z4">
-        <v>-14.86</v>
+        <v>-13.14</v>
       </c>
       <c r="AA4">
-        <v>-18.41</v>
+        <v>-17.36</v>
       </c>
       <c r="AB4">
-        <v>3.55</v>
+        <v>4.21</v>
       </c>
       <c r="AC4">
-        <v>74.98</v>
+        <v>79.61</v>
       </c>
       <c r="AD4">
-        <v>83.20999999999999</v>
+        <v>79.38</v>
       </c>
       <c r="AE4">
-        <v>18.66</v>
+        <v>18.95</v>
       </c>
       <c r="AF4">
-        <v>-65.83</v>
+        <v>-5.76</v>
       </c>
       <c r="AG4">
-        <v>888.88</v>
+        <v>889.15</v>
       </c>
       <c r="AH4">
-        <v>839.0700000000001</v>
+        <v>839.17</v>
       </c>
       <c r="AI4">
         <v>891.26</v>
@@ -1218,7 +1246,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>26.16</v>
+        <v>26.48</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>985.8</v>
+        <v>998</v>
       </c>
       <c r="D5">
-        <v>0.04</v>
+        <v>1.24</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,46 +1269,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-30.46</v>
+        <v>-29.6</v>
       </c>
       <c r="H5">
-        <v>31.62</v>
+        <v>33.24</v>
       </c>
       <c r="I5">
-        <v>-5.23</v>
+        <v>-4.5</v>
       </c>
       <c r="J5">
-        <v>-13.02</v>
+        <v>-11.08</v>
       </c>
       <c r="K5">
-        <v>-28.69</v>
+        <v>-25.34</v>
       </c>
       <c r="L5">
-        <v>-10.87</v>
+        <v>-6.89</v>
       </c>
       <c r="M5">
-        <v>11.26</v>
+        <v>11.55</v>
       </c>
       <c r="N5">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O5">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P5">
-        <v>1009.52</v>
+        <v>1000.12</v>
       </c>
       <c r="Q5">
-        <v>1069.61</v>
+        <v>1063.17</v>
       </c>
       <c r="R5">
-        <v>1157.04</v>
+        <v>1150.65</v>
       </c>
       <c r="S5">
-        <v>1072.92</v>
+        <v>1072.88</v>
       </c>
       <c r="T5">
-        <v>-8.119999999999999</v>
+        <v>-6.98</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1295,43 +1323,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>25.07</v>
+        <v>29.52</v>
       </c>
       <c r="Z5">
-        <v>-44.54</v>
+        <v>-44.19</v>
       </c>
       <c r="AA5">
-        <v>-39.24</v>
+        <v>-40.23</v>
       </c>
       <c r="AB5">
-        <v>-5.3</v>
+        <v>-3.96</v>
       </c>
       <c r="AC5">
-        <v>8.26</v>
+        <v>14.63</v>
       </c>
       <c r="AD5">
-        <v>21.81</v>
+        <v>14.45</v>
       </c>
       <c r="AE5">
-        <v>36.82</v>
+        <v>36.04</v>
       </c>
       <c r="AF5">
-        <v>-71.04000000000001</v>
+        <v>17.97</v>
       </c>
       <c r="AG5">
-        <v>1166.38</v>
+        <v>1161.05</v>
       </c>
       <c r="AH5">
-        <v>972.84</v>
+        <v>965.29</v>
       </c>
       <c r="AI5">
-        <v>1105.62</v>
+        <v>1101.68</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>38.52</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1544.5</v>
+        <v>1594.3</v>
       </c>
       <c r="D6">
-        <v>-0.35</v>
+        <v>3.22</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,46 +1382,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-33.44</v>
+        <v>-31.29</v>
       </c>
       <c r="H6">
-        <v>4.98</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="I6">
-        <v>-3.46</v>
+        <v>-0.98</v>
       </c>
       <c r="J6">
-        <v>-16.83</v>
+        <v>-14.83</v>
       </c>
       <c r="K6">
-        <v>-28.58</v>
+        <v>-24.35</v>
       </c>
       <c r="L6">
-        <v>-25.51</v>
+        <v>-21.59</v>
       </c>
       <c r="M6">
-        <v>-8.710000000000001</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="N6">
         <v>21</v>
       </c>
       <c r="O6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P6">
-        <v>1563.74</v>
+        <v>1560.6</v>
       </c>
       <c r="Q6">
-        <v>1643.22</v>
+        <v>1635.53</v>
       </c>
       <c r="R6">
-        <v>1867.29</v>
+        <v>1857.06</v>
       </c>
       <c r="S6">
-        <v>1821.15</v>
+        <v>1819.03</v>
       </c>
       <c r="T6">
-        <v>-15.19</v>
+        <v>-12.35</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1408,34 +1436,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>25.16</v>
+        <v>35.2</v>
       </c>
       <c r="Z6">
-        <v>-90.59</v>
+        <v>-84.97</v>
       </c>
       <c r="AA6">
-        <v>-89.25</v>
+        <v>-88.40000000000001</v>
       </c>
       <c r="AB6">
-        <v>-1.34</v>
+        <v>3.43</v>
       </c>
       <c r="AC6">
-        <v>21.19</v>
+        <v>54.53</v>
       </c>
       <c r="AD6">
-        <v>18.46</v>
+        <v>29.98</v>
       </c>
       <c r="AE6">
-        <v>46.8</v>
+        <v>47.77</v>
       </c>
       <c r="AF6">
-        <v>-53.87</v>
+        <v>-40.06</v>
       </c>
       <c r="AG6">
-        <v>1764.63</v>
+        <v>1748.15</v>
       </c>
       <c r="AH6">
-        <v>1521.8</v>
+        <v>1522.91</v>
       </c>
       <c r="AI6">
         <v>1690.77</v>
@@ -1444,7 +1472,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>65.95</v>
+        <v>62.09</v>
       </c>
     </row>
   </sheetData>
@@ -1605,12 +1633,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1618,734 +1681,734 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>10.03</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-3.96</v>
       </c>
-      <c r="E7" s="6">
-        <v>-13.99</v>
+      <c r="D7" s="6">
+        <v>1.34</v>
+      </c>
+      <c r="E7" s="7">
+        <v>5.3</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-6.7</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-6.62</v>
       </c>
+      <c r="D8" s="6">
+        <v>-5.84</v>
+      </c>
       <c r="E8" s="7">
-        <v>0.08</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-0.52</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-1.36</v>
       </c>
-      <c r="E9" s="6">
-        <v>-0.84</v>
+      <c r="D9" s="6">
+        <v>-0.13</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.23</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-13.86</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-13.02</v>
       </c>
+      <c r="D10" s="6">
+        <v>-11.08</v>
+      </c>
       <c r="E10" s="7">
-        <v>0.84</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-18.7</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-16.83</v>
       </c>
+      <c r="D11" s="6">
+        <v>-14.83</v>
+      </c>
       <c r="E11" s="7">
-        <v>1.87</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>2.92</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>2.55</v>
       </c>
-      <c r="E12" s="6">
-        <v>-0.37</v>
+      <c r="D12" s="6">
+        <v>2.94</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.39</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-0.55</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-1.7</v>
       </c>
-      <c r="E13" s="6">
-        <v>-1.15</v>
+      <c r="D13" s="6">
+        <v>-2.21</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>2.44</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>1.8</v>
       </c>
-      <c r="E14" s="6">
-        <v>-0.64</v>
+      <c r="D14" s="6">
+        <v>-0.43</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-2.23</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-3.35</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-5.23</v>
       </c>
-      <c r="E15" s="6">
-        <v>-1.88</v>
+      <c r="D15" s="6">
+        <v>-4.5</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.73</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-2.87</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-3.46</v>
       </c>
-      <c r="E16" s="6">
+      <c r="D16" s="6">
+        <v>-0.98</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-7.75</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-7.4</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-6.54</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-5.66</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-25.07</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-22.11</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-10.87</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-6.89</v>
+      </c>
+      <c r="E20" s="7">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-25.51</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-21.59</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6">
+        <v>6.44</v>
+      </c>
+      <c r="D22" s="6">
+        <v>6.29</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>11.43</v>
+      </c>
+      <c r="D23" s="6">
+        <v>12.95</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-20.27</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-18.17</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-28.69</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-25.34</v>
+      </c>
+      <c r="E25" s="7">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-28.58</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-24.35</v>
+      </c>
+      <c r="E26" s="7">
+        <v>4.23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-20.45</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-21.04</v>
+      </c>
+      <c r="E27" s="8">
         <v>-0.59</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-6.81</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-6.26</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-31.42</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-30.07</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-30.46</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-29.6</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-33.44</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-31.29</v>
+      </c>
+      <c r="E31" s="7">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-8.69</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-7.75</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6">
+        <v>730.85</v>
+      </c>
+      <c r="D32" s="6">
+        <v>725.4</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-5.45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-6.83</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-6.54</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>630</v>
+      </c>
+      <c r="D33" s="6">
+        <v>633.75</v>
+      </c>
+      <c r="E33" s="7">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-23.99</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-25.07</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>852.05</v>
+      </c>
+      <c r="D34" s="6">
+        <v>868.75</v>
+      </c>
+      <c r="E34" s="7">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-12.52</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-10.87</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>985.8</v>
+      </c>
+      <c r="D35" s="6">
+        <v>998</v>
+      </c>
+      <c r="E35" s="7">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-24.63</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-25.51</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5">
-        <v>5.82</v>
-      </c>
-      <c r="D22" s="5">
-        <v>6.44</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5">
-        <v>11.79</v>
-      </c>
-      <c r="D23" s="5">
-        <v>11.43</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>1544.5</v>
+      </c>
+      <c r="D36" s="6">
+        <v>1594.3</v>
+      </c>
+      <c r="E36" s="7">
+        <v>49.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-20.94</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-20.27</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="6">
+        <v>60</v>
+      </c>
+      <c r="D37" s="6">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-30.49</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-28.69</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-27.33</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-28.58</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-20.62</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-20.45</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-7.04</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-6.81</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-30.74</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-31.42</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="E37" s="8">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-30.49</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-30.46</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-33.2</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-33.44</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>729.3</v>
-      </c>
-      <c r="D32" s="5">
-        <v>730.85</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>628.45</v>
-      </c>
-      <c r="D33" s="5">
-        <v>630</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>860.5</v>
-      </c>
-      <c r="D34" s="5">
-        <v>852.05</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-8.449999999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="6">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5">
-        <v>985.4</v>
-      </c>
-      <c r="D35" s="5">
-        <v>985.8</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
-        <v>1550</v>
-      </c>
-      <c r="D36" s="5">
-        <v>1544.5</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="5">
-        <v>99</v>
-      </c>
-      <c r="D37" s="5">
-        <v>79</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="5">
-        <v>79</v>
-      </c>
-      <c r="D38" s="5">
-        <v>99</v>
+      <c r="D38" s="6">
+        <v>60</v>
       </c>
       <c r="E38" s="7">
         <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="5">
-        <v>54.91</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="C39" s="6">
         <v>55.13</v>
       </c>
-      <c r="E39" s="7">
-        <v>0.22</v>
+      <c r="D39" s="6">
+        <v>54.15</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="5">
-        <v>45.74</v>
-      </c>
-      <c r="D40" s="5">
+      <c r="C40" s="6">
         <v>46.42</v>
       </c>
+      <c r="D40" s="6">
+        <v>48.11</v>
+      </c>
       <c r="E40" s="7">
-        <v>0.68</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="5">
-        <v>41.98</v>
-      </c>
-      <c r="D41" s="5">
+      <c r="C41" s="6">
         <v>39.14</v>
       </c>
-      <c r="E41" s="6">
-        <v>-2.84</v>
+      <c r="D41" s="6">
+        <v>46.79</v>
+      </c>
+      <c r="E41" s="7">
+        <v>7.65</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="5">
-        <v>24.92</v>
-      </c>
-      <c r="D42" s="5">
+      <c r="C42" s="6">
         <v>25.07</v>
       </c>
+      <c r="D42" s="6">
+        <v>29.52</v>
+      </c>
       <c r="E42" s="7">
-        <v>0.15</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="5">
-        <v>25.56</v>
-      </c>
-      <c r="D43" s="5">
+      <c r="C43" s="6">
         <v>25.16</v>
       </c>
-      <c r="E43" s="6">
-        <v>-0.4</v>
+      <c r="D43" s="6">
+        <v>35.2</v>
+      </c>
+      <c r="E43" s="7">
+        <v>10.04</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="5">
-        <v>-94.44</v>
-      </c>
-      <c r="D44" s="5">
+      <c r="C44" s="6">
         <v>-95.84</v>
       </c>
-      <c r="E44" s="6">
-        <v>-1.4</v>
+      <c r="D44" s="6">
+        <v>-87.09999999999999</v>
+      </c>
+      <c r="E44" s="7">
+        <v>8.74</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="5">
-        <v>-52.18</v>
-      </c>
-      <c r="D45" s="5">
+      <c r="C45" s="6">
         <v>-69.26000000000001</v>
       </c>
-      <c r="E45" s="6">
-        <v>-17.08</v>
+      <c r="D45" s="6">
+        <v>-73.93000000000001</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-4.67</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C46" s="5">
-        <v>-39.91</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C46" s="6">
         <v>-65.83</v>
       </c>
-      <c r="E46" s="6">
-        <v>-25.92</v>
+      <c r="D46" s="6">
+        <v>-5.76</v>
+      </c>
+      <c r="E46" s="7">
+        <v>60.07</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="5">
-        <v>-40.42</v>
-      </c>
-      <c r="D47" s="5">
+      <c r="C47" s="6">
         <v>-71.04000000000001</v>
       </c>
-      <c r="E47" s="6">
-        <v>-30.62</v>
+      <c r="D47" s="6">
+        <v>17.97</v>
+      </c>
+      <c r="E47" s="7">
+        <v>89.01000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C48" s="5">
-        <v>-54.2</v>
-      </c>
-      <c r="D48" s="5">
+      <c r="C48" s="6">
         <v>-53.87</v>
       </c>
+      <c r="D48" s="6">
+        <v>-40.06</v>
+      </c>
       <c r="E48" s="7">
-        <v>0.33</v>
+        <v>13.81</v>
       </c>
     </row>
   </sheetData>
@@ -2371,60 +2434,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>49.92</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>38.2</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>42.8</v>
+      </c>
+      <c r="E2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="10">
-        <v>-8.4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-11.9</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-6.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2526,36 +2589,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.1126</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0149</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0277</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.08710000000000001</v>
-      </c>
-      <c r="E2" s="13">
+      <c r="A2" s="14">
+        <v>0.1155</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0072</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0299</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.083</v>
+      </c>
+      <c r="E2" s="14">
         <v>-0.1074</v>
       </c>
     </row>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -184,16 +184,16 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>25.2 → 35.2</t>
+    <t>29.5 → 31.7</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>25.2</t>
-  </si>
-  <si>
-    <t>35.2</t>
+    <t>29.5</t>
+  </si>
+  <si>
+    <t>31.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -918,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>725.4</v>
+        <v>721.35</v>
       </c>
       <c r="D2">
-        <v>-0.75</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -930,46 +930,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-21.04</v>
+        <v>-21.49</v>
       </c>
       <c r="H2">
-        <v>39.01</v>
+        <v>38.23</v>
       </c>
       <c r="I2">
-        <v>2.94</v>
+        <v>-3.59</v>
       </c>
       <c r="J2">
-        <v>1.34</v>
+        <v>3.08</v>
       </c>
       <c r="K2">
-        <v>6.29</v>
+        <v>5.66</v>
       </c>
       <c r="L2">
-        <v>-7.4</v>
+        <v>-5.53</v>
       </c>
       <c r="M2">
-        <v>-10.74</v>
+        <v>-10.87</v>
       </c>
       <c r="N2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P2">
-        <v>729.7</v>
+        <v>724.33</v>
       </c>
       <c r="Q2">
-        <v>723.1</v>
+        <v>725.48</v>
       </c>
       <c r="R2">
-        <v>655.25</v>
+        <v>657.11</v>
       </c>
       <c r="S2">
-        <v>668.1900000000001</v>
+        <v>668.21</v>
       </c>
       <c r="T2">
-        <v>8.56</v>
+        <v>7.95</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -984,34 +984,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>54.15</v>
+        <v>53.38</v>
       </c>
       <c r="Z2">
-        <v>18.26</v>
+        <v>16.91</v>
       </c>
       <c r="AA2">
-        <v>21.49</v>
+        <v>20.57</v>
       </c>
       <c r="AB2">
-        <v>-3.22</v>
+        <v>-3.66</v>
       </c>
       <c r="AC2">
-        <v>20.57</v>
+        <v>21.42</v>
       </c>
       <c r="AD2">
-        <v>19.21</v>
+        <v>18.99</v>
       </c>
       <c r="AE2">
-        <v>42.96</v>
+        <v>41.67</v>
       </c>
       <c r="AF2">
-        <v>-87.09999999999999</v>
+        <v>-94.34</v>
       </c>
       <c r="AG2">
-        <v>781.33</v>
+        <v>778.9</v>
       </c>
       <c r="AH2">
-        <v>664.87</v>
+        <v>672.0599999999999</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -1020,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>39.01</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,10 +1031,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>633.75</v>
+        <v>627.9</v>
       </c>
       <c r="D3">
-        <v>0.6</v>
+        <v>-0.92</v>
       </c>
       <c r="E3">
         <v>676.05</v>
@@ -1043,46 +1043,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-6.26</v>
+        <v>-7.12</v>
       </c>
       <c r="H3">
-        <v>23.54</v>
+        <v>22.4</v>
       </c>
       <c r="I3">
-        <v>-2.21</v>
+        <v>-1.83</v>
       </c>
       <c r="J3">
-        <v>-5.84</v>
+        <v>-7.09</v>
       </c>
       <c r="K3">
-        <v>12.95</v>
+        <v>8.93</v>
       </c>
       <c r="L3">
-        <v>-5.66</v>
+        <v>-5.9</v>
       </c>
       <c r="M3">
-        <v>0.72</v>
+        <v>0.98</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O3">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P3">
-        <v>634.35</v>
+        <v>632.01</v>
       </c>
       <c r="Q3">
-        <v>645.83</v>
+        <v>644.96</v>
       </c>
       <c r="R3">
-        <v>620.7</v>
+        <v>621.96</v>
       </c>
       <c r="S3">
-        <v>587.63</v>
+        <v>587.9400000000001</v>
       </c>
       <c r="T3">
-        <v>7.85</v>
+        <v>6.8</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1097,34 +1097,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>48.11</v>
+        <v>45.69</v>
       </c>
       <c r="Z3">
-        <v>0.46</v>
+        <v>-0.44</v>
       </c>
       <c r="AA3">
-        <v>4.65</v>
+        <v>3.63</v>
       </c>
       <c r="AB3">
-        <v>-4.18</v>
+        <v>-4.07</v>
       </c>
       <c r="AC3">
-        <v>12.73</v>
+        <v>12.64</v>
       </c>
       <c r="AD3">
-        <v>16.92</v>
+        <v>13.81</v>
       </c>
       <c r="AE3">
-        <v>20.66</v>
+        <v>20.65</v>
       </c>
       <c r="AF3">
-        <v>-73.93000000000001</v>
+        <v>-49.52</v>
       </c>
       <c r="AG3">
-        <v>674.64</v>
+        <v>674.87</v>
       </c>
       <c r="AH3">
-        <v>617.03</v>
+        <v>615.0599999999999</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1133,7 +1133,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>15.82</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>868.75</v>
+        <v>871.3</v>
       </c>
       <c r="D4">
-        <v>1.96</v>
+        <v>0.29</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1156,25 +1156,25 @@
         <v>837</v>
       </c>
       <c r="G4">
-        <v>-30.07</v>
+        <v>-29.87</v>
       </c>
       <c r="H4">
-        <v>3.79</v>
+        <v>4.1</v>
       </c>
       <c r="I4">
-        <v>-0.43</v>
+        <v>0.66</v>
       </c>
       <c r="J4">
-        <v>-0.13</v>
+        <v>0.73</v>
       </c>
       <c r="K4">
-        <v>-18.17</v>
+        <v>-17.23</v>
       </c>
       <c r="L4">
-        <v>-22.11</v>
+        <v>-21.75</v>
       </c>
       <c r="M4">
-        <v>-2.99</v>
+        <v>-2.56</v>
       </c>
       <c r="N4">
         <v>40</v>
@@ -1183,19 +1183,19 @@
         <v>30</v>
       </c>
       <c r="P4">
-        <v>862.37</v>
+        <v>863.52</v>
       </c>
       <c r="Q4">
-        <v>864.16</v>
+        <v>864.87</v>
       </c>
       <c r="R4">
-        <v>911.04</v>
+        <v>906.75</v>
       </c>
       <c r="S4">
-        <v>1050.34</v>
+        <v>1048.79</v>
       </c>
       <c r="T4">
-        <v>-17.29</v>
+        <v>-16.92</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1210,34 +1210,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>46.79</v>
+        <v>47.87</v>
       </c>
       <c r="Z4">
-        <v>-13.14</v>
+        <v>-11.45</v>
       </c>
       <c r="AA4">
-        <v>-17.36</v>
+        <v>-16.17</v>
       </c>
       <c r="AB4">
-        <v>4.21</v>
+        <v>4.73</v>
       </c>
       <c r="AC4">
-        <v>79.61</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="AD4">
-        <v>79.38</v>
+        <v>80.58</v>
       </c>
       <c r="AE4">
-        <v>18.95</v>
+        <v>18.9</v>
       </c>
       <c r="AF4">
-        <v>-5.76</v>
+        <v>29.4</v>
       </c>
       <c r="AG4">
-        <v>889.15</v>
+        <v>889.8200000000001</v>
       </c>
       <c r="AH4">
-        <v>839.17</v>
+        <v>839.9299999999999</v>
       </c>
       <c r="AI4">
         <v>891.26</v>
@@ -1246,7 +1246,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>26.48</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="D5">
-        <v>1.24</v>
+        <v>0.6</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1269,46 +1269,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-29.6</v>
+        <v>-29.18</v>
       </c>
       <c r="H5">
-        <v>33.24</v>
+        <v>34.05</v>
       </c>
       <c r="I5">
-        <v>-4.5</v>
+        <v>-2.43</v>
       </c>
       <c r="J5">
-        <v>-11.08</v>
+        <v>-10.9</v>
       </c>
       <c r="K5">
-        <v>-25.34</v>
+        <v>-27.21</v>
       </c>
       <c r="L5">
-        <v>-6.89</v>
+        <v>-5.82</v>
       </c>
       <c r="M5">
-        <v>11.55</v>
+        <v>12.02</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="P5">
-        <v>1000.12</v>
+        <v>995.12</v>
       </c>
       <c r="Q5">
-        <v>1063.17</v>
+        <v>1058.17</v>
       </c>
       <c r="R5">
-        <v>1150.65</v>
+        <v>1143.98</v>
       </c>
       <c r="S5">
         <v>1072.88</v>
       </c>
       <c r="T5">
-        <v>-6.98</v>
+        <v>-6.42</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1323,34 +1323,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>29.52</v>
+        <v>31.67</v>
       </c>
       <c r="Z5">
-        <v>-44.19</v>
+        <v>-42.93</v>
       </c>
       <c r="AA5">
-        <v>-40.23</v>
+        <v>-40.77</v>
       </c>
       <c r="AB5">
-        <v>-3.96</v>
+        <v>-2.16</v>
       </c>
       <c r="AC5">
-        <v>14.63</v>
+        <v>31.49</v>
       </c>
       <c r="AD5">
-        <v>14.45</v>
+        <v>18.13</v>
       </c>
       <c r="AE5">
-        <v>36.04</v>
+        <v>34.75</v>
       </c>
       <c r="AF5">
-        <v>17.97</v>
+        <v>-69.39</v>
       </c>
       <c r="AG5">
-        <v>1161.05</v>
+        <v>1157.47</v>
       </c>
       <c r="AH5">
-        <v>965.29</v>
+        <v>958.87</v>
       </c>
       <c r="AI5">
         <v>1101.68</v>
@@ -1359,7 +1359,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>40.25</v>
+        <v>40.36</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1594.3</v>
+        <v>1572.5</v>
       </c>
       <c r="D6">
-        <v>3.22</v>
+        <v>-1.37</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1382,46 +1382,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-31.29</v>
+        <v>-32.23</v>
       </c>
       <c r="H6">
-        <v>8.359999999999999</v>
+        <v>6.88</v>
       </c>
       <c r="I6">
-        <v>-0.98</v>
+        <v>-0.49</v>
       </c>
       <c r="J6">
-        <v>-14.83</v>
+        <v>-10.04</v>
       </c>
       <c r="K6">
-        <v>-24.35</v>
+        <v>-25.28</v>
       </c>
       <c r="L6">
-        <v>-21.59</v>
+        <v>-22.59</v>
       </c>
       <c r="M6">
-        <v>-8.300000000000001</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="N6">
         <v>21</v>
       </c>
       <c r="O6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P6">
-        <v>1560.6</v>
+        <v>1559.06</v>
       </c>
       <c r="Q6">
-        <v>1635.53</v>
+        <v>1631.19</v>
       </c>
       <c r="R6">
-        <v>1857.06</v>
+        <v>1846.72</v>
       </c>
       <c r="S6">
-        <v>1819.03</v>
+        <v>1816.86</v>
       </c>
       <c r="T6">
-        <v>-12.35</v>
+        <v>-13.45</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1436,34 +1436,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>35.2</v>
+        <v>33.11</v>
       </c>
       <c r="Z6">
-        <v>-84.97</v>
+        <v>-81.33</v>
       </c>
       <c r="AA6">
-        <v>-88.40000000000001</v>
+        <v>-86.98</v>
       </c>
       <c r="AB6">
-        <v>3.43</v>
+        <v>5.65</v>
       </c>
       <c r="AC6">
-        <v>54.53</v>
+        <v>71.23</v>
       </c>
       <c r="AD6">
-        <v>29.98</v>
+        <v>48.98</v>
       </c>
       <c r="AE6">
-        <v>47.77</v>
+        <v>46.91</v>
       </c>
       <c r="AF6">
-        <v>-40.06</v>
+        <v>-24.27</v>
       </c>
       <c r="AG6">
-        <v>1748.15</v>
+        <v>1746.61</v>
       </c>
       <c r="AH6">
-        <v>1522.91</v>
+        <v>1515.77</v>
       </c>
       <c r="AI6">
         <v>1690.77</v>
@@ -1472,7 +1472,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>62.09</v>
+        <v>58.75</v>
       </c>
     </row>
   </sheetData>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1705,13 +1705,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-3.96</v>
+        <v>1.34</v>
       </c>
       <c r="D7" s="6">
-        <v>1.34</v>
+        <v>3.08</v>
       </c>
       <c r="E7" s="7">
-        <v>5.3</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1722,13 +1722,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-6.62</v>
+        <v>-5.84</v>
       </c>
       <c r="D8" s="6">
-        <v>-5.84</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.78</v>
+        <v>-7.09</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1739,13 +1739,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-1.36</v>
+        <v>-0.13</v>
       </c>
       <c r="D9" s="6">
-        <v>-0.13</v>
+        <v>0.73</v>
       </c>
       <c r="E9" s="7">
-        <v>1.23</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1756,13 +1756,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-13.02</v>
+        <v>-11.08</v>
       </c>
       <c r="D10" s="6">
-        <v>-11.08</v>
+        <v>-10.9</v>
       </c>
       <c r="E10" s="7">
-        <v>1.94</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1773,13 +1773,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-16.83</v>
+        <v>-14.83</v>
       </c>
       <c r="D11" s="6">
-        <v>-14.83</v>
+        <v>-10.04</v>
       </c>
       <c r="E11" s="7">
-        <v>2</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1790,13 +1790,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>2.55</v>
+        <v>2.94</v>
       </c>
       <c r="D12" s="6">
-        <v>2.94</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.39</v>
+        <v>-3.59</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-6.53</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1807,13 +1807,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-1.7</v>
+        <v>-2.21</v>
       </c>
       <c r="D13" s="6">
-        <v>-2.21</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.51</v>
+        <v>-1.83</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.38</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1824,13 +1824,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>1.8</v>
+        <v>-0.43</v>
       </c>
       <c r="D14" s="6">
-        <v>-0.43</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-2.23</v>
+        <v>0.66</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.09</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1841,13 +1841,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-5.23</v>
+        <v>-4.5</v>
       </c>
       <c r="D15" s="6">
-        <v>-4.5</v>
+        <v>-2.43</v>
       </c>
       <c r="E15" s="7">
-        <v>0.73</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1858,13 +1858,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.46</v>
+        <v>-0.98</v>
       </c>
       <c r="D16" s="6">
-        <v>-0.98</v>
+        <v>-0.49</v>
       </c>
       <c r="E16" s="7">
-        <v>2.48</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1875,13 +1875,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>-7.75</v>
+        <v>-7.4</v>
       </c>
       <c r="D17" s="6">
-        <v>-7.4</v>
+        <v>-5.53</v>
       </c>
       <c r="E17" s="7">
-        <v>0.35</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1892,13 +1892,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>-6.54</v>
+        <v>-5.66</v>
       </c>
       <c r="D18" s="6">
-        <v>-5.66</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.88</v>
+        <v>-5.9</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1909,13 +1909,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-25.07</v>
+        <v>-22.11</v>
       </c>
       <c r="D19" s="6">
-        <v>-22.11</v>
+        <v>-21.75</v>
       </c>
       <c r="E19" s="7">
-        <v>2.96</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1926,13 +1926,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-10.87</v>
+        <v>-6.89</v>
       </c>
       <c r="D20" s="6">
-        <v>-6.89</v>
+        <v>-5.82</v>
       </c>
       <c r="E20" s="7">
-        <v>3.98</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1943,13 +1943,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-25.51</v>
+        <v>-21.59</v>
       </c>
       <c r="D21" s="6">
-        <v>-21.59</v>
-      </c>
-      <c r="E21" s="7">
-        <v>3.92</v>
+        <v>-22.59</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1960,13 +1960,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>6.44</v>
+        <v>6.29</v>
       </c>
       <c r="D22" s="6">
-        <v>6.29</v>
+        <v>5.66</v>
       </c>
       <c r="E22" s="8">
-        <v>-0.15</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1977,13 +1977,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>11.43</v>
+        <v>12.95</v>
       </c>
       <c r="D23" s="6">
-        <v>12.95</v>
-      </c>
-      <c r="E23" s="7">
-        <v>1.52</v>
+        <v>8.93</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-4.02</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1994,13 +1994,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-20.27</v>
+        <v>-18.17</v>
       </c>
       <c r="D24" s="6">
-        <v>-18.17</v>
+        <v>-17.23</v>
       </c>
       <c r="E24" s="7">
-        <v>2.1</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2011,13 +2011,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-28.69</v>
+        <v>-25.34</v>
       </c>
       <c r="D25" s="6">
-        <v>-25.34</v>
-      </c>
-      <c r="E25" s="7">
-        <v>3.35</v>
+        <v>-27.21</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2028,13 +2028,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-28.58</v>
+        <v>-24.35</v>
       </c>
       <c r="D26" s="6">
-        <v>-24.35</v>
-      </c>
-      <c r="E26" s="7">
-        <v>4.23</v>
+        <v>-25.28</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2045,13 +2045,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-20.45</v>
+        <v>-21.04</v>
       </c>
       <c r="D27" s="6">
-        <v>-21.04</v>
+        <v>-21.49</v>
       </c>
       <c r="E27" s="8">
-        <v>-0.59</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2062,13 +2062,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-6.81</v>
+        <v>-6.26</v>
       </c>
       <c r="D28" s="6">
-        <v>-6.26</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.55</v>
+        <v>-7.12</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2079,13 +2079,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-31.42</v>
+        <v>-30.07</v>
       </c>
       <c r="D29" s="6">
-        <v>-30.07</v>
+        <v>-29.87</v>
       </c>
       <c r="E29" s="7">
-        <v>1.35</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2096,13 +2096,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-30.46</v>
+        <v>-29.6</v>
       </c>
       <c r="D30" s="6">
-        <v>-29.6</v>
+        <v>-29.18</v>
       </c>
       <c r="E30" s="7">
-        <v>0.86</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2113,13 +2113,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-33.44</v>
+        <v>-31.29</v>
       </c>
       <c r="D31" s="6">
-        <v>-31.29</v>
-      </c>
-      <c r="E31" s="7">
-        <v>2.15</v>
+        <v>-32.23</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2130,13 +2130,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>730.85</v>
+        <v>725.4</v>
       </c>
       <c r="D32" s="6">
-        <v>725.4</v>
+        <v>721.35</v>
       </c>
       <c r="E32" s="8">
-        <v>-5.45</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2147,13 +2147,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>630</v>
+        <v>633.75</v>
       </c>
       <c r="D33" s="6">
-        <v>633.75</v>
-      </c>
-      <c r="E33" s="7">
-        <v>3.75</v>
+        <v>627.9</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-5.85</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2164,13 +2164,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>852.05</v>
+        <v>868.75</v>
       </c>
       <c r="D34" s="6">
-        <v>868.75</v>
+        <v>871.3</v>
       </c>
       <c r="E34" s="7">
-        <v>16.7</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2181,13 +2181,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>985.8</v>
+        <v>998</v>
       </c>
       <c r="D35" s="6">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="E35" s="7">
-        <v>12.2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2198,47 +2198,47 @@
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>1544.5</v>
+        <v>1594.3</v>
       </c>
       <c r="D36" s="6">
-        <v>1594.3</v>
-      </c>
-      <c r="E36" s="7">
-        <v>49.8</v>
+        <v>1572.5</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-21.8</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C37" s="6">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="D37" s="6">
-        <v>40</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-20</v>
+        <v>99</v>
+      </c>
+      <c r="E37" s="7">
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C38" s="6">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="D38" s="6">
-        <v>60</v>
-      </c>
-      <c r="E38" s="7">
-        <v>20</v>
+        <v>79</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2249,13 +2249,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>55.13</v>
+        <v>54.15</v>
       </c>
       <c r="D39" s="6">
-        <v>54.15</v>
+        <v>53.38</v>
       </c>
       <c r="E39" s="8">
-        <v>-0.98</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2266,13 +2266,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>46.42</v>
+        <v>48.11</v>
       </c>
       <c r="D40" s="6">
-        <v>48.11</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.69</v>
+        <v>45.69</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-2.42</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2283,13 +2283,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>39.14</v>
+        <v>46.79</v>
       </c>
       <c r="D41" s="6">
-        <v>46.79</v>
+        <v>47.87</v>
       </c>
       <c r="E41" s="7">
-        <v>7.65</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2300,13 +2300,13 @@
         <v>24</v>
       </c>
       <c r="C42" s="6">
-        <v>25.07</v>
+        <v>29.52</v>
       </c>
       <c r="D42" s="6">
-        <v>29.52</v>
+        <v>31.67</v>
       </c>
       <c r="E42" s="7">
-        <v>4.45</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2317,13 +2317,13 @@
         <v>24</v>
       </c>
       <c r="C43" s="6">
-        <v>25.16</v>
+        <v>35.2</v>
       </c>
       <c r="D43" s="6">
-        <v>35.2</v>
-      </c>
-      <c r="E43" s="7">
-        <v>10.04</v>
+        <v>33.11</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-2.09</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2334,13 +2334,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>-95.84</v>
+        <v>-87.09999999999999</v>
       </c>
       <c r="D44" s="6">
-        <v>-87.09999999999999</v>
-      </c>
-      <c r="E44" s="7">
-        <v>8.74</v>
+        <v>-94.34</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-7.24</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2351,13 +2351,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>-69.26000000000001</v>
+        <v>-73.93000000000001</v>
       </c>
       <c r="D45" s="6">
-        <v>-73.93000000000001</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-4.67</v>
+        <v>-49.52</v>
+      </c>
+      <c r="E45" s="7">
+        <v>24.41</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2368,13 +2368,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>-65.83</v>
+        <v>-5.76</v>
       </c>
       <c r="D46" s="6">
-        <v>-5.76</v>
+        <v>29.4</v>
       </c>
       <c r="E46" s="7">
-        <v>60.07</v>
+        <v>35.16</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2385,13 +2385,13 @@
         <v>31</v>
       </c>
       <c r="C47" s="6">
-        <v>-71.04000000000001</v>
+        <v>17.97</v>
       </c>
       <c r="D47" s="6">
-        <v>17.97</v>
-      </c>
-      <c r="E47" s="7">
-        <v>89.01000000000001</v>
+        <v>-69.39</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-87.36</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2402,13 +2402,13 @@
         <v>31</v>
       </c>
       <c r="C48" s="6">
-        <v>-53.87</v>
+        <v>-40.06</v>
       </c>
       <c r="D48" s="6">
-        <v>-40.06</v>
+        <v>-24.27</v>
       </c>
       <c r="E48" s="7">
-        <v>13.81</v>
+        <v>15.79</v>
       </c>
     </row>
   </sheetData>
@@ -2473,16 +2473,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-6.1</v>
+        <v>-4.8</v>
       </c>
       <c r="G2" s="11">
-        <v>-9.699999999999999</v>
+        <v>-11</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2607,19 +2607,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.1155</v>
+        <v>0.1202</v>
       </c>
       <c r="B2" s="14">
-        <v>0.0072</v>
+        <v>0.0098</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0299</v>
+        <v>-0.0256</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.083</v>
+        <v>-0.0888</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1074</v>
+        <v>-0.1087</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,34 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.5 → 31.7</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.5</t>
-  </si>
-  <si>
-    <t>31.7</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -395,15 +368,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -918,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>721.35</v>
+        <v>726.5</v>
       </c>
       <c r="D2">
-        <v>-0.5600000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -930,46 +902,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-21.49</v>
+        <v>-20.93</v>
       </c>
       <c r="H2">
-        <v>38.23</v>
+        <v>39.22</v>
       </c>
       <c r="I2">
-        <v>-3.59</v>
+        <v>1.64</v>
       </c>
       <c r="J2">
-        <v>3.08</v>
+        <v>7.84</v>
       </c>
       <c r="K2">
-        <v>5.66</v>
+        <v>3.72</v>
       </c>
       <c r="L2">
-        <v>-5.53</v>
+        <v>-5.13</v>
       </c>
       <c r="M2">
-        <v>-10.87</v>
+        <v>-10.85</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="P2">
-        <v>724.33</v>
+        <v>726.6799999999999</v>
       </c>
       <c r="Q2">
-        <v>725.48</v>
+        <v>728.71</v>
       </c>
       <c r="R2">
-        <v>657.11</v>
+        <v>659.2</v>
       </c>
       <c r="S2">
-        <v>668.21</v>
+        <v>668.29</v>
       </c>
       <c r="T2">
-        <v>7.95</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -984,34 +956,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>53.38</v>
+        <v>54.26</v>
       </c>
       <c r="Z2">
-        <v>16.91</v>
+        <v>16.07</v>
       </c>
       <c r="AA2">
-        <v>20.57</v>
+        <v>19.67</v>
       </c>
       <c r="AB2">
-        <v>-3.66</v>
+        <v>-3.6</v>
       </c>
       <c r="AC2">
-        <v>21.42</v>
+        <v>26.41</v>
       </c>
       <c r="AD2">
-        <v>18.99</v>
+        <v>22.8</v>
       </c>
       <c r="AE2">
-        <v>41.67</v>
+        <v>40.53</v>
       </c>
       <c r="AF2">
-        <v>-94.34</v>
+        <v>-92.87</v>
       </c>
       <c r="AG2">
-        <v>778.9</v>
+        <v>772.98</v>
       </c>
       <c r="AH2">
-        <v>672.0599999999999</v>
+        <v>684.4400000000001</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -1020,7 +992,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>37.81</v>
+        <v>36.11</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,10 +1003,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>627.9</v>
+        <v>620.2</v>
       </c>
       <c r="D3">
-        <v>-0.92</v>
+        <v>-1.23</v>
       </c>
       <c r="E3">
         <v>676.05</v>
@@ -1043,25 +1015,25 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-7.12</v>
+        <v>-8.26</v>
       </c>
       <c r="H3">
-        <v>22.4</v>
+        <v>20.9</v>
       </c>
       <c r="I3">
-        <v>-1.83</v>
+        <v>-3.09</v>
       </c>
       <c r="J3">
-        <v>-7.09</v>
+        <v>-3.89</v>
       </c>
       <c r="K3">
-        <v>8.93</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L3">
-        <v>-5.9</v>
+        <v>-6.17</v>
       </c>
       <c r="M3">
-        <v>0.98</v>
+        <v>0.77</v>
       </c>
       <c r="N3">
         <v>79</v>
@@ -1070,19 +1042,19 @@
         <v>65</v>
       </c>
       <c r="P3">
-        <v>632.01</v>
+        <v>628.0599999999999</v>
       </c>
       <c r="Q3">
-        <v>644.96</v>
+        <v>643.61</v>
       </c>
       <c r="R3">
-        <v>621.96</v>
+        <v>623.1</v>
       </c>
       <c r="S3">
-        <v>587.9400000000001</v>
+        <v>588.21</v>
       </c>
       <c r="T3">
-        <v>6.8</v>
+        <v>5.44</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1097,34 +1069,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>45.69</v>
+        <v>42.65</v>
       </c>
       <c r="Z3">
-        <v>-0.44</v>
+        <v>-1.76</v>
       </c>
       <c r="AA3">
-        <v>3.63</v>
+        <v>2.55</v>
       </c>
       <c r="AB3">
-        <v>-4.07</v>
+        <v>-4.31</v>
       </c>
       <c r="AC3">
-        <v>12.64</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AD3">
-        <v>13.81</v>
+        <v>11.44</v>
       </c>
       <c r="AE3">
-        <v>20.65</v>
+        <v>20.03</v>
       </c>
       <c r="AF3">
-        <v>-49.52</v>
+        <v>-81.47</v>
       </c>
       <c r="AG3">
-        <v>674.87</v>
+        <v>675.46</v>
       </c>
       <c r="AH3">
-        <v>615.0599999999999</v>
+        <v>611.76</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1133,7 +1105,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>13.72</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1116,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>871.3</v>
+        <v>869.4</v>
       </c>
       <c r="D4">
-        <v>0.29</v>
+        <v>-0.22</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1156,46 +1128,46 @@
         <v>837</v>
       </c>
       <c r="G4">
-        <v>-29.87</v>
+        <v>-30.02</v>
       </c>
       <c r="H4">
-        <v>4.1</v>
+        <v>3.87</v>
       </c>
       <c r="I4">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
       <c r="J4">
-        <v>0.73</v>
+        <v>1.45</v>
       </c>
       <c r="K4">
-        <v>-17.23</v>
+        <v>-17.8</v>
       </c>
       <c r="L4">
-        <v>-21.75</v>
+        <v>-21.99</v>
       </c>
       <c r="M4">
-        <v>-2.56</v>
+        <v>-2.2</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>863.52</v>
+        <v>864.4</v>
       </c>
       <c r="Q4">
-        <v>864.87</v>
+        <v>865.1900000000001</v>
       </c>
       <c r="R4">
-        <v>906.75</v>
+        <v>902.97</v>
       </c>
       <c r="S4">
-        <v>1048.79</v>
+        <v>1047.17</v>
       </c>
       <c r="T4">
-        <v>-16.92</v>
+        <v>-16.98</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1210,34 +1182,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>47.87</v>
+        <v>47.11</v>
       </c>
       <c r="Z4">
-        <v>-11.45</v>
+        <v>-10.14</v>
       </c>
       <c r="AA4">
-        <v>-16.17</v>
+        <v>-14.97</v>
       </c>
       <c r="AB4">
-        <v>4.73</v>
+        <v>4.83</v>
       </c>
       <c r="AC4">
-        <v>87.15000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="AD4">
-        <v>80.58</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="AE4">
-        <v>18.9</v>
+        <v>18.71</v>
       </c>
       <c r="AF4">
-        <v>29.4</v>
+        <v>-49.77</v>
       </c>
       <c r="AG4">
-        <v>889.8200000000001</v>
+        <v>890.21</v>
       </c>
       <c r="AH4">
-        <v>839.9299999999999</v>
+        <v>840.1799999999999</v>
       </c>
       <c r="AI4">
         <v>891.26</v>
@@ -1246,7 +1218,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>25.8</v>
+        <v>23.09</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1004</v>
+        <v>1030.5</v>
       </c>
       <c r="D5">
-        <v>0.6</v>
+        <v>2.64</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1269,46 +1241,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-29.18</v>
+        <v>-27.31</v>
       </c>
       <c r="H5">
-        <v>34.05</v>
+        <v>37.58</v>
       </c>
       <c r="I5">
-        <v>-2.43</v>
+        <v>2.8</v>
       </c>
       <c r="J5">
-        <v>-10.9</v>
+        <v>-6.66</v>
       </c>
       <c r="K5">
-        <v>-27.21</v>
+        <v>-23.06</v>
       </c>
       <c r="L5">
-        <v>-5.82</v>
+        <v>-4.49</v>
       </c>
       <c r="M5">
-        <v>12.02</v>
+        <v>12.28</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P5">
-        <v>995.12</v>
+        <v>1000.74</v>
       </c>
       <c r="Q5">
-        <v>1058.17</v>
+        <v>1052.87</v>
       </c>
       <c r="R5">
-        <v>1143.98</v>
+        <v>1138.42</v>
       </c>
       <c r="S5">
-        <v>1072.88</v>
+        <v>1073</v>
       </c>
       <c r="T5">
-        <v>-6.42</v>
+        <v>-3.96</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1323,34 +1295,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>31.67</v>
+        <v>40.33</v>
       </c>
       <c r="Z5">
-        <v>-42.93</v>
+        <v>-39.33</v>
       </c>
       <c r="AA5">
-        <v>-40.77</v>
+        <v>-40.48</v>
       </c>
       <c r="AB5">
-        <v>-2.16</v>
+        <v>1.15</v>
       </c>
       <c r="AC5">
-        <v>31.49</v>
+        <v>63.53</v>
       </c>
       <c r="AD5">
-        <v>18.13</v>
+        <v>36.55</v>
       </c>
       <c r="AE5">
-        <v>34.75</v>
+        <v>40.09</v>
       </c>
       <c r="AF5">
-        <v>-69.39</v>
+        <v>1172.92</v>
       </c>
       <c r="AG5">
-        <v>1157.47</v>
+        <v>1145.67</v>
       </c>
       <c r="AH5">
-        <v>958.87</v>
+        <v>960.0700000000001</v>
       </c>
       <c r="AI5">
         <v>1101.68</v>
@@ -1359,7 +1331,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>40.36</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1572.5</v>
+        <v>1616.9</v>
       </c>
       <c r="D6">
-        <v>-1.37</v>
+        <v>2.82</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1382,46 +1354,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-32.23</v>
+        <v>-30.32</v>
       </c>
       <c r="H6">
-        <v>6.88</v>
+        <v>9.9</v>
       </c>
       <c r="I6">
-        <v>-0.49</v>
+        <v>5.4</v>
       </c>
       <c r="J6">
-        <v>-10.04</v>
+        <v>-2.56</v>
       </c>
       <c r="K6">
-        <v>-25.28</v>
+        <v>-22.65</v>
       </c>
       <c r="L6">
-        <v>-22.59</v>
+        <v>-22.71</v>
       </c>
       <c r="M6">
-        <v>-8.880000000000001</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="N6">
         <v>21</v>
       </c>
       <c r="O6">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="P6">
-        <v>1559.06</v>
+        <v>1575.64</v>
       </c>
       <c r="Q6">
-        <v>1631.19</v>
+        <v>1628.77</v>
       </c>
       <c r="R6">
-        <v>1846.72</v>
+        <v>1838.38</v>
       </c>
       <c r="S6">
-        <v>1816.86</v>
+        <v>1814.93</v>
       </c>
       <c r="T6">
-        <v>-13.45</v>
+        <v>-10.91</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1436,34 +1408,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>33.11</v>
+        <v>40.83</v>
       </c>
       <c r="Z6">
-        <v>-81.33</v>
+        <v>-74.02</v>
       </c>
       <c r="AA6">
-        <v>-86.98</v>
+        <v>-84.39</v>
       </c>
       <c r="AB6">
-        <v>5.65</v>
+        <v>10.37</v>
       </c>
       <c r="AC6">
-        <v>71.23</v>
+        <v>94.64</v>
       </c>
       <c r="AD6">
-        <v>48.98</v>
+        <v>73.47</v>
       </c>
       <c r="AE6">
-        <v>46.91</v>
+        <v>48.03</v>
       </c>
       <c r="AF6">
-        <v>-24.27</v>
+        <v>32.11</v>
       </c>
       <c r="AG6">
-        <v>1746.61</v>
+        <v>1743.21</v>
       </c>
       <c r="AH6">
-        <v>1515.77</v>
+        <v>1514.33</v>
       </c>
       <c r="AI6">
         <v>1690.77</v>
@@ -1472,7 +1444,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>58.75</v>
+        <v>51.82</v>
       </c>
     </row>
   </sheetData>
@@ -1613,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1633,47 +1605,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1681,734 +1618,700 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>1.34</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>3.08</v>
       </c>
-      <c r="E7" s="7">
-        <v>1.74</v>
+      <c r="D7" s="5">
+        <v>7.84</v>
+      </c>
+      <c r="E7" s="6">
+        <v>4.76</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-5.84</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-7.09</v>
       </c>
-      <c r="E8" s="8">
-        <v>-1.25</v>
+      <c r="D8" s="5">
+        <v>-3.89</v>
+      </c>
+      <c r="E8" s="6">
+        <v>3.2</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-0.13</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>0.73</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.86</v>
+      <c r="D9" s="5">
+        <v>1.45</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.72</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-11.08</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-10.9</v>
       </c>
-      <c r="E10" s="7">
-        <v>0.18</v>
+      <c r="D10" s="5">
+        <v>-6.66</v>
+      </c>
+      <c r="E10" s="6">
+        <v>4.24</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-14.83</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-10.04</v>
       </c>
-      <c r="E11" s="7">
-        <v>4.79</v>
+      <c r="D11" s="5">
+        <v>-2.56</v>
+      </c>
+      <c r="E11" s="6">
+        <v>7.48</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
-        <v>2.94</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-3.59</v>
       </c>
-      <c r="E12" s="8">
-        <v>-6.53</v>
+      <c r="D12" s="5">
+        <v>1.64</v>
+      </c>
+      <c r="E12" s="6">
+        <v>5.23</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
-        <v>-2.21</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-1.83</v>
       </c>
+      <c r="D13" s="5">
+        <v>-3.09</v>
+      </c>
       <c r="E13" s="7">
-        <v>0.38</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>-0.43</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>0.66</v>
       </c>
+      <c r="D14" s="5">
+        <v>0.51</v>
+      </c>
       <c r="E14" s="7">
-        <v>1.09</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-4.5</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-2.43</v>
       </c>
-      <c r="E15" s="7">
-        <v>2.07</v>
+      <c r="D15" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="E15" s="6">
+        <v>5.23</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-0.98</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-0.49</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.49</v>
+      <c r="D16" s="5">
+        <v>5.4</v>
+      </c>
+      <c r="E16" s="6">
+        <v>5.89</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="6">
-        <v>-7.4</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-5.53</v>
       </c>
-      <c r="E17" s="7">
+      <c r="D17" s="5">
+        <v>-5.13</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-5.9</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-6.17</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-21.75</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-21.99</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-5.82</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-4.49</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-22.59</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-22.71</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>5.66</v>
+      </c>
+      <c r="D22" s="5">
+        <v>3.72</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>8.93</v>
+      </c>
+      <c r="D23" s="5">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-17.23</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-17.8</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-27.21</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-23.06</v>
+      </c>
+      <c r="E25" s="6">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-25.28</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-22.65</v>
+      </c>
+      <c r="E26" s="6">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-21.49</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-20.93</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-7.12</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-8.26</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-29.87</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-30.02</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-29.18</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-27.31</v>
+      </c>
+      <c r="E30" s="6">
         <v>1.87</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-32.23</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-30.32</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>721.35</v>
+      </c>
+      <c r="D32" s="5">
+        <v>726.5</v>
+      </c>
+      <c r="E32" s="6">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-5.66</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-5.9</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>627.9</v>
+      </c>
+      <c r="D33" s="5">
+        <v>620.2</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-7.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-22.11</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-21.75</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>871.3</v>
+      </c>
+      <c r="D34" s="5">
+        <v>869.4</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-6.89</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-5.82</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1004</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1030.5</v>
+      </c>
+      <c r="E35" s="6">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-21.59</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-22.59</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1572.5</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1616.9</v>
+      </c>
+      <c r="E36" s="6">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>6.29</v>
-      </c>
-      <c r="D22" s="6">
-        <v>5.66</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>53.38</v>
+      </c>
+      <c r="D37" s="5">
+        <v>54.26</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>12.95</v>
-      </c>
-      <c r="D23" s="6">
-        <v>8.93</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-4.02</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>45.69</v>
+      </c>
+      <c r="D38" s="5">
+        <v>42.65</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-3.04</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-18.17</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-17.23</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>47.87</v>
+      </c>
+      <c r="D39" s="5">
+        <v>47.11</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-25.34</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-27.21</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>31.67</v>
+      </c>
+      <c r="D40" s="5">
+        <v>40.33</v>
+      </c>
+      <c r="E40" s="6">
+        <v>8.66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-24.35</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-25.28</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>33.11</v>
+      </c>
+      <c r="D41" s="5">
+        <v>40.83</v>
+      </c>
+      <c r="E41" s="6">
+        <v>7.72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-21.04</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-21.49</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-94.34</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-92.87</v>
+      </c>
+      <c r="E42" s="6">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-6.26</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-7.12</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-49.52</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-81.47</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-31.95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-30.07</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-29.87</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>29.4</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-49.77</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-79.17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-29.6</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-29.18</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-69.39</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1172.92</v>
+      </c>
+      <c r="E45" s="6">
+        <v>1242.31</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-31.29</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-32.23</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>725.4</v>
-      </c>
-      <c r="D32" s="6">
-        <v>721.35</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-4.05</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>633.75</v>
-      </c>
-      <c r="D33" s="6">
-        <v>627.9</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-5.85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>868.75</v>
-      </c>
-      <c r="D34" s="6">
-        <v>871.3</v>
-      </c>
-      <c r="E34" s="7">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>998</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1004</v>
-      </c>
-      <c r="E35" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>1594.3</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1572.5</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-21.8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="6">
-        <v>79</v>
-      </c>
-      <c r="D37" s="6">
-        <v>99</v>
-      </c>
-      <c r="E37" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="6">
-        <v>99</v>
-      </c>
-      <c r="D38" s="6">
-        <v>79</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>54.15</v>
-      </c>
-      <c r="D39" s="6">
-        <v>53.38</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>48.11</v>
-      </c>
-      <c r="D40" s="6">
-        <v>45.69</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-2.42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>46.79</v>
-      </c>
-      <c r="D41" s="6">
-        <v>47.87</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>29.52</v>
-      </c>
-      <c r="D42" s="6">
-        <v>31.67</v>
-      </c>
-      <c r="E42" s="7">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>35.2</v>
-      </c>
-      <c r="D43" s="6">
-        <v>33.11</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-2.09</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="6">
-        <v>-87.09999999999999</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-94.34</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-7.24</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-73.93000000000001</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-49.52</v>
-      </c>
-      <c r="E45" s="7">
-        <v>24.41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-5.76</v>
-      </c>
-      <c r="D46" s="6">
-        <v>29.4</v>
-      </c>
-      <c r="E46" s="7">
-        <v>35.16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>17.97</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-69.39</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-87.36</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-40.06</v>
-      </c>
-      <c r="D48" s="6">
+      <c r="C46" s="5">
         <v>-24.27</v>
       </c>
-      <c r="E48" s="7">
-        <v>15.79</v>
+      <c r="D46" s="5">
+        <v>32.11</v>
+      </c>
+      <c r="E46" s="6">
+        <v>56.38</v>
       </c>
     </row>
   </sheetData>
@@ -2434,60 +2337,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>49.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>42.3</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>45</v>
+      </c>
+      <c r="E2" s="10">
         <v>40</v>
       </c>
-      <c r="F2" s="11">
-        <v>-4.8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-11</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-0.8</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-10.3</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2589,37 +2492,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1202</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0098</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0256</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0888</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1087</v>
+      <c r="A2" s="13">
+        <v>0.1228</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0077</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.022</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.08380000000000001</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1085</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -252,14 +252,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -750,7 +750,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -890,10 +891,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>726.5</v>
+        <v>710.45</v>
       </c>
       <c r="D2">
-        <v>0.71</v>
+        <v>-2.21</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,46 +903,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-20.93</v>
+        <v>-22.67</v>
       </c>
       <c r="H2">
-        <v>39.22</v>
+        <v>36.14</v>
       </c>
       <c r="I2">
-        <v>1.64</v>
+        <v>-2.58</v>
       </c>
       <c r="J2">
-        <v>7.84</v>
+        <v>7.33</v>
       </c>
       <c r="K2">
-        <v>3.72</v>
+        <v>2.85</v>
       </c>
       <c r="L2">
-        <v>-5.13</v>
+        <v>-4.87</v>
       </c>
       <c r="M2">
-        <v>-10.85</v>
+        <v>-11.24</v>
       </c>
       <c r="N2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O2">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="P2">
-        <v>726.6799999999999</v>
+        <v>722.91</v>
       </c>
       <c r="Q2">
-        <v>728.71</v>
+        <v>726.48</v>
       </c>
       <c r="R2">
-        <v>659.2</v>
+        <v>661.0700000000001</v>
       </c>
       <c r="S2">
-        <v>668.29</v>
+        <v>668.3200000000001</v>
       </c>
       <c r="T2">
-        <v>8.710000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -956,34 +957,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>54.26</v>
+        <v>51.03</v>
       </c>
       <c r="Z2">
-        <v>16.07</v>
+        <v>13.95</v>
       </c>
       <c r="AA2">
-        <v>19.67</v>
+        <v>18.53</v>
       </c>
       <c r="AB2">
-        <v>-3.6</v>
+        <v>-4.58</v>
       </c>
       <c r="AC2">
-        <v>26.41</v>
+        <v>18.85</v>
       </c>
       <c r="AD2">
-        <v>22.8</v>
+        <v>22.23</v>
       </c>
       <c r="AE2">
-        <v>40.53</v>
+        <v>39.53</v>
       </c>
       <c r="AF2">
-        <v>-92.87</v>
+        <v>-92.36</v>
       </c>
       <c r="AG2">
-        <v>772.98</v>
+        <v>769.63</v>
       </c>
       <c r="AH2">
-        <v>684.4400000000001</v>
+        <v>683.3200000000001</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -992,7 +993,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>36.11</v>
+        <v>33.87</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,10 +1004,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>620.2</v>
+        <v>632.85</v>
       </c>
       <c r="D3">
-        <v>-1.23</v>
+        <v>2.04</v>
       </c>
       <c r="E3">
         <v>676.05</v>
@@ -1015,46 +1016,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-8.26</v>
+        <v>-6.39</v>
       </c>
       <c r="H3">
-        <v>20.9</v>
+        <v>23.36</v>
       </c>
       <c r="I3">
-        <v>-3.09</v>
+        <v>0.7</v>
       </c>
       <c r="J3">
-        <v>-3.89</v>
+        <v>-2.24</v>
       </c>
       <c r="K3">
-        <v>8.460000000000001</v>
+        <v>11.46</v>
       </c>
       <c r="L3">
-        <v>-6.17</v>
+        <v>-5.54</v>
       </c>
       <c r="M3">
-        <v>0.77</v>
+        <v>1.18</v>
       </c>
       <c r="N3">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O3">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P3">
-        <v>628.0599999999999</v>
+        <v>628.9400000000001</v>
       </c>
       <c r="Q3">
-        <v>643.61</v>
+        <v>642.5700000000001</v>
       </c>
       <c r="R3">
-        <v>623.1</v>
+        <v>624.42</v>
       </c>
       <c r="S3">
-        <v>588.21</v>
+        <v>588.5599999999999</v>
       </c>
       <c r="T3">
-        <v>5.44</v>
+        <v>7.52</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1069,34 +1070,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>42.65</v>
+        <v>48.69</v>
       </c>
       <c r="Z3">
         <v>-1.76</v>
       </c>
       <c r="AA3">
-        <v>2.55</v>
+        <v>1.69</v>
       </c>
       <c r="AB3">
-        <v>-4.31</v>
+        <v>-3.45</v>
       </c>
       <c r="AC3">
-        <v>8.960000000000001</v>
+        <v>21.51</v>
       </c>
       <c r="AD3">
-        <v>11.44</v>
+        <v>14.37</v>
       </c>
       <c r="AE3">
-        <v>20.03</v>
+        <v>20.92</v>
       </c>
       <c r="AF3">
-        <v>-81.47</v>
+        <v>63</v>
       </c>
       <c r="AG3">
-        <v>675.46</v>
+        <v>674.4</v>
       </c>
       <c r="AH3">
-        <v>611.76</v>
+        <v>610.74</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1105,7 +1106,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>13.61</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,10 +1117,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>869.4</v>
+        <v>855</v>
       </c>
       <c r="D4">
-        <v>-0.22</v>
+        <v>-1.66</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1128,46 +1129,46 @@
         <v>837</v>
       </c>
       <c r="G4">
-        <v>-30.02</v>
+        <v>-31.18</v>
       </c>
       <c r="H4">
-        <v>3.87</v>
+        <v>2.15</v>
       </c>
       <c r="I4">
-        <v>0.51</v>
+        <v>-0.64</v>
       </c>
       <c r="J4">
-        <v>1.45</v>
+        <v>-0.93</v>
       </c>
       <c r="K4">
-        <v>-17.8</v>
+        <v>-20.24</v>
       </c>
       <c r="L4">
-        <v>-21.99</v>
+        <v>-21.97</v>
       </c>
       <c r="M4">
-        <v>-2.2</v>
+        <v>-2.53</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="P4">
-        <v>864.4</v>
+        <v>863.3</v>
       </c>
       <c r="Q4">
-        <v>865.1900000000001</v>
+        <v>864.29</v>
       </c>
       <c r="R4">
-        <v>902.97</v>
+        <v>898.6900000000001</v>
       </c>
       <c r="S4">
-        <v>1047.17</v>
+        <v>1045.46</v>
       </c>
       <c r="T4">
-        <v>-16.98</v>
+        <v>-18.22</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1182,34 +1183,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>47.11</v>
+        <v>41.67</v>
       </c>
       <c r="Z4">
         <v>-10.14</v>
       </c>
       <c r="AA4">
-        <v>-14.97</v>
+        <v>-14</v>
       </c>
       <c r="AB4">
-        <v>4.83</v>
+        <v>3.86</v>
       </c>
       <c r="AC4">
-        <v>98.7</v>
+        <v>88.19</v>
       </c>
       <c r="AD4">
-        <v>88.48999999999999</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="AE4">
-        <v>18.71</v>
+        <v>19.27</v>
       </c>
       <c r="AF4">
-        <v>-49.77</v>
+        <v>33.16</v>
       </c>
       <c r="AG4">
-        <v>890.21</v>
+        <v>889.42</v>
       </c>
       <c r="AH4">
-        <v>840.1799999999999</v>
+        <v>839.17</v>
       </c>
       <c r="AI4">
         <v>891.26</v>
@@ -1218,7 +1219,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>23.09</v>
+        <v>24.73</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1230,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1030.5</v>
+        <v>1044.2</v>
       </c>
       <c r="D5">
-        <v>2.64</v>
+        <v>1.33</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,25 +1242,25 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-27.31</v>
+        <v>-26.35</v>
       </c>
       <c r="H5">
-        <v>37.58</v>
+        <v>39.41</v>
       </c>
       <c r="I5">
-        <v>2.8</v>
+        <v>5.97</v>
       </c>
       <c r="J5">
-        <v>-6.66</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="K5">
-        <v>-23.06</v>
+        <v>-21.77</v>
       </c>
       <c r="L5">
-        <v>-4.49</v>
+        <v>-0.41</v>
       </c>
       <c r="M5">
-        <v>12.28</v>
+        <v>12.57</v>
       </c>
       <c r="N5">
         <v>60</v>
@@ -1268,19 +1269,19 @@
         <v>37</v>
       </c>
       <c r="P5">
-        <v>1000.74</v>
+        <v>1012.5</v>
       </c>
       <c r="Q5">
-        <v>1052.87</v>
+        <v>1048.71</v>
       </c>
       <c r="R5">
-        <v>1138.42</v>
+        <v>1132.89</v>
       </c>
       <c r="S5">
-        <v>1073</v>
+        <v>1073.24</v>
       </c>
       <c r="T5">
-        <v>-3.96</v>
+        <v>-2.71</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1295,34 +1296,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>40.33</v>
+        <v>44.27</v>
       </c>
       <c r="Z5">
-        <v>-39.33</v>
+        <v>-34.98</v>
       </c>
       <c r="AA5">
-        <v>-40.48</v>
+        <v>-39.38</v>
       </c>
       <c r="AB5">
-        <v>1.15</v>
+        <v>4.4</v>
       </c>
       <c r="AC5">
-        <v>63.53</v>
+        <v>84.45</v>
       </c>
       <c r="AD5">
-        <v>36.55</v>
+        <v>59.82</v>
       </c>
       <c r="AE5">
-        <v>40.09</v>
+        <v>39.44</v>
       </c>
       <c r="AF5">
-        <v>1172.92</v>
+        <v>-53.83</v>
       </c>
       <c r="AG5">
-        <v>1145.67</v>
+        <v>1134.67</v>
       </c>
       <c r="AH5">
-        <v>960.0700000000001</v>
+        <v>962.76</v>
       </c>
       <c r="AI5">
         <v>1101.68</v>
@@ -1331,7 +1332,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>39.58</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1343,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1616.9</v>
+        <v>1603.3</v>
       </c>
       <c r="D6">
-        <v>2.82</v>
+        <v>-0.84</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,46 +1355,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-30.32</v>
+        <v>-30.9</v>
       </c>
       <c r="H6">
-        <v>9.9</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="I6">
-        <v>5.4</v>
+        <v>3.44</v>
       </c>
       <c r="J6">
-        <v>-2.56</v>
+        <v>-3.72</v>
       </c>
       <c r="K6">
-        <v>-22.65</v>
+        <v>-23.73</v>
       </c>
       <c r="L6">
-        <v>-22.71</v>
+        <v>-23.54</v>
       </c>
       <c r="M6">
-        <v>-8.380000000000001</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="N6">
         <v>21</v>
       </c>
       <c r="O6">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="P6">
-        <v>1575.64</v>
+        <v>1586.3</v>
       </c>
       <c r="Q6">
-        <v>1628.77</v>
+        <v>1625.03</v>
       </c>
       <c r="R6">
-        <v>1838.38</v>
+        <v>1828.47</v>
       </c>
       <c r="S6">
-        <v>1814.93</v>
+        <v>1812.96</v>
       </c>
       <c r="T6">
-        <v>-10.91</v>
+        <v>-11.56</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1408,34 +1409,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>40.83</v>
+        <v>39.34</v>
       </c>
       <c r="Z6">
-        <v>-74.02</v>
+        <v>-68.52</v>
       </c>
       <c r="AA6">
-        <v>-84.39</v>
+        <v>-81.22</v>
       </c>
       <c r="AB6">
-        <v>10.37</v>
+        <v>12.69</v>
       </c>
       <c r="AC6">
-        <v>94.64</v>
+        <v>91.97</v>
       </c>
       <c r="AD6">
-        <v>73.47</v>
+        <v>85.95</v>
       </c>
       <c r="AE6">
-        <v>48.03</v>
+        <v>48.04</v>
       </c>
       <c r="AF6">
-        <v>32.11</v>
+        <v>-13.92</v>
       </c>
       <c r="AG6">
-        <v>1743.21</v>
+        <v>1737.54</v>
       </c>
       <c r="AH6">
-        <v>1514.33</v>
+        <v>1512.51</v>
       </c>
       <c r="AI6">
         <v>1690.77</v>
@@ -1444,7 +1445,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>51.82</v>
+        <v>45.82</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1642,13 +1643,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>3.08</v>
+        <v>7.84</v>
       </c>
       <c r="D7" s="5">
-        <v>7.84</v>
+        <v>7.33</v>
       </c>
       <c r="E7" s="6">
-        <v>4.76</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1659,13 +1660,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-7.09</v>
+        <v>-3.89</v>
       </c>
       <c r="D8" s="5">
-        <v>-3.89</v>
-      </c>
-      <c r="E8" s="6">
-        <v>3.2</v>
+        <v>-2.24</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.65</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1676,13 +1677,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>0.73</v>
+        <v>1.45</v>
       </c>
       <c r="D9" s="5">
-        <v>1.45</v>
+        <v>-0.93</v>
       </c>
       <c r="E9" s="6">
-        <v>0.72</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1693,13 +1694,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-10.9</v>
+        <v>-6.66</v>
       </c>
       <c r="D10" s="5">
-        <v>-6.66</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="E10" s="6">
-        <v>4.24</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1710,13 +1711,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-10.04</v>
+        <v>-2.56</v>
       </c>
       <c r="D11" s="5">
-        <v>-2.56</v>
+        <v>-3.72</v>
       </c>
       <c r="E11" s="6">
-        <v>7.48</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1727,13 +1728,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-3.59</v>
+        <v>1.64</v>
       </c>
       <c r="D12" s="5">
-        <v>1.64</v>
+        <v>-2.58</v>
       </c>
       <c r="E12" s="6">
-        <v>5.23</v>
+        <v>-4.22</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1744,13 +1745,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-1.83</v>
+        <v>-3.09</v>
       </c>
       <c r="D13" s="5">
-        <v>-3.09</v>
+        <v>0.7</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.26</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1761,13 +1762,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
       <c r="D14" s="5">
-        <v>0.51</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.15</v>
+        <v>-0.64</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1778,13 +1779,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-2.43</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="5">
-        <v>2.8</v>
-      </c>
-      <c r="E15" s="6">
-        <v>5.23</v>
+        <v>5.97</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.17</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1795,13 +1796,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-0.49</v>
+        <v>5.4</v>
       </c>
       <c r="D16" s="5">
-        <v>5.4</v>
+        <v>3.44</v>
       </c>
       <c r="E16" s="6">
-        <v>5.89</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1812,13 +1813,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>-5.53</v>
+        <v>-5.13</v>
       </c>
       <c r="D17" s="5">
-        <v>-5.13</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.4</v>
+        <v>-4.87</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.26</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1829,13 +1830,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-5.9</v>
+        <v>-6.17</v>
       </c>
       <c r="D18" s="5">
-        <v>-6.17</v>
+        <v>-5.54</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.27</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1846,13 +1847,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-21.75</v>
+        <v>-21.99</v>
       </c>
       <c r="D19" s="5">
-        <v>-21.99</v>
+        <v>-21.97</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.24</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1863,13 +1864,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-5.82</v>
+        <v>-4.49</v>
       </c>
       <c r="D20" s="5">
-        <v>-4.49</v>
-      </c>
-      <c r="E20" s="6">
-        <v>1.33</v>
+        <v>-0.41</v>
+      </c>
+      <c r="E20" s="7">
+        <v>4.08</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1880,13 +1881,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-22.59</v>
+        <v>-22.71</v>
       </c>
       <c r="D21" s="5">
-        <v>-22.71</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.12</v>
+        <v>-23.54</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1897,13 +1898,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>5.66</v>
+        <v>3.72</v>
       </c>
       <c r="D22" s="5">
-        <v>3.72</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.94</v>
+        <v>2.85</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1914,13 +1915,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>8.93</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="D23" s="5">
-        <v>8.460000000000001</v>
+        <v>11.46</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1931,13 +1932,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-17.23</v>
+        <v>-17.8</v>
       </c>
       <c r="D24" s="5">
-        <v>-17.8</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.57</v>
+        <v>-20.24</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-2.44</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1948,13 +1949,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-27.21</v>
+        <v>-23.06</v>
       </c>
       <c r="D25" s="5">
-        <v>-23.06</v>
-      </c>
-      <c r="E25" s="6">
-        <v>4.15</v>
+        <v>-21.77</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.29</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1965,13 +1966,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-25.28</v>
+        <v>-22.65</v>
       </c>
       <c r="D26" s="5">
-        <v>-22.65</v>
+        <v>-23.73</v>
       </c>
       <c r="E26" s="6">
-        <v>2.63</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1982,13 +1983,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-21.49</v>
+        <v>-20.93</v>
       </c>
       <c r="D27" s="5">
-        <v>-20.93</v>
+        <v>-22.67</v>
       </c>
       <c r="E27" s="6">
-        <v>0.5600000000000001</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1999,13 +2000,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-7.12</v>
+        <v>-8.26</v>
       </c>
       <c r="D28" s="5">
-        <v>-8.26</v>
+        <v>-6.39</v>
       </c>
       <c r="E28" s="7">
-        <v>-1.14</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2016,13 +2017,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-29.87</v>
+        <v>-30.02</v>
       </c>
       <c r="D29" s="5">
-        <v>-30.02</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.15</v>
+        <v>-31.18</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2033,13 +2034,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-29.18</v>
+        <v>-27.31</v>
       </c>
       <c r="D30" s="5">
-        <v>-27.31</v>
-      </c>
-      <c r="E30" s="6">
-        <v>1.87</v>
+        <v>-26.35</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.96</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2050,13 +2051,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-32.23</v>
+        <v>-30.32</v>
       </c>
       <c r="D31" s="5">
-        <v>-30.32</v>
+        <v>-30.9</v>
       </c>
       <c r="E31" s="6">
-        <v>1.91</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2067,13 +2068,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>721.35</v>
+        <v>726.5</v>
       </c>
       <c r="D32" s="5">
-        <v>726.5</v>
+        <v>710.45</v>
       </c>
       <c r="E32" s="6">
-        <v>5.15</v>
+        <v>-16.05</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2084,13 +2085,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>627.9</v>
+        <v>620.2</v>
       </c>
       <c r="D33" s="5">
-        <v>620.2</v>
+        <v>632.85</v>
       </c>
       <c r="E33" s="7">
-        <v>-7.7</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2101,13 +2102,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>871.3</v>
+        <v>869.4</v>
       </c>
       <c r="D34" s="5">
-        <v>869.4</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.9</v>
+        <v>855</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-14.4</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2118,13 +2119,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>1004</v>
+        <v>1030.5</v>
       </c>
       <c r="D35" s="5">
-        <v>1030.5</v>
-      </c>
-      <c r="E35" s="6">
-        <v>26.5</v>
+        <v>1044.2</v>
+      </c>
+      <c r="E35" s="7">
+        <v>13.7</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2135,13 +2136,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>1572.5</v>
+        <v>1616.9</v>
       </c>
       <c r="D36" s="5">
-        <v>1616.9</v>
+        <v>1603.3</v>
       </c>
       <c r="E36" s="6">
-        <v>44.4</v>
+        <v>-13.6</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2149,16 +2150,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C37" s="5">
-        <v>53.38</v>
+        <v>99</v>
       </c>
       <c r="D37" s="5">
-        <v>54.26</v>
+        <v>79</v>
       </c>
       <c r="E37" s="6">
-        <v>0.88</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2166,152 +2167,186 @@
         <v>38</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C38" s="5">
-        <v>45.69</v>
+        <v>79</v>
       </c>
       <c r="D38" s="5">
-        <v>42.65</v>
+        <v>99</v>
       </c>
       <c r="E38" s="7">
-        <v>-3.04</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>47.87</v>
+        <v>54.26</v>
       </c>
       <c r="D39" s="5">
-        <v>47.11</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.76</v>
+        <v>51.03</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-3.23</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>31.67</v>
+        <v>42.65</v>
       </c>
       <c r="D40" s="5">
-        <v>40.33</v>
-      </c>
-      <c r="E40" s="6">
-        <v>8.66</v>
+        <v>48.69</v>
+      </c>
+      <c r="E40" s="7">
+        <v>6.04</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>33.11</v>
+        <v>47.11</v>
       </c>
       <c r="D41" s="5">
-        <v>40.83</v>
+        <v>41.67</v>
       </c>
       <c r="E41" s="6">
-        <v>7.72</v>
+        <v>-5.44</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C42" s="5">
-        <v>-94.34</v>
+        <v>40.33</v>
       </c>
       <c r="D42" s="5">
-        <v>-92.87</v>
-      </c>
-      <c r="E42" s="6">
-        <v>1.47</v>
+        <v>44.27</v>
+      </c>
+      <c r="E42" s="7">
+        <v>3.94</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C43" s="5">
-        <v>-49.52</v>
+        <v>40.83</v>
       </c>
       <c r="D43" s="5">
-        <v>-81.47</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-31.95</v>
+        <v>39.34</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>29.4</v>
+        <v>-92.87</v>
       </c>
       <c r="D44" s="5">
-        <v>-49.77</v>
+        <v>-92.36</v>
       </c>
       <c r="E44" s="7">
-        <v>-79.17</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-69.39</v>
+        <v>-81.47</v>
       </c>
       <c r="D45" s="5">
-        <v>1172.92</v>
-      </c>
-      <c r="E45" s="6">
-        <v>1242.31</v>
+        <v>63</v>
+      </c>
+      <c r="E45" s="7">
+        <v>144.47</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>-24.27</v>
+        <v>-49.77</v>
       </c>
       <c r="D46" s="5">
+        <v>33.16</v>
+      </c>
+      <c r="E46" s="7">
+        <v>82.93000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="5">
+        <v>1172.92</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-53.83</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-1226.75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="5">
         <v>32.11</v>
       </c>
-      <c r="E46" s="6">
-        <v>56.38</v>
+      <c r="D48" s="5">
+        <v>-13.92</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-46.03</v>
       </c>
     </row>
   </sheetData>
@@ -2382,7 +2417,7 @@
         <v>40</v>
       </c>
       <c r="F2" s="10">
-        <v>-0.8</v>
+        <v>-1.5</v>
       </c>
       <c r="G2" s="10">
         <v>-10.3</v>
@@ -2510,19 +2545,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.1228</v>
+        <v>0.1257</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0077</v>
+        <v>0.0118</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.022</v>
+        <v>-0.0253</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.08380000000000001</v>
+        <v>-0.08529999999999999</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1085</v>
+        <v>-0.1124</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>51.0 → 48.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.0</t>
+  </si>
+  <si>
+    <t>48.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -368,14 +395,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -750,8 +778,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -891,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>710.45</v>
+        <v>696.25</v>
       </c>
       <c r="D2">
-        <v>-2.21</v>
+        <v>-2</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -903,46 +930,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-22.67</v>
+        <v>-24.22</v>
       </c>
       <c r="H2">
-        <v>36.14</v>
+        <v>33.42</v>
       </c>
       <c r="I2">
-        <v>-2.58</v>
+        <v>-4.73</v>
       </c>
       <c r="J2">
-        <v>7.33</v>
+        <v>-7.8</v>
       </c>
       <c r="K2">
-        <v>2.85</v>
+        <v>1.52</v>
       </c>
       <c r="L2">
-        <v>-4.87</v>
+        <v>-5.49</v>
       </c>
       <c r="M2">
-        <v>-11.24</v>
+        <v>-11.25</v>
       </c>
       <c r="N2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>722.91</v>
+        <v>715.99</v>
       </c>
       <c r="Q2">
-        <v>726.48</v>
+        <v>724.95</v>
       </c>
       <c r="R2">
-        <v>661.0700000000001</v>
+        <v>662.59</v>
       </c>
       <c r="S2">
-        <v>668.3200000000001</v>
+        <v>668.28</v>
       </c>
       <c r="T2">
-        <v>6.3</v>
+        <v>4.19</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -957,34 +984,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>51.03</v>
+        <v>48.28</v>
       </c>
       <c r="Z2">
-        <v>13.95</v>
+        <v>10.99</v>
       </c>
       <c r="AA2">
-        <v>18.53</v>
+        <v>17.02</v>
       </c>
       <c r="AB2">
-        <v>-4.58</v>
+        <v>-6.03</v>
       </c>
       <c r="AC2">
-        <v>18.85</v>
+        <v>11.73</v>
       </c>
       <c r="AD2">
-        <v>22.23</v>
+        <v>19</v>
       </c>
       <c r="AE2">
-        <v>39.53</v>
+        <v>39.58</v>
       </c>
       <c r="AF2">
-        <v>-92.36</v>
+        <v>-89.34999999999999</v>
       </c>
       <c r="AG2">
-        <v>769.63</v>
+        <v>770.17</v>
       </c>
       <c r="AH2">
-        <v>683.3200000000001</v>
+        <v>679.73</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -993,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>33.87</v>
+        <v>29.46</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1004,10 +1031,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>632.85</v>
+        <v>634.15</v>
       </c>
       <c r="D3">
-        <v>2.04</v>
+        <v>0.21</v>
       </c>
       <c r="E3">
         <v>676.05</v>
@@ -1016,46 +1043,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-6.39</v>
+        <v>-6.2</v>
       </c>
       <c r="H3">
-        <v>23.36</v>
+        <v>23.62</v>
       </c>
       <c r="I3">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="J3">
-        <v>-2.24</v>
+        <v>-2.98</v>
       </c>
       <c r="K3">
-        <v>11.46</v>
+        <v>10.88</v>
       </c>
       <c r="L3">
-        <v>-5.54</v>
+        <v>-3.39</v>
       </c>
       <c r="M3">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P3">
-        <v>628.9400000000001</v>
+        <v>629.77</v>
       </c>
       <c r="Q3">
-        <v>642.5700000000001</v>
+        <v>641.2</v>
       </c>
       <c r="R3">
-        <v>624.42</v>
+        <v>626.2</v>
       </c>
       <c r="S3">
-        <v>588.5599999999999</v>
+        <v>588.9299999999999</v>
       </c>
       <c r="T3">
-        <v>7.52</v>
+        <v>7.68</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1070,34 +1097,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>48.69</v>
+        <v>49.28</v>
       </c>
       <c r="Z3">
-        <v>-1.76</v>
+        <v>-1.64</v>
       </c>
       <c r="AA3">
-        <v>1.69</v>
+        <v>1.02</v>
       </c>
       <c r="AB3">
-        <v>-3.45</v>
+        <v>-2.66</v>
       </c>
       <c r="AC3">
-        <v>21.51</v>
+        <v>39.96</v>
       </c>
       <c r="AD3">
-        <v>14.37</v>
+        <v>23.47</v>
       </c>
       <c r="AE3">
-        <v>20.92</v>
+        <v>20.6</v>
       </c>
       <c r="AF3">
-        <v>63</v>
+        <v>-53.03</v>
       </c>
       <c r="AG3">
-        <v>674.4</v>
+        <v>671.92</v>
       </c>
       <c r="AH3">
-        <v>610.74</v>
+        <v>610.47</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1106,7 +1133,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>16.73</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1117,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="D4">
-        <v>-1.66</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1129,22 +1156,22 @@
         <v>837</v>
       </c>
       <c r="G4">
-        <v>-31.18</v>
+        <v>-31.83</v>
       </c>
       <c r="H4">
-        <v>2.15</v>
+        <v>1.19</v>
       </c>
       <c r="I4">
-        <v>-0.64</v>
+        <v>-0.59</v>
       </c>
       <c r="J4">
-        <v>-0.93</v>
+        <v>-2.98</v>
       </c>
       <c r="K4">
-        <v>-20.24</v>
+        <v>-20.45</v>
       </c>
       <c r="L4">
-        <v>-21.97</v>
+        <v>-22.04</v>
       </c>
       <c r="M4">
         <v>-2.53</v>
@@ -1153,22 +1180,22 @@
         <v>40</v>
       </c>
       <c r="O4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P4">
-        <v>863.3</v>
+        <v>862.29</v>
       </c>
       <c r="Q4">
-        <v>864.29</v>
+        <v>862.64</v>
       </c>
       <c r="R4">
-        <v>898.6900000000001</v>
+        <v>894.08</v>
       </c>
       <c r="S4">
-        <v>1045.46</v>
+        <v>1043.69</v>
       </c>
       <c r="T4">
-        <v>-18.22</v>
+        <v>-18.85</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1183,34 +1210,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>41.67</v>
+        <v>38.97</v>
       </c>
       <c r="Z4">
-        <v>-10.14</v>
+        <v>-10.67</v>
       </c>
       <c r="AA4">
-        <v>-14</v>
+        <v>-13.34</v>
       </c>
       <c r="AB4">
-        <v>3.86</v>
+        <v>2.67</v>
       </c>
       <c r="AC4">
-        <v>88.19</v>
+        <v>73.12</v>
       </c>
       <c r="AD4">
-        <v>91.34999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="AE4">
-        <v>19.27</v>
+        <v>18.94</v>
       </c>
       <c r="AF4">
-        <v>33.16</v>
+        <v>-23.58</v>
       </c>
       <c r="AG4">
-        <v>889.42</v>
+        <v>887.76</v>
       </c>
       <c r="AH4">
-        <v>839.17</v>
+        <v>837.53</v>
       </c>
       <c r="AI4">
         <v>891.26</v>
@@ -1219,7 +1246,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>24.73</v>
+        <v>26.15</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1230,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1044.2</v>
+        <v>1020</v>
       </c>
       <c r="D5">
-        <v>1.33</v>
+        <v>-2.32</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1242,46 +1269,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-26.35</v>
+        <v>-28.05</v>
       </c>
       <c r="H5">
-        <v>39.41</v>
+        <v>36.18</v>
       </c>
       <c r="I5">
-        <v>5.97</v>
+        <v>3.47</v>
       </c>
       <c r="J5">
-        <v>-8.119999999999999</v>
+        <v>-9.52</v>
       </c>
       <c r="K5">
-        <v>-21.77</v>
+        <v>-25.26</v>
       </c>
       <c r="L5">
-        <v>-0.41</v>
+        <v>-4.04</v>
       </c>
       <c r="M5">
-        <v>12.57</v>
+        <v>12.49</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="P5">
-        <v>1012.5</v>
+        <v>1019.34</v>
       </c>
       <c r="Q5">
-        <v>1048.71</v>
+        <v>1044.34</v>
       </c>
       <c r="R5">
-        <v>1132.89</v>
+        <v>1127.2</v>
       </c>
       <c r="S5">
-        <v>1073.24</v>
+        <v>1073.5</v>
       </c>
       <c r="T5">
-        <v>-2.71</v>
+        <v>-4.98</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1296,34 +1323,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>44.27</v>
+        <v>39.33</v>
       </c>
       <c r="Z5">
-        <v>-34.98</v>
+        <v>-33.1</v>
       </c>
       <c r="AA5">
-        <v>-39.38</v>
+        <v>-38.12</v>
       </c>
       <c r="AB5">
-        <v>4.4</v>
+        <v>5.02</v>
       </c>
       <c r="AC5">
-        <v>84.45</v>
+        <v>91.66</v>
       </c>
       <c r="AD5">
-        <v>59.82</v>
+        <v>79.88</v>
       </c>
       <c r="AE5">
-        <v>39.44</v>
+        <v>39.08</v>
       </c>
       <c r="AF5">
-        <v>-53.83</v>
+        <v>-59.53</v>
       </c>
       <c r="AG5">
-        <v>1134.67</v>
+        <v>1126.55</v>
       </c>
       <c r="AH5">
-        <v>962.76</v>
+        <v>962.14</v>
       </c>
       <c r="AI5">
         <v>1101.68</v>
@@ -1332,7 +1359,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>38.9</v>
+        <v>37.11</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1343,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1603.3</v>
+        <v>1589</v>
       </c>
       <c r="D6">
-        <v>-0.84</v>
+        <v>-0.89</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1355,46 +1382,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-30.9</v>
+        <v>-31.52</v>
       </c>
       <c r="H6">
-        <v>8.970000000000001</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>3.44</v>
+        <v>2.88</v>
       </c>
       <c r="J6">
-        <v>-3.72</v>
+        <v>-5.32</v>
       </c>
       <c r="K6">
-        <v>-23.73</v>
+        <v>-25</v>
       </c>
       <c r="L6">
-        <v>-23.54</v>
+        <v>-22.77</v>
       </c>
       <c r="M6">
-        <v>-8.529999999999999</v>
+        <v>-7.84</v>
       </c>
       <c r="N6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O6">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="P6">
-        <v>1586.3</v>
+        <v>1595.2</v>
       </c>
       <c r="Q6">
-        <v>1625.03</v>
+        <v>1619.92</v>
       </c>
       <c r="R6">
-        <v>1828.47</v>
+        <v>1818.61</v>
       </c>
       <c r="S6">
-        <v>1812.96</v>
+        <v>1811.02</v>
       </c>
       <c r="T6">
-        <v>-11.56</v>
+        <v>-12.26</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1409,34 +1436,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>39.34</v>
+        <v>37.77</v>
       </c>
       <c r="Z6">
-        <v>-68.52</v>
+        <v>-64.58</v>
       </c>
       <c r="AA6">
-        <v>-81.22</v>
+        <v>-77.89</v>
       </c>
       <c r="AB6">
-        <v>12.69</v>
+        <v>13.31</v>
       </c>
       <c r="AC6">
-        <v>91.97</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="AD6">
-        <v>85.95</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="AE6">
-        <v>48.04</v>
+        <v>48.06</v>
       </c>
       <c r="AF6">
-        <v>-13.92</v>
+        <v>-43.37</v>
       </c>
       <c r="AG6">
-        <v>1737.54</v>
+        <v>1729.02</v>
       </c>
       <c r="AH6">
-        <v>1512.51</v>
+        <v>1510.82</v>
       </c>
       <c r="AI6">
         <v>1690.77</v>
@@ -1445,12 +1472,72 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>45.82</v>
+        <v>41.06</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AK6"/>
   <conditionalFormatting sqref="AF2:AF6">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D6">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I6">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J6">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K6">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L6">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1462,8 +1549,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="N2:N6">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThanOrEqual">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1472,72 +1565,6 @@
         <color rgb="FFFFFFFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I6">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J6">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K6">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L6">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N6">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" operator="greaterThanOrEqual">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="lessThanOrEqual">
-      <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T6">
@@ -1549,26 +1576,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U6">
-    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V6">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W6">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1606,12 +1633,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1619,734 +1681,734 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>7.84</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>7.33</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.51</v>
+      <c r="D7" s="6">
+        <v>-7.8</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-15.13</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-3.89</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-2.24</v>
       </c>
+      <c r="D8" s="6">
+        <v>-2.98</v>
+      </c>
       <c r="E8" s="7">
-        <v>1.65</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>1.45</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-0.93</v>
       </c>
-      <c r="E9" s="6">
-        <v>-2.38</v>
+      <c r="D9" s="6">
+        <v>-2.98</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-6.66</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-8.119999999999999</v>
       </c>
-      <c r="E10" s="6">
-        <v>-1.46</v>
+      <c r="D10" s="6">
+        <v>-9.52</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-2.56</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-3.72</v>
       </c>
-      <c r="E11" s="6">
-        <v>-1.16</v>
+      <c r="D11" s="6">
+        <v>-5.32</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>1.64</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-2.58</v>
       </c>
-      <c r="E12" s="6">
-        <v>-4.22</v>
+      <c r="D12" s="6">
+        <v>-4.73</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-3.09</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>0.7</v>
       </c>
+      <c r="D13" s="6">
+        <v>0.66</v>
+      </c>
       <c r="E13" s="7">
-        <v>3.79</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>0.51</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-0.64</v>
       </c>
-      <c r="E14" s="6">
-        <v>-1.15</v>
+      <c r="D14" s="6">
+        <v>-0.59</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.05</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>2.8</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>5.97</v>
       </c>
+      <c r="D15" s="6">
+        <v>3.47</v>
+      </c>
       <c r="E15" s="7">
-        <v>3.17</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>5.4</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>3.44</v>
       </c>
-      <c r="E16" s="6">
-        <v>-1.96</v>
+      <c r="D16" s="6">
+        <v>2.88</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>-5.13</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-4.87</v>
       </c>
+      <c r="D17" s="6">
+        <v>-5.49</v>
+      </c>
       <c r="E17" s="7">
-        <v>0.26</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>-6.17</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-5.54</v>
       </c>
-      <c r="E18" s="7">
-        <v>0.63</v>
+      <c r="D18" s="6">
+        <v>-3.39</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.15</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-21.99</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-21.97</v>
       </c>
+      <c r="D19" s="6">
+        <v>-22.04</v>
+      </c>
       <c r="E19" s="7">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>-4.49</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-0.41</v>
       </c>
+      <c r="D20" s="6">
+        <v>-4.04</v>
+      </c>
       <c r="E20" s="7">
-        <v>4.08</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-22.71</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-23.54</v>
       </c>
-      <c r="E21" s="6">
-        <v>-0.83</v>
+      <c r="D21" s="6">
+        <v>-22.77</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.77</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>3.72</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>2.85</v>
       </c>
-      <c r="E22" s="6">
-        <v>-0.87</v>
+      <c r="D22" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="5">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>11.46</v>
       </c>
+      <c r="D23" s="6">
+        <v>10.88</v>
+      </c>
       <c r="E23" s="7">
-        <v>3</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="5">
-        <v>-17.8</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>-20.24</v>
       </c>
-      <c r="E24" s="6">
-        <v>-2.44</v>
+      <c r="D24" s="6">
+        <v>-20.45</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
-        <v>-23.06</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C25" s="6">
         <v>-21.77</v>
       </c>
+      <c r="D25" s="6">
+        <v>-25.26</v>
+      </c>
       <c r="E25" s="7">
-        <v>1.29</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="5">
-        <v>-22.65</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C26" s="6">
         <v>-23.73</v>
       </c>
-      <c r="E26" s="6">
-        <v>-1.08</v>
+      <c r="D26" s="6">
+        <v>-25</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="5">
-        <v>-20.93</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="6">
         <v>-22.67</v>
       </c>
-      <c r="E27" s="6">
-        <v>-1.74</v>
+      <c r="D27" s="6">
+        <v>-24.22</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="5">
-        <v>-8.26</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C28" s="6">
         <v>-6.39</v>
       </c>
-      <c r="E28" s="7">
-        <v>1.87</v>
+      <c r="D28" s="6">
+        <v>-6.2</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.19</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="5">
-        <v>-30.02</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C29" s="6">
         <v>-31.18</v>
       </c>
-      <c r="E29" s="6">
-        <v>-1.16</v>
+      <c r="D29" s="6">
+        <v>-31.83</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="5">
-        <v>-27.31</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-26.35</v>
       </c>
+      <c r="D30" s="6">
+        <v>-28.05</v>
+      </c>
       <c r="E30" s="7">
-        <v>0.96</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="5">
-        <v>-30.32</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C31" s="6">
         <v>-30.9</v>
       </c>
-      <c r="E31" s="6">
-        <v>-0.58</v>
+      <c r="D31" s="6">
+        <v>-31.52</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="5">
-        <v>726.5</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C32" s="6">
         <v>710.45</v>
       </c>
-      <c r="E32" s="6">
-        <v>-16.05</v>
+      <c r="D32" s="6">
+        <v>696.25</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-14.2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="5">
-        <v>620.2</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C33" s="6">
         <v>632.85</v>
       </c>
-      <c r="E33" s="7">
-        <v>12.65</v>
+      <c r="D33" s="6">
+        <v>634.15</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1.3</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="5">
-        <v>869.4</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C34" s="6">
         <v>855</v>
       </c>
-      <c r="E34" s="6">
-        <v>-14.4</v>
+      <c r="D34" s="6">
+        <v>847</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-8</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="5">
-        <v>1030.5</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C35" s="6">
         <v>1044.2</v>
       </c>
+      <c r="D35" s="6">
+        <v>1020</v>
+      </c>
       <c r="E35" s="7">
-        <v>13.7</v>
+        <v>-24.2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="5">
-        <v>1616.9</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="C36" s="6">
         <v>1603.3</v>
       </c>
-      <c r="E36" s="6">
-        <v>-13.6</v>
+      <c r="D36" s="6">
+        <v>1589</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-14.3</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="5">
-        <v>99</v>
-      </c>
-      <c r="D37" s="5">
+      <c r="C37" s="6">
         <v>79</v>
       </c>
-      <c r="E37" s="6">
-        <v>-20</v>
+      <c r="D37" s="6">
+        <v>80</v>
+      </c>
+      <c r="E37" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="6">
+        <v>21</v>
+      </c>
+      <c r="D38" s="6">
+        <v>20</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>51.03</v>
+      </c>
+      <c r="D39" s="6">
+        <v>48.28</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-2.75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="5">
-        <v>79</v>
-      </c>
-      <c r="D38" s="5">
-        <v>99</v>
-      </c>
-      <c r="E38" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>48.69</v>
+      </c>
+      <c r="D40" s="6">
+        <v>49.28</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>41.67</v>
+      </c>
+      <c r="D41" s="6">
+        <v>38.97</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>44.27</v>
+      </c>
+      <c r="D42" s="6">
+        <v>39.33</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-4.94</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>39.34</v>
+      </c>
+      <c r="D43" s="6">
+        <v>37.77</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>54.26</v>
-      </c>
-      <c r="D39" s="5">
-        <v>51.03</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-3.23</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-92.36</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-89.34999999999999</v>
+      </c>
+      <c r="E44" s="8">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>42.65</v>
-      </c>
-      <c r="D40" s="5">
-        <v>48.69</v>
-      </c>
-      <c r="E40" s="7">
-        <v>6.04</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>63</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-53.03</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-116.03</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>47.11</v>
-      </c>
-      <c r="D41" s="5">
-        <v>41.67</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-5.44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="6">
+        <v>33.16</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-23.58</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-56.74</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="5">
-        <v>40.33</v>
-      </c>
-      <c r="D42" s="5">
-        <v>44.27</v>
-      </c>
-      <c r="E42" s="7">
-        <v>3.94</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-53.83</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-59.53</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-5.7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>40.83</v>
-      </c>
-      <c r="D43" s="5">
-        <v>39.34</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="5">
-        <v>-92.87</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-92.36</v>
-      </c>
-      <c r="E44" s="7">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-81.47</v>
-      </c>
-      <c r="D45" s="5">
-        <v>63</v>
-      </c>
-      <c r="E45" s="7">
-        <v>144.47</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-49.77</v>
-      </c>
-      <c r="D46" s="5">
-        <v>33.16</v>
-      </c>
-      <c r="E46" s="7">
-        <v>82.93000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="5">
-        <v>1172.92</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-53.83</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-1226.75</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="5">
-        <v>32.11</v>
-      </c>
-      <c r="D48" s="5">
+      <c r="C48" s="6">
         <v>-13.92</v>
       </c>
-      <c r="E48" s="6">
-        <v>-46.03</v>
+      <c r="D48" s="6">
+        <v>-43.37</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-29.45</v>
       </c>
     </row>
   </sheetData>
@@ -2372,60 +2434,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>49.92</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>45</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>42.7</v>
+      </c>
+      <c r="E2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="10">
-        <v>-1.5</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-10.3</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-5.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-11.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2527,37 +2589,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.1257</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0118</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="A2" s="14">
+        <v>0.1249</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.014</v>
+      </c>
+      <c r="C2" s="14">
         <v>-0.0253</v>
       </c>
-      <c r="D2" s="13">
-        <v>-0.08529999999999999</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1124</v>
+      <c r="D2" s="14">
+        <v>-0.0784</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1125</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,19 +181,13 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>51.0 → 48.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.0</t>
-  </si>
-  <si>
-    <t>48.3</t>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -918,10 +912,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>696.25</v>
+        <v>665.9</v>
       </c>
       <c r="D2">
-        <v>-2</v>
+        <v>-4.36</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -930,46 +924,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-24.22</v>
+        <v>-27.52</v>
       </c>
       <c r="H2">
-        <v>33.42</v>
+        <v>27.6</v>
       </c>
       <c r="I2">
-        <v>-4.73</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="J2">
-        <v>-7.8</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="K2">
-        <v>1.52</v>
+        <v>-1.86</v>
       </c>
       <c r="L2">
-        <v>-5.49</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="M2">
-        <v>-11.25</v>
+        <v>-11.49</v>
       </c>
       <c r="N2">
         <v>80</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P2">
-        <v>715.99</v>
+        <v>704.09</v>
       </c>
       <c r="Q2">
-        <v>724.95</v>
+        <v>722.28</v>
       </c>
       <c r="R2">
-        <v>662.59</v>
+        <v>663.5</v>
       </c>
       <c r="S2">
-        <v>668.28</v>
+        <v>668.08</v>
       </c>
       <c r="T2">
-        <v>4.19</v>
+        <v>-0.33</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -981,37 +975,37 @@
         <v>44</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>48.28</v>
+        <v>42.96</v>
       </c>
       <c r="Z2">
-        <v>10.99</v>
+        <v>6.13</v>
       </c>
       <c r="AA2">
-        <v>17.02</v>
+        <v>14.84</v>
       </c>
       <c r="AB2">
-        <v>-6.03</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="AC2">
-        <v>11.73</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>19</v>
+        <v>10.19</v>
       </c>
       <c r="AE2">
-        <v>39.58</v>
+        <v>39.83</v>
       </c>
       <c r="AF2">
-        <v>-89.34999999999999</v>
+        <v>-82.65000000000001</v>
       </c>
       <c r="AG2">
-        <v>770.17</v>
+        <v>774.64</v>
       </c>
       <c r="AH2">
-        <v>679.73</v>
+        <v>669.91</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -1020,7 +1014,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>29.46</v>
+        <v>29.14</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,10 +1025,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>634.15</v>
+        <v>619.7</v>
       </c>
       <c r="D3">
-        <v>0.21</v>
+        <v>-2.28</v>
       </c>
       <c r="E3">
         <v>676.05</v>
@@ -1043,46 +1037,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-6.2</v>
+        <v>-8.34</v>
       </c>
       <c r="H3">
-        <v>23.62</v>
+        <v>20.8</v>
       </c>
       <c r="I3">
-        <v>0.66</v>
+        <v>-2.22</v>
       </c>
       <c r="J3">
-        <v>-2.98</v>
+        <v>-6.33</v>
       </c>
       <c r="K3">
-        <v>10.88</v>
+        <v>7.68</v>
       </c>
       <c r="L3">
-        <v>-3.39</v>
+        <v>-5.09</v>
       </c>
       <c r="M3">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P3">
-        <v>629.77</v>
+        <v>626.96</v>
       </c>
       <c r="Q3">
-        <v>641.2</v>
+        <v>639.15</v>
       </c>
       <c r="R3">
-        <v>626.2</v>
+        <v>627.73</v>
       </c>
       <c r="S3">
-        <v>588.9299999999999</v>
+        <v>589.17</v>
       </c>
       <c r="T3">
-        <v>7.68</v>
+        <v>5.18</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1097,34 +1091,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>49.28</v>
+        <v>43.31</v>
       </c>
       <c r="Z3">
-        <v>-1.64</v>
+        <v>-2.68</v>
       </c>
       <c r="AA3">
-        <v>1.02</v>
+        <v>0.28</v>
       </c>
       <c r="AB3">
-        <v>-2.66</v>
+        <v>-2.96</v>
       </c>
       <c r="AC3">
-        <v>39.96</v>
+        <v>42.03</v>
       </c>
       <c r="AD3">
-        <v>23.47</v>
+        <v>34.5</v>
       </c>
       <c r="AE3">
-        <v>20.6</v>
+        <v>20.51</v>
       </c>
       <c r="AF3">
-        <v>-53.03</v>
+        <v>-45.61</v>
       </c>
       <c r="AG3">
-        <v>671.92</v>
+        <v>669.88</v>
       </c>
       <c r="AH3">
-        <v>610.47</v>
+        <v>608.42</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1133,7 +1127,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>17.67</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1138,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="D4">
-        <v>-0.9399999999999999</v>
+        <v>1.42</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1156,46 +1150,46 @@
         <v>837</v>
       </c>
       <c r="G4">
-        <v>-31.83</v>
+        <v>-30.86</v>
       </c>
       <c r="H4">
-        <v>1.19</v>
+        <v>2.63</v>
       </c>
       <c r="I4">
-        <v>-0.59</v>
+        <v>-1.12</v>
       </c>
       <c r="J4">
-        <v>-2.98</v>
+        <v>-2.39</v>
       </c>
       <c r="K4">
-        <v>-20.45</v>
+        <v>-18.52</v>
       </c>
       <c r="L4">
-        <v>-22.04</v>
+        <v>-21.59</v>
       </c>
       <c r="M4">
-        <v>-2.53</v>
+        <v>-1.65</v>
       </c>
       <c r="N4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O4">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>862.29</v>
+        <v>860.34</v>
       </c>
       <c r="Q4">
-        <v>862.64</v>
+        <v>862.22</v>
       </c>
       <c r="R4">
-        <v>894.08</v>
+        <v>890.26</v>
       </c>
       <c r="S4">
-        <v>1043.69</v>
+        <v>1041.94</v>
       </c>
       <c r="T4">
-        <v>-18.85</v>
+        <v>-17.56</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1210,34 +1204,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.97</v>
+        <v>44.74</v>
       </c>
       <c r="Z4">
-        <v>-10.67</v>
+        <v>-10</v>
       </c>
       <c r="AA4">
-        <v>-13.34</v>
+        <v>-12.67</v>
       </c>
       <c r="AB4">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="AC4">
-        <v>73.12</v>
+        <v>69.12</v>
       </c>
       <c r="AD4">
-        <v>86.67</v>
+        <v>76.81</v>
       </c>
       <c r="AE4">
-        <v>18.94</v>
+        <v>18.61</v>
       </c>
       <c r="AF4">
-        <v>-23.58</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="AG4">
-        <v>887.76</v>
+        <v>887.28</v>
       </c>
       <c r="AH4">
-        <v>837.53</v>
+        <v>837.16</v>
       </c>
       <c r="AI4">
         <v>891.26</v>
@@ -1246,7 +1240,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>26.15</v>
+        <v>26.98</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1251,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1020</v>
+        <v>976.2</v>
       </c>
       <c r="D5">
-        <v>-2.32</v>
+        <v>-4.29</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1269,46 +1263,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-28.05</v>
+        <v>-31.14</v>
       </c>
       <c r="H5">
-        <v>36.18</v>
+        <v>30.33</v>
       </c>
       <c r="I5">
-        <v>3.47</v>
+        <v>-2.18</v>
       </c>
       <c r="J5">
-        <v>-9.52</v>
+        <v>-11.85</v>
       </c>
       <c r="K5">
-        <v>-25.26</v>
+        <v>-29.29</v>
       </c>
       <c r="L5">
-        <v>-4.04</v>
+        <v>-8.82</v>
       </c>
       <c r="M5">
-        <v>12.49</v>
+        <v>11.14</v>
       </c>
       <c r="N5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O5">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="P5">
-        <v>1019.34</v>
+        <v>1014.98</v>
       </c>
       <c r="Q5">
-        <v>1044.34</v>
+        <v>1038.07</v>
       </c>
       <c r="R5">
-        <v>1127.2</v>
+        <v>1120.49</v>
       </c>
       <c r="S5">
-        <v>1073.5</v>
+        <v>1073.37</v>
       </c>
       <c r="T5">
-        <v>-4.98</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1323,34 +1317,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>39.33</v>
+        <v>32.32</v>
       </c>
       <c r="Z5">
-        <v>-33.1</v>
+        <v>-34.74</v>
       </c>
       <c r="AA5">
-        <v>-38.12</v>
+        <v>-37.45</v>
       </c>
       <c r="AB5">
-        <v>5.02</v>
+        <v>2.7</v>
       </c>
       <c r="AC5">
-        <v>91.66</v>
+        <v>71.45</v>
       </c>
       <c r="AD5">
-        <v>79.88</v>
+        <v>82.52</v>
       </c>
       <c r="AE5">
-        <v>39.08</v>
+        <v>40.11</v>
       </c>
       <c r="AF5">
-        <v>-59.53</v>
+        <v>-46.85</v>
       </c>
       <c r="AG5">
-        <v>1126.55</v>
+        <v>1120.99</v>
       </c>
       <c r="AH5">
-        <v>962.14</v>
+        <v>955.15</v>
       </c>
       <c r="AI5">
         <v>1101.68</v>
@@ -1359,7 +1353,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>37.11</v>
+        <v>33.16</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1364,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1589</v>
+        <v>1564.3</v>
       </c>
       <c r="D6">
-        <v>-0.89</v>
+        <v>-1.55</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1382,88 +1376,88 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-31.52</v>
+        <v>-32.58</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>6.32</v>
       </c>
       <c r="I6">
-        <v>2.88</v>
+        <v>-1.88</v>
       </c>
       <c r="J6">
-        <v>-5.32</v>
+        <v>-7.5</v>
       </c>
       <c r="K6">
-        <v>-25</v>
+        <v>-27.72</v>
       </c>
       <c r="L6">
-        <v>-22.77</v>
+        <v>-26.75</v>
       </c>
       <c r="M6">
-        <v>-7.84</v>
+        <v>-7.28</v>
       </c>
       <c r="N6">
         <v>20</v>
       </c>
       <c r="O6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P6">
-        <v>1595.2</v>
+        <v>1589.2</v>
       </c>
       <c r="Q6">
-        <v>1619.92</v>
+        <v>1613.29</v>
       </c>
       <c r="R6">
-        <v>1818.61</v>
+        <v>1808.5</v>
       </c>
       <c r="S6">
-        <v>1811.02</v>
+        <v>1808.81</v>
       </c>
       <c r="T6">
-        <v>-12.26</v>
+        <v>-13.52</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W6" t="s">
         <v>44</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>37.77</v>
+        <v>35.16</v>
       </c>
       <c r="Z6">
-        <v>-64.58</v>
+        <v>-62.73</v>
       </c>
       <c r="AA6">
-        <v>-77.89</v>
+        <v>-74.86</v>
       </c>
       <c r="AB6">
-        <v>13.31</v>
+        <v>12.13</v>
       </c>
       <c r="AC6">
-        <v>91.84999999999999</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="AD6">
-        <v>92.81999999999999</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="AE6">
-        <v>48.06</v>
+        <v>49.43</v>
       </c>
       <c r="AF6">
-        <v>-43.37</v>
+        <v>15.75</v>
       </c>
       <c r="AG6">
-        <v>1729.02</v>
+        <v>1718.75</v>
       </c>
       <c r="AH6">
-        <v>1510.82</v>
+        <v>1507.83</v>
       </c>
       <c r="AI6">
         <v>1690.77</v>
@@ -1472,7 +1466,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>41.06</v>
+        <v>38.13</v>
       </c>
     </row>
   </sheetData>
@@ -1653,7 +1647,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1665,15 +1659,15 @@
         <v>55</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1685,16 +1679,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1705,13 +1699,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>7.33</v>
+        <v>-7.8</v>
       </c>
       <c r="D7" s="6">
-        <v>-7.8</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="E7" s="7">
-        <v>-15.13</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1722,13 +1716,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-2.24</v>
+        <v>-2.98</v>
       </c>
       <c r="D8" s="6">
-        <v>-2.98</v>
+        <v>-6.33</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.74</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1739,13 +1733,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-0.93</v>
+        <v>-2.98</v>
       </c>
       <c r="D9" s="6">
-        <v>-2.98</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-2.05</v>
+        <v>-2.39</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.59</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1756,13 +1750,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-8.119999999999999</v>
+        <v>-9.52</v>
       </c>
       <c r="D10" s="6">
-        <v>-9.52</v>
+        <v>-11.85</v>
       </c>
       <c r="E10" s="7">
-        <v>-1.4</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1773,13 +1767,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-3.72</v>
+        <v>-5.32</v>
       </c>
       <c r="D11" s="6">
-        <v>-5.32</v>
+        <v>-7.5</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.6</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1790,13 +1784,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-2.58</v>
+        <v>-4.73</v>
       </c>
       <c r="D12" s="6">
-        <v>-4.73</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="E12" s="7">
-        <v>-2.15</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1807,13 +1801,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="D13" s="6">
-        <v>0.66</v>
+        <v>-2.22</v>
       </c>
       <c r="E13" s="7">
-        <v>-0.04</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1824,13 +1818,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-0.64</v>
+        <v>-0.59</v>
       </c>
       <c r="D14" s="6">
-        <v>-0.59</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.05</v>
+        <v>-1.12</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1841,13 +1835,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>5.97</v>
+        <v>3.47</v>
       </c>
       <c r="D15" s="6">
-        <v>3.47</v>
+        <v>-2.18</v>
       </c>
       <c r="E15" s="7">
-        <v>-2.5</v>
+        <v>-5.65</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1858,13 +1852,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>3.44</v>
+        <v>2.88</v>
       </c>
       <c r="D16" s="6">
-        <v>2.88</v>
+        <v>-1.88</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.5600000000000001</v>
+        <v>-4.76</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1875,13 +1869,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.87</v>
+        <v>-5.49</v>
       </c>
       <c r="D17" s="6">
-        <v>-5.49</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.62</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1892,13 +1886,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>-5.54</v>
+        <v>-3.39</v>
       </c>
       <c r="D18" s="6">
-        <v>-3.39</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.15</v>
+        <v>-5.09</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1909,13 +1903,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-21.97</v>
+        <v>-22.04</v>
       </c>
       <c r="D19" s="6">
-        <v>-22.04</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.07000000000000001</v>
+        <v>-21.59</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.45</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1926,13 +1920,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-0.41</v>
+        <v>-4.04</v>
       </c>
       <c r="D20" s="6">
-        <v>-4.04</v>
+        <v>-8.82</v>
       </c>
       <c r="E20" s="7">
-        <v>-3.63</v>
+        <v>-4.78</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1943,13 +1937,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-23.54</v>
+        <v>-22.77</v>
       </c>
       <c r="D21" s="6">
-        <v>-22.77</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.77</v>
+        <v>-26.75</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-3.98</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1960,13 +1954,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>2.85</v>
+        <v>1.52</v>
       </c>
       <c r="D22" s="6">
-        <v>1.52</v>
+        <v>-1.86</v>
       </c>
       <c r="E22" s="7">
-        <v>-1.33</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1977,13 +1971,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>11.46</v>
+        <v>10.88</v>
       </c>
       <c r="D23" s="6">
-        <v>10.88</v>
+        <v>7.68</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.58</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1994,13 +1988,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-20.24</v>
+        <v>-20.45</v>
       </c>
       <c r="D24" s="6">
-        <v>-20.45</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.21</v>
+        <v>-18.52</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.93</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2011,13 +2005,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-21.77</v>
+        <v>-25.26</v>
       </c>
       <c r="D25" s="6">
-        <v>-25.26</v>
+        <v>-29.29</v>
       </c>
       <c r="E25" s="7">
-        <v>-3.49</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2028,13 +2022,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-23.73</v>
+        <v>-25</v>
       </c>
       <c r="D26" s="6">
-        <v>-25</v>
+        <v>-27.72</v>
       </c>
       <c r="E26" s="7">
-        <v>-1.27</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2045,13 +2039,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-22.67</v>
+        <v>-24.22</v>
       </c>
       <c r="D27" s="6">
-        <v>-24.22</v>
+        <v>-27.52</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.55</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2062,13 +2056,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-6.39</v>
+        <v>-6.2</v>
       </c>
       <c r="D28" s="6">
-        <v>-6.2</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.19</v>
+        <v>-8.34</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2079,13 +2073,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-31.18</v>
+        <v>-31.83</v>
       </c>
       <c r="D29" s="6">
-        <v>-31.83</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.65</v>
+        <v>-30.86</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.97</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2096,13 +2090,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-26.35</v>
+        <v>-28.05</v>
       </c>
       <c r="D30" s="6">
-        <v>-28.05</v>
+        <v>-31.14</v>
       </c>
       <c r="E30" s="7">
-        <v>-1.7</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2113,13 +2107,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-30.9</v>
+        <v>-31.52</v>
       </c>
       <c r="D31" s="6">
-        <v>-31.52</v>
+        <v>-32.58</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.62</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2130,13 +2124,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>710.45</v>
+        <v>696.25</v>
       </c>
       <c r="D32" s="6">
-        <v>696.25</v>
+        <v>665.9</v>
       </c>
       <c r="E32" s="7">
-        <v>-14.2</v>
+        <v>-30.35</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2147,13 +2141,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>632.85</v>
+        <v>634.15</v>
       </c>
       <c r="D33" s="6">
-        <v>634.15</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.3</v>
+        <v>619.7</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-14.45</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2164,13 +2158,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="D34" s="6">
-        <v>847</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-8</v>
+        <v>859</v>
+      </c>
+      <c r="E34" s="8">
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2181,13 +2175,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>1044.2</v>
+        <v>1020</v>
       </c>
       <c r="D35" s="6">
-        <v>1020</v>
+        <v>976.2</v>
       </c>
       <c r="E35" s="7">
-        <v>-24.2</v>
+        <v>-43.8</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2198,47 +2192,47 @@
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>1603.3</v>
+        <v>1589</v>
       </c>
       <c r="D36" s="6">
-        <v>1589</v>
+        <v>1564.3</v>
       </c>
       <c r="E36" s="7">
-        <v>-14.3</v>
+        <v>-24.7</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C37" s="6">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="D37" s="6">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E37" s="8">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C38" s="6">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="D38" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E38" s="7">
-        <v>-1</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2249,13 +2243,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>51.03</v>
+        <v>48.28</v>
       </c>
       <c r="D39" s="6">
-        <v>48.28</v>
+        <v>42.96</v>
       </c>
       <c r="E39" s="7">
-        <v>-2.75</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2266,13 +2260,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>48.69</v>
+        <v>49.28</v>
       </c>
       <c r="D40" s="6">
-        <v>49.28</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.59</v>
+        <v>43.31</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-5.97</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2283,13 +2277,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>41.67</v>
+        <v>38.97</v>
       </c>
       <c r="D41" s="6">
-        <v>38.97</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-2.7</v>
+        <v>44.74</v>
+      </c>
+      <c r="E41" s="8">
+        <v>5.77</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2300,13 +2294,13 @@
         <v>24</v>
       </c>
       <c r="C42" s="6">
-        <v>44.27</v>
+        <v>39.33</v>
       </c>
       <c r="D42" s="6">
-        <v>39.33</v>
+        <v>32.32</v>
       </c>
       <c r="E42" s="7">
-        <v>-4.94</v>
+        <v>-7.01</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2317,13 +2311,13 @@
         <v>24</v>
       </c>
       <c r="C43" s="6">
-        <v>39.34</v>
+        <v>37.77</v>
       </c>
       <c r="D43" s="6">
-        <v>37.77</v>
+        <v>35.16</v>
       </c>
       <c r="E43" s="7">
-        <v>-1.57</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2334,13 +2328,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>-92.36</v>
+        <v>-89.34999999999999</v>
       </c>
       <c r="D44" s="6">
-        <v>-89.34999999999999</v>
+        <v>-82.65000000000001</v>
       </c>
       <c r="E44" s="8">
-        <v>3.01</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2351,13 +2345,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>63</v>
+        <v>-53.03</v>
       </c>
       <c r="D45" s="6">
-        <v>-53.03</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-116.03</v>
+        <v>-45.61</v>
+      </c>
+      <c r="E45" s="8">
+        <v>7.42</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2368,13 +2362,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>33.16</v>
+        <v>-23.58</v>
       </c>
       <c r="D46" s="6">
-        <v>-23.58</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-56.74</v>
+        <v>97.81999999999999</v>
+      </c>
+      <c r="E46" s="8">
+        <v>121.4</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2385,13 +2379,13 @@
         <v>31</v>
       </c>
       <c r="C47" s="6">
-        <v>-53.83</v>
+        <v>-59.53</v>
       </c>
       <c r="D47" s="6">
-        <v>-59.53</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-5.7</v>
+        <v>-46.85</v>
+      </c>
+      <c r="E47" s="8">
+        <v>12.68</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2402,13 +2396,13 @@
         <v>31</v>
       </c>
       <c r="C48" s="6">
-        <v>-13.92</v>
+        <v>-43.37</v>
       </c>
       <c r="D48" s="6">
-        <v>-43.37</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-29.45</v>
+        <v>15.75</v>
+      </c>
+      <c r="E48" s="8">
+        <v>59.12</v>
       </c>
     </row>
   </sheetData>
@@ -2438,28 +2432,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2467,22 +2461,22 @@
         <v>42</v>
       </c>
       <c r="B2" s="11">
-        <v>49.92</v>
+        <v>41.92</v>
       </c>
       <c r="C2" s="12">
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>42.7</v>
+        <v>39.7</v>
       </c>
       <c r="E2" s="11">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-5.7</v>
+        <v>-7.3</v>
       </c>
       <c r="G2" s="11">
-        <v>-11.7</v>
+        <v>-13.9</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2607,19 +2601,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.1249</v>
+        <v>0.1114</v>
       </c>
       <c r="B2" s="14">
-        <v>0.014</v>
+        <v>0.0113</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0253</v>
+        <v>-0.0165</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.0784</v>
+        <v>-0.0728</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1125</v>
+        <v>-0.1149</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,28 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 DEATH CROSS</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +252,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,15 +368,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -912,10 +890,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>665.9</v>
+        <v>669.2</v>
       </c>
       <c r="D2">
-        <v>-4.36</v>
+        <v>0.5</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -924,22 +902,22 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-27.52</v>
+        <v>-27.16</v>
       </c>
       <c r="H2">
-        <v>27.6</v>
+        <v>28.24</v>
       </c>
       <c r="I2">
-        <v>-8.199999999999999</v>
+        <v>-7.23</v>
       </c>
       <c r="J2">
-        <v>-8.369999999999999</v>
+        <v>-6.98</v>
       </c>
       <c r="K2">
-        <v>-1.86</v>
+        <v>-0.53</v>
       </c>
       <c r="L2">
-        <v>-8.640000000000001</v>
+        <v>-8.06</v>
       </c>
       <c r="M2">
         <v>-11.49</v>
@@ -948,22 +926,22 @@
         <v>80</v>
       </c>
       <c r="O2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P2">
-        <v>704.09</v>
+        <v>693.66</v>
       </c>
       <c r="Q2">
-        <v>722.28</v>
+        <v>716.01</v>
       </c>
       <c r="R2">
-        <v>663.5</v>
+        <v>664.47</v>
       </c>
       <c r="S2">
-        <v>668.08</v>
+        <v>667.88</v>
       </c>
       <c r="T2">
-        <v>-0.33</v>
+        <v>0.2</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -975,37 +953,37 @@
         <v>44</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>42.96</v>
+        <v>43.69</v>
       </c>
       <c r="Z2">
-        <v>6.13</v>
+        <v>2.52</v>
       </c>
       <c r="AA2">
-        <v>14.84</v>
+        <v>12.38</v>
       </c>
       <c r="AB2">
-        <v>-8.710000000000001</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD2">
-        <v>10.19</v>
+        <v>4.43</v>
       </c>
       <c r="AE2">
-        <v>39.83</v>
+        <v>41.4</v>
       </c>
       <c r="AF2">
-        <v>-82.65000000000001</v>
+        <v>-71.68000000000001</v>
       </c>
       <c r="AG2">
-        <v>774.64</v>
+        <v>761.53</v>
       </c>
       <c r="AH2">
-        <v>669.91</v>
+        <v>670.49</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -1014,7 +992,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>29.14</v>
+        <v>27.22</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1025,10 +1003,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>619.7</v>
+        <v>633</v>
       </c>
       <c r="D3">
-        <v>-2.28</v>
+        <v>2.15</v>
       </c>
       <c r="E3">
         <v>676.05</v>
@@ -1037,46 +1015,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-8.34</v>
+        <v>-6.37</v>
       </c>
       <c r="H3">
-        <v>20.8</v>
+        <v>23.39</v>
       </c>
       <c r="I3">
-        <v>-2.22</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J3">
-        <v>-6.33</v>
+        <v>-4.19</v>
       </c>
       <c r="K3">
-        <v>7.68</v>
+        <v>11.19</v>
       </c>
       <c r="L3">
-        <v>-5.09</v>
+        <v>-3.96</v>
       </c>
       <c r="M3">
-        <v>1.13</v>
+        <v>1.74</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="P3">
-        <v>626.96</v>
+        <v>627.98</v>
       </c>
       <c r="Q3">
-        <v>639.15</v>
+        <v>638.11</v>
       </c>
       <c r="R3">
-        <v>627.73</v>
+        <v>629.27</v>
       </c>
       <c r="S3">
-        <v>589.17</v>
+        <v>589.49</v>
       </c>
       <c r="T3">
-        <v>5.18</v>
+        <v>7.38</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1091,34 +1069,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>43.31</v>
+        <v>49.39</v>
       </c>
       <c r="Z3">
-        <v>-2.68</v>
+        <v>-2.4</v>
       </c>
       <c r="AA3">
-        <v>0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="AB3">
-        <v>-2.96</v>
+        <v>-2.15</v>
       </c>
       <c r="AC3">
-        <v>42.03</v>
+        <v>44.23</v>
       </c>
       <c r="AD3">
-        <v>34.5</v>
+        <v>42.07</v>
       </c>
       <c r="AE3">
-        <v>20.51</v>
+        <v>21.08</v>
       </c>
       <c r="AF3">
-        <v>-45.61</v>
+        <v>-50.31</v>
       </c>
       <c r="AG3">
-        <v>669.88</v>
+        <v>668.13</v>
       </c>
       <c r="AH3">
-        <v>608.42</v>
+        <v>608.08</v>
       </c>
       <c r="AI3">
         <v>613.74</v>
@@ -1127,7 +1105,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>20.13</v>
+        <v>23.26</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1138,10 +1116,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>859</v>
+        <v>860.2</v>
       </c>
       <c r="D4">
-        <v>1.42</v>
+        <v>0.14</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1150,46 +1128,46 @@
         <v>837</v>
       </c>
       <c r="G4">
-        <v>-30.86</v>
+        <v>-30.76</v>
       </c>
       <c r="H4">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="I4">
-        <v>-1.12</v>
+        <v>-1.27</v>
       </c>
       <c r="J4">
-        <v>-2.39</v>
+        <v>-0.84</v>
       </c>
       <c r="K4">
-        <v>-18.52</v>
+        <v>-19.52</v>
       </c>
       <c r="L4">
-        <v>-21.59</v>
+        <v>-22.15</v>
       </c>
       <c r="M4">
-        <v>-1.65</v>
+        <v>-1.29</v>
       </c>
       <c r="N4">
         <v>60</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P4">
-        <v>860.34</v>
+        <v>858.12</v>
       </c>
       <c r="Q4">
-        <v>862.22</v>
+        <v>861.55</v>
       </c>
       <c r="R4">
-        <v>890.26</v>
+        <v>886.8099999999999</v>
       </c>
       <c r="S4">
-        <v>1041.94</v>
+        <v>1040.08</v>
       </c>
       <c r="T4">
-        <v>-17.56</v>
+        <v>-17.29</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1204,34 +1182,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>44.74</v>
+        <v>45.3</v>
       </c>
       <c r="Z4">
-        <v>-10</v>
+        <v>-9.27</v>
       </c>
       <c r="AA4">
-        <v>-12.67</v>
+        <v>-11.99</v>
       </c>
       <c r="AB4">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="AC4">
-        <v>69.12</v>
+        <v>75.27</v>
       </c>
       <c r="AD4">
-        <v>76.81</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="AE4">
-        <v>18.61</v>
+        <v>18.76</v>
       </c>
       <c r="AF4">
-        <v>97.81999999999999</v>
+        <v>-22.84</v>
       </c>
       <c r="AG4">
-        <v>887.28</v>
+        <v>886.04</v>
       </c>
       <c r="AH4">
-        <v>837.16</v>
+        <v>837.0599999999999</v>
       </c>
       <c r="AI4">
         <v>891.26</v>
@@ -1240,7 +1218,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>26.98</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1251,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>976.2</v>
+        <v>951.9</v>
       </c>
       <c r="D5">
-        <v>-4.29</v>
+        <v>-2.49</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1263,46 +1241,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-31.14</v>
+        <v>-32.86</v>
       </c>
       <c r="H5">
-        <v>30.33</v>
+        <v>27.09</v>
       </c>
       <c r="I5">
-        <v>-2.18</v>
+        <v>-5.19</v>
       </c>
       <c r="J5">
-        <v>-11.85</v>
+        <v>-13.6</v>
       </c>
       <c r="K5">
-        <v>-29.29</v>
+        <v>-29.74</v>
       </c>
       <c r="L5">
-        <v>-8.82</v>
+        <v>-12.06</v>
       </c>
       <c r="M5">
-        <v>11.14</v>
+        <v>10.46</v>
       </c>
       <c r="N5">
         <v>40</v>
       </c>
       <c r="O5">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P5">
-        <v>1014.98</v>
+        <v>1004.56</v>
       </c>
       <c r="Q5">
-        <v>1038.07</v>
+        <v>1030.68</v>
       </c>
       <c r="R5">
-        <v>1120.49</v>
+        <v>1113.69</v>
       </c>
       <c r="S5">
-        <v>1073.37</v>
+        <v>1072.98</v>
       </c>
       <c r="T5">
-        <v>-9.050000000000001</v>
+        <v>-11.28</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1317,43 +1295,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>32.32</v>
+        <v>29.2</v>
       </c>
       <c r="Z5">
-        <v>-34.74</v>
+        <v>-37.58</v>
       </c>
       <c r="AA5">
-        <v>-37.45</v>
+        <v>-37.47</v>
       </c>
       <c r="AB5">
-        <v>2.7</v>
+        <v>-0.1</v>
       </c>
       <c r="AC5">
-        <v>71.45</v>
+        <v>45.98</v>
       </c>
       <c r="AD5">
-        <v>82.52</v>
+        <v>69.7</v>
       </c>
       <c r="AE5">
-        <v>40.11</v>
+        <v>39.21</v>
       </c>
       <c r="AF5">
-        <v>-46.85</v>
+        <v>-64.58</v>
       </c>
       <c r="AG5">
-        <v>1120.99</v>
+        <v>1116.78</v>
       </c>
       <c r="AH5">
-        <v>955.15</v>
+        <v>944.59</v>
       </c>
       <c r="AI5">
-        <v>1101.68</v>
+        <v>1080.42</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>33.16</v>
+        <v>31.09</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1364,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1564.3</v>
+        <v>1565</v>
       </c>
       <c r="D6">
-        <v>-1.55</v>
+        <v>0.04</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1376,46 +1354,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-32.58</v>
+        <v>-32.55</v>
       </c>
       <c r="H6">
-        <v>6.32</v>
+        <v>6.37</v>
       </c>
       <c r="I6">
-        <v>-1.88</v>
+        <v>-0.48</v>
       </c>
       <c r="J6">
-        <v>-7.5</v>
+        <v>-7.77</v>
       </c>
       <c r="K6">
-        <v>-27.72</v>
+        <v>-24.8</v>
       </c>
       <c r="L6">
-        <v>-26.75</v>
+        <v>-29.03</v>
       </c>
       <c r="M6">
-        <v>-7.28</v>
+        <v>-7.82</v>
       </c>
       <c r="N6">
         <v>20</v>
       </c>
       <c r="O6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P6">
-        <v>1589.2</v>
+        <v>1587.7</v>
       </c>
       <c r="Q6">
-        <v>1613.29</v>
+        <v>1606.57</v>
       </c>
       <c r="R6">
-        <v>1808.5</v>
+        <v>1797.63</v>
       </c>
       <c r="S6">
-        <v>1808.81</v>
+        <v>1806.56</v>
       </c>
       <c r="T6">
-        <v>-13.52</v>
+        <v>-13.37</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1430,34 +1408,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>35.16</v>
+        <v>35.29</v>
       </c>
       <c r="Z6">
-        <v>-62.73</v>
+        <v>-60.5</v>
       </c>
       <c r="AA6">
-        <v>-74.86</v>
+        <v>-71.98999999999999</v>
       </c>
       <c r="AB6">
-        <v>12.13</v>
+        <v>11.48</v>
       </c>
       <c r="AC6">
-        <v>81.70999999999999</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="AD6">
-        <v>88.51000000000001</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="AE6">
-        <v>49.43</v>
+        <v>49.12</v>
       </c>
       <c r="AF6">
-        <v>15.75</v>
+        <v>6.82</v>
       </c>
       <c r="AG6">
-        <v>1718.75</v>
+        <v>1705.85</v>
       </c>
       <c r="AH6">
-        <v>1507.83</v>
+        <v>1507.28</v>
       </c>
       <c r="AI6">
         <v>1690.77</v>
@@ -1466,7 +1444,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>38.13</v>
+        <v>36.1</v>
       </c>
     </row>
   </sheetData>
@@ -1607,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1627,47 +1605,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1675,734 +1618,700 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-7.8</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-8.369999999999999</v>
       </c>
-      <c r="E7" s="7">
-        <v>-0.57</v>
+      <c r="D7" s="5">
+        <v>-6.98</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.39</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-2.98</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-6.33</v>
       </c>
-      <c r="E8" s="7">
-        <v>-3.35</v>
+      <c r="D8" s="5">
+        <v>-4.19</v>
+      </c>
+      <c r="E8" s="6">
+        <v>2.14</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-2.98</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-2.39</v>
       </c>
-      <c r="E9" s="8">
-        <v>0.59</v>
+      <c r="D9" s="5">
+        <v>-0.84</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-9.52</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-11.85</v>
       </c>
+      <c r="D10" s="5">
+        <v>-13.6</v>
+      </c>
       <c r="E10" s="7">
-        <v>-2.33</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-5.32</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-7.5</v>
       </c>
+      <c r="D11" s="5">
+        <v>-7.77</v>
+      </c>
       <c r="E11" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-7.23</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-2.22</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E13" s="6">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-1.12</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-1.27</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
         <v>-2.18</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D15" s="5">
+        <v>-5.19</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-3.01</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-1.88</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.48</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-4.73</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-3.47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-8.640000000000001</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-8.06</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.66</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-2.22</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-2.88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-5.09</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-3.96</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-0.59</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-1.12</v>
-      </c>
-      <c r="E14" s="7">
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-21.59</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-22.15</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-8.82</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-12.06</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-3.24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-26.75</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-29.03</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-2.28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-1.86</v>
+      </c>
+      <c r="D22" s="5">
         <v>-0.53</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="E22" s="6">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>7.68</v>
+      </c>
+      <c r="D23" s="5">
+        <v>11.19</v>
+      </c>
+      <c r="E23" s="6">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-18.52</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-19.52</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>3.47</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-2.18</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-5.65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-29.29</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-29.74</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>2.88</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-1.88</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-4.76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-27.72</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-24.8</v>
+      </c>
+      <c r="E26" s="6">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-5.49</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-8.640000000000001</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-3.15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-27.52</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-27.16</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-3.39</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-5.09</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-8.34</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-6.37</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-22.04</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-21.59</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-30.86</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-30.76</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-4.04</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-8.82</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-4.78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-31.14</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-32.86</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-22.77</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-26.75</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-3.98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-32.58</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-32.55</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>1.52</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-1.86</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-3.38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>665.9</v>
+      </c>
+      <c r="D32" s="5">
+        <v>669.2</v>
+      </c>
+      <c r="E32" s="6">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>10.88</v>
-      </c>
-      <c r="D23" s="6">
-        <v>7.68</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>619.7</v>
+      </c>
+      <c r="D33" s="5">
+        <v>633</v>
+      </c>
+      <c r="E33" s="6">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-20.45</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-18.52</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.93</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>859</v>
+      </c>
+      <c r="D34" s="5">
+        <v>860.2</v>
+      </c>
+      <c r="E34" s="6">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-25.26</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-29.29</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-4.03</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>976.2</v>
+      </c>
+      <c r="D35" s="5">
+        <v>951.9</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-24.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-25</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-27.72</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1564.3</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1565</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-24.22</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-27.52</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-3.3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>42.96</v>
+      </c>
+      <c r="D37" s="5">
+        <v>43.69</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-6.2</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-8.34</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>43.31</v>
+      </c>
+      <c r="D38" s="5">
+        <v>49.39</v>
+      </c>
+      <c r="E38" s="6">
+        <v>6.08</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-31.83</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-30.86</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>44.74</v>
+      </c>
+      <c r="D39" s="5">
+        <v>45.3</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-28.05</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-31.14</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-3.09</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>32.32</v>
+      </c>
+      <c r="D40" s="5">
+        <v>29.2</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-3.12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-31.52</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-32.58</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>35.16</v>
+      </c>
+      <c r="D41" s="5">
+        <v>35.29</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>696.25</v>
-      </c>
-      <c r="D32" s="6">
-        <v>665.9</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-30.35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-82.65000000000001</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-71.68000000000001</v>
+      </c>
+      <c r="E42" s="6">
+        <v>10.97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>634.15</v>
-      </c>
-      <c r="D33" s="6">
-        <v>619.7</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-14.45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-45.61</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-50.31</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-4.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>847</v>
-      </c>
-      <c r="D34" s="6">
-        <v>859</v>
-      </c>
-      <c r="E34" s="8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>97.81999999999999</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-22.84</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-120.66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1020</v>
-      </c>
-      <c r="D35" s="6">
-        <v>976.2</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-43.8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-46.85</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-64.58</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-17.73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>1589</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1564.3</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-24.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="6">
-        <v>40</v>
-      </c>
-      <c r="D37" s="6">
-        <v>60</v>
-      </c>
-      <c r="E37" s="8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="6">
-        <v>60</v>
-      </c>
-      <c r="D38" s="6">
-        <v>40</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>48.28</v>
-      </c>
-      <c r="D39" s="6">
-        <v>42.96</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-5.32</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>49.28</v>
-      </c>
-      <c r="D40" s="6">
-        <v>43.31</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-5.97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>38.97</v>
-      </c>
-      <c r="D41" s="6">
-        <v>44.74</v>
-      </c>
-      <c r="E41" s="8">
-        <v>5.77</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>39.33</v>
-      </c>
-      <c r="D42" s="6">
-        <v>32.32</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-7.01</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>37.77</v>
-      </c>
-      <c r="D43" s="6">
-        <v>35.16</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-2.61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="6">
-        <v>-89.34999999999999</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-82.65000000000001</v>
-      </c>
-      <c r="E44" s="8">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-53.03</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-45.61</v>
-      </c>
-      <c r="E45" s="8">
-        <v>7.42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-23.58</v>
-      </c>
-      <c r="D46" s="6">
-        <v>97.81999999999999</v>
-      </c>
-      <c r="E46" s="8">
-        <v>121.4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-59.53</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-46.85</v>
-      </c>
-      <c r="E47" s="8">
-        <v>12.68</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-43.37</v>
-      </c>
-      <c r="D48" s="6">
+      <c r="C46" s="5">
         <v>15.75</v>
       </c>
-      <c r="E48" s="8">
-        <v>59.12</v>
+      <c r="D46" s="5">
+        <v>6.82</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-8.93</v>
       </c>
     </row>
   </sheetData>
@@ -2428,60 +2337,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>68</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
-        <v>41.92</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="10">
+        <v>49.92</v>
+      </c>
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.7</v>
-      </c>
-      <c r="E2" s="11">
-        <v>20</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-7.3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-13.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="10">
+        <v>40.6</v>
+      </c>
+      <c r="E2" s="10">
+        <v>40</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-6.7</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-12.7</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2583,36 +2492,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1114</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0113</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0165</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0728</v>
-      </c>
-      <c r="E2" s="14">
+      <c r="A2" s="13">
+        <v>0.1046</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0174</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0129</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.07820000000000001</v>
+      </c>
+      <c r="E2" s="13">
         <v>-0.1149</v>
       </c>
     </row>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -252,14 +252,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -750,7 +750,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -890,10 +892,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>669.2</v>
+        <v>663.7</v>
       </c>
       <c r="D2">
-        <v>0.5</v>
+        <v>-0.82</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -902,46 +904,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-27.16</v>
+        <v>-27.76</v>
       </c>
       <c r="H2">
-        <v>28.24</v>
+        <v>27.18</v>
       </c>
       <c r="I2">
-        <v>-7.23</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="J2">
-        <v>-6.98</v>
+        <v>-16.46</v>
       </c>
       <c r="K2">
-        <v>-0.53</v>
+        <v>-0.28</v>
       </c>
       <c r="L2">
-        <v>-8.06</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="M2">
-        <v>-11.49</v>
+        <v>-11.08</v>
       </c>
       <c r="N2">
         <v>80</v>
       </c>
       <c r="O2">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="P2">
-        <v>693.66</v>
+        <v>681.1</v>
       </c>
       <c r="Q2">
-        <v>716.01</v>
+        <v>711.3200000000001</v>
       </c>
       <c r="R2">
-        <v>664.47</v>
+        <v>665.4400000000001</v>
       </c>
       <c r="S2">
-        <v>667.88</v>
+        <v>667.63</v>
       </c>
       <c r="T2">
-        <v>0.2</v>
+        <v>-0.59</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -953,37 +955,37 @@
         <v>44</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>43.69</v>
+        <v>42.71</v>
       </c>
       <c r="Z2">
-        <v>2.52</v>
+        <v>-0.78</v>
       </c>
       <c r="AA2">
-        <v>12.38</v>
+        <v>9.75</v>
       </c>
       <c r="AB2">
-        <v>-9.859999999999999</v>
+        <v>-10.53</v>
       </c>
       <c r="AC2">
         <v>1.57</v>
       </c>
       <c r="AD2">
-        <v>4.43</v>
+        <v>1.05</v>
       </c>
       <c r="AE2">
-        <v>41.4</v>
+        <v>41.16</v>
       </c>
       <c r="AF2">
-        <v>-71.68000000000001</v>
+        <v>-84.98999999999999</v>
       </c>
       <c r="AG2">
-        <v>761.53</v>
+        <v>758.16</v>
       </c>
       <c r="AH2">
-        <v>670.49</v>
+        <v>664.48</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -992,7 +994,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>27.22</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,10 +1005,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>633</v>
+        <v>607.5</v>
       </c>
       <c r="D3">
-        <v>2.15</v>
+        <v>-4.03</v>
       </c>
       <c r="E3">
         <v>676.05</v>
@@ -1015,46 +1017,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-6.37</v>
+        <v>-10.14</v>
       </c>
       <c r="H3">
-        <v>23.39</v>
+        <v>18.42</v>
       </c>
       <c r="I3">
-        <v>0.8100000000000001</v>
+        <v>-2.05</v>
       </c>
       <c r="J3">
-        <v>-4.19</v>
+        <v>-7.1</v>
       </c>
       <c r="K3">
-        <v>11.19</v>
+        <v>8.25</v>
       </c>
       <c r="L3">
-        <v>-3.96</v>
+        <v>-7.6</v>
       </c>
       <c r="M3">
-        <v>1.74</v>
+        <v>2.03</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="P3">
-        <v>627.98</v>
+        <v>625.4400000000001</v>
       </c>
       <c r="Q3">
-        <v>638.11</v>
+        <v>634.98</v>
       </c>
       <c r="R3">
-        <v>629.27</v>
+        <v>630.49</v>
       </c>
       <c r="S3">
-        <v>589.49</v>
+        <v>589.66</v>
       </c>
       <c r="T3">
-        <v>7.38</v>
+        <v>3.03</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1069,43 +1071,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>49.39</v>
+        <v>40.43</v>
       </c>
       <c r="Z3">
-        <v>-2.4</v>
+        <v>-4.19</v>
       </c>
       <c r="AA3">
-        <v>-0.26</v>
+        <v>-1.04</v>
       </c>
       <c r="AB3">
-        <v>-2.15</v>
+        <v>-3.15</v>
       </c>
       <c r="AC3">
-        <v>44.23</v>
+        <v>23.32</v>
       </c>
       <c r="AD3">
-        <v>42.07</v>
+        <v>36.53</v>
       </c>
       <c r="AE3">
-        <v>21.08</v>
+        <v>21.71</v>
       </c>
       <c r="AF3">
-        <v>-50.31</v>
+        <v>-4.64</v>
       </c>
       <c r="AG3">
-        <v>668.13</v>
+        <v>664.01</v>
       </c>
       <c r="AH3">
-        <v>608.08</v>
+        <v>605.95</v>
       </c>
       <c r="AI3">
-        <v>613.74</v>
+        <v>682.52</v>
       </c>
       <c r="AJ3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AK3">
-        <v>23.26</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,10 +1118,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>860.2</v>
+        <v>856.35</v>
       </c>
       <c r="D4">
-        <v>0.14</v>
+        <v>-0.45</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1128,46 +1130,46 @@
         <v>837</v>
       </c>
       <c r="G4">
-        <v>-30.76</v>
+        <v>-31.07</v>
       </c>
       <c r="H4">
-        <v>2.77</v>
+        <v>2.31</v>
       </c>
       <c r="I4">
-        <v>-1.27</v>
+        <v>-1.5</v>
       </c>
       <c r="J4">
-        <v>-0.84</v>
+        <v>-1.97</v>
       </c>
       <c r="K4">
-        <v>-19.52</v>
+        <v>-19.11</v>
       </c>
       <c r="L4">
-        <v>-22.15</v>
+        <v>-23.32</v>
       </c>
       <c r="M4">
-        <v>-1.29</v>
+        <v>-0.99</v>
       </c>
       <c r="N4">
         <v>60</v>
       </c>
       <c r="O4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="P4">
-        <v>858.12</v>
+        <v>855.51</v>
       </c>
       <c r="Q4">
-        <v>861.55</v>
+        <v>860.38</v>
       </c>
       <c r="R4">
-        <v>886.8099999999999</v>
+        <v>883.4400000000001</v>
       </c>
       <c r="S4">
-        <v>1040.08</v>
+        <v>1038.24</v>
       </c>
       <c r="T4">
-        <v>-17.29</v>
+        <v>-17.52</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1182,34 +1184,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>45.3</v>
+        <v>43.77</v>
       </c>
       <c r="Z4">
-        <v>-9.27</v>
+        <v>-8.9</v>
       </c>
       <c r="AA4">
-        <v>-11.99</v>
+        <v>-11.37</v>
       </c>
       <c r="AB4">
-        <v>2.72</v>
+        <v>2.47</v>
       </c>
       <c r="AC4">
-        <v>75.27</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AD4">
-        <v>72.51000000000001</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="AE4">
-        <v>18.76</v>
+        <v>19.22</v>
       </c>
       <c r="AF4">
-        <v>-22.84</v>
+        <v>-16.73</v>
       </c>
       <c r="AG4">
-        <v>886.04</v>
+        <v>883.4</v>
       </c>
       <c r="AH4">
-        <v>837.0599999999999</v>
+        <v>837.36</v>
       </c>
       <c r="AI4">
         <v>891.26</v>
@@ -1218,7 +1220,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>25.1</v>
+        <v>25.43</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1231,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>951.9</v>
+        <v>925.7</v>
       </c>
       <c r="D5">
-        <v>-2.49</v>
+        <v>-2.75</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1241,25 +1243,25 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-32.86</v>
+        <v>-34.7</v>
       </c>
       <c r="H5">
-        <v>27.09</v>
+        <v>23.59</v>
       </c>
       <c r="I5">
-        <v>-5.19</v>
+        <v>-10.17</v>
       </c>
       <c r="J5">
-        <v>-13.6</v>
+        <v>-15.81</v>
       </c>
       <c r="K5">
-        <v>-29.74</v>
+        <v>-31.21</v>
       </c>
       <c r="L5">
-        <v>-12.06</v>
+        <v>-14.44</v>
       </c>
       <c r="M5">
-        <v>10.46</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N5">
         <v>40</v>
@@ -1268,19 +1270,19 @@
         <v>25</v>
       </c>
       <c r="P5">
-        <v>1004.56</v>
+        <v>983.6</v>
       </c>
       <c r="Q5">
-        <v>1030.68</v>
+        <v>1021.67</v>
       </c>
       <c r="R5">
-        <v>1113.69</v>
+        <v>1106.4</v>
       </c>
       <c r="S5">
-        <v>1072.98</v>
+        <v>1072.5</v>
       </c>
       <c r="T5">
-        <v>-11.28</v>
+        <v>-13.69</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1295,43 +1297,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>29.2</v>
+        <v>26.26</v>
       </c>
       <c r="Z5">
-        <v>-37.58</v>
+        <v>-41.45</v>
       </c>
       <c r="AA5">
-        <v>-37.47</v>
+        <v>-38.27</v>
       </c>
       <c r="AB5">
-        <v>-0.1</v>
+        <v>-3.18</v>
       </c>
       <c r="AC5">
-        <v>45.98</v>
+        <v>23.3</v>
       </c>
       <c r="AD5">
-        <v>69.7</v>
+        <v>46.91</v>
       </c>
       <c r="AE5">
-        <v>39.21</v>
+        <v>39.61</v>
       </c>
       <c r="AF5">
-        <v>-64.58</v>
+        <v>-1.91</v>
       </c>
       <c r="AG5">
-        <v>1116.78</v>
+        <v>1112.21</v>
       </c>
       <c r="AH5">
-        <v>944.59</v>
+        <v>931.13</v>
       </c>
       <c r="AI5">
-        <v>1080.42</v>
+        <v>1048.49</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>31.09</v>
+        <v>31.84</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1344,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1565</v>
+        <v>1496.5</v>
       </c>
       <c r="D6">
-        <v>0.04</v>
+        <v>-4.38</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1354,46 +1356,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-32.55</v>
+        <v>-35.5</v>
       </c>
       <c r="H6">
-        <v>6.37</v>
+        <v>1.71</v>
       </c>
       <c r="I6">
-        <v>-0.48</v>
+        <v>-7.45</v>
       </c>
       <c r="J6">
-        <v>-7.77</v>
+        <v>-11.94</v>
       </c>
       <c r="K6">
-        <v>-24.8</v>
+        <v>-26.68</v>
       </c>
       <c r="L6">
-        <v>-29.03</v>
+        <v>-33.08</v>
       </c>
       <c r="M6">
-        <v>-7.82</v>
+        <v>-8.08</v>
       </c>
       <c r="N6">
         <v>20</v>
       </c>
       <c r="O6">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P6">
-        <v>1587.7</v>
+        <v>1563.62</v>
       </c>
       <c r="Q6">
-        <v>1606.57</v>
+        <v>1596.01</v>
       </c>
       <c r="R6">
-        <v>1797.63</v>
+        <v>1786.8</v>
       </c>
       <c r="S6">
-        <v>1806.56</v>
+        <v>1803.7</v>
       </c>
       <c r="T6">
-        <v>-13.37</v>
+        <v>-17.03</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1408,43 +1410,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>35.29</v>
+        <v>28.89</v>
       </c>
       <c r="Z6">
-        <v>-60.5</v>
+        <v>-63.54</v>
       </c>
       <c r="AA6">
-        <v>-71.98999999999999</v>
+        <v>-70.3</v>
       </c>
       <c r="AB6">
-        <v>11.48</v>
+        <v>6.76</v>
       </c>
       <c r="AC6">
-        <v>74.48999999999999</v>
+        <v>58.64</v>
       </c>
       <c r="AD6">
-        <v>82.68000000000001</v>
+        <v>71.62</v>
       </c>
       <c r="AE6">
-        <v>49.12</v>
+        <v>53.17</v>
       </c>
       <c r="AF6">
-        <v>6.82</v>
+        <v>110.28</v>
       </c>
       <c r="AG6">
-        <v>1705.85</v>
+        <v>1694.95</v>
       </c>
       <c r="AH6">
-        <v>1507.28</v>
+        <v>1497.07</v>
       </c>
       <c r="AI6">
-        <v>1690.77</v>
+        <v>1680.86</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>36.1</v>
+        <v>38.32</v>
       </c>
     </row>
   </sheetData>
@@ -1642,13 +1644,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-8.369999999999999</v>
+        <v>-6.98</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.98</v>
+        <v>-16.46</v>
       </c>
       <c r="E7" s="6">
-        <v>1.39</v>
+        <v>-9.48</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1659,13 +1661,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-6.33</v>
+        <v>-4.19</v>
       </c>
       <c r="D8" s="5">
-        <v>-4.19</v>
+        <v>-7.1</v>
       </c>
       <c r="E8" s="6">
-        <v>2.14</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1676,13 +1678,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-2.39</v>
+        <v>-0.84</v>
       </c>
       <c r="D9" s="5">
-        <v>-0.84</v>
+        <v>-1.97</v>
       </c>
       <c r="E9" s="6">
-        <v>1.55</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1693,13 +1695,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-11.85</v>
+        <v>-13.6</v>
       </c>
       <c r="D10" s="5">
-        <v>-13.6</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.75</v>
+        <v>-15.81</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-2.21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1710,13 +1712,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-7.5</v>
+        <v>-7.77</v>
       </c>
       <c r="D11" s="5">
-        <v>-7.77</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.27</v>
+        <v>-11.94</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-4.17</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1727,13 +1729,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-8.199999999999999</v>
+        <v>-7.23</v>
       </c>
       <c r="D12" s="5">
-        <v>-7.23</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="E12" s="6">
-        <v>0.97</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1744,13 +1746,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-2.22</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D13" s="5">
-        <v>0.8100000000000001</v>
+        <v>-2.05</v>
       </c>
       <c r="E13" s="6">
-        <v>3.03</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1761,13 +1763,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-1.12</v>
+        <v>-1.27</v>
       </c>
       <c r="D14" s="5">
-        <v>-1.27</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.15</v>
+        <v>-1.5</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1778,13 +1780,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-2.18</v>
+        <v>-5.19</v>
       </c>
       <c r="D15" s="5">
-        <v>-5.19</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-3.01</v>
+        <v>-10.17</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-4.98</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1795,13 +1797,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-1.88</v>
+        <v>-0.48</v>
       </c>
       <c r="D16" s="5">
-        <v>-0.48</v>
+        <v>-7.45</v>
       </c>
       <c r="E16" s="6">
-        <v>1.4</v>
+        <v>-6.97</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1812,13 +1814,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>-8.640000000000001</v>
+        <v>-8.06</v>
       </c>
       <c r="D17" s="5">
-        <v>-8.06</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="E17" s="6">
-        <v>0.58</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1829,13 +1831,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-5.09</v>
+        <v>-3.96</v>
       </c>
       <c r="D18" s="5">
-        <v>-3.96</v>
+        <v>-7.6</v>
       </c>
       <c r="E18" s="6">
-        <v>1.13</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1846,13 +1848,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-21.59</v>
+        <v>-22.15</v>
       </c>
       <c r="D19" s="5">
-        <v>-22.15</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.5600000000000001</v>
+        <v>-23.32</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.17</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1863,13 +1865,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-8.82</v>
+        <v>-12.06</v>
       </c>
       <c r="D20" s="5">
-        <v>-12.06</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-3.24</v>
+        <v>-14.44</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-2.38</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1880,13 +1882,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-26.75</v>
+        <v>-29.03</v>
       </c>
       <c r="D21" s="5">
-        <v>-29.03</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-2.28</v>
+        <v>-33.08</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-4.05</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1897,13 +1899,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-1.86</v>
+        <v>-0.53</v>
       </c>
       <c r="D22" s="5">
-        <v>-0.53</v>
-      </c>
-      <c r="E22" s="6">
-        <v>1.33</v>
+        <v>-0.28</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.25</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1914,13 +1916,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>7.68</v>
+        <v>11.19</v>
       </c>
       <c r="D23" s="5">
-        <v>11.19</v>
+        <v>8.25</v>
       </c>
       <c r="E23" s="6">
-        <v>3.51</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1931,13 +1933,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-18.52</v>
+        <v>-19.52</v>
       </c>
       <c r="D24" s="5">
-        <v>-19.52</v>
+        <v>-19.11</v>
       </c>
       <c r="E24" s="7">
-        <v>-1</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1948,13 +1950,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-29.29</v>
+        <v>-29.74</v>
       </c>
       <c r="D25" s="5">
-        <v>-29.74</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.45</v>
+        <v>-31.21</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1965,13 +1967,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-27.72</v>
+        <v>-24.8</v>
       </c>
       <c r="D26" s="5">
-        <v>-24.8</v>
+        <v>-26.68</v>
       </c>
       <c r="E26" s="6">
-        <v>2.92</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1982,13 +1984,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-27.52</v>
+        <v>-27.16</v>
       </c>
       <c r="D27" s="5">
-        <v>-27.16</v>
+        <v>-27.76</v>
       </c>
       <c r="E27" s="6">
-        <v>0.36</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1999,13 +2001,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-8.34</v>
+        <v>-6.37</v>
       </c>
       <c r="D28" s="5">
-        <v>-6.37</v>
+        <v>-10.14</v>
       </c>
       <c r="E28" s="6">
-        <v>1.97</v>
+        <v>-3.77</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2016,13 +2018,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-30.86</v>
+        <v>-30.76</v>
       </c>
       <c r="D29" s="5">
-        <v>-30.76</v>
+        <v>-31.07</v>
       </c>
       <c r="E29" s="6">
-        <v>0.1</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2033,13 +2035,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-31.14</v>
+        <v>-32.86</v>
       </c>
       <c r="D30" s="5">
-        <v>-32.86</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.72</v>
+        <v>-34.7</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2050,13 +2052,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-32.58</v>
+        <v>-32.55</v>
       </c>
       <c r="D31" s="5">
-        <v>-32.55</v>
+        <v>-35.5</v>
       </c>
       <c r="E31" s="6">
-        <v>0.03</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2067,13 +2069,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>665.9</v>
+        <v>669.2</v>
       </c>
       <c r="D32" s="5">
-        <v>669.2</v>
+        <v>663.7</v>
       </c>
       <c r="E32" s="6">
-        <v>3.3</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2084,13 +2086,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>619.7</v>
+        <v>633</v>
       </c>
       <c r="D33" s="5">
-        <v>633</v>
+        <v>607.5</v>
       </c>
       <c r="E33" s="6">
-        <v>13.3</v>
+        <v>-25.5</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2101,13 +2103,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>859</v>
+        <v>860.2</v>
       </c>
       <c r="D34" s="5">
-        <v>860.2</v>
+        <v>856.35</v>
       </c>
       <c r="E34" s="6">
-        <v>1.2</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2118,13 +2120,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>976.2</v>
+        <v>951.9</v>
       </c>
       <c r="D35" s="5">
-        <v>951.9</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-24.3</v>
+        <v>925.7</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-26.2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2135,13 +2137,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>1564.3</v>
+        <v>1565</v>
       </c>
       <c r="D36" s="5">
-        <v>1565</v>
+        <v>1496.5</v>
       </c>
       <c r="E36" s="6">
-        <v>0.7</v>
+        <v>-68.5</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2152,13 +2154,13 @@
         <v>24</v>
       </c>
       <c r="C37" s="5">
-        <v>42.96</v>
+        <v>43.69</v>
       </c>
       <c r="D37" s="5">
-        <v>43.69</v>
+        <v>42.71</v>
       </c>
       <c r="E37" s="6">
-        <v>0.73</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2169,13 +2171,13 @@
         <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>43.31</v>
+        <v>49.39</v>
       </c>
       <c r="D38" s="5">
-        <v>49.39</v>
+        <v>40.43</v>
       </c>
       <c r="E38" s="6">
-        <v>6.08</v>
+        <v>-8.960000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2186,13 +2188,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>44.74</v>
+        <v>45.3</v>
       </c>
       <c r="D39" s="5">
-        <v>45.3</v>
+        <v>43.77</v>
       </c>
       <c r="E39" s="6">
-        <v>0.5600000000000001</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2203,13 +2205,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>32.32</v>
+        <v>29.2</v>
       </c>
       <c r="D40" s="5">
-        <v>29.2</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-3.12</v>
+        <v>26.26</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-2.94</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2220,13 +2222,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>35.16</v>
+        <v>35.29</v>
       </c>
       <c r="D41" s="5">
-        <v>35.29</v>
+        <v>28.89</v>
       </c>
       <c r="E41" s="6">
-        <v>0.13</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2237,13 +2239,13 @@
         <v>31</v>
       </c>
       <c r="C42" s="5">
-        <v>-82.65000000000001</v>
+        <v>-71.68000000000001</v>
       </c>
       <c r="D42" s="5">
-        <v>-71.68000000000001</v>
+        <v>-84.98999999999999</v>
       </c>
       <c r="E42" s="6">
-        <v>10.97</v>
+        <v>-13.31</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2254,13 +2256,13 @@
         <v>31</v>
       </c>
       <c r="C43" s="5">
-        <v>-45.61</v>
+        <v>-50.31</v>
       </c>
       <c r="D43" s="5">
-        <v>-50.31</v>
+        <v>-4.64</v>
       </c>
       <c r="E43" s="7">
-        <v>-4.7</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2271,13 +2273,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>97.81999999999999</v>
+        <v>-22.84</v>
       </c>
       <c r="D44" s="5">
-        <v>-22.84</v>
+        <v>-16.73</v>
       </c>
       <c r="E44" s="7">
-        <v>-120.66</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2288,13 +2290,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-46.85</v>
+        <v>-64.58</v>
       </c>
       <c r="D45" s="5">
-        <v>-64.58</v>
+        <v>-1.91</v>
       </c>
       <c r="E45" s="7">
-        <v>-17.73</v>
+        <v>62.67</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2305,13 +2307,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>15.75</v>
+        <v>6.82</v>
       </c>
       <c r="D46" s="5">
-        <v>6.82</v>
+        <v>110.28</v>
       </c>
       <c r="E46" s="7">
-        <v>-8.93</v>
+        <v>103.46</v>
       </c>
     </row>
   </sheetData>
@@ -2370,22 +2372,22 @@
         <v>42</v>
       </c>
       <c r="B2" s="10">
-        <v>49.92</v>
+        <v>41.92</v>
       </c>
       <c r="C2" s="11">
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>40.6</v>
+        <v>36.4</v>
       </c>
       <c r="E2" s="10">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F2" s="10">
-        <v>-6.7</v>
+        <v>-10.7</v>
       </c>
       <c r="G2" s="10">
-        <v>-12.7</v>
+        <v>-13.8</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2510,19 +2512,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.1046</v>
+        <v>0.09949999999999999</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0174</v>
+        <v>0.0203</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0129</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.07820000000000001</v>
+        <v>-0.0808</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1149</v>
+        <v>-0.1108</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,43 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>26.3 → 32.8</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>26.3</t>
+  </si>
+  <si>
+    <t>32.8</t>
+  </si>
+  <si>
+    <t>28.9 → 34.3</t>
+  </si>
+  <si>
+    <t>28.9</t>
+  </si>
+  <si>
+    <t>34.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -252,14 +288,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +328,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,14 +404,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -750,9 +787,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -892,10 +928,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>663.7</v>
+        <v>652.85</v>
       </c>
       <c r="D2">
-        <v>-0.82</v>
+        <v>-1.63</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -904,46 +940,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-27.76</v>
+        <v>-28.94</v>
       </c>
       <c r="H2">
-        <v>27.18</v>
+        <v>25.1</v>
       </c>
       <c r="I2">
-        <v>-8.640000000000001</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="J2">
-        <v>-16.46</v>
+        <v>-13.81</v>
       </c>
       <c r="K2">
-        <v>-0.28</v>
+        <v>-0.95</v>
       </c>
       <c r="L2">
-        <v>-8.960000000000001</v>
+        <v>-7.61</v>
       </c>
       <c r="M2">
-        <v>-11.08</v>
+        <v>-11.74</v>
       </c>
       <c r="N2">
         <v>80</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P2">
-        <v>681.1</v>
+        <v>669.58</v>
       </c>
       <c r="Q2">
-        <v>711.3200000000001</v>
+        <v>707.52</v>
       </c>
       <c r="R2">
-        <v>665.4400000000001</v>
+        <v>666.34</v>
       </c>
       <c r="S2">
-        <v>667.63</v>
+        <v>667.34</v>
       </c>
       <c r="T2">
-        <v>-0.59</v>
+        <v>-2.17</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -958,34 +994,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>42.71</v>
+        <v>40.77</v>
       </c>
       <c r="Z2">
-        <v>-0.78</v>
+        <v>-4.22</v>
       </c>
       <c r="AA2">
-        <v>9.75</v>
+        <v>6.95</v>
       </c>
       <c r="AB2">
-        <v>-10.53</v>
+        <v>-11.18</v>
       </c>
       <c r="AC2">
         <v>1.57</v>
       </c>
       <c r="AD2">
-        <v>1.05</v>
+        <v>1.57</v>
       </c>
       <c r="AE2">
-        <v>41.16</v>
+        <v>40.63</v>
       </c>
       <c r="AF2">
-        <v>-84.98999999999999</v>
+        <v>-68.56999999999999</v>
       </c>
       <c r="AG2">
-        <v>758.16</v>
+        <v>760.33</v>
       </c>
       <c r="AH2">
-        <v>664.48</v>
+        <v>654.72</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -994,7 +1030,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>26.58</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1005,10 +1041,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>607.5</v>
+        <v>613.15</v>
       </c>
       <c r="D3">
-        <v>-4.03</v>
+        <v>0.93</v>
       </c>
       <c r="E3">
         <v>676.05</v>
@@ -1017,46 +1053,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-10.14</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="H3">
-        <v>18.42</v>
+        <v>19.52</v>
       </c>
       <c r="I3">
-        <v>-2.05</v>
+        <v>-3.11</v>
       </c>
       <c r="J3">
-        <v>-7.1</v>
+        <v>-8.49</v>
       </c>
       <c r="K3">
-        <v>8.25</v>
+        <v>6.9</v>
       </c>
       <c r="L3">
-        <v>-7.6</v>
+        <v>-7.4</v>
       </c>
       <c r="M3">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P3">
-        <v>625.4400000000001</v>
+        <v>621.5</v>
       </c>
       <c r="Q3">
-        <v>634.98</v>
+        <v>631.83</v>
       </c>
       <c r="R3">
-        <v>630.49</v>
+        <v>631.71</v>
       </c>
       <c r="S3">
-        <v>589.66</v>
+        <v>589.87</v>
       </c>
       <c r="T3">
-        <v>3.03</v>
+        <v>3.95</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1071,43 +1107,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>40.43</v>
+        <v>42.9</v>
       </c>
       <c r="Z3">
-        <v>-4.19</v>
+        <v>-5.1</v>
       </c>
       <c r="AA3">
-        <v>-1.04</v>
+        <v>-1.85</v>
       </c>
       <c r="AB3">
-        <v>-3.15</v>
+        <v>-3.24</v>
       </c>
       <c r="AC3">
-        <v>23.32</v>
+        <v>27.69</v>
       </c>
       <c r="AD3">
-        <v>36.53</v>
+        <v>31.75</v>
       </c>
       <c r="AE3">
-        <v>21.71</v>
+        <v>21.6</v>
       </c>
       <c r="AF3">
-        <v>-4.64</v>
+        <v>-44.46</v>
       </c>
       <c r="AG3">
-        <v>664.01</v>
+        <v>655.21</v>
       </c>
       <c r="AH3">
-        <v>605.95</v>
+        <v>608.46</v>
       </c>
       <c r="AI3">
-        <v>682.52</v>
+        <v>670.9</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>26.77</v>
+        <v>30.84</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1118,58 +1154,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>856.35</v>
+        <v>833.15</v>
       </c>
       <c r="D4">
-        <v>-0.45</v>
+        <v>-2.71</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
       </c>
       <c r="F4">
-        <v>837</v>
+        <v>833.15</v>
       </c>
       <c r="G4">
-        <v>-31.07</v>
+        <v>-32.94</v>
       </c>
       <c r="H4">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-1.5</v>
+        <v>-2.56</v>
       </c>
       <c r="J4">
-        <v>-1.97</v>
+        <v>-5.3</v>
       </c>
       <c r="K4">
-        <v>-19.11</v>
+        <v>-21.36</v>
       </c>
       <c r="L4">
-        <v>-23.32</v>
+        <v>-25.68</v>
       </c>
       <c r="M4">
-        <v>-0.99</v>
+        <v>-1.98</v>
       </c>
       <c r="N4">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O4">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>855.51</v>
+        <v>851.14</v>
       </c>
       <c r="Q4">
-        <v>860.38</v>
+        <v>858.29</v>
       </c>
       <c r="R4">
-        <v>883.4400000000001</v>
+        <v>881.9</v>
       </c>
       <c r="S4">
-        <v>1038.24</v>
+        <v>1036.24</v>
       </c>
       <c r="T4">
-        <v>-17.52</v>
+        <v>-19.6</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1184,34 +1220,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>43.77</v>
+        <v>35.93</v>
       </c>
       <c r="Z4">
-        <v>-8.9</v>
+        <v>-10.36</v>
       </c>
       <c r="AA4">
-        <v>-11.37</v>
+        <v>-11.17</v>
       </c>
       <c r="AB4">
-        <v>2.47</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AC4">
-        <v>83.40000000000001</v>
+        <v>55.37</v>
       </c>
       <c r="AD4">
-        <v>75.93000000000001</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="AE4">
-        <v>19.22</v>
+        <v>19.95</v>
       </c>
       <c r="AF4">
-        <v>-16.73</v>
+        <v>27.73</v>
       </c>
       <c r="AG4">
-        <v>883.4</v>
+        <v>883.24</v>
       </c>
       <c r="AH4">
-        <v>837.36</v>
+        <v>833.34</v>
       </c>
       <c r="AI4">
         <v>891.26</v>
@@ -1220,7 +1256,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>25.43</v>
+        <v>27.62</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1231,10 +1267,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>925.7</v>
+        <v>949.3</v>
       </c>
       <c r="D5">
-        <v>-2.75</v>
+        <v>2.55</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1243,46 +1279,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-34.7</v>
+        <v>-33.04</v>
       </c>
       <c r="H5">
-        <v>23.59</v>
+        <v>26.74</v>
       </c>
       <c r="I5">
-        <v>-10.17</v>
+        <v>-9.09</v>
       </c>
       <c r="J5">
-        <v>-15.81</v>
+        <v>-14.17</v>
       </c>
       <c r="K5">
-        <v>-31.21</v>
+        <v>-28.74</v>
       </c>
       <c r="L5">
-        <v>-14.44</v>
+        <v>-13.75</v>
       </c>
       <c r="M5">
-        <v>9.949999999999999</v>
+        <v>10.53</v>
       </c>
       <c r="N5">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O5">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="P5">
-        <v>983.6</v>
+        <v>964.62</v>
       </c>
       <c r="Q5">
-        <v>1021.67</v>
+        <v>1014.18</v>
       </c>
       <c r="R5">
-        <v>1106.4</v>
+        <v>1100.69</v>
       </c>
       <c r="S5">
-        <v>1072.5</v>
+        <v>1072.22</v>
       </c>
       <c r="T5">
-        <v>-13.69</v>
+        <v>-11.46</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1297,43 +1333,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>26.26</v>
+        <v>32.82</v>
       </c>
       <c r="Z5">
-        <v>-41.45</v>
+        <v>-42.14</v>
       </c>
       <c r="AA5">
-        <v>-38.27</v>
+        <v>-39.04</v>
       </c>
       <c r="AB5">
-        <v>-3.18</v>
+        <v>-3.1</v>
       </c>
       <c r="AC5">
-        <v>23.3</v>
+        <v>23.78</v>
       </c>
       <c r="AD5">
-        <v>46.91</v>
+        <v>31.02</v>
       </c>
       <c r="AE5">
-        <v>39.61</v>
+        <v>41.53</v>
       </c>
       <c r="AF5">
-        <v>-1.91</v>
+        <v>-55.71</v>
       </c>
       <c r="AG5">
-        <v>1112.21</v>
+        <v>1102.53</v>
       </c>
       <c r="AH5">
-        <v>931.13</v>
+        <v>925.84</v>
       </c>
       <c r="AI5">
-        <v>1048.49</v>
+        <v>1047.78</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>31.84</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1344,10 +1380,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1496.5</v>
+        <v>1525.2</v>
       </c>
       <c r="D6">
-        <v>-4.38</v>
+        <v>1.92</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1356,46 +1392,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-35.5</v>
+        <v>-34.27</v>
       </c>
       <c r="H6">
-        <v>1.71</v>
+        <v>3.66</v>
       </c>
       <c r="I6">
-        <v>-7.45</v>
+        <v>-4.87</v>
       </c>
       <c r="J6">
-        <v>-11.94</v>
+        <v>-10.68</v>
       </c>
       <c r="K6">
-        <v>-26.68</v>
+        <v>-24.82</v>
       </c>
       <c r="L6">
-        <v>-33.08</v>
+        <v>-33.45</v>
       </c>
       <c r="M6">
-        <v>-8.08</v>
+        <v>-8.25</v>
       </c>
       <c r="N6">
         <v>20</v>
       </c>
       <c r="O6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P6">
-        <v>1563.62</v>
+        <v>1548</v>
       </c>
       <c r="Q6">
-        <v>1596.01</v>
+        <v>1588.71</v>
       </c>
       <c r="R6">
-        <v>1786.8</v>
+        <v>1777.01</v>
       </c>
       <c r="S6">
-        <v>1803.7</v>
+        <v>1800.71</v>
       </c>
       <c r="T6">
-        <v>-17.03</v>
+        <v>-15.3</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1410,43 +1446,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>28.89</v>
+        <v>34.27</v>
       </c>
       <c r="Z6">
-        <v>-63.54</v>
+        <v>-62.9</v>
       </c>
       <c r="AA6">
-        <v>-70.3</v>
+        <v>-68.81999999999999</v>
       </c>
       <c r="AB6">
-        <v>6.76</v>
+        <v>5.92</v>
       </c>
       <c r="AC6">
-        <v>58.64</v>
+        <v>57.06</v>
       </c>
       <c r="AD6">
-        <v>71.62</v>
+        <v>63.4</v>
       </c>
       <c r="AE6">
-        <v>53.17</v>
+        <v>54.49</v>
       </c>
       <c r="AF6">
-        <v>110.28</v>
+        <v>86.48</v>
       </c>
       <c r="AG6">
-        <v>1694.95</v>
+        <v>1685.82</v>
       </c>
       <c r="AH6">
-        <v>1497.07</v>
+        <v>1491.6</v>
       </c>
       <c r="AI6">
-        <v>1680.86</v>
+        <v>1674.86</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>38.32</v>
+        <v>40.24</v>
       </c>
     </row>
   </sheetData>
@@ -1587,7 +1623,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1607,719 +1643,808 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-6.98</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-16.46</v>
       </c>
-      <c r="E7" s="6">
-        <v>-9.48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-13.81</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-4.19</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-7.1</v>
       </c>
-      <c r="E8" s="6">
-        <v>-2.91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-8.49</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-0.84</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-1.97</v>
       </c>
-      <c r="E9" s="6">
-        <v>-1.13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-5.3</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-3.33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-13.6</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-15.81</v>
       </c>
-      <c r="E10" s="6">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-14.17</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-7.77</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-11.94</v>
       </c>
-      <c r="E11" s="6">
-        <v>-4.17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-10.68</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-7.23</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>-8.640000000000001</v>
       </c>
-      <c r="E12" s="6">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-8.109999999999999</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>-2.05</v>
       </c>
-      <c r="E13" s="6">
-        <v>-2.86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>-3.11</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-1.27</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>-1.5</v>
       </c>
-      <c r="E14" s="6">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-2.56</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-5.19</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-10.17</v>
       </c>
-      <c r="E15" s="6">
-        <v>-4.98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-9.09</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-0.48</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>-7.45</v>
       </c>
-      <c r="E16" s="6">
-        <v>-6.97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-4.87</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>-8.06</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>-8.960000000000001</v>
       </c>
-      <c r="E17" s="6">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>-7.61</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>-3.96</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="6">
         <v>-7.6</v>
       </c>
-      <c r="E18" s="6">
-        <v>-3.64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="6">
+        <v>-7.4</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-22.15</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="6">
         <v>-23.32</v>
       </c>
-      <c r="E19" s="6">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-25.68</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>-12.06</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="6">
         <v>-14.44</v>
       </c>
-      <c r="E20" s="6">
-        <v>-2.38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="6">
+        <v>-13.75</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-29.03</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="6">
         <v>-33.08</v>
       </c>
-      <c r="E21" s="6">
-        <v>-4.05</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="6">
+        <v>-33.45</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>-0.53</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="6">
         <v>-0.28</v>
       </c>
-      <c r="E22" s="7">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="6">
+        <v>-0.95</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="5">
-        <v>11.19</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="6">
         <v>8.25</v>
       </c>
-      <c r="E23" s="6">
-        <v>-2.94</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D24" s="6">
+        <v>6.9</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="5">
-        <v>-19.52</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C25" s="6">
         <v>-19.11</v>
       </c>
-      <c r="E24" s="7">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D25" s="6">
+        <v>-21.36</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
-        <v>-29.74</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C26" s="6">
         <v>-31.21</v>
       </c>
-      <c r="E25" s="6">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D26" s="6">
+        <v>-28.74</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="5">
-        <v>-24.8</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C27" s="6">
         <v>-26.68</v>
       </c>
-      <c r="E26" s="6">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D27" s="6">
+        <v>-24.82</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="5">
-        <v>-27.16</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C28" s="6">
         <v>-27.76</v>
       </c>
-      <c r="E27" s="6">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D28" s="6">
+        <v>-28.94</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="5">
-        <v>-6.37</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C29" s="6">
         <v>-10.14</v>
       </c>
-      <c r="E28" s="6">
-        <v>-3.77</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D29" s="6">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="5">
-        <v>-30.76</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C30" s="6">
         <v>-31.07</v>
       </c>
-      <c r="E29" s="6">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D30" s="6">
+        <v>-32.94</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="5">
-        <v>-32.86</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C31" s="6">
         <v>-34.7</v>
       </c>
-      <c r="E30" s="6">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="D31" s="6">
+        <v>-33.04</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="5">
-        <v>-32.55</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C32" s="6">
         <v>-35.5</v>
       </c>
-      <c r="E31" s="6">
-        <v>-2.95</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="D32" s="6">
+        <v>-34.27</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="5">
-        <v>669.2</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C33" s="6">
         <v>663.7</v>
       </c>
-      <c r="E32" s="6">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="D33" s="6">
+        <v>652.85</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-10.85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="5">
-        <v>633</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C34" s="6">
         <v>607.5</v>
       </c>
-      <c r="E33" s="6">
-        <v>-25.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="D34" s="6">
+        <v>613.15</v>
+      </c>
+      <c r="E34" s="7">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="5">
-        <v>860.2</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C35" s="6">
         <v>856.35</v>
       </c>
-      <c r="E34" s="6">
-        <v>-3.85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="D35" s="6">
+        <v>833.15</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-23.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="5">
-        <v>951.9</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C36" s="6">
         <v>925.7</v>
       </c>
-      <c r="E35" s="6">
-        <v>-26.2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="D36" s="6">
+        <v>949.3</v>
+      </c>
+      <c r="E36" s="7">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B37" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="5">
-        <v>1565</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="C37" s="6">
         <v>1496.5</v>
       </c>
-      <c r="E36" s="6">
-        <v>-68.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="D37" s="6">
+        <v>1525.2</v>
+      </c>
+      <c r="E37" s="7">
+        <v>28.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="6">
+        <v>60</v>
+      </c>
+      <c r="D38" s="6">
+        <v>40</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="6">
+        <v>40</v>
+      </c>
+      <c r="D39" s="6">
+        <v>60</v>
+      </c>
+      <c r="E39" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C37" s="5">
-        <v>43.69</v>
-      </c>
-      <c r="D37" s="5">
+      <c r="C40" s="6">
         <v>42.71</v>
       </c>
-      <c r="E37" s="6">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="D40" s="6">
+        <v>40.77</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="5">
-        <v>49.39</v>
-      </c>
-      <c r="D38" s="5">
+      <c r="C41" s="6">
         <v>40.43</v>
       </c>
-      <c r="E38" s="6">
-        <v>-8.960000000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="D41" s="6">
+        <v>42.9</v>
+      </c>
+      <c r="E41" s="7">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C39" s="5">
-        <v>45.3</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="C42" s="6">
         <v>43.77</v>
       </c>
-      <c r="E39" s="6">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="D42" s="6">
+        <v>35.93</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-7.84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="5">
-        <v>29.2</v>
-      </c>
-      <c r="D40" s="5">
+      <c r="C43" s="6">
         <v>26.26</v>
       </c>
-      <c r="E40" s="6">
-        <v>-2.94</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="D43" s="6">
+        <v>32.82</v>
+      </c>
+      <c r="E43" s="7">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B44" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C41" s="5">
-        <v>35.29</v>
-      </c>
-      <c r="D41" s="5">
+      <c r="C44" s="6">
         <v>28.89</v>
       </c>
-      <c r="E41" s="6">
-        <v>-6.4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="D44" s="6">
+        <v>34.27</v>
+      </c>
+      <c r="E44" s="7">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="5">
-        <v>-71.68000000000001</v>
-      </c>
-      <c r="D42" s="5">
+      <c r="C45" s="6">
         <v>-84.98999999999999</v>
       </c>
-      <c r="E42" s="6">
-        <v>-13.31</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="D45" s="6">
+        <v>-68.56999999999999</v>
+      </c>
+      <c r="E45" s="7">
+        <v>16.42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="5">
-        <v>-50.31</v>
-      </c>
-      <c r="D43" s="5">
+      <c r="C46" s="6">
         <v>-4.64</v>
       </c>
-      <c r="E43" s="7">
-        <v>45.67</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="D46" s="6">
+        <v>-44.46</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-39.82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B47" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="5">
-        <v>-22.84</v>
-      </c>
-      <c r="D44" s="5">
+      <c r="C47" s="6">
         <v>-16.73</v>
       </c>
-      <c r="E44" s="7">
-        <v>6.11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="D47" s="6">
+        <v>27.73</v>
+      </c>
+      <c r="E47" s="7">
+        <v>44.46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="5">
-        <v>-64.58</v>
-      </c>
-      <c r="D45" s="5">
+      <c r="C48" s="6">
         <v>-1.91</v>
       </c>
-      <c r="E45" s="7">
-        <v>62.67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="D48" s="6">
+        <v>-55.71</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-53.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B49" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C46" s="5">
-        <v>6.82</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C49" s="6">
         <v>110.28</v>
       </c>
-      <c r="E46" s="7">
-        <v>103.46</v>
+      <c r="D49" s="6">
+        <v>86.48</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-23.8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2339,60 +2464,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
+      <c r="B1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>41.92</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>36.4</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>37.3</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-10.7</v>
-      </c>
-      <c r="G2" s="10">
+      <c r="F2" s="11">
+        <v>-10.5</v>
+      </c>
+      <c r="G2" s="11">
         <v>-13.8</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2494,37 +2619,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.09949999999999999</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0203</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.009899999999999999</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0808</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1108</v>
+      <c r="A2" s="14">
+        <v>0.1053</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.0194</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0198</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0825</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1174</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,28 +181,25 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>26.3 → 32.8</t>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 GOLDEN CROSS</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>26.3</t>
-  </si>
-  <si>
-    <t>32.8</t>
-  </si>
-  <si>
-    <t>28.9 → 34.3</t>
-  </si>
-  <si>
-    <t>28.9</t>
-  </si>
-  <si>
-    <t>34.3</t>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -404,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -412,6 +409,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -787,8 +785,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -928,10 +925,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>652.85</v>
+        <v>643.5</v>
       </c>
       <c r="D2">
-        <v>-1.63</v>
+        <v>-1.43</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -940,88 +937,88 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-28.94</v>
+        <v>-29.96</v>
       </c>
       <c r="H2">
-        <v>25.1</v>
+        <v>23.31</v>
       </c>
       <c r="I2">
-        <v>-8.109999999999999</v>
+        <v>-7.58</v>
       </c>
       <c r="J2">
-        <v>-13.81</v>
+        <v>-11.7</v>
       </c>
       <c r="K2">
-        <v>-0.95</v>
+        <v>-3.17</v>
       </c>
       <c r="L2">
-        <v>-7.61</v>
+        <v>-8.01</v>
       </c>
       <c r="M2">
-        <v>-11.74</v>
+        <v>-12.18</v>
       </c>
       <c r="N2">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="O2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P2">
-        <v>669.58</v>
+        <v>659.03</v>
       </c>
       <c r="Q2">
-        <v>707.52</v>
+        <v>702.75</v>
       </c>
       <c r="R2">
-        <v>666.34</v>
+        <v>667.17</v>
       </c>
       <c r="S2">
-        <v>667.34</v>
+        <v>667.09</v>
       </c>
       <c r="T2">
-        <v>-2.17</v>
+        <v>-3.54</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
       </c>
       <c r="V2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>40.77</v>
+        <v>39.13</v>
       </c>
       <c r="Z2">
-        <v>-4.22</v>
+        <v>-7.62</v>
       </c>
       <c r="AA2">
-        <v>6.95</v>
+        <v>4.04</v>
       </c>
       <c r="AB2">
-        <v>-11.18</v>
+        <v>-11.66</v>
       </c>
       <c r="AC2">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>1.57</v>
+        <v>1.05</v>
       </c>
       <c r="AE2">
-        <v>40.63</v>
+        <v>41.64</v>
       </c>
       <c r="AF2">
-        <v>-68.56999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AG2">
-        <v>760.33</v>
+        <v>760.6</v>
       </c>
       <c r="AH2">
-        <v>654.72</v>
+        <v>644.9</v>
       </c>
       <c r="AI2">
         <v>628.4</v>
@@ -1030,7 +1027,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>26.67</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1041,10 +1038,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>613.15</v>
+        <v>584.5</v>
       </c>
       <c r="D3">
-        <v>0.93</v>
+        <v>-4.67</v>
       </c>
       <c r="E3">
         <v>676.05</v>
@@ -1053,88 +1050,88 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-9.300000000000001</v>
+        <v>-13.54</v>
       </c>
       <c r="H3">
-        <v>19.52</v>
+        <v>13.94</v>
       </c>
       <c r="I3">
-        <v>-3.11</v>
+        <v>-7.83</v>
       </c>
       <c r="J3">
-        <v>-8.49</v>
+        <v>-13.54</v>
       </c>
       <c r="K3">
-        <v>6.9</v>
+        <v>1.77</v>
       </c>
       <c r="L3">
-        <v>-7.4</v>
+        <v>-13.03</v>
       </c>
       <c r="M3">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="O3">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="P3">
-        <v>621.5</v>
+        <v>611.5700000000001</v>
       </c>
       <c r="Q3">
-        <v>631.83</v>
+        <v>628.17</v>
       </c>
       <c r="R3">
-        <v>631.71</v>
+        <v>632.16</v>
       </c>
       <c r="S3">
-        <v>589.87</v>
+        <v>589.97</v>
       </c>
       <c r="T3">
-        <v>3.95</v>
+        <v>-0.93</v>
       </c>
       <c r="U3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>42.9</v>
+        <v>34.98</v>
       </c>
       <c r="Z3">
-        <v>-5.1</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="AA3">
-        <v>-1.85</v>
+        <v>-3.09</v>
       </c>
       <c r="AB3">
-        <v>-3.24</v>
+        <v>-4.94</v>
       </c>
       <c r="AC3">
-        <v>27.69</v>
+        <v>6.44</v>
       </c>
       <c r="AD3">
-        <v>31.75</v>
+        <v>19.15</v>
       </c>
       <c r="AE3">
-        <v>21.6</v>
+        <v>23</v>
       </c>
       <c r="AF3">
-        <v>-44.46</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AG3">
-        <v>655.21</v>
+        <v>656.79</v>
       </c>
       <c r="AH3">
-        <v>608.46</v>
+        <v>599.54</v>
       </c>
       <c r="AI3">
         <v>670.9</v>
@@ -1143,7 +1140,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>30.84</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1154,58 +1151,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>833.15</v>
+        <v>828.8</v>
       </c>
       <c r="D4">
-        <v>-2.71</v>
+        <v>-0.52</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
       </c>
       <c r="F4">
-        <v>833.15</v>
+        <v>828.8</v>
       </c>
       <c r="G4">
-        <v>-32.94</v>
+        <v>-33.29</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-2.56</v>
+        <v>-2.15</v>
       </c>
       <c r="J4">
-        <v>-5.3</v>
+        <v>-5.28</v>
       </c>
       <c r="K4">
-        <v>-21.36</v>
+        <v>-22.81</v>
       </c>
       <c r="L4">
-        <v>-25.68</v>
+        <v>-25.89</v>
       </c>
       <c r="M4">
-        <v>-1.98</v>
+        <v>-2.99</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P4">
-        <v>851.14</v>
+        <v>847.5</v>
       </c>
       <c r="Q4">
-        <v>858.29</v>
+        <v>855.73</v>
       </c>
       <c r="R4">
-        <v>881.9</v>
+        <v>879.74</v>
       </c>
       <c r="S4">
-        <v>1036.24</v>
+        <v>1034.17</v>
       </c>
       <c r="T4">
-        <v>-19.6</v>
+        <v>-19.86</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1220,43 +1217,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>35.93</v>
+        <v>34.67</v>
       </c>
       <c r="Z4">
-        <v>-10.36</v>
+        <v>-11.73</v>
       </c>
       <c r="AA4">
-        <v>-11.17</v>
+        <v>-11.28</v>
       </c>
       <c r="AB4">
-        <v>0.8100000000000001</v>
+        <v>-0.45</v>
       </c>
       <c r="AC4">
-        <v>55.37</v>
+        <v>26.4</v>
       </c>
       <c r="AD4">
-        <v>71.34999999999999</v>
+        <v>55.06</v>
       </c>
       <c r="AE4">
-        <v>19.95</v>
+        <v>19.74</v>
       </c>
       <c r="AF4">
-        <v>27.73</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AG4">
-        <v>883.24</v>
+        <v>881.78</v>
       </c>
       <c r="AH4">
-        <v>833.34</v>
+        <v>829.6799999999999</v>
       </c>
       <c r="AI4">
-        <v>891.26</v>
+        <v>888.71</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>27.62</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1267,10 +1264,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>949.3</v>
+        <v>943.8</v>
       </c>
       <c r="D5">
-        <v>2.55</v>
+        <v>-0.58</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1279,46 +1276,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-33.04</v>
+        <v>-33.43</v>
       </c>
       <c r="H5">
-        <v>26.74</v>
+        <v>26.01</v>
       </c>
       <c r="I5">
-        <v>-9.09</v>
+        <v>-7.47</v>
       </c>
       <c r="J5">
-        <v>-14.17</v>
+        <v>-14.12</v>
       </c>
       <c r="K5">
-        <v>-28.74</v>
+        <v>-29.19</v>
       </c>
       <c r="L5">
-        <v>-13.75</v>
+        <v>-14.7</v>
       </c>
       <c r="M5">
-        <v>10.53</v>
+        <v>10.39</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="P5">
-        <v>964.62</v>
+        <v>949.38</v>
       </c>
       <c r="Q5">
-        <v>1014.18</v>
+        <v>1006.11</v>
       </c>
       <c r="R5">
-        <v>1100.69</v>
+        <v>1094.45</v>
       </c>
       <c r="S5">
-        <v>1072.22</v>
+        <v>1071.84</v>
       </c>
       <c r="T5">
-        <v>-11.46</v>
+        <v>-11.95</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1333,34 +1330,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>32.82</v>
+        <v>32.1</v>
       </c>
       <c r="Z5">
-        <v>-42.14</v>
+        <v>-42.63</v>
       </c>
       <c r="AA5">
-        <v>-39.04</v>
+        <v>-39.76</v>
       </c>
       <c r="AB5">
-        <v>-3.1</v>
+        <v>-2.87</v>
       </c>
       <c r="AC5">
-        <v>23.78</v>
+        <v>28.29</v>
       </c>
       <c r="AD5">
-        <v>31.02</v>
+        <v>25.12</v>
       </c>
       <c r="AE5">
-        <v>41.53</v>
+        <v>40.89</v>
       </c>
       <c r="AF5">
-        <v>-55.71</v>
+        <v>-57.91</v>
       </c>
       <c r="AG5">
-        <v>1102.53</v>
+        <v>1088.72</v>
       </c>
       <c r="AH5">
-        <v>925.84</v>
+        <v>923.5</v>
       </c>
       <c r="AI5">
         <v>1047.78</v>
@@ -1369,7 +1366,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>33.33</v>
+        <v>33.17</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1380,10 +1377,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1525.2</v>
+        <v>1585.6</v>
       </c>
       <c r="D6">
-        <v>1.92</v>
+        <v>3.96</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1392,46 +1389,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-34.27</v>
+        <v>-31.66</v>
       </c>
       <c r="H6">
-        <v>3.66</v>
+        <v>7.77</v>
       </c>
       <c r="I6">
-        <v>-4.87</v>
+        <v>-0.21</v>
       </c>
       <c r="J6">
-        <v>-10.68</v>
+        <v>-5.12</v>
       </c>
       <c r="K6">
-        <v>-24.82</v>
+        <v>-23.73</v>
       </c>
       <c r="L6">
-        <v>-33.45</v>
+        <v>-30.87</v>
       </c>
       <c r="M6">
-        <v>-8.25</v>
+        <v>-7.83</v>
       </c>
       <c r="N6">
         <v>20</v>
       </c>
       <c r="O6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P6">
-        <v>1548</v>
+        <v>1547.32</v>
       </c>
       <c r="Q6">
-        <v>1588.71</v>
+        <v>1582.99</v>
       </c>
       <c r="R6">
-        <v>1777.01</v>
+        <v>1768.16</v>
       </c>
       <c r="S6">
-        <v>1800.71</v>
+        <v>1798</v>
       </c>
       <c r="T6">
-        <v>-15.3</v>
+        <v>-11.81</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1446,34 +1443,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>34.27</v>
+        <v>43.9</v>
       </c>
       <c r="Z6">
-        <v>-62.9</v>
+        <v>-56.86</v>
       </c>
       <c r="AA6">
-        <v>-68.81999999999999</v>
+        <v>-66.43000000000001</v>
       </c>
       <c r="AB6">
-        <v>5.92</v>
+        <v>9.56</v>
       </c>
       <c r="AC6">
-        <v>57.06</v>
+        <v>66.95</v>
       </c>
       <c r="AD6">
-        <v>63.4</v>
+        <v>60.89</v>
       </c>
       <c r="AE6">
-        <v>54.49</v>
+        <v>54.98</v>
       </c>
       <c r="AF6">
-        <v>86.48</v>
+        <v>64.3</v>
       </c>
       <c r="AG6">
-        <v>1685.82</v>
+        <v>1664.73</v>
       </c>
       <c r="AH6">
-        <v>1491.6</v>
+        <v>1501.24</v>
       </c>
       <c r="AI6">
         <v>1674.86</v>
@@ -1482,7 +1479,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>40.24</v>
+        <v>37.34</v>
       </c>
     </row>
   </sheetData>
@@ -1623,7 +1620,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1663,7 +1660,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1675,776 +1672,816 @@
         <v>55</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-13.81</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-11.7</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-8.49</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-13.54</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-5.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-5.3</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-5.28</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-14.17</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-14.12</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-10.68</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-5.12</v>
+      </c>
+      <c r="E14" s="8">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-16.46</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-13.81</v>
-      </c>
-      <c r="E8" s="7">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-8.109999999999999</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-7.58</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-7.1</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-8.49</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-3.11</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-7.83</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-4.72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-1.97</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-5.3</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-3.33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-2.56</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-2.15</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-15.81</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-14.17</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-9.09</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-7.47</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-11.94</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-10.68</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-4.87</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-0.21</v>
+      </c>
+      <c r="E19" s="8">
+        <v>4.66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-8.640000000000001</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-8.109999999999999</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-7.61</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-8.01</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.05</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-3.11</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-7.4</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-13.03</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-5.63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-1.5</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-2.56</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-25.68</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-25.89</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-10.17</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-9.09</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-13.75</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-14.7</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-7.45</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-4.87</v>
-      </c>
-      <c r="E17" s="7">
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-33.45</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-30.87</v>
+      </c>
+      <c r="E24" s="8">
         <v>2.58</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-7.61</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-0.95</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-3.17</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-2.22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-7.6</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-7.4</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="7">
+        <v>6.9</v>
+      </c>
+      <c r="D26" s="7">
+        <v>1.77</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-5.13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-23.32</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-25.68</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-2.36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-21.36</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-22.81</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-14.44</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-13.75</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-28.74</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-29.19</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-33.08</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-33.45</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-24.82</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-23.73</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-0.28</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-0.95</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B30" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-28.94</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-29.96</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>8.25</v>
-      </c>
-      <c r="D24" s="6">
-        <v>6.9</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B31" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-13.54</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-4.24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-19.11</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-21.36</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B32" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-32.94</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-33.29</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-31.21</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-28.74</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B33" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-33.04</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-33.43</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-26.68</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-24.82</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B34" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-34.27</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-31.66</v>
+      </c>
+      <c r="E34" s="8">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-27.76</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-28.94</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B35" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="7">
+        <v>652.85</v>
+      </c>
+      <c r="D35" s="7">
+        <v>643.5</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-9.35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-10.14</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B36" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="7">
+        <v>613.15</v>
+      </c>
+      <c r="D36" s="7">
+        <v>584.5</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-28.65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-31.07</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-32.94</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B37" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="7">
+        <v>833.15</v>
+      </c>
+      <c r="D37" s="7">
+        <v>828.8</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-4.35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-34.7</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-33.04</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B38" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="7">
+        <v>949.3</v>
+      </c>
+      <c r="D38" s="7">
+        <v>943.8</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-35.5</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-34.27</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B39" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="7">
+        <v>1525.2</v>
+      </c>
+      <c r="D39" s="7">
+        <v>1585.6</v>
+      </c>
+      <c r="E39" s="8">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>663.7</v>
-      </c>
-      <c r="D33" s="6">
-        <v>652.85</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-10.85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B40" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="7">
+        <v>80</v>
+      </c>
+      <c r="D40" s="7">
+        <v>99</v>
+      </c>
+      <c r="E40" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>607.5</v>
-      </c>
-      <c r="D34" s="6">
-        <v>613.15</v>
-      </c>
-      <c r="E34" s="7">
-        <v>5.65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B41" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="7">
+        <v>99</v>
+      </c>
+      <c r="D41" s="7">
+        <v>80</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="7">
+        <v>40.77</v>
+      </c>
+      <c r="D42" s="7">
+        <v>39.13</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="7">
+        <v>42.9</v>
+      </c>
+      <c r="D43" s="7">
+        <v>34.98</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-7.92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>856.35</v>
-      </c>
-      <c r="D35" s="6">
-        <v>833.15</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-23.2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="7">
+        <v>35.93</v>
+      </c>
+      <c r="D44" s="7">
+        <v>34.67</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>925.7</v>
-      </c>
-      <c r="D36" s="6">
-        <v>949.3</v>
-      </c>
-      <c r="E36" s="7">
-        <v>23.6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="7">
+        <v>32.82</v>
+      </c>
+      <c r="D45" s="7">
+        <v>32.1</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>1496.5</v>
-      </c>
-      <c r="D37" s="6">
-        <v>1525.2</v>
-      </c>
-      <c r="E37" s="7">
-        <v>28.7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="7">
+        <v>34.27</v>
+      </c>
+      <c r="D46" s="7">
+        <v>43.9</v>
+      </c>
+      <c r="E46" s="8">
+        <v>9.630000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-68.56999999999999</v>
+      </c>
+      <c r="D47" s="7">
+        <v>3.6</v>
+      </c>
+      <c r="E47" s="8">
+        <v>72.17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-44.46</v>
+      </c>
+      <c r="D48" s="7">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="E48" s="8">
+        <v>52.92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="6">
-        <v>60</v>
-      </c>
-      <c r="D38" s="6">
+      <c r="B49" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="7">
+        <v>27.73</v>
+      </c>
+      <c r="D49" s="7">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-17.84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="8">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="6">
-        <v>40</v>
-      </c>
-      <c r="D39" s="6">
-        <v>60</v>
-      </c>
-      <c r="E39" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>42.71</v>
-      </c>
-      <c r="D40" s="6">
-        <v>40.77</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>40.43</v>
-      </c>
-      <c r="D41" s="6">
-        <v>42.9</v>
-      </c>
-      <c r="E41" s="7">
-        <v>2.47</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>43.77</v>
-      </c>
-      <c r="D42" s="6">
-        <v>35.93</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-7.84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>26.26</v>
-      </c>
-      <c r="D43" s="6">
-        <v>32.82</v>
-      </c>
-      <c r="E43" s="7">
-        <v>6.56</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="B50" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-55.71</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-57.91</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="6">
-        <v>28.89</v>
-      </c>
-      <c r="D44" s="6">
-        <v>34.27</v>
-      </c>
-      <c r="E44" s="7">
-        <v>5.38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="5" t="s">
+      <c r="B51" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="6">
-        <v>-84.98999999999999</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-68.56999999999999</v>
-      </c>
-      <c r="E45" s="7">
-        <v>16.42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-4.64</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-44.46</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-39.82</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-16.73</v>
-      </c>
-      <c r="D47" s="6">
-        <v>27.73</v>
-      </c>
-      <c r="E47" s="7">
-        <v>44.46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-1.91</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-55.71</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-53.8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="6">
-        <v>110.28</v>
-      </c>
-      <c r="D49" s="6">
+      <c r="C51" s="7">
         <v>86.48</v>
       </c>
-      <c r="E49" s="8">
-        <v>-23.8</v>
+      <c r="D51" s="7">
+        <v>64.3</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-22.18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2464,60 +2501,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
-        <v>41.92</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="12">
+        <v>33.92</v>
+      </c>
+      <c r="C2" s="13">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>37.3</v>
-      </c>
-      <c r="E2" s="11">
-        <v>20</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-10.5</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-13.8</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="12">
+        <v>37</v>
+      </c>
+      <c r="E2" s="12">
+        <v>0</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-10</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-15.4</v>
+      </c>
+      <c r="H2" s="12">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>20</v>
       </c>
     </row>
@@ -2619,37 +2656,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.1053</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0194</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0198</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0825</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1174</v>
+      <c r="A2" s="15">
+        <v>0.1039</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.0101</v>
+      </c>
+      <c r="C2" s="15">
+        <v>-0.0299</v>
+      </c>
+      <c r="D2" s="15">
+        <v>-0.07829999999999999</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.1218</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="61">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,49 +157,13 @@
     <t>No</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>DOWN</t>
   </si>
   <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 GOLDEN CROSS</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +249,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +289,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,16 +365,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -785,7 +747,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -925,10 +889,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>643.5</v>
+        <v>602.95</v>
       </c>
       <c r="D2">
-        <v>-1.43</v>
+        <v>-6.3</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -937,46 +901,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-29.96</v>
+        <v>-34.37</v>
       </c>
       <c r="H2">
-        <v>23.31</v>
+        <v>15.54</v>
       </c>
       <c r="I2">
-        <v>-7.58</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="J2">
-        <v>-11.7</v>
+        <v>-18.41</v>
       </c>
       <c r="K2">
-        <v>-3.17</v>
+        <v>-7.16</v>
       </c>
       <c r="L2">
-        <v>-8.01</v>
+        <v>-12.34</v>
       </c>
       <c r="M2">
-        <v>-12.18</v>
+        <v>-13.56</v>
       </c>
       <c r="N2">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="O2">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="P2">
-        <v>659.03</v>
+        <v>646.4400000000001</v>
       </c>
       <c r="Q2">
-        <v>702.75</v>
+        <v>697.3099999999999</v>
       </c>
       <c r="R2">
-        <v>667.17</v>
+        <v>667.35</v>
       </c>
       <c r="S2">
-        <v>667.09</v>
+        <v>666.66</v>
       </c>
       <c r="T2">
-        <v>-3.54</v>
+        <v>-9.56</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -991,43 +955,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>39.13</v>
+        <v>32.92</v>
       </c>
       <c r="Z2">
-        <v>-7.62</v>
+        <v>-13.43</v>
       </c>
       <c r="AA2">
-        <v>4.04</v>
+        <v>0.54</v>
       </c>
       <c r="AB2">
-        <v>-11.66</v>
+        <v>-13.97</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>1.05</v>
+        <v>0.52</v>
       </c>
       <c r="AE2">
-        <v>41.64</v>
+        <v>43.51</v>
       </c>
       <c r="AF2">
-        <v>3.6</v>
+        <v>-3.66</v>
       </c>
       <c r="AG2">
-        <v>760.6</v>
+        <v>770.12</v>
       </c>
       <c r="AH2">
-        <v>644.9</v>
+        <v>624.49</v>
       </c>
       <c r="AI2">
-        <v>628.4</v>
+        <v>757.35</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>28.8</v>
+        <v>31.29</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1038,10 +1002,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>584.5</v>
+        <v>579.45</v>
       </c>
       <c r="D3">
-        <v>-4.67</v>
+        <v>-0.86</v>
       </c>
       <c r="E3">
         <v>676.05</v>
@@ -1050,46 +1014,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-13.54</v>
+        <v>-14.29</v>
       </c>
       <c r="H3">
-        <v>13.94</v>
+        <v>12.95</v>
       </c>
       <c r="I3">
-        <v>-7.83</v>
+        <v>-6.5</v>
       </c>
       <c r="J3">
-        <v>-13.54</v>
+        <v>-11.91</v>
       </c>
       <c r="K3">
-        <v>1.77</v>
+        <v>0.41</v>
       </c>
       <c r="L3">
-        <v>-13.03</v>
+        <v>-12.36</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>0.79</v>
       </c>
       <c r="N3">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="O3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P3">
-        <v>611.5700000000001</v>
+        <v>603.52</v>
       </c>
       <c r="Q3">
-        <v>628.17</v>
+        <v>625.02</v>
       </c>
       <c r="R3">
-        <v>632.16</v>
+        <v>632.14</v>
       </c>
       <c r="S3">
-        <v>589.97</v>
+        <v>590.01</v>
       </c>
       <c r="T3">
-        <v>-0.93</v>
+        <v>-1.79</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1104,43 +1068,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>34.98</v>
+        <v>33.8</v>
       </c>
       <c r="Z3">
-        <v>-8.029999999999999</v>
+        <v>-10.64</v>
       </c>
       <c r="AA3">
-        <v>-3.09</v>
+        <v>-4.6</v>
       </c>
       <c r="AB3">
-        <v>-4.94</v>
+        <v>-6.04</v>
       </c>
       <c r="AC3">
         <v>6.44</v>
       </c>
       <c r="AD3">
-        <v>19.15</v>
+        <v>13.52</v>
       </c>
       <c r="AE3">
-        <v>23</v>
+        <v>22.17</v>
       </c>
       <c r="AF3">
-        <v>8.460000000000001</v>
+        <v>-35.55</v>
       </c>
       <c r="AG3">
-        <v>656.79</v>
+        <v>660.14</v>
       </c>
       <c r="AH3">
-        <v>599.54</v>
+        <v>589.89</v>
       </c>
       <c r="AI3">
-        <v>670.9</v>
+        <v>647.83</v>
       </c>
       <c r="AJ3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK3">
-        <v>35.7</v>
+        <v>40.39</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1151,58 +1115,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>828.8</v>
+        <v>822</v>
       </c>
       <c r="D4">
-        <v>-0.52</v>
+        <v>-0.82</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
       </c>
       <c r="F4">
-        <v>828.8</v>
+        <v>822</v>
       </c>
       <c r="G4">
-        <v>-33.29</v>
+        <v>-33.84</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-2.15</v>
+        <v>-4.31</v>
       </c>
       <c r="J4">
-        <v>-5.28</v>
+        <v>-6.59</v>
       </c>
       <c r="K4">
-        <v>-22.81</v>
+        <v>-22.95</v>
       </c>
       <c r="L4">
-        <v>-25.89</v>
+        <v>-26.41</v>
       </c>
       <c r="M4">
-        <v>-2.99</v>
+        <v>-2.66</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>847.5</v>
+        <v>840.1</v>
       </c>
       <c r="Q4">
-        <v>855.73</v>
+        <v>853.4299999999999</v>
       </c>
       <c r="R4">
-        <v>879.74</v>
+        <v>877.49</v>
       </c>
       <c r="S4">
-        <v>1034.17</v>
+        <v>1032.1</v>
       </c>
       <c r="T4">
-        <v>-19.86</v>
+        <v>-20.36</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1217,43 +1181,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.67</v>
+        <v>32.75</v>
       </c>
       <c r="Z4">
-        <v>-11.73</v>
+        <v>-13.22</v>
       </c>
       <c r="AA4">
-        <v>-11.28</v>
+        <v>-11.67</v>
       </c>
       <c r="AB4">
-        <v>-0.45</v>
+        <v>-1.55</v>
       </c>
       <c r="AC4">
-        <v>26.4</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>55.06</v>
+        <v>27.26</v>
       </c>
       <c r="AE4">
-        <v>19.74</v>
+        <v>19.88</v>
       </c>
       <c r="AF4">
-        <v>9.890000000000001</v>
+        <v>-27.23</v>
       </c>
       <c r="AG4">
-        <v>881.78</v>
+        <v>882.8200000000001</v>
       </c>
       <c r="AH4">
-        <v>829.6799999999999</v>
+        <v>824.03</v>
       </c>
       <c r="AI4">
-        <v>888.71</v>
+        <v>885.92</v>
       </c>
       <c r="AJ4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK4">
-        <v>30.43</v>
+        <v>33.65</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1264,10 +1228,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>943.8</v>
+        <v>944.8</v>
       </c>
       <c r="D5">
-        <v>-0.58</v>
+        <v>0.11</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1276,46 +1240,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-33.43</v>
+        <v>-33.36</v>
       </c>
       <c r="H5">
-        <v>26.01</v>
+        <v>26.14</v>
       </c>
       <c r="I5">
-        <v>-7.47</v>
+        <v>-3.22</v>
       </c>
       <c r="J5">
-        <v>-14.12</v>
+        <v>-14.52</v>
       </c>
       <c r="K5">
-        <v>-29.19</v>
+        <v>-27.83</v>
       </c>
       <c r="L5">
-        <v>-14.7</v>
+        <v>-13.74</v>
       </c>
       <c r="M5">
-        <v>10.39</v>
+        <v>10.82</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P5">
-        <v>949.38</v>
+        <v>943.1</v>
       </c>
       <c r="Q5">
-        <v>1006.11</v>
+        <v>999.54</v>
       </c>
       <c r="R5">
-        <v>1094.45</v>
+        <v>1088.3</v>
       </c>
       <c r="S5">
-        <v>1071.84</v>
+        <v>1071.29</v>
       </c>
       <c r="T5">
-        <v>-11.95</v>
+        <v>-11.81</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1330,43 +1294,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>32.1</v>
+        <v>32.39</v>
       </c>
       <c r="Z5">
-        <v>-42.63</v>
+        <v>-42.46</v>
       </c>
       <c r="AA5">
-        <v>-39.76</v>
+        <v>-40.3</v>
       </c>
       <c r="AB5">
-        <v>-2.87</v>
+        <v>-2.16</v>
       </c>
       <c r="AC5">
-        <v>28.29</v>
+        <v>38.85</v>
       </c>
       <c r="AD5">
-        <v>25.12</v>
+        <v>30.31</v>
       </c>
       <c r="AE5">
-        <v>40.89</v>
+        <v>39.31</v>
       </c>
       <c r="AF5">
-        <v>-57.91</v>
+        <v>-88.23999999999999</v>
       </c>
       <c r="AG5">
-        <v>1088.72</v>
+        <v>1079.57</v>
       </c>
       <c r="AH5">
-        <v>923.5</v>
+        <v>919.52</v>
       </c>
       <c r="AI5">
         <v>1047.78</v>
       </c>
       <c r="AJ5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK5">
-        <v>33.17</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1377,10 +1341,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1585.6</v>
+        <v>1587</v>
       </c>
       <c r="D6">
-        <v>3.96</v>
+        <v>0.09</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1389,46 +1353,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-31.66</v>
+        <v>-31.6</v>
       </c>
       <c r="H6">
-        <v>7.77</v>
+        <v>7.86</v>
       </c>
       <c r="I6">
-        <v>-0.21</v>
+        <v>1.45</v>
       </c>
       <c r="J6">
-        <v>-5.12</v>
+        <v>-6.65</v>
       </c>
       <c r="K6">
-        <v>-23.73</v>
+        <v>-25.72</v>
       </c>
       <c r="L6">
-        <v>-30.87</v>
+        <v>-30.36</v>
       </c>
       <c r="M6">
-        <v>-7.83</v>
+        <v>-6.91</v>
       </c>
       <c r="N6">
         <v>20</v>
       </c>
       <c r="O6">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P6">
-        <v>1547.32</v>
+        <v>1551.86</v>
       </c>
       <c r="Q6">
-        <v>1582.99</v>
+        <v>1578.85</v>
       </c>
       <c r="R6">
-        <v>1768.16</v>
+        <v>1760.1</v>
       </c>
       <c r="S6">
-        <v>1798</v>
+        <v>1795.24</v>
       </c>
       <c r="T6">
-        <v>-11.81</v>
+        <v>-11.6</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1443,43 +1407,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>43.9</v>
+        <v>44.1</v>
       </c>
       <c r="Z6">
-        <v>-56.86</v>
+        <v>-51.38</v>
       </c>
       <c r="AA6">
-        <v>-66.43000000000001</v>
+        <v>-63.42</v>
       </c>
       <c r="AB6">
-        <v>9.56</v>
+        <v>12.04</v>
       </c>
       <c r="AC6">
-        <v>66.95</v>
+        <v>88.28</v>
       </c>
       <c r="AD6">
-        <v>60.89</v>
+        <v>70.77</v>
       </c>
       <c r="AE6">
-        <v>54.98</v>
+        <v>53.72</v>
       </c>
       <c r="AF6">
-        <v>64.3</v>
+        <v>40.61</v>
       </c>
       <c r="AG6">
-        <v>1664.73</v>
+        <v>1649.75</v>
       </c>
       <c r="AH6">
-        <v>1501.24</v>
+        <v>1507.94</v>
       </c>
       <c r="AI6">
         <v>1674.86</v>
       </c>
       <c r="AJ6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK6">
-        <v>37.34</v>
+        <v>33.45</v>
       </c>
     </row>
   </sheetData>
@@ -1620,7 +1584,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1630,7 +1594,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1640,848 +1604,753 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-11.7</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-18.41</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-6.71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-13.54</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-11.91</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.63</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>64</v>
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-5.28</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-6.59</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-14.12</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-14.52</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-5.12</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-6.65</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-13.81</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-11.7</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2.11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-7.58</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-9.449999999999999</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-8.49</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-7.83</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-6.5</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-2.15</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-4.31</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-2.16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-7.47</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-3.22</v>
+      </c>
+      <c r="E15" s="7">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-0.21</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1.45</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-8.01</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-12.34</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-4.33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-13.03</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-12.36</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-25.89</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-26.41</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-14.7</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-13.74</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-30.87</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-30.36</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-3.17</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-7.16</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-3.99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1.77</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0.41</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-1.36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-22.81</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-22.95</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-29.19</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-27.83</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-23.73</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-25.72</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-29.96</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-34.37</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-4.41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
         <v>-13.54</v>
       </c>
-      <c r="E11" s="9">
+      <c r="D28" s="5">
+        <v>-14.29</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-33.29</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-33.84</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-33.43</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-33.36</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-31.66</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-31.6</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>643.5</v>
+      </c>
+      <c r="D32" s="5">
+        <v>602.95</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-40.55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>584.5</v>
+      </c>
+      <c r="D33" s="5">
+        <v>579.45</v>
+      </c>
+      <c r="E33" s="6">
         <v>-5.05</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-5.3</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-5.28</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>828.8</v>
+      </c>
+      <c r="D34" s="5">
+        <v>822</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-6.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-14.17</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-14.12</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>943.8</v>
+      </c>
+      <c r="D35" s="5">
+        <v>944.8</v>
+      </c>
+      <c r="E35" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-10.68</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-5.12</v>
-      </c>
-      <c r="E14" s="8">
-        <v>5.56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1585.6</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1587</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-8.109999999999999</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-7.58</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="5">
+        <v>99</v>
+      </c>
+      <c r="D37" s="5">
+        <v>80</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-3.11</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-7.83</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-4.72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="5">
+        <v>80</v>
+      </c>
+      <c r="D38" s="5">
+        <v>99</v>
+      </c>
+      <c r="E38" s="7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>39.13</v>
+      </c>
+      <c r="D39" s="5">
+        <v>32.92</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-6.21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>34.98</v>
+      </c>
+      <c r="D40" s="5">
+        <v>33.8</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-2.56</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-2.15</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>34.67</v>
+      </c>
+      <c r="D41" s="5">
+        <v>32.75</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-9.09</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-7.47</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="5">
+        <v>32.1</v>
+      </c>
+      <c r="D42" s="5">
+        <v>32.39</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-4.87</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-0.21</v>
-      </c>
-      <c r="E19" s="8">
-        <v>4.66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>43.9</v>
+      </c>
+      <c r="D43" s="5">
+        <v>44.1</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-7.61</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-8.01</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-3.66</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-7.26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-7.4</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-13.03</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-5.63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-35.55</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-44.01</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-25.68</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-25.89</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="5">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-27.23</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-37.12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-13.75</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-14.7</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-57.91</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-88.23999999999999</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-30.33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-33.45</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-30.87</v>
-      </c>
-      <c r="E24" s="8">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-0.95</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-3.17</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-2.22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7">
-        <v>6.9</v>
-      </c>
-      <c r="D26" s="7">
-        <v>1.77</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-5.13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-21.36</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-22.81</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-28.74</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-29.19</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-24.82</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-23.73</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-28.94</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-29.96</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-13.54</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-4.24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-32.94</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-33.29</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-33.04</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-33.43</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-34.27</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-31.66</v>
-      </c>
-      <c r="E34" s="8">
-        <v>2.61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="7">
-        <v>652.85</v>
-      </c>
-      <c r="D35" s="7">
-        <v>643.5</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-9.35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="7">
-        <v>613.15</v>
-      </c>
-      <c r="D36" s="7">
-        <v>584.5</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-28.65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="7">
-        <v>833.15</v>
-      </c>
-      <c r="D37" s="7">
-        <v>828.8</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-4.35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="7">
-        <v>949.3</v>
-      </c>
-      <c r="D38" s="7">
-        <v>943.8</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="7">
-        <v>1525.2</v>
-      </c>
-      <c r="D39" s="7">
-        <v>1585.6</v>
-      </c>
-      <c r="E39" s="8">
-        <v>60.4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="7">
-        <v>80</v>
-      </c>
-      <c r="D40" s="7">
-        <v>99</v>
-      </c>
-      <c r="E40" s="8">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="7">
-        <v>99</v>
-      </c>
-      <c r="D41" s="7">
-        <v>80</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="7">
-        <v>40.77</v>
-      </c>
-      <c r="D42" s="7">
-        <v>39.13</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-1.64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="7">
-        <v>42.9</v>
-      </c>
-      <c r="D43" s="7">
-        <v>34.98</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-7.92</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="7">
-        <v>35.93</v>
-      </c>
-      <c r="D44" s="7">
-        <v>34.67</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="7">
-        <v>32.82</v>
-      </c>
-      <c r="D45" s="7">
-        <v>32.1</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="7">
-        <v>34.27</v>
-      </c>
-      <c r="D46" s="7">
-        <v>43.9</v>
-      </c>
-      <c r="E46" s="8">
-        <v>9.630000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="6" t="s">
+      <c r="B48" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="7">
-        <v>-68.56999999999999</v>
-      </c>
-      <c r="D47" s="7">
-        <v>3.6</v>
-      </c>
-      <c r="E47" s="8">
-        <v>72.17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-44.46</v>
-      </c>
-      <c r="D48" s="7">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="E48" s="8">
-        <v>52.92</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="7">
-        <v>27.73</v>
-      </c>
-      <c r="D49" s="7">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-17.84</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-55.71</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-57.91</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="7">
-        <v>86.48</v>
-      </c>
-      <c r="D51" s="7">
+      <c r="C48" s="5">
         <v>64.3</v>
       </c>
-      <c r="E51" s="9">
-        <v>-22.18</v>
+      <c r="D48" s="5">
+        <v>40.61</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-23.69</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2501,60 +2370,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>72</v>
+      <c r="B1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>33.92</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="12">
-        <v>37</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="10">
+        <v>35.2</v>
+      </c>
+      <c r="E2" s="10">
         <v>0</v>
       </c>
-      <c r="F2" s="12">
-        <v>-10</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-15.4</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="10">
+        <v>-11.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-16.6</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2656,37 +2525,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="15">
-        <v>0.1039</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.0101</v>
-      </c>
-      <c r="C2" s="15">
-        <v>-0.0299</v>
-      </c>
-      <c r="D2" s="15">
-        <v>-0.07829999999999999</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.1218</v>
+      <c r="A2" s="13">
+        <v>0.1082</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0266</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.06909999999999999</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1356</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -249,14 +249,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -289,13 +289,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -747,9 +747,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -889,10 +887,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>602.95</v>
+        <v>581.05</v>
       </c>
       <c r="D2">
-        <v>-6.3</v>
+        <v>-3.63</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -901,46 +899,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-34.37</v>
+        <v>-36.76</v>
       </c>
       <c r="H2">
-        <v>15.54</v>
+        <v>11.34</v>
       </c>
       <c r="I2">
-        <v>-9.449999999999999</v>
+        <v>-13.17</v>
       </c>
       <c r="J2">
-        <v>-18.41</v>
+        <v>-18.37</v>
       </c>
       <c r="K2">
-        <v>-7.16</v>
+        <v>-9.59</v>
       </c>
       <c r="L2">
-        <v>-12.34</v>
+        <v>-13.05</v>
       </c>
       <c r="M2">
-        <v>-13.56</v>
+        <v>-14.35</v>
       </c>
       <c r="N2">
         <v>80</v>
       </c>
       <c r="O2">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="P2">
-        <v>646.4400000000001</v>
+        <v>628.8099999999999</v>
       </c>
       <c r="Q2">
-        <v>697.3099999999999</v>
+        <v>691.55</v>
       </c>
       <c r="R2">
-        <v>667.35</v>
+        <v>667.09</v>
       </c>
       <c r="S2">
-        <v>666.66</v>
+        <v>666.24</v>
       </c>
       <c r="T2">
-        <v>-9.56</v>
+        <v>-12.79</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -955,43 +953,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>32.92</v>
+        <v>30.14</v>
       </c>
       <c r="Z2">
-        <v>-13.43</v>
+        <v>-19.57</v>
       </c>
       <c r="AA2">
-        <v>0.54</v>
+        <v>-3.48</v>
       </c>
       <c r="AB2">
-        <v>-13.97</v>
+        <v>-16.09</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>43.51</v>
+        <v>43.08</v>
       </c>
       <c r="AF2">
-        <v>-3.66</v>
+        <v>-33.78</v>
       </c>
       <c r="AG2">
-        <v>770.12</v>
+        <v>781.03</v>
       </c>
       <c r="AH2">
-        <v>624.49</v>
+        <v>602.0599999999999</v>
       </c>
       <c r="AI2">
-        <v>757.35</v>
+        <v>717.45</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>31.29</v>
+        <v>34.94</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1002,10 +1000,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>579.45</v>
+        <v>587.45</v>
       </c>
       <c r="D3">
-        <v>-0.86</v>
+        <v>1.38</v>
       </c>
       <c r="E3">
         <v>676.05</v>
@@ -1014,46 +1012,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-14.29</v>
+        <v>-13.11</v>
       </c>
       <c r="H3">
-        <v>12.95</v>
+        <v>14.51</v>
       </c>
       <c r="I3">
-        <v>-6.5</v>
+        <v>-7.2</v>
       </c>
       <c r="J3">
-        <v>-11.91</v>
+        <v>-8.57</v>
       </c>
       <c r="K3">
-        <v>0.41</v>
+        <v>4.84</v>
       </c>
       <c r="L3">
-        <v>-12.36</v>
+        <v>-11.78</v>
       </c>
       <c r="M3">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P3">
-        <v>603.52</v>
+        <v>594.41</v>
       </c>
       <c r="Q3">
-        <v>625.02</v>
+        <v>622.8</v>
       </c>
       <c r="R3">
-        <v>632.14</v>
+        <v>632.28</v>
       </c>
       <c r="S3">
-        <v>590.01</v>
+        <v>590.15</v>
       </c>
       <c r="T3">
-        <v>-1.79</v>
+        <v>-0.46</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1068,43 +1066,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>33.8</v>
+        <v>37.41</v>
       </c>
       <c r="Z3">
-        <v>-10.64</v>
+        <v>-11.93</v>
       </c>
       <c r="AA3">
-        <v>-4.6</v>
+        <v>-6.07</v>
       </c>
       <c r="AB3">
-        <v>-6.04</v>
+        <v>-5.86</v>
       </c>
       <c r="AC3">
-        <v>6.44</v>
+        <v>7.73</v>
       </c>
       <c r="AD3">
-        <v>13.52</v>
+        <v>6.87</v>
       </c>
       <c r="AE3">
-        <v>22.17</v>
+        <v>21.58</v>
       </c>
       <c r="AF3">
-        <v>-35.55</v>
+        <v>-57.46</v>
       </c>
       <c r="AG3">
-        <v>660.14</v>
+        <v>661.55</v>
       </c>
       <c r="AH3">
-        <v>589.89</v>
+        <v>584.0599999999999</v>
       </c>
       <c r="AI3">
-        <v>647.83</v>
+        <v>646.77</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>40.39</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1115,10 +1113,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>822</v>
+        <v>837</v>
       </c>
       <c r="D4">
-        <v>-0.82</v>
+        <v>1.82</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
@@ -1127,46 +1125,46 @@
         <v>822</v>
       </c>
       <c r="G4">
-        <v>-33.84</v>
+        <v>-32.63</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="I4">
-        <v>-4.31</v>
+        <v>-2.7</v>
       </c>
       <c r="J4">
-        <v>-6.59</v>
+        <v>-3.57</v>
       </c>
       <c r="K4">
-        <v>-22.95</v>
+        <v>-22.25</v>
       </c>
       <c r="L4">
-        <v>-26.41</v>
+        <v>-24.94</v>
       </c>
       <c r="M4">
-        <v>-2.66</v>
+        <v>-1.74</v>
       </c>
       <c r="N4">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P4">
-        <v>840.1</v>
+        <v>835.46</v>
       </c>
       <c r="Q4">
-        <v>853.4299999999999</v>
+        <v>852.53</v>
       </c>
       <c r="R4">
-        <v>877.49</v>
+        <v>875.54</v>
       </c>
       <c r="S4">
-        <v>1032.1</v>
+        <v>1030.13</v>
       </c>
       <c r="T4">
-        <v>-20.36</v>
+        <v>-18.75</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1181,34 +1179,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>32.75</v>
+        <v>40.59</v>
       </c>
       <c r="Z4">
-        <v>-13.22</v>
+        <v>-13.03</v>
       </c>
       <c r="AA4">
-        <v>-11.67</v>
+        <v>-11.94</v>
       </c>
       <c r="AB4">
-        <v>-1.55</v>
+        <v>-1.09</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>17.28</v>
       </c>
       <c r="AD4">
-        <v>27.26</v>
+        <v>14.56</v>
       </c>
       <c r="AE4">
-        <v>19.88</v>
+        <v>20.89</v>
       </c>
       <c r="AF4">
-        <v>-27.23</v>
+        <v>-24.48</v>
       </c>
       <c r="AG4">
-        <v>882.8200000000001</v>
+        <v>882.8099999999999</v>
       </c>
       <c r="AH4">
-        <v>824.03</v>
+        <v>822.24</v>
       </c>
       <c r="AI4">
         <v>885.92</v>
@@ -1217,7 +1215,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>33.65</v>
+        <v>33.53</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1228,10 +1226,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>944.8</v>
+        <v>928.5</v>
       </c>
       <c r="D5">
-        <v>0.11</v>
+        <v>-1.73</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1240,46 +1238,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-33.36</v>
+        <v>-34.51</v>
       </c>
       <c r="H5">
-        <v>26.14</v>
+        <v>23.97</v>
       </c>
       <c r="I5">
-        <v>-3.22</v>
+        <v>-2.46</v>
       </c>
       <c r="J5">
-        <v>-14.52</v>
+        <v>-13.72</v>
       </c>
       <c r="K5">
-        <v>-27.83</v>
+        <v>-28.21</v>
       </c>
       <c r="L5">
-        <v>-13.74</v>
+        <v>-14.56</v>
       </c>
       <c r="M5">
-        <v>10.82</v>
+        <v>9.85</v>
       </c>
       <c r="N5">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O5">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P5">
-        <v>943.1</v>
+        <v>938.42</v>
       </c>
       <c r="Q5">
-        <v>999.54</v>
+        <v>993.1799999999999</v>
       </c>
       <c r="R5">
-        <v>1088.3</v>
+        <v>1082.41</v>
       </c>
       <c r="S5">
-        <v>1071.29</v>
+        <v>1070.82</v>
       </c>
       <c r="T5">
-        <v>-11.81</v>
+        <v>-13.29</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1294,34 +1292,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>32.39</v>
+        <v>30.14</v>
       </c>
       <c r="Z5">
-        <v>-42.46</v>
+        <v>-43.13</v>
       </c>
       <c r="AA5">
-        <v>-40.3</v>
+        <v>-40.87</v>
       </c>
       <c r="AB5">
-        <v>-2.16</v>
+        <v>-2.27</v>
       </c>
       <c r="AC5">
-        <v>38.85</v>
+        <v>34.24</v>
       </c>
       <c r="AD5">
-        <v>30.31</v>
+        <v>33.8</v>
       </c>
       <c r="AE5">
-        <v>39.31</v>
+        <v>38.8</v>
       </c>
       <c r="AF5">
-        <v>-88.23999999999999</v>
+        <v>-57.48</v>
       </c>
       <c r="AG5">
-        <v>1079.57</v>
+        <v>1074.62</v>
       </c>
       <c r="AH5">
-        <v>919.52</v>
+        <v>911.75</v>
       </c>
       <c r="AI5">
         <v>1047.78</v>
@@ -1330,7 +1328,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>33.35</v>
+        <v>34.03</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1341,10 +1339,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1587</v>
+        <v>1600</v>
       </c>
       <c r="D6">
-        <v>0.09</v>
+        <v>0.82</v>
       </c>
       <c r="E6">
         <v>2320.3</v>
@@ -1353,46 +1351,46 @@
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-31.6</v>
+        <v>-31.04</v>
       </c>
       <c r="H6">
-        <v>7.86</v>
+        <v>8.75</v>
       </c>
       <c r="I6">
-        <v>1.45</v>
+        <v>2.24</v>
       </c>
       <c r="J6">
-        <v>-6.65</v>
+        <v>-4.18</v>
       </c>
       <c r="K6">
-        <v>-25.72</v>
+        <v>-25.79</v>
       </c>
       <c r="L6">
-        <v>-30.36</v>
+        <v>-30.06</v>
       </c>
       <c r="M6">
-        <v>-6.91</v>
+        <v>-6.45</v>
       </c>
       <c r="N6">
         <v>20</v>
       </c>
       <c r="O6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P6">
-        <v>1551.86</v>
+        <v>1558.86</v>
       </c>
       <c r="Q6">
-        <v>1578.85</v>
+        <v>1577.13</v>
       </c>
       <c r="R6">
-        <v>1760.1</v>
+        <v>1751.02</v>
       </c>
       <c r="S6">
-        <v>1795.24</v>
+        <v>1792.77</v>
       </c>
       <c r="T6">
-        <v>-11.6</v>
+        <v>-10.75</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1407,34 +1405,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>44.1</v>
+        <v>46.06</v>
       </c>
       <c r="Z6">
-        <v>-51.38</v>
+        <v>-45.46</v>
       </c>
       <c r="AA6">
-        <v>-63.42</v>
+        <v>-59.82</v>
       </c>
       <c r="AB6">
-        <v>12.04</v>
+        <v>14.37</v>
       </c>
       <c r="AC6">
-        <v>88.28</v>
+        <v>100</v>
       </c>
       <c r="AD6">
-        <v>70.77</v>
+        <v>85.08</v>
       </c>
       <c r="AE6">
-        <v>53.72</v>
+        <v>53.24</v>
       </c>
       <c r="AF6">
-        <v>40.61</v>
+        <v>153.15</v>
       </c>
       <c r="AG6">
-        <v>1649.75</v>
+        <v>1643.9</v>
       </c>
       <c r="AH6">
-        <v>1507.94</v>
+        <v>1510.35</v>
       </c>
       <c r="AI6">
         <v>1674.86</v>
@@ -1443,7 +1441,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>33.45</v>
+        <v>29.47</v>
       </c>
     </row>
   </sheetData>
@@ -1641,13 +1639,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-11.7</v>
+        <v>-18.41</v>
       </c>
       <c r="D7" s="5">
-        <v>-18.41</v>
+        <v>-18.37</v>
       </c>
       <c r="E7" s="6">
-        <v>-6.71</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1658,13 +1656,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-13.54</v>
+        <v>-11.91</v>
       </c>
       <c r="D8" s="5">
-        <v>-11.91</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.63</v>
+        <v>-8.57</v>
+      </c>
+      <c r="E8" s="6">
+        <v>3.34</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1675,13 +1673,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-5.28</v>
+        <v>-6.59</v>
       </c>
       <c r="D9" s="5">
-        <v>-6.59</v>
+        <v>-3.57</v>
       </c>
       <c r="E9" s="6">
-        <v>-1.31</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1692,13 +1690,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-14.12</v>
+        <v>-14.52</v>
       </c>
       <c r="D10" s="5">
-        <v>-14.52</v>
+        <v>-13.72</v>
       </c>
       <c r="E10" s="6">
-        <v>-0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1709,13 +1707,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-5.12</v>
+        <v>-6.65</v>
       </c>
       <c r="D11" s="5">
-        <v>-6.65</v>
+        <v>-4.18</v>
       </c>
       <c r="E11" s="6">
-        <v>-1.53</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1726,13 +1724,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-7.58</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="D12" s="5">
-        <v>-9.449999999999999</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-1.87</v>
+        <v>-13.17</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-3.72</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1743,13 +1741,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-7.83</v>
+        <v>-6.5</v>
       </c>
       <c r="D13" s="5">
-        <v>-6.5</v>
+        <v>-7.2</v>
       </c>
       <c r="E13" s="7">
-        <v>1.33</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1760,13 +1758,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-2.15</v>
+        <v>-4.31</v>
       </c>
       <c r="D14" s="5">
-        <v>-4.31</v>
+        <v>-2.7</v>
       </c>
       <c r="E14" s="6">
-        <v>-2.16</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1777,13 +1775,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-7.47</v>
+        <v>-3.22</v>
       </c>
       <c r="D15" s="5">
-        <v>-3.22</v>
-      </c>
-      <c r="E15" s="7">
-        <v>4.25</v>
+        <v>-2.46</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.76</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1794,13 +1792,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-0.21</v>
+        <v>1.45</v>
       </c>
       <c r="D16" s="5">
-        <v>1.45</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.66</v>
+        <v>2.24</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.79</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1811,13 +1809,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>-8.01</v>
+        <v>-12.34</v>
       </c>
       <c r="D17" s="5">
-        <v>-12.34</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-4.33</v>
+        <v>-13.05</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1828,13 +1826,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-13.03</v>
+        <v>-12.36</v>
       </c>
       <c r="D18" s="5">
-        <v>-12.36</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.67</v>
+        <v>-11.78</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.58</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1845,13 +1843,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-25.89</v>
+        <v>-26.41</v>
       </c>
       <c r="D19" s="5">
-        <v>-26.41</v>
+        <v>-24.94</v>
       </c>
       <c r="E19" s="6">
-        <v>-0.52</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1862,13 +1860,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-14.7</v>
+        <v>-13.74</v>
       </c>
       <c r="D20" s="5">
-        <v>-13.74</v>
+        <v>-14.56</v>
       </c>
       <c r="E20" s="7">
-        <v>0.96</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1879,13 +1877,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-30.87</v>
+        <v>-30.36</v>
       </c>
       <c r="D21" s="5">
-        <v>-30.36</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.51</v>
+        <v>-30.06</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.3</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1896,13 +1894,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-3.17</v>
+        <v>-7.16</v>
       </c>
       <c r="D22" s="5">
-        <v>-7.16</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-3.99</v>
+        <v>-9.59</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.43</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1913,13 +1911,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>1.77</v>
+        <v>0.41</v>
       </c>
       <c r="D23" s="5">
-        <v>0.41</v>
+        <v>4.84</v>
       </c>
       <c r="E23" s="6">
-        <v>-1.36</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1930,13 +1928,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-22.81</v>
+        <v>-22.95</v>
       </c>
       <c r="D24" s="5">
-        <v>-22.95</v>
+        <v>-22.25</v>
       </c>
       <c r="E24" s="6">
-        <v>-0.14</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1947,13 +1945,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-29.19</v>
+        <v>-27.83</v>
       </c>
       <c r="D25" s="5">
-        <v>-27.83</v>
+        <v>-28.21</v>
       </c>
       <c r="E25" s="7">
-        <v>1.36</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1964,13 +1962,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-23.73</v>
+        <v>-25.72</v>
       </c>
       <c r="D26" s="5">
-        <v>-25.72</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-1.99</v>
+        <v>-25.79</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1981,13 +1979,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-29.96</v>
+        <v>-34.37</v>
       </c>
       <c r="D27" s="5">
-        <v>-34.37</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-4.41</v>
+        <v>-36.76</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.39</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1998,13 +1996,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-13.54</v>
+        <v>-14.29</v>
       </c>
       <c r="D28" s="5">
-        <v>-14.29</v>
+        <v>-13.11</v>
       </c>
       <c r="E28" s="6">
-        <v>-0.75</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2015,13 +2013,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-33.29</v>
+        <v>-33.84</v>
       </c>
       <c r="D29" s="5">
-        <v>-33.84</v>
+        <v>-32.63</v>
       </c>
       <c r="E29" s="6">
-        <v>-0.55</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2032,13 +2030,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-33.43</v>
+        <v>-33.36</v>
       </c>
       <c r="D30" s="5">
-        <v>-33.36</v>
+        <v>-34.51</v>
       </c>
       <c r="E30" s="7">
-        <v>0.07000000000000001</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2049,13 +2047,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-31.66</v>
+        <v>-31.6</v>
       </c>
       <c r="D31" s="5">
-        <v>-31.6</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.06</v>
+        <v>-31.04</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2066,13 +2064,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>643.5</v>
+        <v>602.95</v>
       </c>
       <c r="D32" s="5">
-        <v>602.95</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-40.55</v>
+        <v>581.05</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-21.9</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2083,13 +2081,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>584.5</v>
+        <v>579.45</v>
       </c>
       <c r="D33" s="5">
-        <v>579.45</v>
+        <v>587.45</v>
       </c>
       <c r="E33" s="6">
-        <v>-5.05</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2100,13 +2098,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>828.8</v>
+        <v>822</v>
       </c>
       <c r="D34" s="5">
-        <v>822</v>
+        <v>837</v>
       </c>
       <c r="E34" s="6">
-        <v>-6.8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2117,13 +2115,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>943.8</v>
+        <v>944.8</v>
       </c>
       <c r="D35" s="5">
-        <v>944.8</v>
+        <v>928.5</v>
       </c>
       <c r="E35" s="7">
-        <v>1</v>
+        <v>-16.3</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2134,47 +2132,47 @@
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>1585.6</v>
+        <v>1587</v>
       </c>
       <c r="D36" s="5">
-        <v>1587</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1.4</v>
+        <v>1600</v>
+      </c>
+      <c r="E36" s="6">
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C37" s="5">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="D37" s="5">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E37" s="6">
-        <v>-19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C38" s="5">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D38" s="5">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="E38" s="7">
-        <v>19</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2185,13 +2183,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>39.13</v>
+        <v>32.92</v>
       </c>
       <c r="D39" s="5">
-        <v>32.92</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-6.21</v>
+        <v>30.14</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-2.78</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2202,13 +2200,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>34.98</v>
+        <v>33.8</v>
       </c>
       <c r="D40" s="5">
-        <v>33.8</v>
+        <v>37.41</v>
       </c>
       <c r="E40" s="6">
-        <v>-1.18</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2219,13 +2217,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>34.67</v>
+        <v>32.75</v>
       </c>
       <c r="D41" s="5">
-        <v>32.75</v>
+        <v>40.59</v>
       </c>
       <c r="E41" s="6">
-        <v>-1.92</v>
+        <v>7.84</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2236,13 +2234,13 @@
         <v>24</v>
       </c>
       <c r="C42" s="5">
-        <v>32.1</v>
+        <v>32.39</v>
       </c>
       <c r="D42" s="5">
-        <v>32.39</v>
+        <v>30.14</v>
       </c>
       <c r="E42" s="7">
-        <v>0.29</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2253,13 +2251,13 @@
         <v>24</v>
       </c>
       <c r="C43" s="5">
-        <v>43.9</v>
+        <v>44.1</v>
       </c>
       <c r="D43" s="5">
-        <v>44.1</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.2</v>
+        <v>46.06</v>
+      </c>
+      <c r="E43" s="6">
+        <v>1.96</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2270,13 +2268,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>3.6</v>
+        <v>-3.66</v>
       </c>
       <c r="D44" s="5">
-        <v>-3.66</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-7.26</v>
+        <v>-33.78</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-30.12</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2287,13 +2285,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>8.460000000000001</v>
+        <v>-35.55</v>
       </c>
       <c r="D45" s="5">
-        <v>-35.55</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-44.01</v>
+        <v>-57.46</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-21.91</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2304,13 +2302,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>9.890000000000001</v>
+        <v>-27.23</v>
       </c>
       <c r="D46" s="5">
-        <v>-27.23</v>
+        <v>-24.48</v>
       </c>
       <c r="E46" s="6">
-        <v>-37.12</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2321,13 +2319,13 @@
         <v>31</v>
       </c>
       <c r="C47" s="5">
-        <v>-57.91</v>
+        <v>-88.23999999999999</v>
       </c>
       <c r="D47" s="5">
-        <v>-88.23999999999999</v>
+        <v>-57.48</v>
       </c>
       <c r="E47" s="6">
-        <v>-30.33</v>
+        <v>30.76</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2338,13 +2336,13 @@
         <v>31</v>
       </c>
       <c r="C48" s="5">
-        <v>64.3</v>
+        <v>40.61</v>
       </c>
       <c r="D48" s="5">
-        <v>40.61</v>
+        <v>153.15</v>
       </c>
       <c r="E48" s="6">
-        <v>-23.69</v>
+        <v>112.54</v>
       </c>
     </row>
   </sheetData>
@@ -2409,16 +2407,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>35.2</v>
+        <v>36.9</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-11.6</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="G2" s="10">
-        <v>-16.6</v>
+        <v>-16.2</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2543,19 +2541,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.1082</v>
+        <v>0.09849999999999999</v>
       </c>
       <c r="B2" s="13">
-        <v>0.007900000000000001</v>
+        <v>0.0106</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0266</v>
+        <v>-0.0174</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.06909999999999999</v>
+        <v>-0.0645</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1356</v>
+        <v>-0.1435</v>
       </c>
     </row>
   </sheetData>

--- a/GODREJ_GROUP_Technical_Metrics.xlsx
+++ b/GODREJ_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="61">
   <si>
     <t>Symbol</t>
   </si>
@@ -249,14 +249,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -289,13 +289,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -747,7 +747,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -887,10 +889,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>581.05</v>
+        <v>545.55</v>
       </c>
       <c r="D2">
-        <v>-3.63</v>
+        <v>-6.11</v>
       </c>
       <c r="E2">
         <v>918.75</v>
@@ -899,46 +901,46 @@
         <v>521.85</v>
       </c>
       <c r="G2">
-        <v>-36.76</v>
+        <v>-40.62</v>
       </c>
       <c r="H2">
-        <v>11.34</v>
+        <v>4.54</v>
       </c>
       <c r="I2">
-        <v>-13.17</v>
+        <v>-17.8</v>
       </c>
       <c r="J2">
-        <v>-18.37</v>
+        <v>-21.64</v>
       </c>
       <c r="K2">
-        <v>-9.59</v>
+        <v>-12.99</v>
       </c>
       <c r="L2">
-        <v>-13.05</v>
+        <v>-17.32</v>
       </c>
       <c r="M2">
-        <v>-14.35</v>
+        <v>-16.02</v>
       </c>
       <c r="N2">
         <v>80</v>
       </c>
       <c r="O2">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="P2">
-        <v>628.8099999999999</v>
+        <v>605.1799999999999</v>
       </c>
       <c r="Q2">
-        <v>691.55</v>
+        <v>682.6900000000001</v>
       </c>
       <c r="R2">
-        <v>667.09</v>
+        <v>666.29</v>
       </c>
       <c r="S2">
-        <v>666.24</v>
+        <v>665.77</v>
       </c>
       <c r="T2">
-        <v>-12.79</v>
+        <v>-18.06</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -953,16 +955,16 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>30.14</v>
+        <v>26.26</v>
       </c>
       <c r="Z2">
-        <v>-19.57</v>
+        <v>-26.99</v>
       </c>
       <c r="AA2">
-        <v>-3.48</v>
+        <v>-8.18</v>
       </c>
       <c r="AB2">
-        <v>-16.09</v>
+        <v>-18.81</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -971,25 +973,25 @@
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>43.08</v>
+        <v>42.96</v>
       </c>
       <c r="AF2">
-        <v>-33.78</v>
+        <v>-33.89</v>
       </c>
       <c r="AG2">
-        <v>781.03</v>
+        <v>792.05</v>
       </c>
       <c r="AH2">
-        <v>602.0599999999999</v>
+        <v>573.33</v>
       </c>
       <c r="AI2">
-        <v>717.45</v>
+        <v>692.05</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>34.94</v>
+        <v>39.22</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1000,10 +1002,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>587.45</v>
+        <v>553.2</v>
       </c>
       <c r="D3">
-        <v>1.38</v>
+        <v>-5.83</v>
       </c>
       <c r="E3">
         <v>676.05</v>
@@ -1012,46 +1014,46 @@
         <v>513</v>
       </c>
       <c r="G3">
-        <v>-13.11</v>
+        <v>-18.17</v>
       </c>
       <c r="H3">
-        <v>14.51</v>
+        <v>7.84</v>
       </c>
       <c r="I3">
-        <v>-7.2</v>
+        <v>-8.94</v>
       </c>
       <c r="J3">
-        <v>-8.57</v>
+        <v>-12.43</v>
       </c>
       <c r="K3">
-        <v>4.84</v>
+        <v>-1.11</v>
       </c>
       <c r="L3">
-        <v>-11.78</v>
+        <v>-17.19</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>0.08</v>
       </c>
       <c r="N3">
         <v>99</v>
       </c>
       <c r="O3">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="P3">
-        <v>594.41</v>
+        <v>583.55</v>
       </c>
       <c r="Q3">
-        <v>622.8</v>
+        <v>619.29</v>
       </c>
       <c r="R3">
-        <v>632.28</v>
+        <v>631.5700000000001</v>
       </c>
       <c r="S3">
-        <v>590.15</v>
+        <v>590.13</v>
       </c>
       <c r="T3">
-        <v>-0.46</v>
+        <v>-6.26</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1066,43 +1068,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>37.41</v>
+        <v>29.89</v>
       </c>
       <c r="Z3">
-        <v>-11.93</v>
+        <v>-15.53</v>
       </c>
       <c r="AA3">
-        <v>-6.07</v>
+        <v>-7.96</v>
       </c>
       <c r="AB3">
-        <v>-5.86</v>
+        <v>-7.57</v>
       </c>
       <c r="AC3">
         <v>7.73</v>
       </c>
       <c r="AD3">
-        <v>6.87</v>
+        <v>7.3</v>
       </c>
       <c r="AE3">
-        <v>21.58</v>
+        <v>22.7</v>
       </c>
       <c r="AF3">
-        <v>-57.46</v>
+        <v>139.48</v>
       </c>
       <c r="AG3">
-        <v>661.55</v>
+        <v>668.97</v>
       </c>
       <c r="AH3">
-        <v>584.0599999999999</v>
+        <v>569.6</v>
       </c>
       <c r="AI3">
-        <v>646.77</v>
+        <v>637.08</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>43.58</v>
+        <v>48.03</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1113,58 +1115,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>837</v>
+        <v>818</v>
       </c>
       <c r="D4">
-        <v>1.82</v>
+        <v>-2.27</v>
       </c>
       <c r="E4">
         <v>1242.4</v>
       </c>
       <c r="F4">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="G4">
-        <v>-32.63</v>
+        <v>-34.16</v>
       </c>
       <c r="H4">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-2.7</v>
+        <v>-4.48</v>
       </c>
       <c r="J4">
-        <v>-3.57</v>
+        <v>-4.33</v>
       </c>
       <c r="K4">
-        <v>-22.25</v>
+        <v>-23.7</v>
       </c>
       <c r="L4">
-        <v>-24.94</v>
+        <v>-26.27</v>
       </c>
       <c r="M4">
-        <v>-1.74</v>
+        <v>-2.55</v>
       </c>
       <c r="N4">
         <v>60</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>835.46</v>
+        <v>827.79</v>
       </c>
       <c r="Q4">
-        <v>852.53</v>
+        <v>850.9299999999999</v>
       </c>
       <c r="R4">
-        <v>875.54</v>
+        <v>873.28</v>
       </c>
       <c r="S4">
-        <v>1030.13</v>
+        <v>1028.13</v>
       </c>
       <c r="T4">
-        <v>-18.75</v>
+        <v>-20.44</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1179,43 +1181,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>40.59</v>
+        <v>35.02</v>
       </c>
       <c r="Z4">
-        <v>-13.03</v>
+        <v>-14.25</v>
       </c>
       <c r="AA4">
-        <v>-11.94</v>
+        <v>-12.4</v>
       </c>
       <c r="AB4">
-        <v>-1.09</v>
+        <v>-1.85</v>
       </c>
       <c r="AC4">
-        <v>17.28</v>
+        <v>22.28</v>
       </c>
       <c r="AD4">
-        <v>14.56</v>
+        <v>13.19</v>
       </c>
       <c r="AE4">
-        <v>20.89</v>
+        <v>23.67</v>
       </c>
       <c r="AF4">
-        <v>-24.48</v>
+        <v>864.5700000000001</v>
       </c>
       <c r="AG4">
-        <v>882.8099999999999</v>
+        <v>884.9299999999999</v>
       </c>
       <c r="AH4">
-        <v>822.24</v>
+        <v>816.9299999999999</v>
       </c>
       <c r="AI4">
-        <v>885.92</v>
+        <v>868.62</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>33.53</v>
+        <v>37.32</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1226,10 +1228,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>928.5</v>
+        <v>904.9</v>
       </c>
       <c r="D5">
-        <v>-1.73</v>
+        <v>-2.54</v>
       </c>
       <c r="E5">
         <v>1417.7</v>
@@ -1238,46 +1240,46 @@
         <v>749</v>
       </c>
       <c r="G5">
-        <v>-34.51</v>
+        <v>-36.17</v>
       </c>
       <c r="H5">
-        <v>23.97</v>
+        <v>20.81</v>
       </c>
       <c r="I5">
-        <v>-2.46</v>
+        <v>-2.25</v>
       </c>
       <c r="J5">
-        <v>-13.72</v>
+        <v>-14.28</v>
       </c>
       <c r="K5">
-        <v>-28.21</v>
+        <v>-30.89</v>
       </c>
       <c r="L5">
-        <v>-14.56</v>
+        <v>-17.35</v>
       </c>
       <c r="M5">
-        <v>9.85</v>
+        <v>9.24</v>
       </c>
       <c r="N5">
         <v>40</v>
       </c>
       <c r="O5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P5">
-        <v>938.42</v>
+        <v>934.26</v>
       </c>
       <c r="Q5">
-        <v>993.1799999999999</v>
+        <v>986.46</v>
       </c>
       <c r="R5">
-        <v>1082.41</v>
+        <v>1075.91</v>
       </c>
       <c r="S5">
-        <v>1070.82</v>
+        <v>1070.22</v>
       </c>
       <c r="T5">
-        <v>-13.29</v>
+        <v>-15.45</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1292,43 +1294,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>30.14</v>
+        <v>27.19</v>
       </c>
       <c r="Z5">
-        <v>-43.13</v>
+        <v>-45.05</v>
       </c>
       <c r="AA5">
-        <v>-40.87</v>
+        <v>-41.7</v>
       </c>
       <c r="AB5">
-        <v>-2.27</v>
+        <v>-3.35</v>
       </c>
       <c r="AC5">
-        <v>34.24</v>
+        <v>25.55</v>
       </c>
       <c r="AD5">
-        <v>33.8</v>
+        <v>32.88</v>
       </c>
       <c r="AE5">
-        <v>38.8</v>
+        <v>38.21</v>
       </c>
       <c r="AF5">
-        <v>-57.48</v>
+        <v>-70.20999999999999</v>
       </c>
       <c r="AG5">
-        <v>1074.62</v>
+        <v>1073.83</v>
       </c>
       <c r="AH5">
-        <v>911.75</v>
+        <v>899.09</v>
       </c>
       <c r="AI5">
-        <v>1047.78</v>
+        <v>1031.28</v>
       </c>
       <c r="AJ5" t="s">
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>34.03</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1339,58 +1341,58 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>1600</v>
+        <v>1568</v>
       </c>
       <c r="D6">
-        <v>0.82</v>
+        <v>-2</v>
       </c>
       <c r="E6">
-        <v>2320.3</v>
+        <v>2311.3</v>
       </c>
       <c r="F6">
         <v>1471.3</v>
       </c>
       <c r="G6">
-        <v>-31.04</v>
+        <v>-32.16</v>
       </c>
       <c r="H6">
-        <v>8.75</v>
+        <v>6.57</v>
       </c>
       <c r="I6">
-        <v>2.24</v>
+        <v>4.78</v>
       </c>
       <c r="J6">
-        <v>-4.18</v>
+        <v>-4.06</v>
       </c>
       <c r="K6">
-        <v>-25.79</v>
+        <v>-25.72</v>
       </c>
       <c r="L6">
-        <v>-30.06</v>
+        <v>-32.42</v>
       </c>
       <c r="M6">
-        <v>-6.45</v>
+        <v>-7.75</v>
       </c>
       <c r="N6">
         <v>20</v>
       </c>
       <c r="O6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P6">
-        <v>1558.86</v>
+        <v>1573.16</v>
       </c>
       <c r="Q6">
-        <v>1577.13</v>
+        <v>1574.1</v>
       </c>
       <c r="R6">
-        <v>1751.02</v>
+        <v>1742.43</v>
       </c>
       <c r="S6">
-        <v>1792.77</v>
+        <v>1790.65</v>
       </c>
       <c r="T6">
-        <v>-10.75</v>
+        <v>-12.43</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1405,34 +1407,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>46.06</v>
+        <v>42.14</v>
       </c>
       <c r="Z6">
-        <v>-45.46</v>
+        <v>-42.85</v>
       </c>
       <c r="AA6">
-        <v>-59.82</v>
+        <v>-56.43</v>
       </c>
       <c r="AB6">
-        <v>14.37</v>
+        <v>13.58</v>
       </c>
       <c r="AC6">
-        <v>100</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="AD6">
-        <v>85.08</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="AE6">
-        <v>53.24</v>
+        <v>52.57</v>
       </c>
       <c r="AF6">
-        <v>153.15</v>
+        <v>16.36</v>
       </c>
       <c r="AG6">
-        <v>1643.9</v>
+        <v>1636.41</v>
       </c>
       <c r="AH6">
-        <v>1510.35</v>
+        <v>1511.79</v>
       </c>
       <c r="AI6">
         <v>1674.86</v>
@@ -1441,7 +1443,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>29.47</v>
+        <v>25.83</v>
       </c>
     </row>
   </sheetData>
@@ -1545,27 +1547,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U6">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="16" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V6">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="18" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W6">
-    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y6">
@@ -1582,7 +1584,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1639,13 +1641,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-18.41</v>
+        <v>-18.37</v>
       </c>
       <c r="D7" s="5">
-        <v>-18.37</v>
+        <v>-21.64</v>
       </c>
       <c r="E7" s="6">
-        <v>0.04</v>
+        <v>-3.27</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1656,13 +1658,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-11.91</v>
+        <v>-8.57</v>
       </c>
       <c r="D8" s="5">
-        <v>-8.57</v>
+        <v>-12.43</v>
       </c>
       <c r="E8" s="6">
-        <v>3.34</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1673,13 +1675,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-6.59</v>
+        <v>-3.57</v>
       </c>
       <c r="D9" s="5">
-        <v>-3.57</v>
+        <v>-4.33</v>
       </c>
       <c r="E9" s="6">
-        <v>3.02</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1690,13 +1692,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-14.52</v>
+        <v>-13.72</v>
       </c>
       <c r="D10" s="5">
-        <v>-13.72</v>
+        <v>-14.28</v>
       </c>
       <c r="E10" s="6">
-        <v>0.8</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1707,13 +1709,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-6.65</v>
+        <v>-4.18</v>
       </c>
       <c r="D11" s="5">
-        <v>-4.18</v>
-      </c>
-      <c r="E11" s="6">
-        <v>2.47</v>
+        <v>-4.06</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1724,13 +1726,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-9.449999999999999</v>
+        <v>-13.17</v>
       </c>
       <c r="D12" s="5">
-        <v>-13.17</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-3.72</v>
+        <v>-17.8</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-4.63</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1741,13 +1743,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-6.5</v>
+        <v>-7.2</v>
       </c>
       <c r="D13" s="5">
-        <v>-7.2</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.7</v>
+        <v>-8.94</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-1.74</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1758,13 +1760,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-4.31</v>
+        <v>-2.7</v>
       </c>
       <c r="D14" s="5">
-        <v>-2.7</v>
+        <v>-4.48</v>
       </c>
       <c r="E14" s="6">
-        <v>1.61</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1775,13 +1777,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-3.22</v>
+        <v>-2.46</v>
       </c>
       <c r="D15" s="5">
-        <v>-2.46</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.76</v>
+        <v>-2.25</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.21</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1792,13 +1794,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>1.45</v>
+        <v>2.24</v>
       </c>
       <c r="D16" s="5">
-        <v>2.24</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.79</v>
+        <v>4.78</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.54</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1809,13 +1811,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>-12.34</v>
+        <v>-13.05</v>
       </c>
       <c r="D17" s="5">
-        <v>-13.05</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.71</v>
+        <v>-17.32</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-4.27</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1826,13 +1828,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-12.36</v>
+        <v>-11.78</v>
       </c>
       <c r="D18" s="5">
-        <v>-11.78</v>
+        <v>-17.19</v>
       </c>
       <c r="E18" s="6">
-        <v>0.58</v>
+        <v>-5.41</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1843,13 +1845,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-26.41</v>
+        <v>-24.94</v>
       </c>
       <c r="D19" s="5">
-        <v>-24.94</v>
+        <v>-26.27</v>
       </c>
       <c r="E19" s="6">
-        <v>1.47</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1860,13 +1862,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-13.74</v>
+        <v>-14.56</v>
       </c>
       <c r="D20" s="5">
-        <v>-14.56</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.82</v>
+        <v>-17.35</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-2.79</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1877,13 +1879,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-30.36</v>
+        <v>-30.06</v>
       </c>
       <c r="D21" s="5">
-        <v>-30.06</v>
+        <v>-32.42</v>
       </c>
       <c r="E21" s="6">
-        <v>0.3</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1894,13 +1896,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-7.16</v>
+        <v>-9.59</v>
       </c>
       <c r="D22" s="5">
-        <v>-9.59</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2.43</v>
+        <v>-12.99</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-3.4</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1911,13 +1913,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>0.41</v>
+        <v>4.84</v>
       </c>
       <c r="D23" s="5">
-        <v>4.84</v>
+        <v>-1.11</v>
       </c>
       <c r="E23" s="6">
-        <v>4.43</v>
+        <v>-5.95</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1928,13 +1930,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-22.95</v>
+        <v>-22.25</v>
       </c>
       <c r="D24" s="5">
-        <v>-22.25</v>
+        <v>-23.7</v>
       </c>
       <c r="E24" s="6">
-        <v>0.7</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1945,13 +1947,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-27.83</v>
+        <v>-28.21</v>
       </c>
       <c r="D25" s="5">
-        <v>-28.21</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.38</v>
+        <v>-30.89</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1962,13 +1964,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
+        <v>-25.79</v>
+      </c>
+      <c r="D26" s="5">
         <v>-25.72</v>
       </c>
-      <c r="D26" s="5">
-        <v>-25.79</v>
-      </c>
       <c r="E26" s="7">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1979,13 +1981,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-34.37</v>
+        <v>-36.76</v>
       </c>
       <c r="D27" s="5">
-        <v>-36.76</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.39</v>
+        <v>-40.62</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-3.86</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1996,13 +1998,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-14.29</v>
+        <v>-13.11</v>
       </c>
       <c r="D28" s="5">
-        <v>-13.11</v>
+        <v>-18.17</v>
       </c>
       <c r="E28" s="6">
-        <v>1.18</v>
+        <v>-5.06</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2013,13 +2015,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-33.84</v>
+        <v>-32.63</v>
       </c>
       <c r="D29" s="5">
-        <v>-32.63</v>
+        <v>-34.16</v>
       </c>
       <c r="E29" s="6">
-        <v>1.21</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2030,13 +2032,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-33.36</v>
+        <v>-34.51</v>
       </c>
       <c r="D30" s="5">
-        <v>-34.51</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.15</v>
+        <v>-36.17</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2047,13 +2049,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-31.6</v>
+        <v>-31.04</v>
       </c>
       <c r="D31" s="5">
-        <v>-31.04</v>
+        <v>-32.16</v>
       </c>
       <c r="E31" s="6">
-        <v>0.5600000000000001</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2064,13 +2066,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>602.95</v>
+        <v>581.05</v>
       </c>
       <c r="D32" s="5">
-        <v>581.05</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-21.9</v>
+        <v>545.55</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-35.5</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2081,13 +2083,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>579.45</v>
+        <v>587.45</v>
       </c>
       <c r="D33" s="5">
-        <v>587.45</v>
+        <v>553.2</v>
       </c>
       <c r="E33" s="6">
-        <v>8</v>
+        <v>-34.25</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2098,13 +2100,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>822</v>
+        <v>837</v>
       </c>
       <c r="D34" s="5">
-        <v>837</v>
+        <v>818</v>
       </c>
       <c r="E34" s="6">
-        <v>15</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2115,13 +2117,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>944.8</v>
+        <v>928.5</v>
       </c>
       <c r="D35" s="5">
-        <v>928.5</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-16.3</v>
+        <v>904.9</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-23.6</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2132,217 +2134,183 @@
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>1587</v>
+        <v>1600</v>
       </c>
       <c r="D36" s="5">
-        <v>1600</v>
+        <v>1568</v>
       </c>
       <c r="E36" s="6">
-        <v>13</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C37" s="5">
-        <v>40</v>
+        <v>30.14</v>
       </c>
       <c r="D37" s="5">
-        <v>60</v>
+        <v>26.26</v>
       </c>
       <c r="E37" s="6">
-        <v>20</v>
+        <v>-3.88</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>60</v>
+        <v>37.41</v>
       </c>
       <c r="D38" s="5">
-        <v>40</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-20</v>
+        <v>29.89</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-7.52</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>32.92</v>
+        <v>40.59</v>
       </c>
       <c r="D39" s="5">
-        <v>30.14</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-2.78</v>
+        <v>35.02</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-5.57</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>33.8</v>
+        <v>30.14</v>
       </c>
       <c r="D40" s="5">
-        <v>37.41</v>
+        <v>27.19</v>
       </c>
       <c r="E40" s="6">
-        <v>3.61</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>32.75</v>
+        <v>46.06</v>
       </c>
       <c r="D41" s="5">
-        <v>40.59</v>
+        <v>42.14</v>
       </c>
       <c r="E41" s="6">
-        <v>7.84</v>
+        <v>-3.92</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C42" s="5">
-        <v>32.39</v>
+        <v>-33.78</v>
       </c>
       <c r="D42" s="5">
-        <v>30.14</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-2.25</v>
+        <v>-33.89</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C43" s="5">
-        <v>44.1</v>
+        <v>-57.46</v>
       </c>
       <c r="D43" s="5">
-        <v>46.06</v>
-      </c>
-      <c r="E43" s="6">
-        <v>1.96</v>
+        <v>139.48</v>
+      </c>
+      <c r="E43" s="7">
+        <v>196.94</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>-3.66</v>
+        <v>-24.48</v>
       </c>
       <c r="D44" s="5">
-        <v>-33.78</v>
+        <v>864.5700000000001</v>
       </c>
       <c r="E44" s="7">
-        <v>-30.12</v>
+        <v>889.05</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-35.55</v>
+        <v>-57.48</v>
       </c>
       <c r="D45" s="5">
-        <v>-57.46</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-21.91</v>
+        <v>-70.20999999999999</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-12.73</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>-27.23</v>
+        <v>153.15</v>
       </c>
       <c r="D46" s="5">
-        <v>-24.48</v>
+        <v>16.36</v>
       </c>
       <c r="E46" s="6">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-88.23999999999999</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-57.48</v>
-      </c>
-      <c r="E47" s="6">
-        <v>30.76</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="5">
-        <v>40.61</v>
-      </c>
-      <c r="D48" s="5">
-        <v>153.15</v>
-      </c>
-      <c r="E48" s="6">
-        <v>112.54</v>
+        <v>-136.79</v>
       </c>
     </row>
   </sheetData>
@@ -2401,22 +2369,22 @@
         <v>42</v>
       </c>
       <c r="B2" s="10">
-        <v>33.92</v>
+        <v>33.9</v>
       </c>
       <c r="C2" s="11">
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>36.9</v>
+        <v>32.1</v>
       </c>
       <c r="E2" s="10">
         <v>0</v>
       </c>
       <c r="F2" s="10">
-        <v>-9.699999999999999</v>
+        <v>-11.3</v>
       </c>
       <c r="G2" s="10">
-        <v>-16.2</v>
+        <v>-18.9</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2541,19 +2509,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.09849999999999999</v>
+        <v>0.0924</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0106</v>
+        <v>0.0008</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0174</v>
+        <v>-0.0255</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.0645</v>
+        <v>-0.0775</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1435</v>
+        <v>-0.1602</v>
       </c>
     </row>
   </sheetData>
